--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 12:47:51</t>
+          <t>更新时间: 2026-09-13 17:46:36</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 17:46:36</t>
+          <t>更新时间: 2026-09-13 21:55:23</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 21:55:23</t>
+          <t>更新时间: 2026-09-14 01:09:22</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 01:09:22</t>
+          <t>更新时间: 2026-09-14 03:26:13</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 03:26:13</t>
+          <t>更新时间: 2026-09-14 05:32:38</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -185,10 +185,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 05:40:37</t>
+          <t>更新时间: 2026-09-16 07:42:04</t>
         </is>
       </c>
     </row>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>770.8</v>
+        <v>770.38</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E232"/>
+  <dimension ref="A1:E233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18444,7 +18444,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 770.80 | 最高: 782.950 | 最低: 770.240 | 总记录数: 228</t>
+          <t>最新价: 770.38 | 最高: 782.950 | 最低: 770.240 | 总记录数: 229</t>
         </is>
       </c>
     </row>
@@ -18481,15 +18481,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>770.8</v>
+        <v>770.38</v>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -18504,15 +18504,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>770.8200000000001</v>
+        <v>770.8</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>+0.400</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -18527,15 +18527,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>770.42</v>
+        <v>770.8200000000001</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -18550,15 +18550,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>770.24</v>
+        <v>770.42</v>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>-0.810</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -18573,11 +18573,11 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>771.05</v>
+        <v>770.24</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -18596,15 +18596,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>771.86</v>
+        <v>771.05</v>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>+1.540</t>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -18619,15 +18619,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>770.3200000000001</v>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>771.86</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -18642,15 +18642,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>771.76</v>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>-2.140</t>
+        <v>770.3200000000001</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -18665,15 +18665,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12 05:00:53</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>773.9</v>
+        <v>771.76</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-2.140</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -18688,15 +18688,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15:57</t>
+          <t>2026-09-12 05:00:53</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>774.33</v>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>-0.730</t>
+        <v>773.9</v>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -18711,15 +18711,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-12 02:15:57</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>+1.400</t>
+        <v>774.33</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -18734,15 +18734,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>773.66</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>-1.440</t>
+          <t>+1.400</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -18757,15 +18757,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>775.1</v>
+        <v>773.66</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>-0.500</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -18780,15 +18780,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:18:12</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>775.6</v>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>-0.410</t>
+        <v>775.1</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>-0.500</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -18803,15 +18803,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 09:18:12</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>776.01</v>
+        <v>775.6</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -18826,15 +18826,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>776.38</v>
+        <v>776.01</v>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>+0.550</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -18849,15 +18849,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>775.83</v>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>776.38</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -18872,15 +18872,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>776.53</v>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>775.83</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -18895,15 +18895,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.53</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -18918,15 +18918,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 06:08:04</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>776.7</v>
+        <v>776.91</v>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -18941,15 +18941,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 06:08:04</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>776.8</v>
+        <v>776.7</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -18964,15 +18964,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>777.27</v>
+        <v>776.8</v>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>+0.760</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -18987,15 +18987,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>776.51</v>
+        <v>777.27</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.760</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -19010,15 +19010,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>776.29</v>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>+0.390</t>
+        <v>776.51</v>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -19033,15 +19033,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>775.9</v>
+        <v>776.29</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -19056,15 +19056,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>775.58</v>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>775.9</v>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -19079,15 +19079,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>775.48</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>775.58</v>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -19102,15 +19102,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>776.29</v>
+        <v>775.48</v>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -19125,15 +19125,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 06:18:23</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>776.0700000000001</v>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>776.29</v>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -19148,15 +19148,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 06:18:23</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>776.54</v>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>776.0700000000001</v>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -19171,15 +19171,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>776.59</v>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>776.54</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -19194,15 +19194,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>776.13</v>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>+0.810</t>
+        <v>776.59</v>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -19217,15 +19217,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>775.3200000000001</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>776.13</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -19240,15 +19240,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 08:56:04</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>775.6900000000001</v>
+        <v>775.3200000000001</v>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -19263,15 +19263,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 07:06:50</t>
+          <t>2026-09-07 08:56:04</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>775.63</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>775.6900000000001</v>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -19286,15 +19286,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-05 07:06:50</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>776.02</v>
+        <v>775.63</v>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>+0.260</t>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -19309,15 +19309,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>775.76</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>-0.720</t>
+        <v>776.02</v>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -19332,15 +19332,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>776.48</v>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>-0.580</t>
+        <v>775.76</v>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -19355,15 +19355,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>777.0599999999999</v>
+        <v>776.48</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.580</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -19378,15 +19378,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 07:59:45</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>777.13</v>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>-0.540</t>
+        <v>777.0599999999999</v>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -19401,15 +19401,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 07:59:45</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>777.67</v>
+        <v>777.13</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>-0.300</t>
+          <t>-0.540</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -19424,15 +19424,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>777.97</v>
+        <v>777.67</v>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>+1.580</t>
+          <t>-0.300</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -19447,15 +19447,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>776.39</v>
+        <v>777.97</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>+1.580</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -19470,15 +19470,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>776.01</v>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>+0.660</t>
+        <v>776.39</v>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -19493,15 +19493,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>775.35</v>
+        <v>776.01</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>+0.700</t>
+          <t>+0.660</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -19516,15 +19516,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 06:35:56</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>774.65</v>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>775.35</v>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>+0.700</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -19539,15 +19539,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 04:09:22</t>
+          <t>2026-09-03 06:35:56</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>774.64</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>-0.270</t>
+        <v>774.65</v>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -19562,15 +19562,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 04:09:22</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>774.91</v>
+        <v>774.64</v>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>+0.390</t>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -19585,15 +19585,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>774.52</v>
+        <v>774.91</v>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>+0.230</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -19608,15 +19608,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 17:58:25</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>774.29</v>
+        <v>774.52</v>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.230</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -19631,15 +19631,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 17:58:25</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>774.36</v>
+        <v>774.29</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>-0.860</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -19654,15 +19654,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>775.22</v>
+        <v>774.36</v>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>+0.350</t>
+          <t>-0.860</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -19677,15 +19677,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 02:48:49</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>774.87</v>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>775.22</v>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -19700,15 +19700,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 02:48:49</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>775.47</v>
+        <v>774.87</v>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -19723,15 +19723,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>775.25</v>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>-1.030</t>
+        <v>775.47</v>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -19746,15 +19746,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>776.28</v>
-      </c>
-      <c r="D60" s="16" t="inlineStr">
-        <is>
-          <t>-0.280</t>
+        <v>775.25</v>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>-1.030</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -19769,15 +19769,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 09:25:49</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>776.5599999999999</v>
+        <v>776.28</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -19792,15 +19792,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 06:48:36</t>
+          <t>2026-09-01 09:25:49</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>776.58</v>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>776.5599999999999</v>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -19815,15 +19815,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 02:10:52</t>
+          <t>2026-09-01 06:48:36</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>776.63</v>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>+1.230</t>
+        <v>776.58</v>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -19838,15 +19838,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 02:10:52</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>775.4</v>
-      </c>
-      <c r="D64" s="15" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.63</v>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -19861,15 +19861,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>775.4</v>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -19884,15 +19884,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 08:13:17</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>775.92</v>
+        <v>775.22</v>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -19907,15 +19907,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 08:13:17</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>775.85</v>
-      </c>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t>-2.850</t>
+        <v>775.92</v>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -19930,15 +19930,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>778.7</v>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>775.85</v>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>-2.850</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -19953,15 +19953,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>779.1</v>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>778.7</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -19976,15 +19976,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>778.72</v>
+        <v>779.1</v>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>-0.640</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -19999,15 +19999,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>779.36</v>
+        <v>778.72</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>-0.200</t>
+          <t>-0.640</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -20022,15 +20022,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 04:13:31</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>779.5599999999999</v>
+        <v>779.36</v>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -20045,15 +20045,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 04:13:31</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>779.39</v>
-      </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>779.5599999999999</v>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -20068,15 +20068,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>779.6</v>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>-0.430</t>
+        <v>779.39</v>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -20091,15 +20091,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>780.03</v>
+        <v>779.6</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -20114,15 +20114,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 18:53:28</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>780.15</v>
-      </c>
-      <c r="D76" s="16" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>780.03</v>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -20137,15 +20137,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 18:53:28</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>780.62</v>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>+0.560</t>
+        <v>780.15</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -20160,15 +20160,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>780.0599999999999</v>
+        <v>780.62</v>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>+0.560</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -20183,15 +20183,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>780.17</v>
+        <v>780.0599999999999</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -20206,15 +20206,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>780.38</v>
+        <v>780.17</v>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -20229,15 +20229,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 10:07:59</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>780.36</v>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>780.38</v>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -20252,15 +20252,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 07:52:24</t>
+          <t>2026-08-26 10:07:59</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>780.6</v>
+        <v>780.36</v>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -20275,15 +20275,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 01:49:35</t>
+          <t>2026-08-26 07:52:24</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>780.4299999999999</v>
+        <v>780.6</v>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -20298,15 +20298,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 01:49:35</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>780.35</v>
-      </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>780.4299999999999</v>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -20321,15 +20321,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.35</v>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>+0.410</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -20344,15 +20344,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:05:53</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>779.9</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>-0.260</t>
+          <t>+0.410</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -20367,15 +20367,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 21:05:53</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>780.16</v>
+        <v>779.9</v>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>-0.230</t>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -20390,15 +20390,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>780.39</v>
+        <v>780.16</v>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>-0.230</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -20413,15 +20413,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>780.15</v>
+        <v>780.39</v>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>+0.540</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -20436,15 +20436,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:26</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>779.61</v>
+        <v>780.15</v>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.540</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -20459,15 +20459,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:01:55</t>
+          <t>2026-08-25 15:51:26</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>779.65</v>
+        <v>779.61</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -20482,15 +20482,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 15:01:55</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>779.73</v>
-      </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>779.65</v>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -20505,15 +20505,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>780.11</v>
+        <v>779.73</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -20528,15 +20528,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>780.4</v>
+        <v>780.11</v>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -20551,15 +20551,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:57:56</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.4</v>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -20574,15 +20574,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 06:50:27</t>
+          <t>2026-08-25 09:57:56</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>780.1900000000001</v>
-      </c>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>780.3099999999999</v>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -20597,15 +20597,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 06:50:27</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>780.1799999999999</v>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
-        <is>
-          <t>-0.450</t>
+        <v>780.1900000000001</v>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -20620,15 +20620,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>780.63</v>
+        <v>780.1799999999999</v>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>+0.460</t>
+          <t>-0.450</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -20643,15 +20643,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>780.17</v>
-      </c>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.63</v>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -20666,15 +20666,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>780.61</v>
+        <v>780.17</v>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -20689,15 +20689,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>780.14</v>
-      </c>
-      <c r="D101" s="12" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>780.61</v>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -20712,15 +20712,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>780.23</v>
-      </c>
-      <c r="D102" s="16" t="inlineStr">
-        <is>
-          <t>-0.530</t>
+        <v>780.14</v>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -20735,15 +20735,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>780.76</v>
+        <v>780.23</v>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -20758,15 +20758,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>780.91</v>
-      </c>
-      <c r="D104" s="16" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.76</v>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -20781,15 +20781,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>781.35</v>
+        <v>780.91</v>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -20804,15 +20804,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>781.38</v>
+        <v>781.35</v>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -20827,15 +20827,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>781.09</v>
-      </c>
-      <c r="D107" s="12" t="inlineStr">
-        <is>
-          <t>-0.350</t>
+        <v>781.38</v>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -20850,15 +20850,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>781.4400000000001</v>
-      </c>
-      <c r="D108" s="16" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>781.09</v>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>-0.350</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -20873,15 +20873,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>781.55</v>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.4400000000001</v>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -20896,15 +20896,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 09:42:15</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>781.23</v>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>781.55</v>
+      </c>
+      <c r="D110" s="16" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -20919,15 +20919,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 10:32:40</t>
+          <t>2026-08-24 09:42:15</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>781.01</v>
-      </c>
-      <c r="D111" s="12" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>781.23</v>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -20942,15 +20942,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 05:00:11</t>
+          <t>2026-08-22 10:32:40</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>781.11</v>
-      </c>
-      <c r="D112" s="16" t="inlineStr">
-        <is>
-          <t>-0.180</t>
+        <v>781.01</v>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -20965,15 +20965,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 02:00:51</t>
+          <t>2026-08-22 05:00:11</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>781.29</v>
+        <v>781.11</v>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -20988,15 +20988,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-22 02:00:51</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>781.34</v>
+        <v>781.29</v>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>+0.550</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -21011,15 +21011,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>780.79</v>
+        <v>781.34</v>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -21034,15 +21034,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>780.6799999999999</v>
+        <v>780.79</v>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>-0.610</t>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -21057,15 +21057,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>781.29</v>
+        <v>780.6799999999999</v>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>-1.420</t>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -21080,15 +21080,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>782.71</v>
-      </c>
-      <c r="D118" s="16" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>781.29</v>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>-1.420</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -21103,15 +21103,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>782.95</v>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>+1.080</t>
+        <v>782.71</v>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -21126,15 +21126,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>781.87</v>
+        <v>782.95</v>
       </c>
       <c r="D120" s="16" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>+1.080</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -21149,15 +21149,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>782.25</v>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>781.87</v>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -21172,15 +21172,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>781.99</v>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>782.25</v>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -21195,15 +21195,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>781.95</v>
-      </c>
-      <c r="D123" s="12" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>781.99</v>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -21218,15 +21218,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>781.99</v>
-      </c>
-      <c r="D124" s="16" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>781.95</v>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -21241,15 +21241,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>782.39</v>
-      </c>
-      <c r="D125" s="9" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>781.99</v>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -21264,15 +21264,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:13</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>782.03</v>
-      </c>
-      <c r="D126" s="15" t="inlineStr">
-        <is>
-          <t>+0.400</t>
+        <v>782.39</v>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -21287,15 +21287,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 06:49:01</t>
+          <t>2026-08-21 09:10:13</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>781.63</v>
+        <v>782.03</v>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -21310,15 +21310,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 06:49:01</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>780.95</v>
+        <v>781.63</v>
       </c>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>-0.780</t>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -21333,15 +21333,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>781.73</v>
+        <v>780.95</v>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -21356,15 +21356,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D130" s="16" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>781.73</v>
+      </c>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -21379,15 +21379,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>782.1900000000001</v>
-      </c>
-      <c r="D131" s="9" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>781.79</v>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -21402,15 +21402,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>782.04</v>
+        <v>782.1900000000001</v>
       </c>
       <c r="D132" s="16" t="inlineStr">
         <is>
-          <t>-0.700</t>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -21425,15 +21425,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>782.74</v>
-      </c>
-      <c r="D133" s="9" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>782.04</v>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -21448,15 +21448,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>782.42</v>
-      </c>
-      <c r="D134" s="15" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>782.74</v>
+      </c>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -21471,15 +21471,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>781.95</v>
+        <v>782.42</v>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -21494,15 +21494,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>781.14</v>
+        <v>781.95</v>
       </c>
       <c r="D136" s="16" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -21517,15 +21517,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>781.39</v>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>781.14</v>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -21540,15 +21540,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>781.2</v>
-      </c>
-      <c r="D138" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>781.39</v>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -21563,15 +21563,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>781.17</v>
-      </c>
-      <c r="D139" s="12" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.2</v>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -21586,15 +21586,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 10:06:13</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>781.42</v>
-      </c>
-      <c r="D140" s="16" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>781.17</v>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -21609,15 +21609,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 07:36:53</t>
+          <t>2026-08-20 10:06:13</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D141" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>781.42</v>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -21632,15 +21632,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 06:33:42</t>
+          <t>2026-08-20 07:36:53</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>781.77</v>
-      </c>
-      <c r="D142" s="15" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.79</v>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -21655,15 +21655,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 06:33:42</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>781.45</v>
+        <v>781.77</v>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>+0.850</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -21678,15 +21678,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>780.6</v>
-      </c>
-      <c r="D144" s="15" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>781.45</v>
+      </c>
+      <c r="D144" s="16" t="inlineStr">
+        <is>
+          <t>+0.850</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -21701,15 +21701,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>780.12</v>
+        <v>780.6</v>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>+1.750</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -21724,15 +21724,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>778.37</v>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>780.12</v>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>+1.750</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -21747,15 +21747,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>778.09</v>
+        <v>778.37</v>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -21770,15 +21770,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>777.41</v>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>778.09</v>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -21793,15 +21793,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>777.3200000000001</v>
+        <v>777.41</v>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -21816,13 +21816,13 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>777.1</v>
-      </c>
-      <c r="D150" s="15" t="inlineStr">
+        <v>777.3200000000001</v>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
         <is>
           <t>+0.220</t>
         </is>
@@ -21839,15 +21839,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>776.88</v>
-      </c>
-      <c r="D151" s="12" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.1</v>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -21862,15 +21862,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>776.89</v>
+        <v>776.88</v>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -21885,15 +21885,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>776.84</v>
-      </c>
-      <c r="D153" s="12" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>776.89</v>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -21908,15 +21908,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 09:12:00</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>776.9</v>
+        <v>776.84</v>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -21931,15 +21931,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 09:12:00</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>776.72</v>
-      </c>
-      <c r="D155" s="12" t="inlineStr">
-        <is>
-          <t>-0.460</t>
+        <v>776.9</v>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -21954,15 +21954,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>777.1799999999999</v>
+        <v>776.72</v>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>-0.460</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -21977,15 +21977,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>776.55</v>
-      </c>
-      <c r="D157" s="12" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>777.1799999999999</v>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -22000,15 +22000,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:24</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>776.62</v>
+        <v>776.55</v>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -22023,15 +22023,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 17:58:24</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>776.53</v>
+        <v>776.62</v>
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -22046,15 +22046,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>776.36</v>
+        <v>776.53</v>
       </c>
       <c r="D160" s="16" t="inlineStr">
         <is>
-          <t>-0.160</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -22069,15 +22069,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>776.52</v>
+        <v>776.36</v>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.160</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -22092,15 +22092,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>776.53</v>
-      </c>
-      <c r="D162" s="16" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>776.52</v>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -22115,15 +22115,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>776.92</v>
-      </c>
-      <c r="D163" s="9" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>776.53</v>
+      </c>
+      <c r="D163" s="12" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -22138,15 +22138,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 10:04:24</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>776.8200000000001</v>
-      </c>
-      <c r="D164" s="15" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.92</v>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -22161,15 +22161,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 07:54:32</t>
+          <t>2026-08-18 10:04:24</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>776.61</v>
-      </c>
-      <c r="D165" s="12" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>776.8200000000001</v>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -22184,15 +22184,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 05:48:09</t>
+          <t>2026-08-18 07:54:32</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>776.74</v>
+        <v>776.61</v>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -22207,15 +22207,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 05:48:09</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>776.5599999999999</v>
-      </c>
-      <c r="D167" s="12" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>776.74</v>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -22230,15 +22230,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>777.16</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>+0.350</t>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -22253,15 +22253,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>776.8099999999999</v>
-      </c>
-      <c r="D169" s="12" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>777.16</v>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -22276,15 +22276,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:45</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>777.21</v>
-      </c>
-      <c r="D170" s="16" t="inlineStr">
-        <is>
-          <t>-0.220</t>
+        <v>776.8099999999999</v>
+      </c>
+      <c r="D170" s="15" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -22299,15 +22299,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 21:10:45</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>777.4299999999999</v>
+        <v>777.21</v>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -22322,15 +22322,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>777.52</v>
+        <v>777.4299999999999</v>
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -22345,15 +22345,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>777.5</v>
+        <v>777.52</v>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>+0.370</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -22368,15 +22368,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>777.13</v>
-      </c>
-      <c r="D174" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>777.5</v>
+      </c>
+      <c r="D174" s="16" t="inlineStr">
+        <is>
+          <t>+0.370</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -22391,15 +22391,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>777.04</v>
+        <v>777.13</v>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -22414,15 +22414,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>776.9</v>
+        <v>777.04</v>
       </c>
       <c r="D176" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -22437,15 +22437,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>776.91</v>
+        <v>776.9</v>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -22460,15 +22460,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>776.96</v>
+        <v>776.91</v>
       </c>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -22483,15 +22483,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 09:21:39</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>776.84</v>
+        <v>776.96</v>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>+0.750</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -22506,15 +22506,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 09:21:39</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>776.09</v>
+        <v>776.84</v>
       </c>
       <c r="D180" s="16" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>+0.750</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -22529,15 +22529,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D181" s="9" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>776.09</v>
+      </c>
+      <c r="D181" s="12" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -22552,15 +22552,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>775.8099999999999</v>
-      </c>
-      <c r="D182" s="15" t="inlineStr">
-        <is>
-          <t>+0.770</t>
+        <v>776.38</v>
+      </c>
+      <c r="D182" s="16" t="inlineStr">
+        <is>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -22575,15 +22575,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>775.04</v>
+        <v>775.8099999999999</v>
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.770</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -22598,15 +22598,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>774.92</v>
-      </c>
-      <c r="D184" s="15" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>775.04</v>
+      </c>
+      <c r="D184" s="16" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -22621,15 +22621,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>774.5599999999999</v>
+        <v>774.92</v>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -22644,15 +22644,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>774.4400000000001</v>
+        <v>774.5599999999999</v>
       </c>
       <c r="D186" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -22667,15 +22667,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>774.46</v>
-      </c>
-      <c r="D187" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>774.4400000000001</v>
+      </c>
+      <c r="D187" s="12" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -22690,15 +22690,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>774.25</v>
-      </c>
-      <c r="D188" s="15" t="inlineStr">
-        <is>
-          <t>+0.310</t>
+        <v>774.46</v>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -22713,15 +22713,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 10:39:02</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>773.9400000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.310</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -22736,15 +22736,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 08:05:13</t>
+          <t>2026-08-14 10:39:02</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>773.9</v>
-      </c>
-      <c r="D190" s="15" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>773.9400000000001</v>
+      </c>
+      <c r="D190" s="16" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -22759,15 +22759,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 07:24:16</t>
+          <t>2026-08-14 08:05:13</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>773.73</v>
+        <v>773.9</v>
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -22782,15 +22782,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 07:24:16</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>773.53</v>
+        <v>773.73</v>
       </c>
       <c r="D192" s="16" t="inlineStr">
         <is>
-          <t>-0.790</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -22805,15 +22805,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>774.3200000000001</v>
-      </c>
-      <c r="D193" s="9" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>773.53</v>
+      </c>
+      <c r="D193" s="12" t="inlineStr">
+        <is>
+          <t>-0.790</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -22828,15 +22828,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>773.75</v>
-      </c>
-      <c r="D194" s="15" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>774.3200000000001</v>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -22851,15 +22851,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>773.7</v>
+        <v>773.75</v>
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -22874,15 +22874,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>773.58</v>
-      </c>
-      <c r="D196" s="15" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>773.7</v>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -22897,15 +22897,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>773.33</v>
-      </c>
-      <c r="D197" s="12" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>773.58</v>
+      </c>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -22920,15 +22920,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>773.39</v>
+        <v>773.33</v>
       </c>
       <c r="D198" s="15" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -22943,15 +22943,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>773.11</v>
-      </c>
-      <c r="D199" s="12" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>773.39</v>
+      </c>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -22966,15 +22966,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>773.24</v>
-      </c>
-      <c r="D200" s="16" t="inlineStr">
-        <is>
-          <t>-0.340</t>
+        <v>773.11</v>
+      </c>
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -22989,15 +22989,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>773.58</v>
+        <v>773.24</v>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -23012,15 +23012,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>773.64</v>
-      </c>
-      <c r="D202" s="16" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>773.58</v>
+      </c>
+      <c r="D202" s="15" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -23035,15 +23035,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>774.11</v>
+        <v>773.64</v>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -23058,15 +23058,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>774.3</v>
-      </c>
-      <c r="D204" s="16" t="inlineStr">
-        <is>
-          <t>-0.740</t>
+        <v>774.11</v>
+      </c>
+      <c r="D204" s="15" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>775.04</v>
-      </c>
-      <c r="D205" s="9" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>774.3</v>
+      </c>
+      <c r="D205" s="12" t="inlineStr">
+        <is>
+          <t>-0.740</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -23104,15 +23104,15 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>774.9</v>
-      </c>
-      <c r="D206" s="15" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>775.04</v>
+      </c>
+      <c r="D206" s="16" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -23127,15 +23127,15 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>774.66</v>
+        <v>774.9</v>
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -23150,15 +23150,15 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>774.34</v>
-      </c>
-      <c r="D208" s="15" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>774.66</v>
+      </c>
+      <c r="D208" s="16" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -23173,15 +23173,15 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C209" s="8" t="n">
-        <v>774.15</v>
-      </c>
-      <c r="D209" s="12" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>774.34</v>
+      </c>
+      <c r="D209" s="9" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -23196,15 +23196,15 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 13:53:42</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>774.25</v>
-      </c>
-      <c r="D210" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>774.15</v>
+      </c>
+      <c r="D210" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -23219,15 +23219,15 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 13:53:42</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
-        <v>774.3200000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -23242,15 +23242,15 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>774.74</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="D212" s="15" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -23265,15 +23265,15 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 01:28:47</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>774.5</v>
+        <v>774.74</v>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -23288,15 +23288,15 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 01:28:47</t>
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>774.37</v>
+        <v>774.5</v>
       </c>
       <c r="D214" s="16" t="inlineStr">
         <is>
-          <t>-0.340</t>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -23311,15 +23311,15 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>774.71</v>
-      </c>
-      <c r="D215" s="9" t="inlineStr">
-        <is>
-          <t>+1.160</t>
+        <v>774.37</v>
+      </c>
+      <c r="D215" s="12" t="inlineStr">
+        <is>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -23334,15 +23334,15 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>773.55</v>
+        <v>774.71</v>
       </c>
       <c r="D216" s="16" t="inlineStr">
         <is>
-          <t>-0.520</t>
+          <t>+1.160</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -23357,15 +23357,15 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
-        <v>774.0700000000001</v>
+        <v>773.55</v>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>-0.690</t>
+          <t>-0.520</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -23380,15 +23380,15 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>774.76</v>
-      </c>
-      <c r="D218" s="16" t="inlineStr">
-        <is>
-          <t>-0.550</t>
+        <v>774.0700000000001</v>
+      </c>
+      <c r="D218" s="15" t="inlineStr">
+        <is>
+          <t>-0.690</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -23403,15 +23403,15 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>775.3099999999999</v>
+        <v>774.76</v>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>775.46</v>
-      </c>
-      <c r="D220" s="16" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>775.3099999999999</v>
+      </c>
+      <c r="D220" s="15" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>775.84</v>
+        <v>775.46</v>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 08:05:33</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>775.9</v>
+        <v>775.84</v>
       </c>
       <c r="D222" s="15" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 08:05:33</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>775.83</v>
+        <v>775.9</v>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>775.2</v>
+        <v>775.83</v>
       </c>
       <c r="D224" s="16" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>775.28</v>
-      </c>
-      <c r="D225" s="9" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>775.2</v>
+      </c>
+      <c r="D225" s="12" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>775.12</v>
-      </c>
-      <c r="D226" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>775.28</v>
+      </c>
+      <c r="D226" s="16" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -23587,11 +23587,11 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>775.09</v>
+        <v>775.12</v>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
@@ -23610,15 +23610,15 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 18:37:13</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C228" s="6" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D228" s="15" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>775.09</v>
+      </c>
+      <c r="D228" s="16" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -23633,15 +23633,15 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 18:37:13</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>774.58</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
@@ -23656,15 +23656,15 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>774.29</v>
-      </c>
-      <c r="D230" s="15" t="inlineStr">
-        <is>
-          <t>+0.490</t>
+        <v>774.58</v>
+      </c>
+      <c r="D230" s="16" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -23679,15 +23679,15 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>773.8</v>
-      </c>
-      <c r="D231" s="12" t="inlineStr">
-        <is>
-          <t>-0.590</t>
+        <v>774.29</v>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>+0.490</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -23702,14 +23702,37 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="n">
+        <v>773.8</v>
+      </c>
+      <c r="D232" s="15" t="inlineStr">
+        <is>
+          <t>-0.590</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="n">
+        <v>229</v>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C232" s="6" t="n">
+      <c r="C233" s="8" t="n">
         <v>774.39</v>
       </c>
-      <c r="D232" s="6" t="inlineStr"/>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="D233" s="8" t="inlineStr"/>
+      <c r="E233" s="8" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>
@@ -23816,7 +23839,7 @@
       <c r="C6" s="6" t="n">
         <v>669.3099999999999</v>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>-0.080</t>
         </is>
@@ -23862,7 +23885,7 @@
       <c r="C8" s="6" t="n">
         <v>669.17</v>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>+0.150</t>
         </is>
@@ -23908,7 +23931,7 @@
       <c r="C10" s="6" t="n">
         <v>669.05</v>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -23954,7 +23977,7 @@
       <c r="C12" s="6" t="n">
         <v>668.85</v>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -24000,7 +24023,7 @@
       <c r="C14" s="6" t="n">
         <v>668.92</v>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
@@ -24046,7 +24069,7 @@
       <c r="C16" s="6" t="n">
         <v>669.34</v>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -24092,7 +24115,7 @@
       <c r="C18" s="6" t="n">
         <v>668.88</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>+0.120</t>
         </is>
@@ -24138,7 +24161,7 @@
       <c r="C20" s="6" t="n">
         <v>668.91</v>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>-0.060</t>
         </is>
@@ -24184,7 +24207,7 @@
       <c r="C22" s="6" t="n">
         <v>668.78</v>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
@@ -24230,7 +24253,7 @@
       <c r="C24" s="6" t="n">
         <v>668.88</v>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>-0.260</t>
         </is>
@@ -24276,7 +24299,7 @@
       <c r="C26" s="6" t="n">
         <v>669.16</v>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -24322,7 +24345,7 @@
       <c r="C28" s="6" t="n">
         <v>669.2</v>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -24368,7 +24391,7 @@
       <c r="C30" s="6" t="n">
         <v>669.22</v>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -24414,7 +24437,7 @@
       <c r="C32" s="6" t="n">
         <v>669.3099999999999</v>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>+0.060</t>
         </is>
@@ -24460,7 +24483,7 @@
       <c r="C34" s="6" t="n">
         <v>669.2</v>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -24506,7 +24529,7 @@
       <c r="C36" s="6" t="n">
         <v>669.78</v>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
@@ -24552,7 +24575,7 @@
       <c r="C38" s="6" t="n">
         <v>669.96</v>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -24598,7 +24621,7 @@
       <c r="C40" s="6" t="n">
         <v>669.9299999999999</v>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -24644,7 +24667,7 @@
       <c r="C42" s="6" t="n">
         <v>670.04</v>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>-0.210</t>
         </is>
@@ -24690,7 +24713,7 @@
       <c r="C44" s="6" t="n">
         <v>670.38</v>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>+0.190</t>
         </is>
@@ -24736,7 +24759,7 @@
       <c r="C46" s="6" t="n">
         <v>670.2</v>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>-0.150</t>
         </is>
@@ -24782,7 +24805,7 @@
       <c r="C48" s="6" t="n">
         <v>670.24</v>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>+0.140</t>
         </is>
@@ -24828,7 +24851,7 @@
       <c r="C50" s="6" t="n">
         <v>670.22</v>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>-0.920</t>
         </is>
@@ -24874,7 +24897,7 @@
       <c r="C52" s="6" t="n">
         <v>670.21</v>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -24920,7 +24943,7 @@
       <c r="C54" s="6" t="n">
         <v>670.13</v>
       </c>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>-0.110</t>
         </is>
@@ -24966,7 +24989,7 @@
       <c r="C56" s="6" t="n">
         <v>670.42</v>
       </c>
-      <c r="D56" s="15" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>+0.080</t>
         </is>
@@ -25012,7 +25035,7 @@
       <c r="C58" s="6" t="n">
         <v>670.1900000000001</v>
       </c>
-      <c r="D58" s="15" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -25058,7 +25081,7 @@
       <c r="C60" s="6" t="n">
         <v>670.27</v>
       </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>+0.050</t>
         </is>
@@ -25104,7 +25127,7 @@
       <c r="C62" s="6" t="n">
         <v>670.26</v>
       </c>
-      <c r="D62" s="15" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -25150,7 +25173,7 @@
       <c r="C64" s="6" t="n">
         <v>670.11</v>
       </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -25196,7 +25219,7 @@
       <c r="C66" s="6" t="n">
         <v>670.2</v>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D66" s="15" t="inlineStr">
         <is>
           <t>-0.200</t>
         </is>
@@ -25242,7 +25265,7 @@
       <c r="C68" s="6" t="n">
         <v>670.47</v>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D68" s="15" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -25288,7 +25311,7 @@
       <c r="C70" s="6" t="n">
         <v>670.51</v>
       </c>
-      <c r="D70" s="15" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>+0.200</t>
         </is>
@@ -25334,7 +25357,7 @@
       <c r="C72" s="6" t="n">
         <v>670.34</v>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="D72" s="15" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -25380,7 +25403,7 @@
       <c r="C74" s="6" t="n">
         <v>670.34</v>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="D74" s="15" t="inlineStr">
         <is>
           <t>-0.090</t>
         </is>
@@ -25426,7 +25449,7 @@
       <c r="C76" s="6" t="n">
         <v>670.46</v>
       </c>
-      <c r="D76" s="15" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -25472,7 +25495,7 @@
       <c r="C78" s="6" t="n">
         <v>670.45</v>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D78" s="15" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -25518,7 +25541,7 @@
       <c r="C80" s="6" t="n">
         <v>670.4400000000001</v>
       </c>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="D80" s="15" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -25564,7 +25587,7 @@
       <c r="C82" s="6" t="n">
         <v>670.48</v>
       </c>
-      <c r="D82" s="15" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -25610,7 +25633,7 @@
       <c r="C84" s="6" t="n">
         <v>670.25</v>
       </c>
-      <c r="D84" s="16" t="inlineStr">
+      <c r="D84" s="15" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -25656,7 +25679,7 @@
       <c r="C86" s="6" t="n">
         <v>670.23</v>
       </c>
-      <c r="D86" s="15" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -25702,7 +25725,7 @@
       <c r="C88" s="6" t="n">
         <v>670.1799999999999</v>
       </c>
-      <c r="D88" s="15" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -25748,7 +25771,7 @@
       <c r="C90" s="6" t="n">
         <v>670.1799999999999</v>
       </c>
-      <c r="D90" s="16" t="inlineStr">
+      <c r="D90" s="15" t="inlineStr">
         <is>
           <t>-0.100</t>
         </is>
@@ -25794,7 +25817,7 @@
       <c r="C92" s="6" t="n">
         <v>670.29</v>
       </c>
-      <c r="D92" s="15" t="inlineStr">
+      <c r="D92" s="16" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -25840,7 +25863,7 @@
       <c r="C94" s="6" t="n">
         <v>670.3099999999999</v>
       </c>
-      <c r="D94" s="16" t="inlineStr">
+      <c r="D94" s="15" t="inlineStr">
         <is>
           <t>-0.140</t>
         </is>
@@ -25886,7 +25909,7 @@
       <c r="C96" s="6" t="n">
         <v>670.62</v>
       </c>
-      <c r="D96" s="15" t="inlineStr">
+      <c r="D96" s="16" t="inlineStr">
         <is>
           <t>+0.120</t>
         </is>
@@ -25932,7 +25955,7 @@
       <c r="C98" s="6" t="n">
         <v>670.4400000000001</v>
       </c>
-      <c r="D98" s="16" t="inlineStr">
+      <c r="D98" s="15" t="inlineStr">
         <is>
           <t>-0.040</t>
         </is>
@@ -25978,7 +26001,7 @@
       <c r="C100" s="6" t="n">
         <v>670.4</v>
       </c>
-      <c r="D100" s="15" t="inlineStr">
+      <c r="D100" s="16" t="inlineStr">
         <is>
           <t>+0.140</t>
         </is>
@@ -26024,7 +26047,7 @@
       <c r="C102" s="6" t="n">
         <v>670.51</v>
       </c>
-      <c r="D102" s="16" t="inlineStr">
+      <c r="D102" s="15" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -26070,7 +26093,7 @@
       <c r="C104" s="6" t="n">
         <v>670.62</v>
       </c>
-      <c r="D104" s="15" t="inlineStr">
+      <c r="D104" s="16" t="inlineStr">
         <is>
           <t>+0.060</t>
         </is>
@@ -26116,7 +26139,7 @@
       <c r="C106" s="6" t="n">
         <v>670.59</v>
       </c>
-      <c r="D106" s="15" t="inlineStr">
+      <c r="D106" s="16" t="inlineStr">
         <is>
           <t>+0.070</t>
         </is>
@@ -26162,7 +26185,7 @@
       <c r="C108" s="6" t="n">
         <v>670.53</v>
       </c>
-      <c r="D108" s="16" t="inlineStr">
+      <c r="D108" s="15" t="inlineStr">
         <is>
           <t>-0.530</t>
         </is>
@@ -26208,7 +26231,7 @@
       <c r="C110" s="6" t="n">
         <v>671.0700000000001</v>
       </c>
-      <c r="D110" s="16" t="inlineStr">
+      <c r="D110" s="15" t="inlineStr">
         <is>
           <t>-0.570</t>
         </is>
@@ -26254,7 +26277,7 @@
       <c r="C112" s="6" t="n">
         <v>671.88</v>
       </c>
-      <c r="D112" s="16" t="inlineStr">
+      <c r="D112" s="15" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -26300,7 +26323,7 @@
       <c r="C114" s="6" t="n">
         <v>672.05</v>
       </c>
-      <c r="D114" s="15" t="inlineStr">
+      <c r="D114" s="16" t="inlineStr">
         <is>
           <t>+0.180</t>
         </is>
@@ -26346,7 +26369,7 @@
       <c r="C116" s="6" t="n">
         <v>672.09</v>
       </c>
-      <c r="D116" s="16" t="inlineStr">
+      <c r="D116" s="15" t="inlineStr">
         <is>
           <t>-0.120</t>
         </is>
@@ -26392,7 +26415,7 @@
       <c r="C118" s="6" t="n">
         <v>672.14</v>
       </c>
-      <c r="D118" s="16" t="inlineStr">
+      <c r="D118" s="15" t="inlineStr">
         <is>
           <t>-0.060</t>
         </is>
@@ -26438,7 +26461,7 @@
       <c r="C120" s="6" t="n">
         <v>672.47</v>
       </c>
-      <c r="D120" s="16" t="inlineStr">
+      <c r="D120" s="15" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -26484,7 +26507,7 @@
       <c r="C122" s="6" t="n">
         <v>672.53</v>
       </c>
-      <c r="D122" s="15" t="inlineStr">
+      <c r="D122" s="16" t="inlineStr">
         <is>
           <t>+0.170</t>
         </is>
@@ -26530,7 +26553,7 @@
       <c r="C124" s="6" t="n">
         <v>672.37</v>
       </c>
-      <c r="D124" s="16" t="inlineStr">
+      <c r="D124" s="15" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -26576,7 +26599,7 @@
       <c r="C126" s="6" t="n">
         <v>672.54</v>
       </c>
-      <c r="D126" s="15" t="inlineStr">
+      <c r="D126" s="16" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -26622,7 +26645,7 @@
       <c r="C128" s="6" t="n">
         <v>672.41</v>
       </c>
-      <c r="D128" s="15" t="inlineStr">
+      <c r="D128" s="16" t="inlineStr">
         <is>
           <t>+0.200</t>
         </is>
@@ -26668,7 +26691,7 @@
       <c r="C130" s="6" t="n">
         <v>672.17</v>
       </c>
-      <c r="D130" s="15" t="inlineStr">
+      <c r="D130" s="16" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -26714,7 +26737,7 @@
       <c r="C132" s="6" t="n">
         <v>671.9400000000001</v>
       </c>
-      <c r="D132" s="16" t="inlineStr">
+      <c r="D132" s="15" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -26760,7 +26783,7 @@
       <c r="C134" s="6" t="n">
         <v>672.02</v>
       </c>
-      <c r="D134" s="16" t="inlineStr">
+      <c r="D134" s="15" t="inlineStr">
         <is>
           <t>-0.200</t>
         </is>
@@ -26806,7 +26829,7 @@
       <c r="C136" s="6" t="n">
         <v>672.26</v>
       </c>
-      <c r="D136" s="16" t="inlineStr">
+      <c r="D136" s="15" t="inlineStr">
         <is>
           <t>-0.100</t>
         </is>
@@ -26852,7 +26875,7 @@
       <c r="C138" s="6" t="n">
         <v>672.24</v>
       </c>
-      <c r="D138" s="15" t="inlineStr">
+      <c r="D138" s="16" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -26898,7 +26921,7 @@
       <c r="C140" s="6" t="n">
         <v>672.36</v>
       </c>
-      <c r="D140" s="15" t="inlineStr">
+      <c r="D140" s="16" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -26944,7 +26967,7 @@
       <c r="C142" s="6" t="n">
         <v>672.24</v>
       </c>
-      <c r="D142" s="16" t="inlineStr">
+      <c r="D142" s="15" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -26990,7 +27013,7 @@
       <c r="C144" s="6" t="n">
         <v>672.3</v>
       </c>
-      <c r="D144" s="16" t="inlineStr">
+      <c r="D144" s="15" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
@@ -27036,7 +27059,7 @@
       <c r="C146" s="6" t="n">
         <v>672.5</v>
       </c>
-      <c r="D146" s="15" t="inlineStr">
+      <c r="D146" s="16" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -27082,7 +27105,7 @@
       <c r="C148" s="6" t="n">
         <v>672.54</v>
       </c>
-      <c r="D148" s="15" t="inlineStr">
+      <c r="D148" s="16" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -27128,7 +27151,7 @@
       <c r="C150" s="6" t="n">
         <v>672.35</v>
       </c>
-      <c r="D150" s="16" t="inlineStr">
+      <c r="D150" s="15" t="inlineStr">
         <is>
           <t>-0.080</t>
         </is>
@@ -27174,7 +27197,7 @@
       <c r="C152" s="6" t="n">
         <v>672.46</v>
       </c>
-      <c r="D152" s="16" t="inlineStr">
+      <c r="D152" s="15" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
@@ -27220,7 +27243,7 @@
       <c r="C154" s="6" t="n">
         <v>672.5700000000001</v>
       </c>
-      <c r="D154" s="15" t="inlineStr">
+      <c r="D154" s="16" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -27266,7 +27289,7 @@
       <c r="C156" s="6" t="n">
         <v>672.54</v>
       </c>
-      <c r="D156" s="15" t="inlineStr">
+      <c r="D156" s="16" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -27312,7 +27335,7 @@
       <c r="C158" s="6" t="n">
         <v>672.61</v>
       </c>
-      <c r="D158" s="15" t="inlineStr">
+      <c r="D158" s="16" t="inlineStr">
         <is>
           <t>+0.060</t>
         </is>
@@ -27358,7 +27381,7 @@
       <c r="C160" s="6" t="n">
         <v>672.5</v>
       </c>
-      <c r="D160" s="15" t="inlineStr">
+      <c r="D160" s="16" t="inlineStr">
         <is>
           <t>+0.160</t>
         </is>
@@ -27404,7 +27427,7 @@
       <c r="C162" s="6" t="n">
         <v>672.33</v>
       </c>
-      <c r="D162" s="15" t="inlineStr">
+      <c r="D162" s="16" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -27450,7 +27473,7 @@
       <c r="C164" s="6" t="n">
         <v>672.41</v>
       </c>
-      <c r="D164" s="16" t="inlineStr">
+      <c r="D164" s="15" t="inlineStr">
         <is>
           <t>-0.250</t>
         </is>
@@ -27496,7 +27519,7 @@
       <c r="C166" s="6" t="n">
         <v>672.78</v>
       </c>
-      <c r="D166" s="15" t="inlineStr">
+      <c r="D166" s="16" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -27542,7 +27565,7 @@
       <c r="C168" s="6" t="n">
         <v>672.71</v>
       </c>
-      <c r="D168" s="15" t="inlineStr">
+      <c r="D168" s="16" t="inlineStr">
         <is>
           <t>+0.040</t>
         </is>
@@ -27588,7 +27611,7 @@
       <c r="C170" s="6" t="n">
         <v>672.59</v>
       </c>
-      <c r="D170" s="16" t="inlineStr">
+      <c r="D170" s="15" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -27634,7 +27657,7 @@
       <c r="C172" s="6" t="n">
         <v>672.8200000000001</v>
       </c>
-      <c r="D172" s="16" t="inlineStr">
+      <c r="D172" s="15" t="inlineStr">
         <is>
           <t>-0.420</t>
         </is>
@@ -27680,7 +27703,7 @@
       <c r="C174" s="6" t="n">
         <v>672.9</v>
       </c>
-      <c r="D174" s="16" t="inlineStr">
+      <c r="D174" s="15" t="inlineStr">
         <is>
           <t>-0.140</t>
         </is>
@@ -27726,7 +27749,7 @@
       <c r="C176" s="6" t="n">
         <v>673.03</v>
       </c>
-      <c r="D176" s="15" t="inlineStr">
+      <c r="D176" s="16" t="inlineStr">
         <is>
           <t>+0.240</t>
         </is>
@@ -27772,7 +27795,7 @@
       <c r="C178" s="6" t="n">
         <v>673.03</v>
       </c>
-      <c r="D178" s="15" t="inlineStr">
+      <c r="D178" s="16" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -27818,7 +27841,7 @@
       <c r="C180" s="6" t="n">
         <v>673.01</v>
       </c>
-      <c r="D180" s="16" t="inlineStr">
+      <c r="D180" s="15" t="inlineStr">
         <is>
           <t>-0.080</t>
         </is>
@@ -27864,7 +27887,7 @@
       <c r="C182" s="6" t="n">
         <v>673.11</v>
       </c>
-      <c r="D182" s="15" t="inlineStr">
+      <c r="D182" s="16" t="inlineStr">
         <is>
           <t>+0.140</t>
         </is>
@@ -27910,7 +27933,7 @@
       <c r="C184" s="6" t="n">
         <v>672.87</v>
       </c>
-      <c r="D184" s="15" t="inlineStr">
+      <c r="D184" s="16" t="inlineStr">
         <is>
           <t>+0.130</t>
         </is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -185,10 +185,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 03:44:55</t>
+          <t>更新时间: 2026-09-17 06:22:21</t>
         </is>
       </c>
     </row>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>769.75</v>
+        <v>765.05</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -765,15 +765,15 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>668.76</v>
+        <v>669.03</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E238"/>
+  <dimension ref="A1:E239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18674,7 +18674,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 769.75 | 最高: 782.950 | 最低: 769.750 | 总记录数: 234</t>
+          <t>最新价: 765.05 | 最高: 782.950 | 最低: 765.050 | 总记录数: 235</t>
         </is>
       </c>
     </row>
@@ -18711,15 +18711,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>769.75</v>
+        <v>765.05</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-4.700</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -18734,15 +18734,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>770.04</v>
+        <v>769.75</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -18757,15 +18757,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>769.95</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>-0.730</t>
+        <v>770.04</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -18780,15 +18780,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>770.6799999999999</v>
+        <v>769.95</v>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -18803,15 +18803,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:40:23</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>770.47</v>
+        <v>770.6799999999999</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -18826,15 +18826,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 07:41:58</t>
+          <t>2026-09-16 09:40:23</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>770.38</v>
+        <v>770.47</v>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -18849,15 +18849,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>770.8</v>
+        <v>770.38</v>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -18872,15 +18872,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>770.8200000000001</v>
+        <v>770.8</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>+0.400</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -18895,15 +18895,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>770.42</v>
+        <v>770.8200000000001</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -18918,15 +18918,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>770.24</v>
+        <v>770.42</v>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>-0.810</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -18941,11 +18941,11 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>771.05</v>
+        <v>770.24</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
@@ -18964,15 +18964,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>771.86</v>
+        <v>771.05</v>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>+1.540</t>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -18987,15 +18987,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>770.3200000000001</v>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>771.86</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -19010,15 +19010,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>771.76</v>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>-2.140</t>
+        <v>770.3200000000001</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -19033,15 +19033,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12 05:00:53</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>773.9</v>
+        <v>771.76</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-2.140</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -19056,15 +19056,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15:57</t>
+          <t>2026-09-12 05:00:53</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>774.33</v>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>-0.730</t>
+        <v>773.9</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -19079,15 +19079,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-12 02:15:57</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>+1.400</t>
+        <v>774.33</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -19102,15 +19102,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>773.66</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>-1.440</t>
+          <t>+1.400</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -19125,15 +19125,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>775.1</v>
+        <v>773.66</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>-0.500</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -19148,15 +19148,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:18:12</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>775.6</v>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>-0.410</t>
+        <v>775.1</v>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>-0.500</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -19171,15 +19171,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 09:18:12</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>776.01</v>
+        <v>775.6</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -19194,15 +19194,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>776.38</v>
+        <v>776.01</v>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>+0.550</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -19217,15 +19217,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>775.83</v>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>776.38</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -19240,15 +19240,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>776.53</v>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>775.83</v>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -19263,15 +19263,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.53</v>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -19286,15 +19286,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 06:08:04</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>776.7</v>
+        <v>776.91</v>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -19309,15 +19309,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 06:08:04</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>776.8</v>
+        <v>776.7</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -19332,15 +19332,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>777.27</v>
+        <v>776.8</v>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>+0.760</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -19355,15 +19355,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>776.51</v>
+        <v>777.27</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.760</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -19378,15 +19378,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>776.29</v>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>+0.390</t>
+        <v>776.51</v>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -19401,15 +19401,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>775.9</v>
+        <v>776.29</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -19424,15 +19424,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>775.58</v>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>775.9</v>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -19447,15 +19447,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>775.48</v>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>775.58</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -19470,15 +19470,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>776.29</v>
+        <v>775.48</v>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -19493,15 +19493,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 06:18:23</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>776.0700000000001</v>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>776.29</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -19516,15 +19516,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 06:18:23</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>776.54</v>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>776.0700000000001</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -19539,15 +19539,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>776.59</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>776.54</v>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -19562,15 +19562,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>776.13</v>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>+0.810</t>
+        <v>776.59</v>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -19585,15 +19585,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>775.3200000000001</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>776.13</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -19608,15 +19608,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 08:56:04</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>775.6900000000001</v>
+        <v>775.3200000000001</v>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -19631,15 +19631,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 07:06:50</t>
+          <t>2026-09-07 08:56:04</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>775.63</v>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>775.6900000000001</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -19654,15 +19654,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-05 07:06:50</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>776.02</v>
+        <v>775.63</v>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>+0.260</t>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -19677,15 +19677,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>775.76</v>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>-0.720</t>
+        <v>776.02</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -19700,15 +19700,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>776.48</v>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>-0.580</t>
+        <v>775.76</v>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -19723,15 +19723,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>777.0599999999999</v>
+        <v>776.48</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.580</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -19746,15 +19746,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 07:59:45</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>777.13</v>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>-0.540</t>
+        <v>777.0599999999999</v>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -19769,15 +19769,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 07:59:45</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>777.67</v>
+        <v>777.13</v>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>-0.300</t>
+          <t>-0.540</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -19792,15 +19792,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>777.97</v>
+        <v>777.67</v>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>+1.580</t>
+          <t>-0.300</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -19815,15 +19815,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>776.39</v>
+        <v>777.97</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>+1.580</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -19838,15 +19838,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>776.01</v>
-      </c>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>+0.660</t>
+        <v>776.39</v>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -19861,15 +19861,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>775.35</v>
+        <v>776.01</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>+0.700</t>
+          <t>+0.660</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -19884,15 +19884,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 06:35:56</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>774.65</v>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>775.35</v>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>+0.700</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -19907,15 +19907,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 04:09:22</t>
+          <t>2026-09-03 06:35:56</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>774.64</v>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>-0.270</t>
+        <v>774.65</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -19930,15 +19930,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 04:09:22</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>774.91</v>
+        <v>774.64</v>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>+0.390</t>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -19953,15 +19953,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>774.52</v>
+        <v>774.91</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>+0.230</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -19976,15 +19976,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 17:58:25</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>774.29</v>
+        <v>774.52</v>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.230</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -19999,15 +19999,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 17:58:25</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>774.36</v>
+        <v>774.29</v>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>-0.860</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -20022,15 +20022,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>775.22</v>
+        <v>774.36</v>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>+0.350</t>
+          <t>-0.860</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -20045,15 +20045,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 02:48:49</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>774.87</v>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>775.22</v>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -20068,15 +20068,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 02:48:49</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>775.47</v>
+        <v>774.87</v>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -20091,15 +20091,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>775.25</v>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>-1.030</t>
+        <v>775.47</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -20114,15 +20114,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>776.28</v>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>-0.280</t>
+        <v>775.25</v>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>-1.030</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -20137,15 +20137,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 09:25:49</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>776.5599999999999</v>
+        <v>776.28</v>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -20160,15 +20160,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 06:48:36</t>
+          <t>2026-09-01 09:25:49</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>776.58</v>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>776.5599999999999</v>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -20183,15 +20183,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 02:10:52</t>
+          <t>2026-09-01 06:48:36</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>776.63</v>
-      </c>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>+1.230</t>
+        <v>776.58</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -20206,15 +20206,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 02:10:52</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>775.4</v>
-      </c>
-      <c r="D70" s="15" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.63</v>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -20229,15 +20229,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>775.4</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -20252,15 +20252,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 08:13:17</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>775.92</v>
+        <v>775.22</v>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -20275,15 +20275,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 08:13:17</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>775.85</v>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>-2.850</t>
+        <v>775.92</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -20298,15 +20298,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>778.7</v>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>775.85</v>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>-2.850</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -20321,15 +20321,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>779.1</v>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>778.7</v>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -20344,15 +20344,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>778.72</v>
+        <v>779.1</v>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>-0.640</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -20367,15 +20367,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>779.36</v>
+        <v>778.72</v>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>-0.200</t>
+          <t>-0.640</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -20390,15 +20390,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 04:13:31</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>779.5599999999999</v>
+        <v>779.36</v>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -20413,15 +20413,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 04:13:31</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>779.39</v>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>779.5599999999999</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -20436,15 +20436,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>779.6</v>
-      </c>
-      <c r="D80" s="16" t="inlineStr">
-        <is>
-          <t>-0.430</t>
+        <v>779.39</v>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -20459,15 +20459,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>780.03</v>
+        <v>779.6</v>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -20482,15 +20482,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 18:53:28</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>780.15</v>
-      </c>
-      <c r="D82" s="16" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>780.03</v>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -20505,15 +20505,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 18:53:28</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>780.62</v>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>+0.560</t>
+        <v>780.15</v>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -20528,15 +20528,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>780.0599999999999</v>
+        <v>780.62</v>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>+0.560</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -20551,15 +20551,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>780.17</v>
+        <v>780.0599999999999</v>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -20574,15 +20574,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>780.38</v>
+        <v>780.17</v>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -20597,15 +20597,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 10:07:59</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>780.36</v>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>780.38</v>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -20620,15 +20620,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 07:52:24</t>
+          <t>2026-08-26 10:07:59</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>780.6</v>
+        <v>780.36</v>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -20643,15 +20643,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 01:49:35</t>
+          <t>2026-08-26 07:52:24</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>780.4299999999999</v>
+        <v>780.6</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -20666,15 +20666,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 01:49:35</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>780.35</v>
-      </c>
-      <c r="D90" s="15" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>780.4299999999999</v>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -20689,15 +20689,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.35</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>+0.410</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -20712,15 +20712,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:05:53</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>779.9</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>-0.260</t>
+          <t>+0.410</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -20735,15 +20735,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 21:05:53</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>780.16</v>
+        <v>779.9</v>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>-0.230</t>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -20758,15 +20758,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>780.39</v>
+        <v>780.16</v>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>-0.230</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -20781,15 +20781,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>780.15</v>
+        <v>780.39</v>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>+0.540</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -20804,15 +20804,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:26</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>779.61</v>
+        <v>780.15</v>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.540</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -20827,15 +20827,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:01:55</t>
+          <t>2026-08-25 15:51:26</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>779.65</v>
+        <v>779.61</v>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -20850,15 +20850,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 15:01:55</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>779.73</v>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>779.65</v>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -20873,15 +20873,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>780.11</v>
+        <v>779.73</v>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -20896,15 +20896,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>780.4</v>
+        <v>780.11</v>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -20919,15 +20919,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:57:56</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.4</v>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -20942,15 +20942,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 06:50:27</t>
+          <t>2026-08-25 09:57:56</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>780.1900000000001</v>
-      </c>
-      <c r="D102" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>780.3099999999999</v>
+      </c>
+      <c r="D102" s="16" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -20965,15 +20965,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 06:50:27</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>780.1799999999999</v>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>-0.450</t>
+        <v>780.1900000000001</v>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -20988,15 +20988,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>780.63</v>
+        <v>780.1799999999999</v>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>+0.460</t>
+          <t>-0.450</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -21011,15 +21011,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>780.17</v>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.63</v>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -21034,15 +21034,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>780.61</v>
+        <v>780.17</v>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -21057,15 +21057,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>780.14</v>
-      </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>780.61</v>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -21080,15 +21080,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>780.23</v>
-      </c>
-      <c r="D108" s="16" t="inlineStr">
-        <is>
-          <t>-0.530</t>
+        <v>780.14</v>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -21103,15 +21103,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>780.76</v>
+        <v>780.23</v>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -21126,15 +21126,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>780.91</v>
-      </c>
-      <c r="D110" s="16" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.76</v>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -21149,15 +21149,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>781.35</v>
+        <v>780.91</v>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -21172,15 +21172,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>781.38</v>
+        <v>781.35</v>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -21195,15 +21195,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>781.09</v>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>-0.350</t>
+        <v>781.38</v>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -21218,15 +21218,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>781.4400000000001</v>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>781.09</v>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>-0.350</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -21241,15 +21241,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>781.55</v>
-      </c>
-      <c r="D115" s="12" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.4400000000001</v>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -21264,15 +21264,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 09:42:15</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>781.23</v>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>781.55</v>
+      </c>
+      <c r="D116" s="16" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -21287,15 +21287,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 10:32:40</t>
+          <t>2026-08-24 09:42:15</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>781.01</v>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>781.23</v>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -21310,15 +21310,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 05:00:11</t>
+          <t>2026-08-22 10:32:40</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>781.11</v>
-      </c>
-      <c r="D118" s="16" t="inlineStr">
-        <is>
-          <t>-0.180</t>
+        <v>781.01</v>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -21333,15 +21333,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 02:00:51</t>
+          <t>2026-08-22 05:00:11</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>781.29</v>
+        <v>781.11</v>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -21356,15 +21356,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-22 02:00:51</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>781.34</v>
+        <v>781.29</v>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>+0.550</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -21379,15 +21379,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>780.79</v>
+        <v>781.34</v>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -21402,15 +21402,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>780.6799999999999</v>
+        <v>780.79</v>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>-0.610</t>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -21425,15 +21425,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>781.29</v>
+        <v>780.6799999999999</v>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>-1.420</t>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -21448,15 +21448,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>782.71</v>
-      </c>
-      <c r="D124" s="16" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>781.29</v>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>-1.420</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -21471,15 +21471,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>782.95</v>
-      </c>
-      <c r="D125" s="12" t="inlineStr">
-        <is>
-          <t>+1.080</t>
+        <v>782.71</v>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -21494,15 +21494,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>781.87</v>
+        <v>782.95</v>
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>+1.080</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -21517,15 +21517,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>782.25</v>
-      </c>
-      <c r="D127" s="12" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>781.87</v>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -21540,15 +21540,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>781.99</v>
-      </c>
-      <c r="D128" s="15" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>782.25</v>
+      </c>
+      <c r="D128" s="16" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -21563,15 +21563,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>781.95</v>
-      </c>
-      <c r="D129" s="9" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>781.99</v>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -21586,15 +21586,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>781.99</v>
-      </c>
-      <c r="D130" s="16" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>781.95</v>
+      </c>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -21609,15 +21609,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>782.39</v>
-      </c>
-      <c r="D131" s="12" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>781.99</v>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -21632,15 +21632,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:13</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>782.03</v>
-      </c>
-      <c r="D132" s="15" t="inlineStr">
-        <is>
-          <t>+0.400</t>
+        <v>782.39</v>
+      </c>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -21655,15 +21655,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 06:49:01</t>
+          <t>2026-08-21 09:10:13</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>781.63</v>
+        <v>782.03</v>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -21678,15 +21678,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 06:49:01</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>780.95</v>
+        <v>781.63</v>
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>-0.780</t>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -21701,15 +21701,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>781.73</v>
+        <v>780.95</v>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -21724,15 +21724,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D136" s="16" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>781.73</v>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -21747,15 +21747,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>782.1900000000001</v>
-      </c>
-      <c r="D137" s="12" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>781.79</v>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -21770,15 +21770,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>782.04</v>
+        <v>782.1900000000001</v>
       </c>
       <c r="D138" s="16" t="inlineStr">
         <is>
-          <t>-0.700</t>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -21793,15 +21793,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>782.74</v>
-      </c>
-      <c r="D139" s="12" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>782.04</v>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -21816,15 +21816,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>782.42</v>
-      </c>
-      <c r="D140" s="15" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>782.74</v>
+      </c>
+      <c r="D140" s="16" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -21839,15 +21839,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>781.95</v>
+        <v>782.42</v>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -21862,15 +21862,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>781.14</v>
+        <v>781.95</v>
       </c>
       <c r="D142" s="16" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -21885,15 +21885,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>781.39</v>
-      </c>
-      <c r="D143" s="12" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>781.14</v>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -21908,15 +21908,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>781.2</v>
-      </c>
-      <c r="D144" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>781.39</v>
+      </c>
+      <c r="D144" s="16" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -21931,15 +21931,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>781.17</v>
-      </c>
-      <c r="D145" s="9" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.2</v>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -21954,15 +21954,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 10:06:13</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>781.42</v>
-      </c>
-      <c r="D146" s="16" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>781.17</v>
+      </c>
+      <c r="D146" s="15" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -21977,15 +21977,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 07:36:53</t>
+          <t>2026-08-20 10:06:13</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D147" s="12" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>781.42</v>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -22000,15 +22000,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 06:33:42</t>
+          <t>2026-08-20 07:36:53</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>781.77</v>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.79</v>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -22023,15 +22023,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 06:33:42</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>781.45</v>
+        <v>781.77</v>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>+0.850</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -22046,15 +22046,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>780.6</v>
-      </c>
-      <c r="D150" s="15" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>781.45</v>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>+0.850</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -22069,15 +22069,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>780.12</v>
+        <v>780.6</v>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>+1.750</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -22092,15 +22092,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>778.37</v>
-      </c>
-      <c r="D152" s="15" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>780.12</v>
+      </c>
+      <c r="D152" s="16" t="inlineStr">
+        <is>
+          <t>+1.750</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -22115,15 +22115,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>778.09</v>
+        <v>778.37</v>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -22138,15 +22138,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>777.41</v>
-      </c>
-      <c r="D154" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>778.09</v>
+      </c>
+      <c r="D154" s="16" t="inlineStr">
+        <is>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -22161,15 +22161,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>777.3200000000001</v>
+        <v>777.41</v>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -22184,13 +22184,13 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>777.1</v>
-      </c>
-      <c r="D156" s="15" t="inlineStr">
+        <v>777.3200000000001</v>
+      </c>
+      <c r="D156" s="16" t="inlineStr">
         <is>
           <t>+0.220</t>
         </is>
@@ -22207,15 +22207,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>776.88</v>
-      </c>
-      <c r="D157" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.1</v>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -22230,15 +22230,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>776.89</v>
+        <v>776.88</v>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -22253,15 +22253,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>776.84</v>
-      </c>
-      <c r="D159" s="9" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>776.89</v>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -22276,15 +22276,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 09:12:00</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>776.9</v>
+        <v>776.84</v>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -22299,15 +22299,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 09:12:00</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>776.72</v>
-      </c>
-      <c r="D161" s="9" t="inlineStr">
-        <is>
-          <t>-0.460</t>
+        <v>776.9</v>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -22322,15 +22322,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>777.1799999999999</v>
+        <v>776.72</v>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>-0.460</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -22345,15 +22345,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>776.55</v>
-      </c>
-      <c r="D163" s="9" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>777.1799999999999</v>
+      </c>
+      <c r="D163" s="12" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -22368,15 +22368,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:24</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>776.62</v>
+        <v>776.55</v>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -22391,15 +22391,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 17:58:24</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>776.53</v>
+        <v>776.62</v>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -22414,15 +22414,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>776.36</v>
+        <v>776.53</v>
       </c>
       <c r="D166" s="16" t="inlineStr">
         <is>
-          <t>-0.160</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -22437,15 +22437,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>776.52</v>
+        <v>776.36</v>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.160</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -22460,15 +22460,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>776.53</v>
-      </c>
-      <c r="D168" s="16" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>776.52</v>
+      </c>
+      <c r="D168" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -22483,15 +22483,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>776.92</v>
-      </c>
-      <c r="D169" s="12" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>776.53</v>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -22506,15 +22506,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 10:04:24</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>776.8200000000001</v>
-      </c>
-      <c r="D170" s="15" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.92</v>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -22529,15 +22529,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 07:54:32</t>
+          <t>2026-08-18 10:04:24</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>776.61</v>
-      </c>
-      <c r="D171" s="9" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>776.8200000000001</v>
+      </c>
+      <c r="D171" s="12" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -22552,15 +22552,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 05:48:09</t>
+          <t>2026-08-18 07:54:32</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>776.74</v>
+        <v>776.61</v>
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -22575,15 +22575,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 05:48:09</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>776.5599999999999</v>
-      </c>
-      <c r="D173" s="9" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>776.74</v>
+      </c>
+      <c r="D173" s="12" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -22598,15 +22598,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>777.16</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>+0.350</t>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -22621,15 +22621,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>776.8099999999999</v>
-      </c>
-      <c r="D175" s="9" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>777.16</v>
+      </c>
+      <c r="D175" s="12" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -22644,15 +22644,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:45</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>777.21</v>
-      </c>
-      <c r="D176" s="16" t="inlineStr">
-        <is>
-          <t>-0.220</t>
+        <v>776.8099999999999</v>
+      </c>
+      <c r="D176" s="15" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -22667,15 +22667,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 21:10:45</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>777.4299999999999</v>
+        <v>777.21</v>
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -22690,15 +22690,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>777.52</v>
+        <v>777.4299999999999</v>
       </c>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -22713,15 +22713,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>777.5</v>
+        <v>777.52</v>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>+0.370</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -22736,15 +22736,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>777.13</v>
-      </c>
-      <c r="D180" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>777.5</v>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>+0.370</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -22759,15 +22759,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>777.04</v>
+        <v>777.13</v>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -22782,15 +22782,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>776.9</v>
+        <v>777.04</v>
       </c>
       <c r="D182" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -22805,15 +22805,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>776.91</v>
+        <v>776.9</v>
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -22828,15 +22828,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>776.96</v>
+        <v>776.91</v>
       </c>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -22851,15 +22851,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 09:21:39</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>776.84</v>
+        <v>776.96</v>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>+0.750</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -22874,15 +22874,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 09:21:39</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>776.09</v>
+        <v>776.84</v>
       </c>
       <c r="D186" s="16" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>+0.750</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -22897,15 +22897,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D187" s="12" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>776.09</v>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -22920,15 +22920,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>775.8099999999999</v>
-      </c>
-      <c r="D188" s="15" t="inlineStr">
-        <is>
-          <t>+0.770</t>
+        <v>776.38</v>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -22943,15 +22943,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>775.04</v>
+        <v>775.8099999999999</v>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.770</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -22966,15 +22966,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>774.92</v>
-      </c>
-      <c r="D190" s="15" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>775.04</v>
+      </c>
+      <c r="D190" s="16" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -22989,15 +22989,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>774.5599999999999</v>
+        <v>774.92</v>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -23012,15 +23012,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>774.4400000000001</v>
+        <v>774.5599999999999</v>
       </c>
       <c r="D192" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -23035,15 +23035,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>774.46</v>
-      </c>
-      <c r="D193" s="12" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>774.4400000000001</v>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -23058,15 +23058,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>774.25</v>
-      </c>
-      <c r="D194" s="15" t="inlineStr">
-        <is>
-          <t>+0.310</t>
+        <v>774.46</v>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 10:39:02</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>773.9400000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.310</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -23104,15 +23104,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 08:05:13</t>
+          <t>2026-08-14 10:39:02</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>773.9</v>
-      </c>
-      <c r="D196" s="15" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>773.9400000000001</v>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -23127,15 +23127,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 07:24:16</t>
+          <t>2026-08-14 08:05:13</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>773.73</v>
+        <v>773.9</v>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -23150,15 +23150,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 07:24:16</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>773.53</v>
+        <v>773.73</v>
       </c>
       <c r="D198" s="16" t="inlineStr">
         <is>
-          <t>-0.790</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -23173,15 +23173,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>774.3200000000001</v>
-      </c>
-      <c r="D199" s="12" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>773.53</v>
+      </c>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>-0.790</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -23196,15 +23196,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>773.75</v>
-      </c>
-      <c r="D200" s="15" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>774.3200000000001</v>
+      </c>
+      <c r="D200" s="16" t="inlineStr">
+        <is>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -23219,15 +23219,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>773.7</v>
+        <v>773.75</v>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -23242,15 +23242,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>773.58</v>
-      </c>
-      <c r="D202" s="15" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>773.7</v>
+      </c>
+      <c r="D202" s="16" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -23265,15 +23265,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>773.33</v>
-      </c>
-      <c r="D203" s="9" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>773.58</v>
+      </c>
+      <c r="D203" s="12" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -23288,15 +23288,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>773.39</v>
+        <v>773.33</v>
       </c>
       <c r="D204" s="15" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -23311,15 +23311,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>773.11</v>
-      </c>
-      <c r="D205" s="9" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>773.39</v>
+      </c>
+      <c r="D205" s="12" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -23334,15 +23334,15 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>773.24</v>
-      </c>
-      <c r="D206" s="16" t="inlineStr">
-        <is>
-          <t>-0.340</t>
+        <v>773.11</v>
+      </c>
+      <c r="D206" s="15" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -23357,15 +23357,15 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>773.58</v>
+        <v>773.24</v>
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -23380,15 +23380,15 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>773.64</v>
-      </c>
-      <c r="D208" s="16" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>773.58</v>
+      </c>
+      <c r="D208" s="15" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -23403,15 +23403,15 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C209" s="8" t="n">
-        <v>774.11</v>
+        <v>773.64</v>
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>774.3</v>
-      </c>
-      <c r="D210" s="16" t="inlineStr">
-        <is>
-          <t>-0.740</t>
+        <v>774.11</v>
+      </c>
+      <c r="D210" s="15" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
-        <v>775.04</v>
-      </c>
-      <c r="D211" s="12" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>774.3</v>
+      </c>
+      <c r="D211" s="9" t="inlineStr">
+        <is>
+          <t>-0.740</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>774.9</v>
-      </c>
-      <c r="D212" s="15" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>775.04</v>
+      </c>
+      <c r="D212" s="16" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>774.66</v>
+        <v>774.9</v>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>774.34</v>
-      </c>
-      <c r="D214" s="15" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>774.66</v>
+      </c>
+      <c r="D214" s="16" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>774.15</v>
-      </c>
-      <c r="D215" s="9" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>774.34</v>
+      </c>
+      <c r="D215" s="12" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 13:53:42</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>774.25</v>
-      </c>
-      <c r="D216" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>774.15</v>
+      </c>
+      <c r="D216" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -23587,15 +23587,15 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 13:53:42</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
-        <v>774.3200000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -23610,15 +23610,15 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>774.74</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="D218" s="15" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -23633,15 +23633,15 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 01:28:47</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>774.5</v>
+        <v>774.74</v>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -23656,15 +23656,15 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 01:28:47</t>
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>774.37</v>
+        <v>774.5</v>
       </c>
       <c r="D220" s="16" t="inlineStr">
         <is>
-          <t>-0.340</t>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -23679,15 +23679,15 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>774.71</v>
-      </c>
-      <c r="D221" s="12" t="inlineStr">
-        <is>
-          <t>+1.160</t>
+        <v>774.37</v>
+      </c>
+      <c r="D221" s="9" t="inlineStr">
+        <is>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -23702,15 +23702,15 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>773.55</v>
+        <v>774.71</v>
       </c>
       <c r="D222" s="16" t="inlineStr">
         <is>
-          <t>-0.520</t>
+          <t>+1.160</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -23725,15 +23725,15 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>774.0700000000001</v>
+        <v>773.55</v>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>-0.690</t>
+          <t>-0.520</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -23748,15 +23748,15 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>774.76</v>
-      </c>
-      <c r="D224" s="16" t="inlineStr">
-        <is>
-          <t>-0.550</t>
+        <v>774.0700000000001</v>
+      </c>
+      <c r="D224" s="15" t="inlineStr">
+        <is>
+          <t>-0.690</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -23771,15 +23771,15 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>775.3099999999999</v>
+        <v>774.76</v>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -23794,15 +23794,15 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>775.46</v>
-      </c>
-      <c r="D226" s="16" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>775.3099999999999</v>
+      </c>
+      <c r="D226" s="15" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -23817,15 +23817,15 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>775.84</v>
+        <v>775.46</v>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -23840,15 +23840,15 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 08:05:33</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C228" s="6" t="n">
-        <v>775.9</v>
+        <v>775.84</v>
       </c>
       <c r="D228" s="15" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -23863,15 +23863,15 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 08:05:33</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>775.83</v>
+        <v>775.9</v>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
@@ -23886,15 +23886,15 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>775.2</v>
+        <v>775.83</v>
       </c>
       <c r="D230" s="16" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -23909,15 +23909,15 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>775.28</v>
-      </c>
-      <c r="D231" s="12" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>775.2</v>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -23932,15 +23932,15 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C232" s="6" t="n">
-        <v>775.12</v>
-      </c>
-      <c r="D232" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>775.28</v>
+      </c>
+      <c r="D232" s="16" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -23955,11 +23955,11 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C233" s="8" t="n">
-        <v>775.09</v>
+        <v>775.12</v>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
@@ -23978,15 +23978,15 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 18:37:13</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C234" s="6" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D234" s="15" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>775.09</v>
+      </c>
+      <c r="D234" s="16" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -24001,15 +24001,15 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 18:37:13</t>
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>774.58</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
@@ -24024,15 +24024,15 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C236" s="6" t="n">
-        <v>774.29</v>
-      </c>
-      <c r="D236" s="15" t="inlineStr">
-        <is>
-          <t>+0.490</t>
+        <v>774.58</v>
+      </c>
+      <c r="D236" s="16" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -24047,15 +24047,15 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
-        <v>773.8</v>
-      </c>
-      <c r="D237" s="9" t="inlineStr">
-        <is>
-          <t>-0.590</t>
+        <v>774.29</v>
+      </c>
+      <c r="D237" s="12" t="inlineStr">
+        <is>
+          <t>+0.490</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
@@ -24070,14 +24070,37 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="n">
+        <v>773.8</v>
+      </c>
+      <c r="D238" s="15" t="inlineStr">
+        <is>
+          <t>-0.590</t>
+        </is>
+      </c>
+      <c r="E238" s="6" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="8" t="n">
+        <v>235</v>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C238" s="6" t="n">
+      <c r="C239" s="8" t="n">
         <v>774.39</v>
       </c>
-      <c r="D238" s="6" t="inlineStr"/>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="D239" s="8" t="inlineStr"/>
+      <c r="E239" s="8" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>
@@ -24098,7 +24121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E190"/>
+  <dimension ref="A1:E191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -24118,7 +24141,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 668.76 | 最高: 673.240 | 最低: 668.760 | 总记录数: 186</t>
+          <t>最新价: 669.03 | 最高: 673.240 | 最低: 668.760 | 总记录数: 187</t>
         </is>
       </c>
     </row>
@@ -24155,15 +24178,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>668.76</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>669.03</v>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>+0.270</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -24178,15 +24201,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>668.77</v>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>668.76</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -24201,15 +24224,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>668.8200000000001</v>
+        <v>668.77</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>-0.280</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -24224,15 +24247,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>669.1</v>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>668.8200000000001</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -24247,15 +24270,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>669.29</v>
+        <v>669.1</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -24270,15 +24293,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>669.3099999999999</v>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>669.29</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -24293,15 +24316,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>669.39</v>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>669.3099999999999</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -24316,15 +24339,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>669.17</v>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>669.39</v>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -24339,15 +24362,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>669.02</v>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>669.17</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -24362,15 +24385,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>669.05</v>
+        <v>669.02</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -24385,11 +24408,11 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>668.95</v>
+        <v>669.05</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -24408,15 +24431,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>668.85</v>
+        <v>668.95</v>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -24431,15 +24454,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>668.87</v>
+        <v>668.85</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -24454,15 +24477,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>668.92</v>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>668.87</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -24477,15 +24500,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>669.09</v>
+        <v>668.92</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -24500,15 +24523,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>669.34</v>
+        <v>669.09</v>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -24523,15 +24546,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>669.33</v>
+        <v>669.34</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>+0.450</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -24546,15 +24569,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>668.88</v>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>669.33</v>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>+0.450</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -24569,15 +24592,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>668.76</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>668.88</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -24592,15 +24615,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>668.91</v>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>668.76</v>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -24615,15 +24638,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>668.97</v>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>668.91</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -24638,15 +24661,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>668.78</v>
+        <v>668.97</v>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -24661,15 +24684,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>668.95</v>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>668.78</v>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -24684,15 +24707,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>668.88</v>
+        <v>668.95</v>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>-0.260</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -24707,15 +24730,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>669.14</v>
+        <v>668.88</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -24730,15 +24753,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>669.16</v>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>669.14</v>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -24753,15 +24776,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>669.23</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>669.16</v>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -24776,15 +24799,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>669.2</v>
+        <v>669.23</v>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -24799,15 +24822,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>669.23</v>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>669.2</v>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -24822,15 +24845,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>669.22</v>
+        <v>669.23</v>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -24845,15 +24868,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>669.24</v>
+        <v>669.22</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -24868,15 +24891,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>669.3099999999999</v>
+        <v>669.24</v>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -24891,15 +24914,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>669.25</v>
+        <v>669.3099999999999</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -24914,15 +24937,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>669.2</v>
+        <v>669.25</v>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -24937,15 +24960,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>669.27</v>
+        <v>669.2</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>-0.510</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -24960,15 +24983,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>669.78</v>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>669.27</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>-0.510</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -24983,15 +25006,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>669.95</v>
+        <v>669.78</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -25006,15 +25029,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>669.96</v>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>669.95</v>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -25029,15 +25052,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>670.03</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>669.96</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -25052,15 +25075,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>669.9299999999999</v>
+        <v>670.03</v>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -25075,15 +25098,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>669.9400000000001</v>
+        <v>669.9299999999999</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -25098,15 +25121,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>670.04</v>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>669.9400000000001</v>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -25121,15 +25144,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>670.25</v>
+        <v>670.04</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -25144,15 +25167,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>670.38</v>
+        <v>670.25</v>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -25167,15 +25190,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>670.1900000000001</v>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.38</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -25190,15 +25213,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>670.2</v>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>670.1900000000001</v>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -25213,15 +25236,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>670.35</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>670.2</v>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -25236,15 +25259,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>670.24</v>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>670.35</v>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -25259,15 +25282,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>670.1</v>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>-0.120</t>
+        <v>670.24</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -25282,15 +25305,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>670.22</v>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>-0.920</t>
+        <v>670.1</v>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -25305,15 +25328,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>671.14</v>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>+0.930</t>
+        <v>670.22</v>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>-0.920</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -25328,15 +25351,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>670.21</v>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>671.14</v>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>+0.930</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -25351,15 +25374,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>670.11</v>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>670.21</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -25374,15 +25397,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>670.13</v>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>670.11</v>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -25397,15 +25420,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>670.24</v>
+        <v>670.13</v>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>-0.180</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -25420,15 +25443,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>670.42</v>
+        <v>670.24</v>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -25443,15 +25466,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>670.34</v>
+        <v>670.42</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>+0.150</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -25466,15 +25489,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>670.1900000000001</v>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>670.34</v>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -25489,15 +25512,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>670.1799999999999</v>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>670.1900000000001</v>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -25512,15 +25535,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>670.27</v>
+        <v>670.1799999999999</v>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -25535,15 +25558,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>670.22</v>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>670.27</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -25558,15 +25581,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>670.26</v>
+        <v>670.22</v>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -25581,15 +25604,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>670.16</v>
+        <v>670.26</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -25604,15 +25627,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>670.11</v>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>670.16</v>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -25627,15 +25650,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>670.1</v>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>670.11</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -25650,15 +25673,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>670.2</v>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>670.1</v>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -25673,15 +25696,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>670.4</v>
+        <v>670.2</v>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -25696,15 +25719,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>670.47</v>
-      </c>
-      <c r="D72" s="16" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.4</v>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -25719,15 +25742,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>670.48</v>
+        <v>670.47</v>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -25742,15 +25765,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>670.51</v>
+        <v>670.48</v>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -25765,15 +25788,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>670.3099999999999</v>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.51</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -25788,15 +25811,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>670.34</v>
-      </c>
-      <c r="D76" s="16" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.3099999999999</v>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -25811,15 +25834,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>670.35</v>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>670.34</v>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -25834,15 +25857,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>670.34</v>
+        <v>670.35</v>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -25857,15 +25880,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>670.4299999999999</v>
+        <v>670.34</v>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -25880,15 +25903,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>670.46</v>
+        <v>670.4299999999999</v>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -25903,15 +25926,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>670.4400000000001</v>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.46</v>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -25926,13 +25949,13 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>670.45</v>
-      </c>
-      <c r="D82" s="16" t="inlineStr">
+        <v>670.4400000000001</v>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -25949,15 +25972,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>670.46</v>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>670.45</v>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -25972,15 +25995,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>670.4400000000001</v>
+        <v>670.46</v>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -25995,15 +26018,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>670.45</v>
+        <v>670.4400000000001</v>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -26018,15 +26041,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>670.48</v>
+        <v>670.45</v>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -26041,15 +26064,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>670.45</v>
+        <v>670.48</v>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -26064,15 +26087,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>670.25</v>
+        <v>670.45</v>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -26087,15 +26110,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>670.26</v>
-      </c>
-      <c r="D89" s="12" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>670.25</v>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -26110,13 +26133,13 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>670.23</v>
-      </c>
-      <c r="D90" s="15" t="inlineStr">
+        <v>670.26</v>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -26133,15 +26156,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>670.2</v>
+        <v>670.23</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -26156,15 +26179,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>670.1799999999999</v>
-      </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>670.2</v>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -26179,15 +26202,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>670.15</v>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.1799999999999</v>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -26202,15 +26225,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>670.1799999999999</v>
-      </c>
-      <c r="D94" s="16" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>670.15</v>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -26225,15 +26248,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>670.28</v>
+        <v>670.1799999999999</v>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -26248,15 +26271,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>670.29</v>
+        <v>670.28</v>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -26271,15 +26294,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>670.28</v>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.29</v>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -26294,15 +26317,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>670.3099999999999</v>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>-0.140</t>
+        <v>670.28</v>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -26317,15 +26340,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>670.45</v>
+        <v>670.3099999999999</v>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -26340,15 +26363,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>670.62</v>
+        <v>670.45</v>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -26363,15 +26386,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>670.5</v>
+        <v>670.62</v>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -26386,15 +26409,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>670.4400000000001</v>
+        <v>670.5</v>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -26409,15 +26432,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>670.48</v>
-      </c>
-      <c r="D103" s="12" t="inlineStr">
-        <is>
-          <t>+0.080</t>
+        <v>670.4400000000001</v>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -26432,15 +26455,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>670.4</v>
-      </c>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>670.48</v>
+      </c>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -26455,15 +26478,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>670.26</v>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>670.4</v>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -26478,15 +26501,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>670.51</v>
-      </c>
-      <c r="D106" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>670.26</v>
+      </c>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -26501,15 +26524,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>670.53</v>
+        <v>670.51</v>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -26524,15 +26547,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 14:59:15</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>670.62</v>
+        <v>670.53</v>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -26547,15 +26570,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 14:59:15</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>670.5599999999999</v>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.62</v>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -26570,15 +26593,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>670.59</v>
+        <v>670.5599999999999</v>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -26593,15 +26616,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>670.52</v>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.59</v>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -26616,15 +26639,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>670.53</v>
-      </c>
-      <c r="D112" s="16" t="inlineStr">
-        <is>
-          <t>-0.530</t>
+        <v>670.52</v>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -26639,15 +26662,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>671.0599999999999</v>
+        <v>670.53</v>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -26662,15 +26685,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>671.0700000000001</v>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>-0.570</t>
+        <v>671.0599999999999</v>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -26685,15 +26708,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>671.64</v>
+        <v>671.0700000000001</v>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-0.570</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -26708,15 +26731,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>671.88</v>
-      </c>
-      <c r="D116" s="16" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>671.64</v>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -26731,15 +26754,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>671.91</v>
+        <v>671.88</v>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -26754,15 +26777,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>672.05</v>
+        <v>671.91</v>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -26777,15 +26800,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>671.87</v>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>-0.220</t>
+        <v>672.05</v>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -26800,15 +26823,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>672.09</v>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>-0.120</t>
+        <v>671.87</v>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -26823,15 +26846,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>672.21</v>
-      </c>
-      <c r="D121" s="12" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>672.09</v>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -26846,15 +26869,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 12:06:08</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>672.14</v>
+        <v>672.21</v>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -26869,15 +26892,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 12:06:08</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>672.2</v>
+        <v>672.14</v>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>-0.270</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -26892,15 +26915,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>672.47</v>
-      </c>
-      <c r="D124" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>672.2</v>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -26915,15 +26938,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>672.54</v>
-      </c>
-      <c r="D125" s="12" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.47</v>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -26938,15 +26961,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>672.53</v>
-      </c>
-      <c r="D126" s="15" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>672.54</v>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -26961,15 +26984,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>672.36</v>
-      </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>672.53</v>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -26984,15 +27007,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>672.37</v>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>672.36</v>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -27007,15 +27030,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>672.4</v>
+        <v>672.37</v>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -27030,15 +27053,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>672.54</v>
+        <v>672.4</v>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -27053,15 +27076,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>672.52</v>
+        <v>672.54</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -27076,15 +27099,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>672.41</v>
-      </c>
-      <c r="D132" s="15" t="inlineStr">
-        <is>
-          <t>+0.200</t>
+        <v>672.52</v>
+      </c>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -27099,15 +27122,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>672.21</v>
+        <v>672.41</v>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -27122,15 +27145,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>672.17</v>
-      </c>
-      <c r="D134" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>672.21</v>
+      </c>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -27145,15 +27168,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>672.14</v>
+        <v>672.17</v>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -27168,15 +27191,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>671.9400000000001</v>
+        <v>672.14</v>
       </c>
       <c r="D136" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -27191,15 +27214,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>671.96</v>
+        <v>671.9400000000001</v>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -27214,15 +27237,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>672.02</v>
-      </c>
-      <c r="D138" s="16" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>671.96</v>
+      </c>
+      <c r="D138" s="15" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -27237,15 +27260,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>672.22</v>
+        <v>672.02</v>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -27260,15 +27283,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>672.26</v>
-      </c>
-      <c r="D140" s="16" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>672.22</v>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -27283,15 +27306,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>672.36</v>
-      </c>
-      <c r="D141" s="12" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>672.26</v>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -27306,15 +27329,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>672.24</v>
-      </c>
-      <c r="D142" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.36</v>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -27329,15 +27352,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>672.23</v>
-      </c>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>672.24</v>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -27352,15 +27375,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>672.36</v>
+        <v>672.23</v>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -27375,15 +27398,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>672.26</v>
+        <v>672.36</v>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -27398,15 +27421,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>672.24</v>
+        <v>672.26</v>
       </c>
       <c r="D146" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -27421,15 +27444,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>672.3099999999999</v>
-      </c>
-      <c r="D147" s="12" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.24</v>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -27444,15 +27467,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>672.3</v>
+        <v>672.3099999999999</v>
       </c>
       <c r="D148" s="16" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -27467,15 +27490,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>672.47</v>
+        <v>672.3</v>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -27490,15 +27513,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>672.5</v>
+        <v>672.47</v>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -27513,15 +27536,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>672.48</v>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>672.5</v>
+      </c>
+      <c r="D151" s="12" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -27536,15 +27559,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>672.54</v>
+        <v>672.48</v>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -27559,15 +27582,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>672.53</v>
+        <v>672.54</v>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -27582,15 +27605,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>672.35</v>
+        <v>672.53</v>
       </c>
       <c r="D154" s="16" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -27605,15 +27628,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>672.4299999999999</v>
+        <v>672.35</v>
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -27628,15 +27651,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>672.46</v>
-      </c>
-      <c r="D156" s="16" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>672.4299999999999</v>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -27651,15 +27674,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>672.63</v>
-      </c>
-      <c r="D157" s="12" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>672.46</v>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -27674,15 +27697,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>672.5700000000001</v>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>672.63</v>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -27697,15 +27720,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>672.55</v>
+        <v>672.5700000000001</v>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -27720,15 +27743,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>672.54</v>
-      </c>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>672.55</v>
+      </c>
+      <c r="D160" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -27743,15 +27766,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>672.51</v>
-      </c>
-      <c r="D161" s="9" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>672.54</v>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -27766,15 +27789,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>672.61</v>
+        <v>672.51</v>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -27789,15 +27812,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>672.55</v>
+        <v>672.61</v>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -27812,15 +27835,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>672.5</v>
-      </c>
-      <c r="D164" s="15" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>672.55</v>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -27835,15 +27858,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>672.34</v>
+        <v>672.5</v>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -27858,15 +27881,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>672.33</v>
-      </c>
-      <c r="D166" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>672.34</v>
+      </c>
+      <c r="D166" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -27881,15 +27904,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>672.3</v>
-      </c>
-      <c r="D167" s="9" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>672.33</v>
+      </c>
+      <c r="D167" s="12" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -27904,15 +27927,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>672.41</v>
-      </c>
-      <c r="D168" s="16" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>672.3</v>
+      </c>
+      <c r="D168" s="15" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -27927,15 +27950,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>672.66</v>
+        <v>672.41</v>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -27950,15 +27973,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>672.78</v>
+        <v>672.66</v>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -27973,15 +27996,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 12:26:44</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>672.76</v>
+        <v>672.78</v>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -27996,15 +28019,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 12:26:44</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>672.71</v>
-      </c>
-      <c r="D172" s="15" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>672.76</v>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -28019,15 +28042,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>672.67</v>
+        <v>672.71</v>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -28042,15 +28065,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>672.59</v>
+        <v>672.67</v>
       </c>
       <c r="D174" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -28065,15 +28088,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>672.6</v>
+        <v>672.59</v>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -28088,15 +28111,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>672.8200000000001</v>
-      </c>
-      <c r="D176" s="16" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>672.6</v>
+      </c>
+      <c r="D176" s="15" t="inlineStr">
+        <is>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -28111,15 +28134,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>673.24</v>
-      </c>
-      <c r="D177" s="12" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>672.8200000000001</v>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -28134,15 +28157,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>672.9</v>
+        <v>673.24</v>
       </c>
       <c r="D178" s="16" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -28157,15 +28180,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>673.04</v>
-      </c>
-      <c r="D179" s="12" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.9</v>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -28180,15 +28203,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>673.03</v>
-      </c>
-      <c r="D180" s="15" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>673.04</v>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -28203,15 +28226,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>672.79</v>
-      </c>
-      <c r="D181" s="9" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>673.03</v>
+      </c>
+      <c r="D181" s="12" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -28226,15 +28249,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>673.03</v>
+        <v>672.79</v>
       </c>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -28249,11 +28272,11 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>673.02</v>
+        <v>673.03</v>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
@@ -28272,15 +28295,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>673.01</v>
+        <v>673.02</v>
       </c>
       <c r="D184" s="16" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -28295,15 +28318,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>673.09</v>
+        <v>673.01</v>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -28318,15 +28341,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>673.11</v>
+        <v>673.09</v>
       </c>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -28341,15 +28364,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>672.97</v>
+        <v>673.11</v>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -28364,15 +28387,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>672.87</v>
-      </c>
-      <c r="D188" s="15" t="inlineStr">
-        <is>
-          <t>+0.130</t>
+        <v>672.97</v>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -28387,15 +28410,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>672.74</v>
-      </c>
-      <c r="D189" s="9" t="inlineStr">
-        <is>
-          <t>-0.300</t>
+        <v>672.87</v>
+      </c>
+      <c r="D189" s="12" t="inlineStr">
+        <is>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -28410,14 +28433,37 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="n">
+        <v>672.74</v>
+      </c>
+      <c r="D190" s="15" t="inlineStr">
+        <is>
+          <t>-0.300</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="n">
+        <v>187</v>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C190" s="6" t="n">
+      <c r="C191" s="8" t="n">
         <v>673.04</v>
       </c>
-      <c r="D190" s="6" t="inlineStr"/>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="D191" s="8" t="inlineStr"/>
+      <c r="E191" s="8" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -185,10 +185,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 05:03:03</t>
+          <t>更新时间: 2026-09-19 07:12:24</t>
         </is>
       </c>
     </row>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>764.83</v>
+        <v>765.54</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -765,15 +765,15 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>668.03</v>
+        <v>667.89</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -19203,7 +19203,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 764.83 | 最高: 782.950 | 最低: 764.540 | 总记录数: 246</t>
+          <t>最新价: 765.54 | 最高: 782.950 | 最低: 764.540 | 总记录数: 247</t>
         </is>
       </c>
     </row>
@@ -19240,15 +19240,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>764.83</v>
+        <v>765.54</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -19263,15 +19263,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>764.54</v>
+        <v>764.83</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -19286,15 +19286,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>764.62</v>
+        <v>764.54</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>-0.770</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -19309,15 +19309,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>765.39</v>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>-0.620</t>
+        <v>764.62</v>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>-0.770</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -19332,15 +19332,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:32:25</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>766.01</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>765.39</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>-0.620</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -19355,15 +19355,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 05:47:34</t>
+          <t>2026-09-18 09:32:25</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>765.63</v>
+        <v>766.01</v>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -19378,15 +19378,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 05:47:34</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>765.8200000000001</v>
+        <v>765.63</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>-1.020</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -19401,15 +19401,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>766.84</v>
+        <v>765.8200000000001</v>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>+1.260</t>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -19424,15 +19424,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>765.58</v>
+        <v>766.84</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>+0.340</t>
+          <t>+1.260</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -19447,15 +19447,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>765.24</v>
+        <v>765.58</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -19470,15 +19470,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 08:40:02</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>765.39</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>765.24</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -19493,15 +19493,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 08:40:02</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>765.05</v>
+        <v>765.39</v>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>-4.700</t>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -19516,15 +19516,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>769.75</v>
+        <v>765.05</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-4.700</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -19539,15 +19539,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>770.04</v>
+        <v>769.75</v>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -19562,15 +19562,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>769.95</v>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>-0.730</t>
+        <v>770.04</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -19585,15 +19585,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>770.6799999999999</v>
+        <v>769.95</v>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -19608,15 +19608,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:40:23</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>770.47</v>
+        <v>770.6799999999999</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -19631,15 +19631,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 07:41:58</t>
+          <t>2026-09-16 09:40:23</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>770.38</v>
+        <v>770.47</v>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -19654,15 +19654,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>770.8</v>
+        <v>770.38</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -19677,15 +19677,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>770.8200000000001</v>
+        <v>770.8</v>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>+0.400</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -19700,15 +19700,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>770.42</v>
+        <v>770.8200000000001</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -19723,15 +19723,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>770.24</v>
+        <v>770.42</v>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>-0.810</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -19746,11 +19746,11 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>771.05</v>
+        <v>770.24</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -19769,15 +19769,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>771.86</v>
+        <v>771.05</v>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>+1.540</t>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -19792,15 +19792,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>770.3200000000001</v>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>771.86</v>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -19815,15 +19815,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>771.76</v>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>-2.140</t>
+        <v>770.3200000000001</v>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -19838,15 +19838,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12 05:00:53</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>773.9</v>
+        <v>771.76</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-2.140</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -19861,15 +19861,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15:57</t>
+          <t>2026-09-12 05:00:53</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>774.33</v>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>-0.730</t>
+        <v>773.9</v>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -19884,15 +19884,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-12 02:15:57</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>+1.400</t>
+        <v>774.33</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -19907,15 +19907,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>773.66</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-1.440</t>
+          <t>+1.400</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -19930,15 +19930,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>775.1</v>
+        <v>773.66</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>-0.500</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -19953,15 +19953,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:18:12</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>775.6</v>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>-0.410</t>
+        <v>775.1</v>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>-0.500</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -19976,15 +19976,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 09:18:12</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>776.01</v>
+        <v>775.6</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -19999,15 +19999,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>776.38</v>
+        <v>776.01</v>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>+0.550</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -20022,15 +20022,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>775.83</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>776.38</v>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -20045,15 +20045,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>776.53</v>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>775.83</v>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -20068,15 +20068,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.53</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -20091,15 +20091,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 06:08:04</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>776.7</v>
+        <v>776.91</v>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -20114,15 +20114,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 06:08:04</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>776.8</v>
+        <v>776.7</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -20137,15 +20137,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>777.27</v>
+        <v>776.8</v>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>+0.760</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -20160,15 +20160,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>776.51</v>
+        <v>777.27</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.760</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -20183,15 +20183,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>776.29</v>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>+0.390</t>
+        <v>776.51</v>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -20206,15 +20206,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>775.9</v>
+        <v>776.29</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -20229,15 +20229,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>775.58</v>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>775.9</v>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -20252,15 +20252,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>775.48</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>775.58</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -20275,15 +20275,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>776.29</v>
+        <v>775.48</v>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -20298,15 +20298,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 06:18:23</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>776.0700000000001</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>776.29</v>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -20321,15 +20321,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 06:18:23</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>776.54</v>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>776.0700000000001</v>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -20344,15 +20344,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>776.59</v>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>776.54</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -20367,15 +20367,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>776.13</v>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>+0.810</t>
+        <v>776.59</v>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -20390,15 +20390,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>775.3200000000001</v>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>776.13</v>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -20413,15 +20413,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 08:56:04</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>775.6900000000001</v>
+        <v>775.3200000000001</v>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -20436,15 +20436,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 07:06:50</t>
+          <t>2026-09-07 08:56:04</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>775.63</v>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>775.6900000000001</v>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -20459,15 +20459,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-05 07:06:50</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>776.02</v>
+        <v>775.63</v>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>+0.260</t>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -20482,15 +20482,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>775.76</v>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>-0.720</t>
+        <v>776.02</v>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -20505,15 +20505,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>776.48</v>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>-0.580</t>
+        <v>775.76</v>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -20528,15 +20528,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>777.0599999999999</v>
+        <v>776.48</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.580</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -20551,15 +20551,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 07:59:45</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>777.13</v>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>-0.540</t>
+        <v>777.0599999999999</v>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -20574,15 +20574,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 07:59:45</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>777.67</v>
+        <v>777.13</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>-0.300</t>
+          <t>-0.540</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -20597,15 +20597,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>777.97</v>
+        <v>777.67</v>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>+1.580</t>
+          <t>-0.300</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -20620,15 +20620,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>776.39</v>
+        <v>777.97</v>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>+1.580</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -20643,15 +20643,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>776.01</v>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>+0.660</t>
+        <v>776.39</v>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -20666,15 +20666,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>775.35</v>
+        <v>776.01</v>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>+0.700</t>
+          <t>+0.660</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -20689,15 +20689,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 06:35:56</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>774.65</v>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>775.35</v>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>+0.700</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -20712,15 +20712,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 04:09:22</t>
+          <t>2026-09-03 06:35:56</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>774.64</v>
-      </c>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>-0.270</t>
+        <v>774.65</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -20735,15 +20735,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 04:09:22</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>774.91</v>
+        <v>774.64</v>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>+0.390</t>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -20758,15 +20758,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>774.52</v>
+        <v>774.91</v>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>+0.230</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -20781,15 +20781,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 17:58:25</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>774.29</v>
+        <v>774.52</v>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.230</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -20804,15 +20804,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 17:58:25</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>774.36</v>
+        <v>774.29</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>-0.860</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -20827,15 +20827,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>775.22</v>
+        <v>774.36</v>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>+0.350</t>
+          <t>-0.860</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -20850,15 +20850,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 02:48:49</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>774.87</v>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>775.22</v>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -20873,15 +20873,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 02:48:49</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>775.47</v>
+        <v>774.87</v>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -20896,15 +20896,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>775.25</v>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
-        <is>
-          <t>-1.030</t>
+        <v>775.47</v>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -20919,15 +20919,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>776.28</v>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>-0.280</t>
+        <v>775.25</v>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>-1.030</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -20942,15 +20942,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 09:25:49</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>776.5599999999999</v>
+        <v>776.28</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -20965,15 +20965,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 06:48:36</t>
+          <t>2026-09-01 09:25:49</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>776.58</v>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>776.5599999999999</v>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -20988,15 +20988,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 02:10:52</t>
+          <t>2026-09-01 06:48:36</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>776.63</v>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>+1.230</t>
+        <v>776.58</v>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -21011,15 +21011,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 02:10:52</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>775.4</v>
-      </c>
-      <c r="D82" s="16" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.63</v>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -21034,15 +21034,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>775.4</v>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -21057,15 +21057,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 08:13:17</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>775.92</v>
+        <v>775.22</v>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -21080,15 +21080,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 08:13:17</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>775.85</v>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>-2.850</t>
+        <v>775.92</v>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -21103,15 +21103,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>778.7</v>
-      </c>
-      <c r="D86" s="15" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>775.85</v>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>-2.850</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -21126,15 +21126,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>779.1</v>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>778.7</v>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -21149,15 +21149,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>778.72</v>
+        <v>779.1</v>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>-0.640</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -21172,15 +21172,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>779.36</v>
+        <v>778.72</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>-0.200</t>
+          <t>-0.640</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -21195,15 +21195,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 04:13:31</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>779.5599999999999</v>
+        <v>779.36</v>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -21218,15 +21218,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 04:13:31</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>779.39</v>
-      </c>
-      <c r="D91" s="12" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>779.5599999999999</v>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -21241,15 +21241,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>779.6</v>
-      </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>-0.430</t>
+        <v>779.39</v>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -21264,15 +21264,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>780.03</v>
+        <v>779.6</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -21287,15 +21287,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 18:53:28</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>780.15</v>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>780.03</v>
+      </c>
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -21310,15 +21310,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 18:53:28</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>780.62</v>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>+0.560</t>
+        <v>780.15</v>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -21333,15 +21333,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>780.0599999999999</v>
+        <v>780.62</v>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>+0.560</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -21356,15 +21356,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>780.17</v>
+        <v>780.0599999999999</v>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -21379,15 +21379,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>780.38</v>
+        <v>780.17</v>
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -21402,15 +21402,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 10:07:59</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>780.36</v>
-      </c>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>780.38</v>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -21425,15 +21425,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 07:52:24</t>
+          <t>2026-08-26 10:07:59</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>780.6</v>
+        <v>780.36</v>
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -21448,15 +21448,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 01:49:35</t>
+          <t>2026-08-26 07:52:24</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>780.4299999999999</v>
+        <v>780.6</v>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -21471,15 +21471,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 01:49:35</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>780.35</v>
-      </c>
-      <c r="D102" s="16" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>780.4299999999999</v>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -21494,15 +21494,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.35</v>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>+0.410</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -21517,15 +21517,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:05:53</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>779.9</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>-0.260</t>
+          <t>+0.410</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -21540,15 +21540,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 21:05:53</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>780.16</v>
+        <v>779.9</v>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>-0.230</t>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -21563,15 +21563,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>780.39</v>
+        <v>780.16</v>
       </c>
       <c r="D106" s="16" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>-0.230</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -21586,15 +21586,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>780.15</v>
+        <v>780.39</v>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>+0.540</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -21609,15 +21609,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:26</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>779.61</v>
+        <v>780.15</v>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.540</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -21632,15 +21632,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:01:55</t>
+          <t>2026-08-25 15:51:26</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>779.65</v>
+        <v>779.61</v>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -21655,15 +21655,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 15:01:55</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>779.73</v>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>779.65</v>
+      </c>
+      <c r="D110" s="16" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -21678,15 +21678,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>780.11</v>
+        <v>779.73</v>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -21701,15 +21701,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>780.4</v>
+        <v>780.11</v>
       </c>
       <c r="D112" s="16" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -21724,15 +21724,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:57:56</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.4</v>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -21747,15 +21747,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 06:50:27</t>
+          <t>2026-08-25 09:57:56</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>780.1900000000001</v>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>780.3099999999999</v>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -21770,15 +21770,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 06:50:27</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>780.1799999999999</v>
-      </c>
-      <c r="D115" s="12" t="inlineStr">
-        <is>
-          <t>-0.450</t>
+        <v>780.1900000000001</v>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -21793,15 +21793,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>780.63</v>
+        <v>780.1799999999999</v>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>+0.460</t>
+          <t>-0.450</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -21816,15 +21816,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>780.17</v>
-      </c>
-      <c r="D117" s="12" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.63</v>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -21839,15 +21839,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>780.61</v>
+        <v>780.17</v>
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -21862,15 +21862,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>780.14</v>
-      </c>
-      <c r="D119" s="12" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>780.61</v>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -21885,15 +21885,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>780.23</v>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>-0.530</t>
+        <v>780.14</v>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -21908,15 +21908,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>780.76</v>
+        <v>780.23</v>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -21931,15 +21931,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>780.91</v>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.76</v>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -21954,15 +21954,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>781.35</v>
+        <v>780.91</v>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -21977,15 +21977,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>781.38</v>
+        <v>781.35</v>
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -22000,15 +22000,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>781.09</v>
-      </c>
-      <c r="D125" s="12" t="inlineStr">
-        <is>
-          <t>-0.350</t>
+        <v>781.38</v>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -22023,15 +22023,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>781.4400000000001</v>
-      </c>
-      <c r="D126" s="15" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>781.09</v>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>-0.350</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -22046,15 +22046,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>781.55</v>
-      </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.4400000000001</v>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -22069,15 +22069,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 09:42:15</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>781.23</v>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>781.55</v>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -22092,15 +22092,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 10:32:40</t>
+          <t>2026-08-24 09:42:15</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>781.01</v>
-      </c>
-      <c r="D129" s="12" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>781.23</v>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -22115,15 +22115,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 05:00:11</t>
+          <t>2026-08-22 10:32:40</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>781.11</v>
-      </c>
-      <c r="D130" s="15" t="inlineStr">
-        <is>
-          <t>-0.180</t>
+        <v>781.01</v>
+      </c>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -22138,15 +22138,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 02:00:51</t>
+          <t>2026-08-22 05:00:11</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>781.29</v>
+        <v>781.11</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -22161,15 +22161,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-22 02:00:51</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>781.34</v>
+        <v>781.29</v>
       </c>
       <c r="D132" s="16" t="inlineStr">
         <is>
-          <t>+0.550</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -22184,15 +22184,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>780.79</v>
+        <v>781.34</v>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -22207,15 +22207,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>780.6799999999999</v>
+        <v>780.79</v>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>-0.610</t>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -22230,15 +22230,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>781.29</v>
+        <v>780.6799999999999</v>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>-1.420</t>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -22253,15 +22253,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>782.71</v>
-      </c>
-      <c r="D136" s="15" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>781.29</v>
+      </c>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>-1.420</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -22276,15 +22276,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>782.95</v>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>+1.080</t>
+        <v>782.71</v>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -22299,15 +22299,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>781.87</v>
+        <v>782.95</v>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>+1.080</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -22322,15 +22322,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>782.25</v>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>781.87</v>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -22345,15 +22345,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>781.99</v>
-      </c>
-      <c r="D140" s="16" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>782.25</v>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -22368,15 +22368,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>781.95</v>
-      </c>
-      <c r="D141" s="12" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>781.99</v>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -22391,15 +22391,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>781.99</v>
-      </c>
-      <c r="D142" s="15" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>781.95</v>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -22414,15 +22414,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>782.39</v>
-      </c>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>781.99</v>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -22437,15 +22437,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:13</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>782.03</v>
-      </c>
-      <c r="D144" s="16" t="inlineStr">
-        <is>
-          <t>+0.400</t>
+        <v>782.39</v>
+      </c>
+      <c r="D144" s="15" t="inlineStr">
+        <is>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -22460,15 +22460,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 06:49:01</t>
+          <t>2026-08-21 09:10:13</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>781.63</v>
+        <v>782.03</v>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -22483,15 +22483,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 06:49:01</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>780.95</v>
+        <v>781.63</v>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>-0.780</t>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -22506,15 +22506,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>781.73</v>
+        <v>780.95</v>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -22529,15 +22529,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>781.73</v>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -22552,15 +22552,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>782.1900000000001</v>
-      </c>
-      <c r="D149" s="9" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>781.79</v>
+      </c>
+      <c r="D149" s="12" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -22575,15 +22575,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>782.04</v>
+        <v>782.1900000000001</v>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>-0.700</t>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -22598,15 +22598,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>782.74</v>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>782.04</v>
+      </c>
+      <c r="D151" s="12" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -22621,15 +22621,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>782.42</v>
-      </c>
-      <c r="D152" s="16" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>782.74</v>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -22644,15 +22644,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>781.95</v>
+        <v>782.42</v>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -22667,15 +22667,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>781.14</v>
+        <v>781.95</v>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -22690,15 +22690,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>781.39</v>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>781.14</v>
+      </c>
+      <c r="D155" s="12" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -22713,15 +22713,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>781.2</v>
-      </c>
-      <c r="D156" s="16" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>781.39</v>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -22736,15 +22736,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>781.17</v>
-      </c>
-      <c r="D157" s="12" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.2</v>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -22759,15 +22759,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 10:06:13</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>781.42</v>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>781.17</v>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -22782,15 +22782,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 07:36:53</t>
+          <t>2026-08-20 10:06:13</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D159" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>781.42</v>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -22805,15 +22805,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 06:33:42</t>
+          <t>2026-08-20 07:36:53</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>781.77</v>
-      </c>
-      <c r="D160" s="16" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.79</v>
+      </c>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -22828,15 +22828,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 06:33:42</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>781.45</v>
+        <v>781.77</v>
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>+0.850</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -22851,15 +22851,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>780.6</v>
-      </c>
-      <c r="D162" s="16" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>781.45</v>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>+0.850</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -22874,15 +22874,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>780.12</v>
+        <v>780.6</v>
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>+1.750</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -22897,15 +22897,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>778.37</v>
-      </c>
-      <c r="D164" s="16" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>780.12</v>
+      </c>
+      <c r="D164" s="15" t="inlineStr">
+        <is>
+          <t>+1.750</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -22920,15 +22920,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>778.09</v>
+        <v>778.37</v>
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -22943,15 +22943,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>777.41</v>
-      </c>
-      <c r="D166" s="16" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>778.09</v>
+      </c>
+      <c r="D166" s="15" t="inlineStr">
+        <is>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -22966,15 +22966,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>777.3200000000001</v>
+        <v>777.41</v>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -22989,13 +22989,13 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>777.1</v>
-      </c>
-      <c r="D168" s="16" t="inlineStr">
+        <v>777.3200000000001</v>
+      </c>
+      <c r="D168" s="15" t="inlineStr">
         <is>
           <t>+0.220</t>
         </is>
@@ -23012,15 +23012,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>776.88</v>
-      </c>
-      <c r="D169" s="12" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.1</v>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -23035,15 +23035,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>776.89</v>
+        <v>776.88</v>
       </c>
       <c r="D170" s="16" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -23058,15 +23058,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>776.84</v>
-      </c>
-      <c r="D171" s="12" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>776.89</v>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 09:12:00</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>776.9</v>
+        <v>776.84</v>
       </c>
       <c r="D172" s="16" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -23104,15 +23104,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 09:12:00</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>776.72</v>
-      </c>
-      <c r="D173" s="12" t="inlineStr">
-        <is>
-          <t>-0.460</t>
+        <v>776.9</v>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -23127,15 +23127,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>777.1799999999999</v>
+        <v>776.72</v>
       </c>
       <c r="D174" s="16" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>-0.460</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -23150,15 +23150,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>776.55</v>
-      </c>
-      <c r="D175" s="12" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>777.1799999999999</v>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -23173,15 +23173,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:24</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>776.62</v>
+        <v>776.55</v>
       </c>
       <c r="D176" s="16" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -23196,15 +23196,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 17:58:24</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>776.53</v>
+        <v>776.62</v>
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -23219,15 +23219,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>776.36</v>
+        <v>776.53</v>
       </c>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>-0.160</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -23242,15 +23242,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>776.52</v>
+        <v>776.36</v>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.160</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -23265,15 +23265,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>776.53</v>
-      </c>
-      <c r="D180" s="15" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>776.52</v>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -23288,15 +23288,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>776.92</v>
-      </c>
-      <c r="D181" s="9" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>776.53</v>
+      </c>
+      <c r="D181" s="12" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -23311,15 +23311,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 10:04:24</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>776.8200000000001</v>
-      </c>
-      <c r="D182" s="16" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.92</v>
+      </c>
+      <c r="D182" s="15" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -23334,15 +23334,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 07:54:32</t>
+          <t>2026-08-18 10:04:24</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>776.61</v>
-      </c>
-      <c r="D183" s="12" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>776.8200000000001</v>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -23357,15 +23357,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 05:48:09</t>
+          <t>2026-08-18 07:54:32</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>776.74</v>
+        <v>776.61</v>
       </c>
       <c r="D184" s="16" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -23380,15 +23380,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 05:48:09</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>776.5599999999999</v>
-      </c>
-      <c r="D185" s="12" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>776.74</v>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -23403,15 +23403,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>777.16</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="D186" s="16" t="inlineStr">
         <is>
-          <t>+0.350</t>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>776.8099999999999</v>
-      </c>
-      <c r="D187" s="12" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>777.16</v>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:45</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>777.21</v>
-      </c>
-      <c r="D188" s="15" t="inlineStr">
-        <is>
-          <t>-0.220</t>
+        <v>776.8099999999999</v>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 21:10:45</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>777.4299999999999</v>
+        <v>777.21</v>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>777.52</v>
+        <v>777.4299999999999</v>
       </c>
       <c r="D190" s="16" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>777.5</v>
+        <v>777.52</v>
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>+0.370</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>777.13</v>
-      </c>
-      <c r="D192" s="16" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>777.5</v>
+      </c>
+      <c r="D192" s="15" t="inlineStr">
+        <is>
+          <t>+0.370</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>777.04</v>
+        <v>777.13</v>
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -23587,15 +23587,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>776.9</v>
+        <v>777.04</v>
       </c>
       <c r="D194" s="15" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -23610,15 +23610,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>776.91</v>
+        <v>776.9</v>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -23633,15 +23633,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>776.96</v>
+        <v>776.91</v>
       </c>
       <c r="D196" s="16" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -23656,15 +23656,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 09:21:39</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>776.84</v>
+        <v>776.96</v>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>+0.750</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -23679,15 +23679,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 09:21:39</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>776.09</v>
+        <v>776.84</v>
       </c>
       <c r="D198" s="15" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>+0.750</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -23702,15 +23702,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D199" s="9" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>776.09</v>
+      </c>
+      <c r="D199" s="12" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -23725,15 +23725,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>775.8099999999999</v>
-      </c>
-      <c r="D200" s="16" t="inlineStr">
-        <is>
-          <t>+0.770</t>
+        <v>776.38</v>
+      </c>
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -23748,15 +23748,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>775.04</v>
+        <v>775.8099999999999</v>
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.770</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -23771,15 +23771,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>774.92</v>
-      </c>
-      <c r="D202" s="16" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>775.04</v>
+      </c>
+      <c r="D202" s="15" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -23794,15 +23794,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>774.5599999999999</v>
+        <v>774.92</v>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -23817,15 +23817,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>774.4400000000001</v>
+        <v>774.5599999999999</v>
       </c>
       <c r="D204" s="15" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -23840,15 +23840,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>774.46</v>
-      </c>
-      <c r="D205" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>774.4400000000001</v>
+      </c>
+      <c r="D205" s="12" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -23863,15 +23863,15 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>774.25</v>
-      </c>
-      <c r="D206" s="16" t="inlineStr">
-        <is>
-          <t>+0.310</t>
+        <v>774.46</v>
+      </c>
+      <c r="D206" s="15" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -23886,15 +23886,15 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 10:39:02</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>773.9400000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.310</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -23909,15 +23909,15 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 08:05:13</t>
+          <t>2026-08-14 10:39:02</t>
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>773.9</v>
-      </c>
-      <c r="D208" s="16" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>773.9400000000001</v>
+      </c>
+      <c r="D208" s="15" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -23932,15 +23932,15 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 07:24:16</t>
+          <t>2026-08-14 08:05:13</t>
         </is>
       </c>
       <c r="C209" s="8" t="n">
-        <v>773.73</v>
+        <v>773.9</v>
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -23955,15 +23955,15 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 07:24:16</t>
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>773.53</v>
+        <v>773.73</v>
       </c>
       <c r="D210" s="15" t="inlineStr">
         <is>
-          <t>-0.790</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -23978,15 +23978,15 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
-        <v>774.3200000000001</v>
-      </c>
-      <c r="D211" s="9" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>773.53</v>
+      </c>
+      <c r="D211" s="12" t="inlineStr">
+        <is>
+          <t>-0.790</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -24001,15 +24001,15 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>773.75</v>
-      </c>
-      <c r="D212" s="16" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>774.3200000000001</v>
+      </c>
+      <c r="D212" s="15" t="inlineStr">
+        <is>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -24024,15 +24024,15 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>773.7</v>
+        <v>773.75</v>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -24047,15 +24047,15 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>773.58</v>
-      </c>
-      <c r="D214" s="16" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>773.7</v>
+      </c>
+      <c r="D214" s="15" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -24070,15 +24070,15 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>773.33</v>
-      </c>
-      <c r="D215" s="12" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>773.58</v>
+      </c>
+      <c r="D215" s="9" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -24093,15 +24093,15 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>773.39</v>
+        <v>773.33</v>
       </c>
       <c r="D216" s="16" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -24116,15 +24116,15 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
-        <v>773.11</v>
-      </c>
-      <c r="D217" s="12" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>773.39</v>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -24139,15 +24139,15 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>773.24</v>
-      </c>
-      <c r="D218" s="15" t="inlineStr">
-        <is>
-          <t>-0.340</t>
+        <v>773.11</v>
+      </c>
+      <c r="D218" s="16" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -24162,15 +24162,15 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>773.58</v>
+        <v>773.24</v>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -24185,15 +24185,15 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>773.64</v>
-      </c>
-      <c r="D220" s="15" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>773.58</v>
+      </c>
+      <c r="D220" s="16" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -24208,15 +24208,15 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>774.11</v>
+        <v>773.64</v>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -24231,15 +24231,15 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>774.3</v>
-      </c>
-      <c r="D222" s="15" t="inlineStr">
-        <is>
-          <t>-0.740</t>
+        <v>774.11</v>
+      </c>
+      <c r="D222" s="16" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -24254,15 +24254,15 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>775.04</v>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>774.3</v>
+      </c>
+      <c r="D223" s="12" t="inlineStr">
+        <is>
+          <t>-0.740</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -24277,15 +24277,15 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>774.9</v>
-      </c>
-      <c r="D224" s="16" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>775.04</v>
+      </c>
+      <c r="D224" s="15" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -24300,15 +24300,15 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>774.66</v>
+        <v>774.9</v>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -24323,15 +24323,15 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>774.34</v>
-      </c>
-      <c r="D226" s="16" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>774.66</v>
+      </c>
+      <c r="D226" s="15" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -24346,15 +24346,15 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>774.15</v>
-      </c>
-      <c r="D227" s="12" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>774.34</v>
+      </c>
+      <c r="D227" s="9" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -24369,15 +24369,15 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 13:53:42</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C228" s="6" t="n">
-        <v>774.25</v>
-      </c>
-      <c r="D228" s="15" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>774.15</v>
+      </c>
+      <c r="D228" s="16" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -24392,15 +24392,15 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 13:53:42</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>774.3200000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
@@ -24415,15 +24415,15 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>774.74</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="D230" s="16" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -24438,15 +24438,15 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 01:28:47</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>774.5</v>
+        <v>774.74</v>
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -24461,15 +24461,15 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 01:28:47</t>
         </is>
       </c>
       <c r="C232" s="6" t="n">
-        <v>774.37</v>
+        <v>774.5</v>
       </c>
       <c r="D232" s="15" t="inlineStr">
         <is>
-          <t>-0.340</t>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -24484,15 +24484,15 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C233" s="8" t="n">
-        <v>774.71</v>
-      </c>
-      <c r="D233" s="9" t="inlineStr">
-        <is>
-          <t>+1.160</t>
+        <v>774.37</v>
+      </c>
+      <c r="D233" s="12" t="inlineStr">
+        <is>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
@@ -24507,15 +24507,15 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C234" s="6" t="n">
-        <v>773.55</v>
+        <v>774.71</v>
       </c>
       <c r="D234" s="15" t="inlineStr">
         <is>
-          <t>-0.520</t>
+          <t>+1.160</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -24530,15 +24530,15 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>774.0700000000001</v>
+        <v>773.55</v>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>-0.690</t>
+          <t>-0.520</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
@@ -24553,15 +24553,15 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C236" s="6" t="n">
-        <v>774.76</v>
-      </c>
-      <c r="D236" s="15" t="inlineStr">
-        <is>
-          <t>-0.550</t>
+        <v>774.0700000000001</v>
+      </c>
+      <c r="D236" s="16" t="inlineStr">
+        <is>
+          <t>-0.690</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -24576,15 +24576,15 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
-        <v>775.3099999999999</v>
+        <v>774.76</v>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
@@ -24599,15 +24599,15 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C238" s="6" t="n">
-        <v>775.46</v>
-      </c>
-      <c r="D238" s="15" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>775.3099999999999</v>
+      </c>
+      <c r="D238" s="16" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -24622,15 +24622,15 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
-        <v>775.84</v>
+        <v>775.46</v>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
@@ -24645,15 +24645,15 @@
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 08:05:33</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C240" s="6" t="n">
-        <v>775.9</v>
+        <v>775.84</v>
       </c>
       <c r="D240" s="16" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -24668,15 +24668,15 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 08:05:33</t>
         </is>
       </c>
       <c r="C241" s="8" t="n">
-        <v>775.83</v>
+        <v>775.9</v>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
@@ -24691,15 +24691,15 @@
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C242" s="6" t="n">
-        <v>775.2</v>
+        <v>775.83</v>
       </c>
       <c r="D242" s="15" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -24714,15 +24714,15 @@
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C243" s="8" t="n">
-        <v>775.28</v>
-      </c>
-      <c r="D243" s="9" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>775.2</v>
+      </c>
+      <c r="D243" s="12" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
@@ -24737,15 +24737,15 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C244" s="6" t="n">
-        <v>775.12</v>
-      </c>
-      <c r="D244" s="16" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>775.28</v>
+      </c>
+      <c r="D244" s="15" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -24760,11 +24760,11 @@
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C245" s="8" t="n">
-        <v>775.09</v>
+        <v>775.12</v>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
@@ -24783,15 +24783,15 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 18:37:13</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C246" s="6" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D246" s="16" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>775.09</v>
+      </c>
+      <c r="D246" s="15" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
@@ -24806,15 +24806,15 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 18:37:13</t>
         </is>
       </c>
       <c r="C247" s="8" t="n">
-        <v>774.58</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
@@ -24829,15 +24829,15 @@
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C248" s="6" t="n">
-        <v>774.29</v>
-      </c>
-      <c r="D248" s="16" t="inlineStr">
-        <is>
-          <t>+0.490</t>
+        <v>774.58</v>
+      </c>
+      <c r="D248" s="15" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -24852,15 +24852,15 @@
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
-        <v>773.8</v>
-      </c>
-      <c r="D249" s="12" t="inlineStr">
-        <is>
-          <t>-0.590</t>
+        <v>774.29</v>
+      </c>
+      <c r="D249" s="9" t="inlineStr">
+        <is>
+          <t>+0.490</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
@@ -24875,14 +24875,37 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C250" s="6" t="n">
+        <v>773.8</v>
+      </c>
+      <c r="D250" s="16" t="inlineStr">
+        <is>
+          <t>-0.590</t>
+        </is>
+      </c>
+      <c r="E250" s="6" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="8" t="n">
+        <v>247</v>
+      </c>
+      <c r="B251" s="8" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C250" s="6" t="n">
+      <c r="C251" s="8" t="n">
         <v>774.39</v>
       </c>
-      <c r="D250" s="6" t="inlineStr"/>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="D251" s="8" t="inlineStr"/>
+      <c r="E251" s="8" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>
@@ -24903,7 +24926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E199"/>
+  <dimension ref="A1:E200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -24923,7 +24946,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 668.03 | 最高: 673.240 | 最低: 667.890 | 总记录数: 195</t>
+          <t>最新价: 667.89 | 最高: 673.240 | 最低: 667.890 | 总记录数: 196</t>
         </is>
       </c>
     </row>
@@ -24960,15 +24983,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>668.03</v>
+        <v>667.89</v>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -24983,15 +25006,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>668.0599999999999</v>
+        <v>668.03</v>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -25006,15 +25029,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>667.89</v>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>-0.220</t>
+        <v>668.0599999999999</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -25029,15 +25052,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>668.11</v>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>-0.630</t>
+        <v>667.89</v>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -25052,15 +25075,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>668.74</v>
+        <v>668.11</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.630</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -25075,15 +25098,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>668.76</v>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>668.74</v>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -25098,15 +25121,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>668.95</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>668.76</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -25121,15 +25144,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>668.9400000000001</v>
+        <v>668.95</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -25144,15 +25167,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>669.03</v>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>+0.270</t>
+        <v>668.9400000000001</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -25167,15 +25190,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>668.76</v>
+        <v>669.03</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.270</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -25190,15 +25213,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>668.77</v>
+        <v>668.76</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -25213,15 +25236,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>668.8200000000001</v>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>-0.280</t>
+        <v>668.77</v>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -25236,15 +25259,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>669.1</v>
+        <v>668.8200000000001</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -25259,15 +25282,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>669.29</v>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>669.1</v>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -25282,15 +25305,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>669.3099999999999</v>
+        <v>669.29</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -25305,15 +25328,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>669.39</v>
+        <v>669.3099999999999</v>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -25328,15 +25351,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>669.17</v>
+        <v>669.39</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>+0.150</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -25351,15 +25374,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>669.02</v>
+        <v>669.17</v>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -25374,15 +25397,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>669.05</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>669.02</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -25397,13 +25420,13 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>668.95</v>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+        <v>669.05</v>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -25420,15 +25443,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>668.85</v>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>668.95</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -25443,15 +25466,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>668.87</v>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>668.85</v>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -25466,15 +25489,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>668.92</v>
+        <v>668.87</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -25489,15 +25512,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>669.09</v>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>668.92</v>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -25512,15 +25535,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>669.34</v>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>669.09</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -25535,15 +25558,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>669.33</v>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>+0.450</t>
+        <v>669.34</v>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -25558,15 +25581,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>668.88</v>
+        <v>669.33</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.450</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -25581,15 +25604,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>668.76</v>
+        <v>668.88</v>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -25604,15 +25627,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>668.91</v>
+        <v>668.76</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -25627,15 +25650,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>668.97</v>
+        <v>668.91</v>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -25650,15 +25673,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>668.78</v>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>668.97</v>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -25673,15 +25696,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>668.95</v>
+        <v>668.78</v>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -25696,15 +25719,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>668.88</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>-0.260</t>
+        <v>668.95</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -25719,15 +25742,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>669.14</v>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>668.88</v>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -25742,15 +25765,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>669.16</v>
+        <v>669.14</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -25765,15 +25788,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>669.23</v>
+        <v>669.16</v>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -25788,15 +25811,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>669.2</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>669.23</v>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -25811,15 +25834,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>669.23</v>
+        <v>669.2</v>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -25834,15 +25857,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>669.22</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>669.23</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -25857,15 +25880,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>669.24</v>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>669.22</v>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -25880,15 +25903,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>669.3099999999999</v>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>669.24</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -25903,15 +25926,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>669.25</v>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>669.3099999999999</v>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -25926,15 +25949,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>669.2</v>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>669.25</v>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -25949,15 +25972,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>669.27</v>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>-0.510</t>
+        <v>669.2</v>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -25972,15 +25995,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>669.78</v>
+        <v>669.27</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>-0.510</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -25995,15 +26018,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>669.95</v>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>669.78</v>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -26018,15 +26041,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>669.96</v>
+        <v>669.95</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -26041,15 +26064,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>670.03</v>
+        <v>669.96</v>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -26064,15 +26087,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>669.9299999999999</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.03</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -26087,15 +26110,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>669.9400000000001</v>
-      </c>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>669.9299999999999</v>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -26110,15 +26133,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>670.04</v>
+        <v>669.9400000000001</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -26133,15 +26156,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>670.25</v>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>670.04</v>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -26156,15 +26179,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>670.38</v>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>670.25</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -26179,15 +26202,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>670.1900000000001</v>
+        <v>670.38</v>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -26202,15 +26225,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>670.2</v>
+        <v>670.1900000000001</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -26225,15 +26248,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>670.35</v>
+        <v>670.2</v>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -26248,15 +26271,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>670.24</v>
+        <v>670.35</v>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -26271,15 +26294,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>670.1</v>
+        <v>670.24</v>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -26294,15 +26317,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>670.22</v>
+        <v>670.1</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>-0.920</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -26317,15 +26340,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>671.14</v>
+        <v>670.22</v>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>+0.930</t>
+          <t>-0.920</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -26340,15 +26363,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>670.21</v>
+        <v>671.14</v>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.930</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -26363,15 +26386,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>670.11</v>
+        <v>670.21</v>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -26386,15 +26409,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>670.13</v>
+        <v>670.11</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -26409,15 +26432,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>670.24</v>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>-0.180</t>
+        <v>670.13</v>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -26432,15 +26455,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>670.42</v>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>+0.080</t>
+        <v>670.24</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -26455,15 +26478,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>670.34</v>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>670.42</v>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -26478,15 +26501,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>670.1900000000001</v>
+        <v>670.34</v>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -26501,15 +26524,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>670.1799999999999</v>
+        <v>670.1900000000001</v>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -26524,15 +26547,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>670.27</v>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>670.1799999999999</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -26547,15 +26570,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>670.22</v>
+        <v>670.27</v>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -26570,15 +26593,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>670.26</v>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>670.22</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -26593,15 +26616,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>670.16</v>
-      </c>
-      <c r="D76" s="16" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>670.26</v>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -26616,15 +26639,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>670.11</v>
+        <v>670.16</v>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -26639,15 +26662,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>670.1</v>
+        <v>670.11</v>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -26662,15 +26685,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>670.2</v>
+        <v>670.1</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>-0.200</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -26685,15 +26708,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>670.4</v>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>670.2</v>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -26708,15 +26731,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>670.47</v>
+        <v>670.4</v>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -26731,15 +26754,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>670.48</v>
-      </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.47</v>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -26754,15 +26777,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>670.51</v>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>+0.200</t>
+        <v>670.48</v>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -26777,15 +26800,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>670.3099999999999</v>
+        <v>670.51</v>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -26800,15 +26823,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>670.34</v>
+        <v>670.3099999999999</v>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -26823,15 +26846,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>670.35</v>
+        <v>670.34</v>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -26846,15 +26869,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>670.34</v>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>670.35</v>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -26869,15 +26892,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>670.4299999999999</v>
-      </c>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.34</v>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -26892,15 +26915,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>670.46</v>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>670.4299999999999</v>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -26915,15 +26938,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>670.4400000000001</v>
+        <v>670.46</v>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -26938,11 +26961,11 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>670.45</v>
+        <v>670.4400000000001</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
@@ -26961,15 +26984,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>670.46</v>
+        <v>670.45</v>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -26984,15 +27007,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>670.4400000000001</v>
-      </c>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.46</v>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -27007,15 +27030,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>670.45</v>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.4400000000001</v>
+      </c>
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -27030,15 +27053,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>670.48</v>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>670.45</v>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -27053,15 +27076,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>670.45</v>
-      </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>+0.200</t>
+        <v>670.48</v>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -27076,15 +27099,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>670.25</v>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.45</v>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -27099,15 +27122,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>670.26</v>
+        <v>670.25</v>
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -27122,11 +27145,11 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>670.23</v>
+        <v>670.26</v>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
@@ -27145,15 +27168,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>670.2</v>
-      </c>
-      <c r="D100" s="16" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>670.23</v>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -27168,15 +27191,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>670.1799999999999</v>
+        <v>670.2</v>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -27191,15 +27214,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>670.15</v>
+        <v>670.1799999999999</v>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -27214,15 +27237,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>670.1799999999999</v>
+        <v>670.15</v>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -27237,15 +27260,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>670.28</v>
-      </c>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.1799999999999</v>
+      </c>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -27260,15 +27283,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>670.29</v>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>670.28</v>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -27283,15 +27306,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>670.28</v>
+        <v>670.29</v>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -27306,15 +27329,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>670.3099999999999</v>
+        <v>670.28</v>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -27329,15 +27352,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>670.45</v>
-      </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>670.3099999999999</v>
+      </c>
+      <c r="D108" s="16" t="inlineStr">
+        <is>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -27352,15 +27375,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>670.62</v>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>670.45</v>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -27375,15 +27398,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>670.5</v>
-      </c>
-      <c r="D110" s="16" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>670.62</v>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -27398,15 +27421,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>670.4400000000001</v>
-      </c>
-      <c r="D111" s="12" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>670.5</v>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -27421,15 +27444,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>670.48</v>
+        <v>670.4400000000001</v>
       </c>
       <c r="D112" s="16" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -27444,15 +27467,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>670.4</v>
+        <v>670.48</v>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -27467,15 +27490,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>670.26</v>
+        <v>670.4</v>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -27490,15 +27513,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>670.51</v>
+        <v>670.26</v>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -27513,15 +27536,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>670.53</v>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>670.51</v>
+      </c>
+      <c r="D116" s="16" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -27536,15 +27559,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 14:59:15</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>670.62</v>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>670.53</v>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -27559,15 +27582,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 14:59:15</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>670.5599999999999</v>
+        <v>670.62</v>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -27582,15 +27605,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>670.59</v>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>670.5599999999999</v>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -27605,15 +27628,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>670.52</v>
+        <v>670.59</v>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -27628,15 +27651,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>670.53</v>
+        <v>670.52</v>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>-0.530</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -27651,15 +27674,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>671.0599999999999</v>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.53</v>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -27674,15 +27697,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>671.0700000000001</v>
+        <v>671.0599999999999</v>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>-0.570</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -27697,15 +27720,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>671.64</v>
-      </c>
-      <c r="D124" s="15" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>671.0700000000001</v>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>-0.570</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -27720,15 +27743,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>671.88</v>
+        <v>671.64</v>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -27743,15 +27766,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>671.91</v>
-      </c>
-      <c r="D126" s="15" t="inlineStr">
-        <is>
-          <t>-0.140</t>
+        <v>671.88</v>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -27766,15 +27789,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>672.05</v>
-      </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>671.91</v>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -27789,15 +27812,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>671.87</v>
+        <v>672.05</v>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -27812,15 +27835,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>672.09</v>
+        <v>671.87</v>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -27835,15 +27858,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>672.21</v>
+        <v>672.09</v>
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -27858,15 +27881,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 12:06:08</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>672.14</v>
-      </c>
-      <c r="D131" s="12" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>672.21</v>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -27881,15 +27904,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 12:06:08</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>672.2</v>
-      </c>
-      <c r="D132" s="15" t="inlineStr">
-        <is>
-          <t>-0.270</t>
+        <v>672.14</v>
+      </c>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -27904,15 +27927,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>672.47</v>
+        <v>672.2</v>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -27927,15 +27950,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>672.54</v>
+        <v>672.47</v>
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -27950,15 +27973,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>672.53</v>
+        <v>672.54</v>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -27973,15 +27996,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>672.36</v>
+        <v>672.53</v>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -27996,15 +28019,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>672.37</v>
+        <v>672.36</v>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -28019,15 +28042,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>672.4</v>
-      </c>
-      <c r="D138" s="15" t="inlineStr">
-        <is>
-          <t>-0.140</t>
+        <v>672.37</v>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -28042,15 +28065,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>672.54</v>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>672.4</v>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -28065,15 +28088,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>672.52</v>
-      </c>
-      <c r="D140" s="16" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>672.54</v>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -28088,15 +28111,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>672.41</v>
+        <v>672.52</v>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -28111,15 +28134,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>672.21</v>
-      </c>
-      <c r="D142" s="16" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>672.41</v>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -28134,15 +28157,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>672.17</v>
+        <v>672.21</v>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -28157,15 +28180,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>672.14</v>
-      </c>
-      <c r="D144" s="16" t="inlineStr">
-        <is>
-          <t>+0.200</t>
+        <v>672.17</v>
+      </c>
+      <c r="D144" s="15" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -28180,15 +28203,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>671.9400000000001</v>
-      </c>
-      <c r="D145" s="12" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>672.14</v>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -28203,15 +28226,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>671.96</v>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>671.9400000000001</v>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -28226,15 +28249,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>672.02</v>
+        <v>671.96</v>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>-0.200</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -28249,15 +28272,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>672.22</v>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>672.02</v>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -28272,15 +28295,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>672.26</v>
+        <v>672.22</v>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -28295,15 +28318,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>672.36</v>
+        <v>672.26</v>
       </c>
       <c r="D150" s="16" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -28318,15 +28341,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>672.24</v>
+        <v>672.36</v>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -28341,15 +28364,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>672.23</v>
+        <v>672.24</v>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -28364,15 +28387,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>672.36</v>
-      </c>
-      <c r="D153" s="9" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>672.23</v>
+      </c>
+      <c r="D153" s="12" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -28387,15 +28410,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>672.26</v>
-      </c>
-      <c r="D154" s="16" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>672.36</v>
+      </c>
+      <c r="D154" s="15" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -28410,15 +28433,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>672.24</v>
-      </c>
-      <c r="D155" s="12" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>672.26</v>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -28433,15 +28456,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>672.3099999999999</v>
+        <v>672.24</v>
       </c>
       <c r="D156" s="16" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -28456,15 +28479,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>672.3</v>
-      </c>
-      <c r="D157" s="12" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>672.3099999999999</v>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -28479,15 +28502,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>672.47</v>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>672.3</v>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -28502,15 +28525,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>672.5</v>
-      </c>
-      <c r="D159" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>672.47</v>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -28525,15 +28548,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>672.48</v>
+        <v>672.5</v>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -28548,15 +28571,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>672.54</v>
-      </c>
-      <c r="D161" s="9" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.48</v>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -28571,15 +28594,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>672.53</v>
-      </c>
-      <c r="D162" s="16" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>672.54</v>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -28594,15 +28617,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>672.35</v>
-      </c>
-      <c r="D163" s="12" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>672.53</v>
+      </c>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -28617,15 +28640,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>672.4299999999999</v>
-      </c>
-      <c r="D164" s="15" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>672.35</v>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -28640,15 +28663,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>672.46</v>
+        <v>672.4299999999999</v>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -28663,15 +28686,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>672.63</v>
+        <v>672.46</v>
       </c>
       <c r="D166" s="16" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -28686,15 +28709,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>672.5700000000001</v>
+        <v>672.63</v>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -28709,15 +28732,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>672.55</v>
-      </c>
-      <c r="D168" s="16" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.5700000000001</v>
+      </c>
+      <c r="D168" s="15" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -28732,15 +28755,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>672.54</v>
+        <v>672.55</v>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -28755,15 +28778,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>672.51</v>
+        <v>672.54</v>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -28778,15 +28801,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>672.61</v>
-      </c>
-      <c r="D171" s="9" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>672.51</v>
+      </c>
+      <c r="D171" s="12" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -28801,15 +28824,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>672.55</v>
-      </c>
-      <c r="D172" s="16" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>672.61</v>
+      </c>
+      <c r="D172" s="15" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -28824,15 +28847,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>672.5</v>
+        <v>672.55</v>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -28847,15 +28870,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>672.34</v>
-      </c>
-      <c r="D174" s="16" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.5</v>
+      </c>
+      <c r="D174" s="15" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -28870,15 +28893,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>672.33</v>
+        <v>672.34</v>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -28893,15 +28916,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>672.3</v>
+        <v>672.33</v>
       </c>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -28916,15 +28939,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>672.41</v>
+        <v>672.3</v>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -28939,15 +28962,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>672.66</v>
-      </c>
-      <c r="D178" s="15" t="inlineStr">
-        <is>
-          <t>-0.120</t>
+        <v>672.41</v>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -28962,15 +28985,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>672.78</v>
-      </c>
-      <c r="D179" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>672.66</v>
+      </c>
+      <c r="D179" s="12" t="inlineStr">
+        <is>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -28985,15 +29008,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 12:26:44</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>672.76</v>
-      </c>
-      <c r="D180" s="16" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>672.78</v>
+      </c>
+      <c r="D180" s="15" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -29008,15 +29031,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 12:26:44</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>672.71</v>
+        <v>672.76</v>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -29031,15 +29054,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>672.67</v>
-      </c>
-      <c r="D182" s="16" t="inlineStr">
-        <is>
-          <t>+0.080</t>
+        <v>672.71</v>
+      </c>
+      <c r="D182" s="15" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -29054,15 +29077,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>672.59</v>
-      </c>
-      <c r="D183" s="12" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>672.67</v>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -29077,15 +29100,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>672.6</v>
-      </c>
-      <c r="D184" s="15" t="inlineStr">
-        <is>
-          <t>-0.220</t>
+        <v>672.59</v>
+      </c>
+      <c r="D184" s="16" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -29100,15 +29123,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>672.8200000000001</v>
+        <v>672.6</v>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -29123,15 +29146,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>673.24</v>
+        <v>672.8200000000001</v>
       </c>
       <c r="D186" s="16" t="inlineStr">
         <is>
-          <t>+0.340</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -29146,15 +29169,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>672.9</v>
-      </c>
-      <c r="D187" s="12" t="inlineStr">
-        <is>
-          <t>-0.140</t>
+        <v>673.24</v>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -29169,15 +29192,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>673.04</v>
+        <v>672.9</v>
       </c>
       <c r="D188" s="16" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -29192,15 +29215,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>673.03</v>
+        <v>673.04</v>
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -29215,15 +29238,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>672.79</v>
+        <v>673.03</v>
       </c>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -29238,15 +29261,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>673.03</v>
-      </c>
-      <c r="D191" s="9" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.79</v>
+      </c>
+      <c r="D191" s="12" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -29261,13 +29284,13 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>673.02</v>
-      </c>
-      <c r="D192" s="16" t="inlineStr">
+        <v>673.03</v>
+      </c>
+      <c r="D192" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -29284,15 +29307,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>673.01</v>
-      </c>
-      <c r="D193" s="12" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>673.02</v>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -29307,15 +29330,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>673.09</v>
-      </c>
-      <c r="D194" s="15" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>673.01</v>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -29330,15 +29353,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>673.11</v>
-      </c>
-      <c r="D195" s="9" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>673.09</v>
+      </c>
+      <c r="D195" s="12" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -29353,15 +29376,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>672.97</v>
-      </c>
-      <c r="D196" s="16" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>673.11</v>
+      </c>
+      <c r="D196" s="15" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -29376,15 +29399,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>672.87</v>
+        <v>672.97</v>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -29399,15 +29422,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>672.74</v>
+        <v>672.87</v>
       </c>
       <c r="D198" s="15" t="inlineStr">
         <is>
-          <t>-0.300</t>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -29422,14 +29445,37 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C199" s="8" t="n">
+        <v>672.74</v>
+      </c>
+      <c r="D199" s="12" t="inlineStr">
+        <is>
+          <t>-0.300</t>
+        </is>
+      </c>
+      <c r="E199" s="8" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="n">
+        <v>196</v>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C199" s="8" t="n">
+      <c r="C200" s="6" t="n">
         <v>673.04</v>
       </c>
-      <c r="D199" s="8" t="inlineStr"/>
-      <c r="E199" s="8" t="inlineStr">
+      <c r="D200" s="6" t="inlineStr"/>
+      <c r="E200" s="6" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 07:12:24</t>
+          <t>更新时间: 2026-09-19 09:09:49</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 09:09:49</t>
+          <t>更新时间: 2026-09-19 13:49:54</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 13:49:54</t>
+          <t>更新时间: 2026-09-19 17:46:17</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 17:46:17</t>
+          <t>更新时间: 2026-09-19 21:28:39</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 21:28:39</t>
+          <t>更新时间: 2026-09-20 00:40:38</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 00:40:38</t>
+          <t>更新时间: 2026-09-20 02:54:20</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 02:54:20</t>
+          <t>更新时间: 2026-09-20 05:10:29</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 05:10:29</t>
+          <t>更新时间: 2026-09-20 07:00:27</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 07:00:27</t>
+          <t>更新时间: 2026-09-20 08:53:33</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 08:53:33</t>
+          <t>更新时间: 2026-09-20 13:29:57</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 13:29:57</t>
+          <t>更新时间: 2026-09-20 18:00:09</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 18:00:09</t>
+          <t>更新时间: 2026-09-20 22:02:40</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 22:02:40</t>
+          <t>更新时间: 2026-09-21 01:24:15</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 01:24:15</t>
+          <t>更新时间: 2026-09-21 03:34:16</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 03:34:16</t>
+          <t>更新时间: 2026-09-21 05:46:35</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -185,10 +185,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 02:58:27</t>
+          <t>更新时间: 2026-09-22 06:28:18</t>
         </is>
       </c>
     </row>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>764.4</v>
+        <v>763.73</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 02:58:23</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -765,15 +765,15 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>667.66</v>
+        <v>667.65</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 21:54:34</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -19387,7 +19387,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 764.40 | 最高: 782.950 | 最低: 764.400 | 总记录数: 251</t>
+          <t>最新价: 763.73 | 最高: 782.950 | 最低: 763.730 | 总记录数: 252</t>
         </is>
       </c>
     </row>
@@ -19424,15 +19424,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 02:58:23</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>764.4</v>
+        <v>763.73</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>-0.750</t>
+          <t>-0.670</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -19447,15 +19447,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 21:54:34</t>
+          <t>2026-09-22 02:58:23</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>765.15</v>
+        <v>764.4</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>+0.510</t>
+          <t>-0.750</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -19470,15 +19470,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:24</t>
+          <t>2026-09-21 21:54:34</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>764.64</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>765.15</v>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>+0.510</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -19493,15 +19493,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 09:33:28</t>
+          <t>2026-09-21 15:01:24</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>765.11</v>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>-0.430</t>
+        <v>764.64</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -19516,15 +19516,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 07:12:19</t>
+          <t>2026-09-21 09:33:28</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>765.54</v>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>+0.710</t>
+        <v>765.11</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -19539,15 +19539,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>764.83</v>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>765.54</v>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -19562,15 +19562,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>764.54</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>764.83</v>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -19585,15 +19585,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>764.62</v>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>-0.770</t>
+        <v>764.54</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -19608,15 +19608,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>765.39</v>
+        <v>764.62</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>-0.620</t>
+          <t>-0.770</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -19631,15 +19631,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:32:25</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>766.01</v>
+        <v>765.39</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>-0.620</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -19654,15 +19654,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 05:47:34</t>
+          <t>2026-09-18 09:32:25</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>765.63</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>766.01</v>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -19677,15 +19677,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 05:47:34</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>765.8200000000001</v>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>-1.020</t>
+        <v>765.63</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -19700,15 +19700,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>766.84</v>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>+1.260</t>
+        <v>765.8200000000001</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -19723,15 +19723,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>765.58</v>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>766.84</v>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>+1.260</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -19746,15 +19746,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>765.24</v>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>765.58</v>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -19769,15 +19769,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 08:40:02</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>765.39</v>
+        <v>765.24</v>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>+0.340</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -19792,15 +19792,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 08:40:02</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>765.05</v>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>-4.700</t>
+        <v>765.39</v>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -19815,15 +19815,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>769.75</v>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>765.05</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>-4.700</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -19838,15 +19838,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>770.04</v>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>769.75</v>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -19861,15 +19861,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>769.95</v>
+        <v>770.04</v>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>-0.730</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -19884,15 +19884,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>770.6799999999999</v>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>769.95</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -19907,15 +19907,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 09:40:23</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>770.47</v>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>770.6799999999999</v>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -19930,15 +19930,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 07:41:58</t>
+          <t>2026-09-16 09:40:23</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>770.38</v>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>770.47</v>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -19953,15 +19953,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>770.8</v>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>770.38</v>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -19976,15 +19976,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>770.8200000000001</v>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>+0.400</t>
+        <v>770.8</v>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -19999,15 +19999,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>770.42</v>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>770.8200000000001</v>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -20022,15 +20022,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>770.24</v>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>770.42</v>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -20045,13 +20045,13 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>771.05</v>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
+        <v>770.24</v>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>-0.810</t>
         </is>
@@ -20068,15 +20068,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>771.86</v>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>+1.540</t>
+        <v>771.05</v>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -20091,15 +20091,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>770.3200000000001</v>
+        <v>771.86</v>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>-1.440</t>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -20114,15 +20114,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>771.76</v>
+        <v>770.3200000000001</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>-2.140</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -20137,15 +20137,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12 05:00:53</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>773.9</v>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>-0.430</t>
+        <v>771.76</v>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>-2.140</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -20160,15 +20160,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15:57</t>
+          <t>2026-09-12 05:00:53</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>774.33</v>
+        <v>773.9</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>-0.730</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -20183,15 +20183,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-12 02:15:57</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>775.0599999999999</v>
+        <v>774.33</v>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>+1.400</t>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -20206,15 +20206,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>773.66</v>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>775.0599999999999</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>+1.400</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -20229,15 +20229,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>775.1</v>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>-0.500</t>
+        <v>773.66</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -20252,15 +20252,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 09:18:12</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>775.6</v>
+        <v>775.1</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.500</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -20275,15 +20275,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 09:18:12</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>776.01</v>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>775.6</v>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -20298,15 +20298,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>776.01</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -20321,15 +20321,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>775.83</v>
+        <v>776.38</v>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>-0.700</t>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -20344,15 +20344,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>776.53</v>
+        <v>775.83</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -20367,15 +20367,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>776.91</v>
+        <v>776.53</v>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -20390,15 +20390,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 06:08:04</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>776.7</v>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>776.91</v>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -20413,15 +20413,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 06:08:04</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>776.8</v>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>776.7</v>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -20436,15 +20436,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>777.27</v>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>+0.760</t>
+        <v>776.8</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -20459,15 +20459,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>776.51</v>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>777.27</v>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>+0.760</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -20482,15 +20482,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>776.29</v>
+        <v>776.51</v>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>+0.390</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -20505,15 +20505,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>775.9</v>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>776.29</v>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -20528,15 +20528,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>775.58</v>
+        <v>775.9</v>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -20551,15 +20551,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>775.48</v>
+        <v>775.58</v>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>-0.810</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -20574,15 +20574,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>776.29</v>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>775.48</v>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -20597,15 +20597,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 06:18:23</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>776.0700000000001</v>
+        <v>776.29</v>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -20620,15 +20620,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 06:18:23</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>776.54</v>
+        <v>776.0700000000001</v>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -20643,15 +20643,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>776.59</v>
+        <v>776.54</v>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>+0.460</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -20666,15 +20666,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>776.13</v>
+        <v>776.59</v>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -20689,15 +20689,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>775.3200000000001</v>
+        <v>776.13</v>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -20712,15 +20712,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 08:56:04</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>775.6900000000001</v>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>775.3200000000001</v>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -20735,15 +20735,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 07:06:50</t>
+          <t>2026-09-07 08:56:04</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>775.63</v>
+        <v>775.6900000000001</v>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>-0.390</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -20758,15 +20758,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-05 07:06:50</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>776.02</v>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>775.63</v>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -20781,15 +20781,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>775.76</v>
+        <v>776.02</v>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>-0.720</t>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -20804,15 +20804,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>776.48</v>
+        <v>775.76</v>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>-0.580</t>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -20827,15 +20827,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>777.0599999999999</v>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>776.48</v>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>-0.580</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -20850,15 +20850,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 07:59:45</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>777.13</v>
+        <v>777.0599999999999</v>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>-0.540</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -20873,15 +20873,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 07:59:45</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>777.67</v>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
-        <is>
-          <t>-0.300</t>
+        <v>777.13</v>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>-0.540</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -20896,15 +20896,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>777.97</v>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>+1.580</t>
+        <v>777.67</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>-0.300</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -20919,15 +20919,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>776.39</v>
-      </c>
-      <c r="D70" s="15" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>777.97</v>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
+          <t>+1.580</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -20942,15 +20942,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>776.01</v>
+        <v>776.39</v>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>+0.660</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -20965,15 +20965,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>775.35</v>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>+0.700</t>
+        <v>776.01</v>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>+0.660</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -20988,15 +20988,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 06:35:56</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>774.65</v>
+        <v>775.35</v>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.700</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -21011,15 +21011,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 04:09:22</t>
+          <t>2026-09-03 06:35:56</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>774.64</v>
+        <v>774.65</v>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>-0.270</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -21034,15 +21034,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 04:09:22</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>774.91</v>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>+0.390</t>
+        <v>774.64</v>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -21057,15 +21057,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>774.52</v>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>+0.230</t>
+        <v>774.91</v>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
+        <is>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -21080,15 +21080,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 17:58:25</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>774.29</v>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>774.52</v>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>+0.230</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -21103,15 +21103,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 17:58:25</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>774.36</v>
-      </c>
-      <c r="D78" s="16" t="inlineStr">
-        <is>
-          <t>-0.860</t>
+        <v>774.29</v>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -21126,15 +21126,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>774.36</v>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>-0.860</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -21149,15 +21149,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 02:48:49</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>774.87</v>
+        <v>775.22</v>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>-0.600</t>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -21172,15 +21172,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 02:48:49</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>775.47</v>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>774.87</v>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -21195,15 +21195,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>775.25</v>
+        <v>775.47</v>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>-1.030</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -21218,15 +21218,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>776.28</v>
+        <v>775.25</v>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>-0.280</t>
+          <t>-1.030</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -21241,15 +21241,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 09:25:49</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>776.5599999999999</v>
-      </c>
-      <c r="D84" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>776.28</v>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -21264,15 +21264,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 06:48:36</t>
+          <t>2026-09-01 09:25:49</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>776.58</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -21287,15 +21287,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 02:10:52</t>
+          <t>2026-09-01 06:48:36</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>776.63</v>
+        <v>776.58</v>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>+1.230</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -21310,15 +21310,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 02:10:52</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>775.4</v>
+        <v>776.63</v>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -21333,15 +21333,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>775.22</v>
+        <v>775.4</v>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>-0.700</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -21356,15 +21356,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 08:13:17</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>775.92</v>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.22</v>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -21379,15 +21379,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 08:13:17</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>775.85</v>
+        <v>775.92</v>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>-2.850</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -21402,15 +21402,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>778.7</v>
+        <v>775.85</v>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-2.850</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -21425,15 +21425,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>779.1</v>
+        <v>778.7</v>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -21448,15 +21448,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>778.72</v>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>-0.640</t>
+        <v>779.1</v>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -21471,15 +21471,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>779.36</v>
-      </c>
-      <c r="D94" s="16" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>778.72</v>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>-0.640</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -21494,15 +21494,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 04:13:31</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>779.5599999999999</v>
-      </c>
-      <c r="D95" s="11" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>779.36</v>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -21517,15 +21517,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 04:13:31</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>779.39</v>
+        <v>779.5599999999999</v>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -21540,15 +21540,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>779.6</v>
+        <v>779.39</v>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -21563,15 +21563,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>780.03</v>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>-0.120</t>
+        <v>779.6</v>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -21586,15 +21586,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 18:53:28</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>780.15</v>
+        <v>780.03</v>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -21609,15 +21609,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 18:53:28</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>780.62</v>
+        <v>780.15</v>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>+0.560</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -21632,15 +21632,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>780.0599999999999</v>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>780.62</v>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>+0.560</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -21655,15 +21655,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>780.17</v>
-      </c>
-      <c r="D102" s="16" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>780.0599999999999</v>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -21678,15 +21678,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>780.38</v>
-      </c>
-      <c r="D103" s="11" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>780.17</v>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -21701,15 +21701,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 10:07:59</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>780.36</v>
+        <v>780.38</v>
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -21724,15 +21724,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 07:52:24</t>
+          <t>2026-08-26 10:07:59</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>780.6</v>
-      </c>
-      <c r="D105" s="11" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>780.36</v>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -21747,15 +21747,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 01:49:35</t>
+          <t>2026-08-26 07:52:24</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>780.4299999999999</v>
-      </c>
-      <c r="D106" s="15" t="inlineStr">
-        <is>
-          <t>+0.080</t>
+        <v>780.6</v>
+      </c>
+      <c r="D106" s="16" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -21770,15 +21770,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 01:49:35</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>780.35</v>
+        <v>780.4299999999999</v>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -21793,15 +21793,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>780.3099999999999</v>
-      </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>+0.410</t>
+        <v>780.35</v>
+      </c>
+      <c r="D108" s="16" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -21816,15 +21816,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:05:53</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>779.9</v>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>-0.260</t>
+        <v>780.3099999999999</v>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>+0.410</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -21839,15 +21839,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 21:05:53</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>780.16</v>
-      </c>
-      <c r="D110" s="16" t="inlineStr">
-        <is>
-          <t>-0.230</t>
+        <v>779.9</v>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -21862,15 +21862,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>780.39</v>
-      </c>
-      <c r="D111" s="11" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>780.16</v>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>-0.230</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -21885,15 +21885,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>780.15</v>
-      </c>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>+0.540</t>
+        <v>780.39</v>
+      </c>
+      <c r="D112" s="16" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -21908,15 +21908,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:26</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>779.61</v>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>780.15</v>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>+0.540</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -21931,15 +21931,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:01:55</t>
+          <t>2026-08-25 15:51:26</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>779.65</v>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>779.61</v>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -21954,15 +21954,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 15:01:55</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>779.73</v>
+        <v>779.65</v>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -21977,15 +21977,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>780.11</v>
-      </c>
-      <c r="D116" s="16" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>779.73</v>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -22000,15 +22000,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>780.4</v>
-      </c>
-      <c r="D117" s="11" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>780.11</v>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -22023,15 +22023,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:57:56</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>780.3099999999999</v>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>780.4</v>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -22046,15 +22046,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 06:50:27</t>
+          <t>2026-08-25 09:57:56</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>780.1900000000001</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -22069,15 +22069,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 06:50:27</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>780.1799999999999</v>
+        <v>780.1900000000001</v>
       </c>
       <c r="D120" s="16" t="inlineStr">
         <is>
-          <t>-0.450</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -22092,15 +22092,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>780.63</v>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>780.1799999999999</v>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>-0.450</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -22115,15 +22115,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>780.17</v>
+        <v>780.63</v>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -22138,15 +22138,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>780.61</v>
-      </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>780.17</v>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -22161,15 +22161,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>780.14</v>
+        <v>780.61</v>
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -22184,15 +22184,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>780.23</v>
+        <v>780.14</v>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>-0.530</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -22207,15 +22207,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>780.76</v>
-      </c>
-      <c r="D126" s="16" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>780.23</v>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -22230,15 +22230,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>780.91</v>
+        <v>780.76</v>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -22253,15 +22253,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>781.35</v>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>780.91</v>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -22276,15 +22276,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>781.38</v>
-      </c>
-      <c r="D129" s="11" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>781.35</v>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -22299,15 +22299,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>781.09</v>
+        <v>781.38</v>
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>-0.350</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -22322,15 +22322,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>781.4400000000001</v>
+        <v>781.09</v>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.350</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -22345,15 +22345,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>781.55</v>
+        <v>781.4400000000001</v>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -22368,15 +22368,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 09:42:15</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>781.23</v>
+        <v>781.55</v>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -22391,15 +22391,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 10:32:40</t>
+          <t>2026-08-24 09:42:15</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>781.01</v>
+        <v>781.23</v>
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -22414,15 +22414,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 05:00:11</t>
+          <t>2026-08-22 10:32:40</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>781.11</v>
+        <v>781.01</v>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>-0.180</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -22437,15 +22437,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 02:00:51</t>
+          <t>2026-08-22 05:00:11</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>781.29</v>
-      </c>
-      <c r="D136" s="16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>781.11</v>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -22460,15 +22460,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-22 02:00:51</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>781.34</v>
-      </c>
-      <c r="D137" s="11" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>781.29</v>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -22483,15 +22483,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>780.79</v>
-      </c>
-      <c r="D138" s="15" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>781.34</v>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -22506,15 +22506,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>780.6799999999999</v>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>-0.610</t>
+        <v>780.79</v>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -22529,15 +22529,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>781.29</v>
-      </c>
-      <c r="D140" s="16" t="inlineStr">
-        <is>
-          <t>-1.420</t>
+        <v>780.6799999999999</v>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -22552,15 +22552,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>782.71</v>
+        <v>781.29</v>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-1.420</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -22575,15 +22575,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>782.95</v>
+        <v>782.71</v>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>+1.080</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -22598,15 +22598,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>781.87</v>
-      </c>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>782.95</v>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>+1.080</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -22621,15 +22621,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>782.25</v>
+        <v>781.87</v>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>+0.260</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -22644,15 +22644,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>781.99</v>
+        <v>782.25</v>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -22667,15 +22667,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>781.95</v>
+        <v>781.99</v>
       </c>
       <c r="D146" s="16" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -22690,15 +22690,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>781.99</v>
+        <v>781.95</v>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -22713,15 +22713,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>782.39</v>
+        <v>781.99</v>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>+0.360</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -22736,15 +22736,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:13</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>782.03</v>
+        <v>782.39</v>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>+0.400</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -22759,15 +22759,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 06:49:01</t>
+          <t>2026-08-21 09:10:13</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>781.63</v>
-      </c>
-      <c r="D150" s="15" t="inlineStr">
-        <is>
-          <t>+0.680</t>
+        <v>782.03</v>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -22782,15 +22782,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 06:49:01</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>780.95</v>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>-0.780</t>
+        <v>781.63</v>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -22805,15 +22805,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>781.73</v>
-      </c>
-      <c r="D152" s="16" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>780.95</v>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -22828,15 +22828,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>781.79</v>
+        <v>781.73</v>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -22851,15 +22851,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>782.1900000000001</v>
+        <v>781.79</v>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>+0.150</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -22874,15 +22874,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>782.04</v>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>782.1900000000001</v>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -22897,15 +22897,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>782.74</v>
+        <v>782.04</v>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -22920,15 +22920,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>782.42</v>
+        <v>782.74</v>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -22943,15 +22943,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>781.95</v>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>+0.810</t>
+        <v>782.42</v>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -22966,15 +22966,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>781.14</v>
-      </c>
-      <c r="D159" s="9" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.95</v>
+      </c>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -22989,15 +22989,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>781.39</v>
+        <v>781.14</v>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -23012,15 +23012,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>781.2</v>
+        <v>781.39</v>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -23035,15 +23035,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>781.17</v>
+        <v>781.2</v>
       </c>
       <c r="D162" s="16" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -23058,15 +23058,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 10:06:13</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>781.42</v>
+        <v>781.17</v>
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 07:36:53</t>
+          <t>2026-08-20 10:06:13</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>781.79</v>
+        <v>781.42</v>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -23104,15 +23104,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 06:33:42</t>
+          <t>2026-08-20 07:36:53</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>781.77</v>
+        <v>781.79</v>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -23127,15 +23127,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 06:33:42</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>781.45</v>
-      </c>
-      <c r="D166" s="15" t="inlineStr">
-        <is>
-          <t>+0.850</t>
+        <v>781.77</v>
+      </c>
+      <c r="D166" s="16" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -23150,15 +23150,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>780.6</v>
+        <v>781.45</v>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.850</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -23173,15 +23173,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>780.12</v>
-      </c>
-      <c r="D168" s="15" t="inlineStr">
-        <is>
-          <t>+1.750</t>
+        <v>780.6</v>
+      </c>
+      <c r="D168" s="16" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -23196,15 +23196,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>778.37</v>
+        <v>780.12</v>
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>+1.750</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -23219,15 +23219,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>778.09</v>
-      </c>
-      <c r="D170" s="15" t="inlineStr">
-        <is>
-          <t>+0.680</t>
+        <v>778.37</v>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -23242,15 +23242,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>777.41</v>
+        <v>778.09</v>
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -23265,15 +23265,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>777.3200000000001</v>
-      </c>
-      <c r="D172" s="15" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>777.41</v>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -23288,11 +23288,11 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>777.1</v>
+        <v>777.3200000000001</v>
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
@@ -23311,15 +23311,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>776.88</v>
+        <v>777.1</v>
       </c>
       <c r="D174" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -23334,15 +23334,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>776.89</v>
-      </c>
-      <c r="D175" s="11" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>776.88</v>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -23357,15 +23357,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>776.84</v>
+        <v>776.89</v>
       </c>
       <c r="D176" s="16" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -23380,15 +23380,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 09:12:00</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D177" s="11" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.84</v>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -23403,15 +23403,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 09:12:00</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>776.72</v>
+        <v>776.9</v>
       </c>
       <c r="D178" s="16" t="inlineStr">
         <is>
-          <t>-0.460</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>777.1799999999999</v>
-      </c>
-      <c r="D179" s="11" t="inlineStr">
-        <is>
-          <t>+0.630</t>
+        <v>776.72</v>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>-0.460</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>776.55</v>
+        <v>777.1799999999999</v>
       </c>
       <c r="D180" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:24</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>776.62</v>
-      </c>
-      <c r="D181" s="11" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>776.55</v>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 17:58:24</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>776.53</v>
-      </c>
-      <c r="D182" s="15" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>776.62</v>
+      </c>
+      <c r="D182" s="16" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>776.36</v>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
-        <is>
-          <t>-0.160</t>
+        <v>776.53</v>
+      </c>
+      <c r="D183" s="11" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>776.52</v>
-      </c>
-      <c r="D184" s="16" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>776.36</v>
+      </c>
+      <c r="D184" s="15" t="inlineStr">
+        <is>
+          <t>-0.160</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>776.53</v>
+        <v>776.52</v>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>-0.390</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -23587,15 +23587,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>776.92</v>
+        <v>776.53</v>
       </c>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -23610,15 +23610,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 10:04:24</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>776.8200000000001</v>
+        <v>776.92</v>
       </c>
       <c r="D187" s="11" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -23633,15 +23633,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 07:54:32</t>
+          <t>2026-08-18 10:04:24</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>776.61</v>
+        <v>776.8200000000001</v>
       </c>
       <c r="D188" s="16" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -23656,15 +23656,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 05:48:09</t>
+          <t>2026-08-18 07:54:32</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>776.74</v>
-      </c>
-      <c r="D189" s="11" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.61</v>
+      </c>
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -23679,15 +23679,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 05:48:09</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>776.5599999999999</v>
+        <v>776.74</v>
       </c>
       <c r="D190" s="16" t="inlineStr">
         <is>
-          <t>-0.600</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -23702,15 +23702,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>777.16</v>
-      </c>
-      <c r="D191" s="11" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>776.5599999999999</v>
+      </c>
+      <c r="D191" s="9" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -23725,15 +23725,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>776.8099999999999</v>
+        <v>777.16</v>
       </c>
       <c r="D192" s="16" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -23748,15 +23748,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:45</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>777.21</v>
+        <v>776.8099999999999</v>
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -23771,15 +23771,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 21:10:45</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>777.4299999999999</v>
-      </c>
-      <c r="D194" s="16" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>777.21</v>
+      </c>
+      <c r="D194" s="15" t="inlineStr">
+        <is>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -23794,15 +23794,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>777.52</v>
-      </c>
-      <c r="D195" s="11" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>777.4299999999999</v>
+      </c>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -23817,15 +23817,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>777.5</v>
-      </c>
-      <c r="D196" s="15" t="inlineStr">
-        <is>
-          <t>+0.370</t>
+        <v>777.52</v>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -23840,15 +23840,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>777.13</v>
+        <v>777.5</v>
       </c>
       <c r="D197" s="11" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.370</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -23863,15 +23863,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>777.04</v>
-      </c>
-      <c r="D198" s="15" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>777.13</v>
+      </c>
+      <c r="D198" s="16" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -23886,15 +23886,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D199" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.04</v>
+      </c>
+      <c r="D199" s="11" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -23909,15 +23909,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="D200" s="16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>776.9</v>
+      </c>
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -23932,15 +23932,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>776.96</v>
-      </c>
-      <c r="D201" s="11" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>776.91</v>
+      </c>
+      <c r="D201" s="9" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -23955,15 +23955,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 09:21:39</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>776.84</v>
-      </c>
-      <c r="D202" s="15" t="inlineStr">
-        <is>
-          <t>+0.750</t>
+        <v>776.96</v>
+      </c>
+      <c r="D202" s="16" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -23978,15 +23978,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 09:21:39</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>776.09</v>
-      </c>
-      <c r="D203" s="9" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>776.84</v>
+      </c>
+      <c r="D203" s="11" t="inlineStr">
+        <is>
+          <t>+0.750</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -24001,15 +24001,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>776.38</v>
+        <v>776.09</v>
       </c>
       <c r="D204" s="15" t="inlineStr">
         <is>
-          <t>+0.570</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -24024,15 +24024,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>775.8099999999999</v>
+        <v>776.38</v>
       </c>
       <c r="D205" s="11" t="inlineStr">
         <is>
-          <t>+0.770</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -24047,15 +24047,15 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>775.04</v>
-      </c>
-      <c r="D206" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>775.8099999999999</v>
+      </c>
+      <c r="D206" s="16" t="inlineStr">
+        <is>
+          <t>+0.770</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -24070,15 +24070,15 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>774.92</v>
+        <v>775.04</v>
       </c>
       <c r="D207" s="11" t="inlineStr">
         <is>
-          <t>+0.360</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -24093,15 +24093,15 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>774.5599999999999</v>
-      </c>
-      <c r="D208" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>774.92</v>
+      </c>
+      <c r="D208" s="16" t="inlineStr">
+        <is>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -24116,15 +24116,15 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C209" s="8" t="n">
-        <v>774.4400000000001</v>
-      </c>
-      <c r="D209" s="9" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>774.5599999999999</v>
+      </c>
+      <c r="D209" s="11" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -24139,15 +24139,15 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>774.46</v>
+        <v>774.4400000000001</v>
       </c>
       <c r="D210" s="15" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -24162,15 +24162,15 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
-        <v>774.25</v>
+        <v>774.46</v>
       </c>
       <c r="D211" s="11" t="inlineStr">
         <is>
-          <t>+0.310</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -24185,15 +24185,15 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 10:39:02</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>773.9400000000001</v>
-      </c>
-      <c r="D212" s="15" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>774.25</v>
+      </c>
+      <c r="D212" s="16" t="inlineStr">
+        <is>
+          <t>+0.310</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -24208,15 +24208,15 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 08:05:13</t>
+          <t>2026-08-14 10:39:02</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>773.9</v>
+        <v>773.9400000000001</v>
       </c>
       <c r="D213" s="11" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -24231,15 +24231,15 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 07:24:16</t>
+          <t>2026-08-14 08:05:13</t>
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>773.73</v>
-      </c>
-      <c r="D214" s="15" t="inlineStr">
-        <is>
-          <t>+0.200</t>
+        <v>773.9</v>
+      </c>
+      <c r="D214" s="16" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -24254,15 +24254,15 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 07:24:16</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>773.53</v>
-      </c>
-      <c r="D215" s="9" t="inlineStr">
-        <is>
-          <t>-0.790</t>
+        <v>773.73</v>
+      </c>
+      <c r="D215" s="11" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -24277,15 +24277,15 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>774.3200000000001</v>
+        <v>773.53</v>
       </c>
       <c r="D216" s="15" t="inlineStr">
         <is>
-          <t>+0.570</t>
+          <t>-0.790</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -24300,15 +24300,15 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
-        <v>773.75</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="D217" s="11" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -24323,15 +24323,15 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>773.7</v>
-      </c>
-      <c r="D218" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>773.75</v>
+      </c>
+      <c r="D218" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -24346,15 +24346,15 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>773.58</v>
+        <v>773.7</v>
       </c>
       <c r="D219" s="11" t="inlineStr">
         <is>
-          <t>+0.250</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -24369,15 +24369,15 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>773.33</v>
+        <v>773.58</v>
       </c>
       <c r="D220" s="16" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -24392,15 +24392,15 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>773.39</v>
-      </c>
-      <c r="D221" s="11" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>773.33</v>
+      </c>
+      <c r="D221" s="9" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -24415,15 +24415,15 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>773.11</v>
+        <v>773.39</v>
       </c>
       <c r="D222" s="16" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -24438,15 +24438,15 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>773.24</v>
+        <v>773.11</v>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>-0.340</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -24461,15 +24461,15 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>773.58</v>
-      </c>
-      <c r="D224" s="16" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>773.24</v>
+      </c>
+      <c r="D224" s="15" t="inlineStr">
+        <is>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -24484,15 +24484,15 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>773.64</v>
+        <v>773.58</v>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -24507,15 +24507,15 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>774.11</v>
-      </c>
-      <c r="D226" s="16" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>773.64</v>
+      </c>
+      <c r="D226" s="15" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -24530,15 +24530,15 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>774.3</v>
+        <v>774.11</v>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>-0.740</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -24553,15 +24553,15 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C228" s="6" t="n">
-        <v>775.04</v>
+        <v>774.3</v>
       </c>
       <c r="D228" s="15" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>-0.740</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -24576,15 +24576,15 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>774.9</v>
+        <v>775.04</v>
       </c>
       <c r="D229" s="11" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
@@ -24599,15 +24599,15 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>774.66</v>
-      </c>
-      <c r="D230" s="15" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>774.9</v>
+      </c>
+      <c r="D230" s="16" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -24622,15 +24622,15 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>774.34</v>
+        <v>774.66</v>
       </c>
       <c r="D231" s="11" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -24645,15 +24645,15 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C232" s="6" t="n">
-        <v>774.15</v>
+        <v>774.34</v>
       </c>
       <c r="D232" s="16" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -24668,15 +24668,15 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 13:53:42</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C233" s="8" t="n">
-        <v>774.25</v>
+        <v>774.15</v>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
@@ -24691,15 +24691,15 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 13:53:42</t>
         </is>
       </c>
       <c r="C234" s="6" t="n">
-        <v>774.3200000000001</v>
-      </c>
-      <c r="D234" s="16" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>774.25</v>
+      </c>
+      <c r="D234" s="15" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -24714,15 +24714,15 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>774.74</v>
-      </c>
-      <c r="D235" s="11" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>774.3200000000001</v>
+      </c>
+      <c r="D235" s="9" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
@@ -24737,15 +24737,15 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 01:28:47</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C236" s="6" t="n">
-        <v>774.5</v>
-      </c>
-      <c r="D236" s="15" t="inlineStr">
-        <is>
-          <t>+0.130</t>
+        <v>774.74</v>
+      </c>
+      <c r="D236" s="16" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -24760,15 +24760,15 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 01:28:47</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
-        <v>774.37</v>
-      </c>
-      <c r="D237" s="9" t="inlineStr">
-        <is>
-          <t>-0.340</t>
+        <v>774.5</v>
+      </c>
+      <c r="D237" s="11" t="inlineStr">
+        <is>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
@@ -24783,15 +24783,15 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C238" s="6" t="n">
-        <v>774.71</v>
+        <v>774.37</v>
       </c>
       <c r="D238" s="15" t="inlineStr">
         <is>
-          <t>+1.160</t>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -24806,15 +24806,15 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
-        <v>773.55</v>
-      </c>
-      <c r="D239" s="9" t="inlineStr">
-        <is>
-          <t>-0.520</t>
+        <v>774.71</v>
+      </c>
+      <c r="D239" s="11" t="inlineStr">
+        <is>
+          <t>+1.160</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
@@ -24829,15 +24829,15 @@
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C240" s="6" t="n">
-        <v>774.0700000000001</v>
-      </c>
-      <c r="D240" s="16" t="inlineStr">
-        <is>
-          <t>-0.690</t>
+        <v>773.55</v>
+      </c>
+      <c r="D240" s="15" t="inlineStr">
+        <is>
+          <t>-0.520</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -24852,15 +24852,15 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C241" s="8" t="n">
-        <v>774.76</v>
+        <v>774.0700000000001</v>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.690</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
@@ -24875,15 +24875,15 @@
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C242" s="6" t="n">
-        <v>775.3099999999999</v>
-      </c>
-      <c r="D242" s="16" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>774.76</v>
+      </c>
+      <c r="D242" s="15" t="inlineStr">
+        <is>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -24898,15 +24898,15 @@
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C243" s="8" t="n">
-        <v>775.46</v>
+        <v>775.3099999999999</v>
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
@@ -24921,15 +24921,15 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C244" s="6" t="n">
-        <v>775.84</v>
-      </c>
-      <c r="D244" s="16" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>775.46</v>
+      </c>
+      <c r="D244" s="15" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -24944,15 +24944,15 @@
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 08:05:33</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C245" s="8" t="n">
-        <v>775.9</v>
-      </c>
-      <c r="D245" s="11" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.84</v>
+      </c>
+      <c r="D245" s="9" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
@@ -24967,15 +24967,15 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 08:05:33</t>
         </is>
       </c>
       <c r="C246" s="6" t="n">
-        <v>775.83</v>
-      </c>
-      <c r="D246" s="15" t="inlineStr">
-        <is>
-          <t>+0.630</t>
+        <v>775.9</v>
+      </c>
+      <c r="D246" s="16" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
@@ -24990,15 +24990,15 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C247" s="8" t="n">
-        <v>775.2</v>
-      </c>
-      <c r="D247" s="9" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>775.83</v>
+      </c>
+      <c r="D247" s="11" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
@@ -25013,15 +25013,15 @@
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C248" s="6" t="n">
-        <v>775.28</v>
+        <v>775.2</v>
       </c>
       <c r="D248" s="15" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -25036,15 +25036,15 @@
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
-        <v>775.12</v>
+        <v>775.28</v>
       </c>
       <c r="D249" s="11" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
@@ -25059,13 +25059,13 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C250" s="6" t="n">
-        <v>775.09</v>
-      </c>
-      <c r="D250" s="15" t="inlineStr">
+        <v>775.12</v>
+      </c>
+      <c r="D250" s="16" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -25082,15 +25082,15 @@
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 18:37:13</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C251" s="8" t="n">
-        <v>775.0599999999999</v>
+        <v>775.09</v>
       </c>
       <c r="D251" s="11" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
@@ -25105,15 +25105,15 @@
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 18:37:13</t>
         </is>
       </c>
       <c r="C252" s="6" t="n">
-        <v>774.58</v>
-      </c>
-      <c r="D252" s="15" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>775.0599999999999</v>
+      </c>
+      <c r="D252" s="16" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
@@ -25128,15 +25128,15 @@
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
-        <v>774.29</v>
+        <v>774.58</v>
       </c>
       <c r="D253" s="11" t="inlineStr">
         <is>
-          <t>+0.490</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
@@ -25151,15 +25151,15 @@
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C254" s="6" t="n">
-        <v>773.8</v>
+        <v>774.29</v>
       </c>
       <c r="D254" s="16" t="inlineStr">
         <is>
-          <t>-0.590</t>
+          <t>+0.490</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
@@ -25174,14 +25174,37 @@
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C255" s="8" t="n">
+        <v>773.8</v>
+      </c>
+      <c r="D255" s="9" t="inlineStr">
+        <is>
+          <t>-0.590</t>
+        </is>
+      </c>
+      <c r="E255" s="8" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="6" t="n">
+        <v>252</v>
+      </c>
+      <c r="B256" s="6" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C255" s="8" t="n">
+      <c r="C256" s="6" t="n">
         <v>774.39</v>
       </c>
-      <c r="D255" s="8" t="inlineStr"/>
-      <c r="E255" s="8" t="inlineStr">
+      <c r="D256" s="6" t="inlineStr"/>
+      <c r="E256" s="6" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>
@@ -25202,7 +25225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E202"/>
+  <dimension ref="A1:E203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25222,7 +25245,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 667.66 | 最高: 673.240 | 最低: 667.660 | 总记录数: 198</t>
+          <t>最新价: 667.65 | 最高: 673.240 | 最低: 667.650 | 总记录数: 199</t>
         </is>
       </c>
     </row>
@@ -25259,15 +25282,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 21:54:34</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>667.66</v>
+        <v>667.65</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -25282,15 +25305,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:24</t>
+          <t>2026-09-21 21:54:34</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>667.76</v>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>667.66</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -25305,15 +25328,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 07:12:19</t>
+          <t>2026-09-21 15:01:24</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>667.89</v>
+        <v>667.76</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -25328,15 +25351,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>668.03</v>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>667.89</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -25351,15 +25374,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>668.0599999999999</v>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>668.03</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -25374,15 +25397,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>667.89</v>
+        <v>668.0599999999999</v>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -25397,15 +25420,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>668.11</v>
+        <v>667.89</v>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>-0.630</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -25420,15 +25443,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>668.74</v>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>668.11</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>-0.630</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -25443,15 +25466,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>668.76</v>
+        <v>668.74</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -25466,15 +25489,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>668.95</v>
+        <v>668.76</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -25489,15 +25512,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>668.9400000000001</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>668.95</v>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -25512,15 +25535,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>669.03</v>
+        <v>668.9400000000001</v>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>+0.270</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -25535,15 +25558,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>668.76</v>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>669.03</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>+0.270</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -25558,15 +25581,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>668.77</v>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>668.76</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -25581,15 +25604,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>668.8200000000001</v>
+        <v>668.77</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>-0.280</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -25604,15 +25627,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>669.1</v>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>668.8200000000001</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -25627,15 +25650,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>669.29</v>
+        <v>669.1</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -25650,15 +25673,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>669.3099999999999</v>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>669.29</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -25673,15 +25696,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>669.39</v>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>669.3099999999999</v>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -25696,15 +25719,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>669.17</v>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>669.39</v>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -25719,15 +25742,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>669.02</v>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>669.17</v>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -25742,15 +25765,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>669.05</v>
+        <v>669.02</v>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -25765,11 +25788,11 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>668.95</v>
+        <v>669.05</v>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
@@ -25788,15 +25811,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>668.85</v>
+        <v>668.95</v>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -25811,15 +25834,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>668.87</v>
+        <v>668.85</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -25834,15 +25857,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>668.92</v>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>668.87</v>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -25857,15 +25880,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>669.09</v>
+        <v>668.92</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -25880,15 +25903,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>669.34</v>
+        <v>669.09</v>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -25903,15 +25926,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>669.33</v>
+        <v>669.34</v>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>+0.450</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -25926,15 +25949,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>668.88</v>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>669.33</v>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>+0.450</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -25949,15 +25972,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>668.76</v>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>668.88</v>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -25972,15 +25995,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>668.91</v>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>668.76</v>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -25995,15 +26018,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>668.97</v>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>668.91</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -26018,15 +26041,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>668.78</v>
+        <v>668.97</v>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -26041,15 +26064,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>668.95</v>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>668.78</v>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -26064,15 +26087,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>668.88</v>
+        <v>668.95</v>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>-0.260</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -26087,15 +26110,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>669.14</v>
+        <v>668.88</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -26110,15 +26133,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>669.16</v>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>669.14</v>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -26133,15 +26156,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>669.23</v>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>669.16</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -26156,15 +26179,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>669.2</v>
+        <v>669.23</v>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -26179,15 +26202,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>669.23</v>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>669.2</v>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -26202,15 +26225,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>669.22</v>
+        <v>669.23</v>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -26225,15 +26248,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>669.24</v>
+        <v>669.22</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -26248,15 +26271,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>669.3099999999999</v>
+        <v>669.24</v>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -26271,15 +26294,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>669.25</v>
+        <v>669.3099999999999</v>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -26294,15 +26317,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>669.2</v>
+        <v>669.25</v>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -26317,15 +26340,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>669.27</v>
+        <v>669.2</v>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>-0.510</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -26340,15 +26363,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>669.78</v>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>669.27</v>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>-0.510</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -26363,15 +26386,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>669.95</v>
+        <v>669.78</v>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -26386,15 +26409,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>669.96</v>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>669.95</v>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -26409,15 +26432,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>670.03</v>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>669.96</v>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -26432,15 +26455,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>669.9299999999999</v>
+        <v>670.03</v>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -26455,15 +26478,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>669.9400000000001</v>
+        <v>669.9299999999999</v>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -26478,15 +26501,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>670.04</v>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>669.9400000000001</v>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -26501,15 +26524,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>670.25</v>
+        <v>670.04</v>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -26524,15 +26547,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>670.38</v>
+        <v>670.25</v>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -26547,15 +26570,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>670.1900000000001</v>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.38</v>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -26570,15 +26593,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>670.2</v>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>670.1900000000001</v>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -26593,15 +26616,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>670.35</v>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>670.2</v>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -26616,15 +26639,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>670.24</v>
-      </c>
-      <c r="D64" s="15" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>670.35</v>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -26639,15 +26662,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>670.1</v>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>-0.120</t>
+        <v>670.24</v>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -26662,15 +26685,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>670.22</v>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>-0.920</t>
+        <v>670.1</v>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -26685,15 +26708,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>671.14</v>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>+0.930</t>
+        <v>670.22</v>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>-0.920</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -26708,15 +26731,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>670.21</v>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>671.14</v>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>+0.930</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -26731,15 +26754,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>670.11</v>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>670.21</v>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -26754,15 +26777,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>670.13</v>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>670.11</v>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -26777,15 +26800,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>670.24</v>
+        <v>670.13</v>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>-0.180</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -26800,15 +26823,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>670.42</v>
+        <v>670.24</v>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -26823,15 +26846,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>670.34</v>
+        <v>670.42</v>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>+0.150</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -26846,15 +26869,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>670.1900000000001</v>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>670.34</v>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -26869,15 +26892,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>670.1799999999999</v>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>670.1900000000001</v>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -26892,15 +26915,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>670.27</v>
+        <v>670.1799999999999</v>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -26915,15 +26938,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>670.22</v>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>670.27</v>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -26938,15 +26961,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>670.26</v>
+        <v>670.22</v>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -26961,15 +26984,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>670.16</v>
+        <v>670.26</v>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -26984,15 +27007,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>670.11</v>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>670.16</v>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -27007,15 +27030,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>670.1</v>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>670.11</v>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -27030,15 +27053,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>670.2</v>
-      </c>
-      <c r="D82" s="16" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>670.1</v>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -27053,15 +27076,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>670.4</v>
+        <v>670.2</v>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -27076,15 +27099,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>670.47</v>
-      </c>
-      <c r="D84" s="16" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.4</v>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -27099,15 +27122,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>670.48</v>
+        <v>670.47</v>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -27122,15 +27145,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>670.51</v>
+        <v>670.48</v>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -27145,15 +27168,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>670.3099999999999</v>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.51</v>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -27168,15 +27191,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>670.34</v>
-      </c>
-      <c r="D88" s="16" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.3099999999999</v>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -27191,15 +27214,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>670.35</v>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>670.34</v>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -27214,15 +27237,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>670.34</v>
+        <v>670.35</v>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -27237,15 +27260,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>670.4299999999999</v>
+        <v>670.34</v>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -27260,15 +27283,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>670.46</v>
+        <v>670.4299999999999</v>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -27283,15 +27306,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>670.4400000000001</v>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.46</v>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -27306,13 +27329,13 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>670.45</v>
-      </c>
-      <c r="D94" s="16" t="inlineStr">
+        <v>670.4400000000001</v>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -27329,15 +27352,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>670.46</v>
-      </c>
-      <c r="D95" s="11" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>670.45</v>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -27352,15 +27375,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>670.4400000000001</v>
+        <v>670.46</v>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -27375,15 +27398,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>670.45</v>
+        <v>670.4400000000001</v>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -27398,15 +27421,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>670.48</v>
+        <v>670.45</v>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -27421,15 +27444,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>670.45</v>
+        <v>670.48</v>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -27444,15 +27467,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>670.25</v>
+        <v>670.45</v>
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -27467,15 +27490,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>670.26</v>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>670.25</v>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -27490,13 +27513,13 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>670.23</v>
-      </c>
-      <c r="D102" s="15" t="inlineStr">
+        <v>670.26</v>
+      </c>
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -27513,15 +27536,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>670.2</v>
+        <v>670.23</v>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -27536,15 +27559,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>670.1799999999999</v>
-      </c>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>670.2</v>
+      </c>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -27559,15 +27582,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>670.15</v>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.1799999999999</v>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -27582,15 +27605,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>670.1799999999999</v>
-      </c>
-      <c r="D106" s="16" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>670.15</v>
+      </c>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -27605,15 +27628,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>670.28</v>
+        <v>670.1799999999999</v>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -27628,15 +27651,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>670.29</v>
+        <v>670.28</v>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -27651,15 +27674,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>670.28</v>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.29</v>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -27674,15 +27697,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>670.3099999999999</v>
-      </c>
-      <c r="D110" s="16" t="inlineStr">
-        <is>
-          <t>-0.140</t>
+        <v>670.28</v>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -27697,15 +27720,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>670.45</v>
+        <v>670.3099999999999</v>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -27720,15 +27743,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>670.62</v>
+        <v>670.45</v>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -27743,15 +27766,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>670.5</v>
+        <v>670.62</v>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -27766,15 +27789,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>670.4400000000001</v>
+        <v>670.5</v>
       </c>
       <c r="D114" s="16" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -27789,15 +27812,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>670.48</v>
-      </c>
-      <c r="D115" s="11" t="inlineStr">
-        <is>
-          <t>+0.080</t>
+        <v>670.4400000000001</v>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -27812,15 +27835,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>670.4</v>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>670.48</v>
+      </c>
+      <c r="D116" s="16" t="inlineStr">
+        <is>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -27835,15 +27858,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>670.26</v>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>670.4</v>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -27858,15 +27881,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>670.51</v>
-      </c>
-      <c r="D118" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>670.26</v>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -27881,15 +27904,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>670.53</v>
+        <v>670.51</v>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -27904,15 +27927,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 14:59:15</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>670.62</v>
+        <v>670.53</v>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -27927,15 +27950,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 14:59:15</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>670.5599999999999</v>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.62</v>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -27950,15 +27973,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>670.59</v>
+        <v>670.5599999999999</v>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -27973,15 +27996,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>670.52</v>
-      </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.59</v>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -27996,15 +28019,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>670.53</v>
-      </c>
-      <c r="D124" s="16" t="inlineStr">
-        <is>
-          <t>-0.530</t>
+        <v>670.52</v>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -28019,15 +28042,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>671.0599999999999</v>
+        <v>670.53</v>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -28042,15 +28065,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>671.0700000000001</v>
-      </c>
-      <c r="D126" s="16" t="inlineStr">
-        <is>
-          <t>-0.570</t>
+        <v>671.0599999999999</v>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -28065,15 +28088,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>671.64</v>
+        <v>671.0700000000001</v>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-0.570</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -28088,15 +28111,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>671.88</v>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>671.64</v>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -28111,15 +28134,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>671.91</v>
+        <v>671.88</v>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -28134,15 +28157,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>672.05</v>
+        <v>671.91</v>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -28157,15 +28180,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>671.87</v>
-      </c>
-      <c r="D131" s="9" t="inlineStr">
-        <is>
-          <t>-0.220</t>
+        <v>672.05</v>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -28180,15 +28203,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>672.09</v>
-      </c>
-      <c r="D132" s="16" t="inlineStr">
-        <is>
-          <t>-0.120</t>
+        <v>671.87</v>
+      </c>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -28203,15 +28226,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>672.21</v>
-      </c>
-      <c r="D133" s="11" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>672.09</v>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -28226,15 +28249,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 12:06:08</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>672.14</v>
+        <v>672.21</v>
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -28249,15 +28272,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 12:06:08</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>672.2</v>
+        <v>672.14</v>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>-0.270</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -28272,15 +28295,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>672.47</v>
-      </c>
-      <c r="D136" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>672.2</v>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -28295,15 +28318,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>672.54</v>
-      </c>
-      <c r="D137" s="11" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.47</v>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -28318,15 +28341,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>672.53</v>
-      </c>
-      <c r="D138" s="15" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>672.54</v>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -28341,15 +28364,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>672.36</v>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>672.53</v>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -28364,15 +28387,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>672.37</v>
-      </c>
-      <c r="D140" s="16" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>672.36</v>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -28387,15 +28410,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>672.4</v>
+        <v>672.37</v>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -28410,15 +28433,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>672.54</v>
+        <v>672.4</v>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -28433,15 +28456,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>672.52</v>
+        <v>672.54</v>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -28456,15 +28479,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>672.41</v>
-      </c>
-      <c r="D144" s="15" t="inlineStr">
-        <is>
-          <t>+0.200</t>
+        <v>672.52</v>
+      </c>
+      <c r="D144" s="16" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -28479,15 +28502,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>672.21</v>
+        <v>672.41</v>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -28502,15 +28525,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>672.17</v>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>672.21</v>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -28525,15 +28548,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>672.14</v>
+        <v>672.17</v>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -28548,15 +28571,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>671.9400000000001</v>
+        <v>672.14</v>
       </c>
       <c r="D148" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -28571,15 +28594,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>671.96</v>
+        <v>671.9400000000001</v>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -28594,15 +28617,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>672.02</v>
-      </c>
-      <c r="D150" s="16" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>671.96</v>
+      </c>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -28617,15 +28640,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>672.22</v>
+        <v>672.02</v>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -28640,15 +28663,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>672.26</v>
-      </c>
-      <c r="D152" s="16" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>672.22</v>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -28663,15 +28686,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>672.36</v>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>672.26</v>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -28686,15 +28709,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>672.24</v>
-      </c>
-      <c r="D154" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.36</v>
+      </c>
+      <c r="D154" s="16" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -28709,15 +28732,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>672.23</v>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>672.24</v>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -28732,15 +28755,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>672.36</v>
+        <v>672.23</v>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -28755,15 +28778,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>672.26</v>
+        <v>672.36</v>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -28778,15 +28801,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>672.24</v>
+        <v>672.26</v>
       </c>
       <c r="D158" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -28801,15 +28824,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>672.3099999999999</v>
-      </c>
-      <c r="D159" s="11" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.24</v>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -28824,15 +28847,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>672.3</v>
+        <v>672.3099999999999</v>
       </c>
       <c r="D160" s="16" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -28847,15 +28870,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>672.47</v>
+        <v>672.3</v>
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -28870,15 +28893,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>672.5</v>
+        <v>672.47</v>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -28893,15 +28916,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>672.48</v>
-      </c>
-      <c r="D163" s="9" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>672.5</v>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -28916,15 +28939,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>672.54</v>
+        <v>672.48</v>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -28939,15 +28962,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>672.53</v>
+        <v>672.54</v>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -28962,15 +28985,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>672.35</v>
+        <v>672.53</v>
       </c>
       <c r="D166" s="16" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -28985,15 +29008,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>672.4299999999999</v>
+        <v>672.35</v>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -29008,15 +29031,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>672.46</v>
-      </c>
-      <c r="D168" s="16" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>672.4299999999999</v>
+      </c>
+      <c r="D168" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -29031,15 +29054,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>672.63</v>
-      </c>
-      <c r="D169" s="11" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>672.46</v>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -29054,15 +29077,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>672.5700000000001</v>
-      </c>
-      <c r="D170" s="15" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>672.63</v>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -29077,15 +29100,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>672.55</v>
+        <v>672.5700000000001</v>
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -29100,15 +29123,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>672.54</v>
-      </c>
-      <c r="D172" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>672.55</v>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -29123,15 +29146,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>672.51</v>
-      </c>
-      <c r="D173" s="9" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>672.54</v>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -29146,15 +29169,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>672.61</v>
+        <v>672.51</v>
       </c>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -29169,15 +29192,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>672.55</v>
+        <v>672.61</v>
       </c>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -29192,15 +29215,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>672.5</v>
-      </c>
-      <c r="D176" s="15" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>672.55</v>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -29215,15 +29238,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>672.34</v>
+        <v>672.5</v>
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -29238,15 +29261,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>672.33</v>
-      </c>
-      <c r="D178" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>672.34</v>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -29261,15 +29284,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>672.3</v>
-      </c>
-      <c r="D179" s="9" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>672.33</v>
+      </c>
+      <c r="D179" s="11" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -29284,15 +29307,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>672.41</v>
-      </c>
-      <c r="D180" s="16" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>672.3</v>
+      </c>
+      <c r="D180" s="15" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -29307,15 +29330,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>672.66</v>
+        <v>672.41</v>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -29330,15 +29353,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>672.78</v>
+        <v>672.66</v>
       </c>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -29353,15 +29376,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 12:26:44</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>672.76</v>
+        <v>672.78</v>
       </c>
       <c r="D183" s="11" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -29376,15 +29399,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 12:26:44</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>672.71</v>
-      </c>
-      <c r="D184" s="15" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>672.76</v>
+      </c>
+      <c r="D184" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -29399,15 +29422,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>672.67</v>
+        <v>672.71</v>
       </c>
       <c r="D185" s="11" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -29422,15 +29445,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>672.59</v>
+        <v>672.67</v>
       </c>
       <c r="D186" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -29445,15 +29468,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>672.6</v>
+        <v>672.59</v>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -29468,15 +29491,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>672.8200000000001</v>
-      </c>
-      <c r="D188" s="16" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>672.6</v>
+      </c>
+      <c r="D188" s="15" t="inlineStr">
+        <is>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -29491,15 +29514,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>673.24</v>
-      </c>
-      <c r="D189" s="11" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>672.8200000000001</v>
+      </c>
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -29514,15 +29537,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>672.9</v>
+        <v>673.24</v>
       </c>
       <c r="D190" s="16" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -29537,15 +29560,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>673.04</v>
-      </c>
-      <c r="D191" s="11" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.9</v>
+      </c>
+      <c r="D191" s="9" t="inlineStr">
+        <is>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -29560,15 +29583,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>673.03</v>
-      </c>
-      <c r="D192" s="15" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>673.04</v>
+      </c>
+      <c r="D192" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -29583,15 +29606,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>672.79</v>
-      </c>
-      <c r="D193" s="9" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>673.03</v>
+      </c>
+      <c r="D193" s="11" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -29606,15 +29629,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>673.03</v>
+        <v>672.79</v>
       </c>
       <c r="D194" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -29629,11 +29652,11 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>673.02</v>
+        <v>673.03</v>
       </c>
       <c r="D195" s="11" t="inlineStr">
         <is>
@@ -29652,15 +29675,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>673.01</v>
+        <v>673.02</v>
       </c>
       <c r="D196" s="16" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -29675,15 +29698,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>673.09</v>
+        <v>673.01</v>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -29698,15 +29721,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>673.11</v>
+        <v>673.09</v>
       </c>
       <c r="D198" s="15" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -29721,15 +29744,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>672.97</v>
+        <v>673.11</v>
       </c>
       <c r="D199" s="11" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -29744,15 +29767,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>672.87</v>
-      </c>
-      <c r="D200" s="15" t="inlineStr">
-        <is>
-          <t>+0.130</t>
+        <v>672.97</v>
+      </c>
+      <c r="D200" s="16" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -29767,15 +29790,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>672.74</v>
-      </c>
-      <c r="D201" s="9" t="inlineStr">
-        <is>
-          <t>-0.300</t>
+        <v>672.87</v>
+      </c>
+      <c r="D201" s="11" t="inlineStr">
+        <is>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -29790,14 +29813,37 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="n">
+        <v>672.74</v>
+      </c>
+      <c r="D202" s="15" t="inlineStr">
+        <is>
+          <t>-0.300</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="n">
+        <v>199</v>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C202" s="6" t="n">
+      <c r="C203" s="8" t="n">
         <v>673.04</v>
       </c>
-      <c r="D202" s="6" t="inlineStr"/>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="D203" s="8" t="inlineStr"/>
+      <c r="E203" s="8" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -185,10 +185,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 03:03:29</t>
+          <t>更新时间: 2026-09-23 05:59:20</t>
         </is>
       </c>
     </row>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>762.41</v>
+        <v>762.89</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 03:03:22</t>
+          <t>2026-09-23 05:59:14</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -765,15 +765,15 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>668.13</v>
+        <v>668.17</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 23:32:15</t>
+          <t>2026-09-23 05:59:14</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E261"/>
+  <dimension ref="A1:E262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -19594,7 +19594,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 762.41 | 最高: 782.950 | 最低: 762.410 | 总记录数: 257</t>
+          <t>最新价: 762.89 | 最高: 782.950 | 最低: 762.410 | 总记录数: 258</t>
         </is>
       </c>
     </row>
@@ -19631,15 +19631,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 03:03:22</t>
+          <t>2026-09-23 05:59:14</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>762.41</v>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>-1.930</t>
+        <v>762.89</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -19654,15 +19654,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 23:32:15</t>
+          <t>2026-09-23 03:03:22</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>764.34</v>
+        <v>762.41</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>+0.250</t>
+          <t>-1.930</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -19677,15 +19677,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 19:17:55</t>
+          <t>2026-09-22 23:32:15</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>764.09</v>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>-0.680</t>
+        <v>764.34</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -19700,15 +19700,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00:07</t>
+          <t>2026-09-22 19:17:55</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>764.77</v>
+        <v>764.09</v>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>+0.880</t>
+          <t>-0.680</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -19723,15 +19723,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 09:01:08</t>
+          <t>2026-09-22 14:00:07</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>763.89</v>
+        <v>764.77</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>+0.880</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -19746,15 +19746,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 06:28:11</t>
+          <t>2026-09-22 09:01:08</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>763.73</v>
+        <v>763.89</v>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>-0.670</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -19769,15 +19769,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 02:58:23</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>764.4</v>
+        <v>763.73</v>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>-0.750</t>
+          <t>-0.670</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -19792,15 +19792,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 21:54:34</t>
+          <t>2026-09-22 02:58:23</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>765.15</v>
+        <v>764.4</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>+0.510</t>
+          <t>-0.750</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -19815,15 +19815,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:24</t>
+          <t>2026-09-21 21:54:34</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>764.64</v>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>765.15</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>+0.510</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -19838,15 +19838,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 09:33:28</t>
+          <t>2026-09-21 15:01:24</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>765.11</v>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>-0.430</t>
+        <v>764.64</v>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -19861,15 +19861,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 07:12:19</t>
+          <t>2026-09-21 09:33:28</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>765.54</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>+0.710</t>
+        <v>765.11</v>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -19884,15 +19884,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>764.83</v>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>765.54</v>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -19907,15 +19907,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>764.54</v>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>764.83</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -19930,15 +19930,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>764.62</v>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>-0.770</t>
+        <v>764.54</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -19953,15 +19953,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>765.39</v>
+        <v>764.62</v>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>-0.620</t>
+          <t>-0.770</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -19976,15 +19976,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:32:25</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>766.01</v>
+        <v>765.39</v>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>-0.620</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -19999,15 +19999,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 05:47:34</t>
+          <t>2026-09-18 09:32:25</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>765.63</v>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>766.01</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -20022,15 +20022,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 05:47:34</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>765.8200000000001</v>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>-1.020</t>
+        <v>765.63</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -20045,15 +20045,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>766.84</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>+1.260</t>
+        <v>765.8200000000001</v>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -20068,15 +20068,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>765.58</v>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>766.84</v>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>+1.260</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -20091,15 +20091,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>765.24</v>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>765.58</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -20114,15 +20114,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 08:40:02</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>765.39</v>
+        <v>765.24</v>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>+0.340</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -20137,15 +20137,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 08:40:02</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>765.05</v>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>-4.700</t>
+        <v>765.39</v>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -20160,15 +20160,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>769.75</v>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>765.05</v>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>-4.700</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -20183,15 +20183,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>770.04</v>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>769.75</v>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -20206,15 +20206,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>769.95</v>
+        <v>770.04</v>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>-0.730</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -20229,15 +20229,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>770.6799999999999</v>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>769.95</v>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -20252,15 +20252,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 09:40:23</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>770.47</v>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>770.6799999999999</v>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -20275,15 +20275,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 07:41:58</t>
+          <t>2026-09-16 09:40:23</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>770.38</v>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>770.47</v>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -20298,15 +20298,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>770.8</v>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>770.38</v>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -20321,15 +20321,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>770.8200000000001</v>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>+0.400</t>
+        <v>770.8</v>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -20344,15 +20344,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>770.42</v>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>770.8200000000001</v>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -20367,15 +20367,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>770.24</v>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>770.42</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -20390,13 +20390,13 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>771.05</v>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
+        <v>770.24</v>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>-0.810</t>
         </is>
@@ -20413,15 +20413,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>771.86</v>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>+1.540</t>
+        <v>771.05</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -20436,15 +20436,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>770.3200000000001</v>
+        <v>771.86</v>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>-1.440</t>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -20459,15 +20459,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>771.76</v>
+        <v>770.3200000000001</v>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>-2.140</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -20482,15 +20482,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12 05:00:53</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>773.9</v>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>-0.430</t>
+        <v>771.76</v>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>-2.140</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -20505,15 +20505,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15:57</t>
+          <t>2026-09-12 05:00:53</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>774.33</v>
+        <v>773.9</v>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>-0.730</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -20528,15 +20528,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-12 02:15:57</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>775.0599999999999</v>
+        <v>774.33</v>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>+1.400</t>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -20551,15 +20551,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>773.66</v>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>775.0599999999999</v>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>+1.400</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -20574,15 +20574,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>775.1</v>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>-0.500</t>
+        <v>773.66</v>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -20597,15 +20597,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 09:18:12</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>775.6</v>
+        <v>775.1</v>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.500</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -20620,15 +20620,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 09:18:12</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>776.01</v>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>775.6</v>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -20643,15 +20643,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>776.01</v>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -20666,15 +20666,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>775.83</v>
+        <v>776.38</v>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>-0.700</t>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -20689,15 +20689,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>776.53</v>
+        <v>775.83</v>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -20712,15 +20712,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>776.91</v>
+        <v>776.53</v>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -20735,15 +20735,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 06:08:04</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>776.7</v>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>776.91</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -20758,15 +20758,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 06:08:04</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>776.8</v>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>776.7</v>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -20781,15 +20781,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>777.27</v>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>+0.760</t>
+        <v>776.8</v>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -20804,15 +20804,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>776.51</v>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>777.27</v>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>+0.760</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -20827,15 +20827,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>776.29</v>
+        <v>776.51</v>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>+0.390</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -20850,15 +20850,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>775.9</v>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>776.29</v>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -20873,15 +20873,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>775.58</v>
+        <v>775.9</v>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -20896,15 +20896,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>775.48</v>
+        <v>775.58</v>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>-0.810</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -20919,15 +20919,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>776.29</v>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>775.48</v>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -20942,15 +20942,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 06:18:23</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>776.0700000000001</v>
+        <v>776.29</v>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -20965,15 +20965,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 06:18:23</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>776.54</v>
+        <v>776.0700000000001</v>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -20988,15 +20988,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>776.59</v>
+        <v>776.54</v>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>+0.460</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -21011,15 +21011,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>776.13</v>
+        <v>776.59</v>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -21034,15 +21034,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>775.3200000000001</v>
+        <v>776.13</v>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -21057,15 +21057,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 08:56:04</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>775.6900000000001</v>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>775.3200000000001</v>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -21080,15 +21080,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 07:06:50</t>
+          <t>2026-09-07 08:56:04</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>775.63</v>
+        <v>775.6900000000001</v>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>-0.390</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -21103,15 +21103,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-05 07:06:50</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>776.02</v>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>775.63</v>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -21126,15 +21126,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>775.76</v>
+        <v>776.02</v>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>-0.720</t>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -21149,15 +21149,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>776.48</v>
+        <v>775.76</v>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>-0.580</t>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -21172,15 +21172,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>777.0599999999999</v>
-      </c>
-      <c r="D72" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>776.48</v>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>-0.580</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -21195,15 +21195,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 07:59:45</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>777.13</v>
+        <v>777.0599999999999</v>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>-0.540</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -21218,15 +21218,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 07:59:45</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>777.67</v>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>-0.300</t>
+        <v>777.13</v>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>-0.540</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -21241,15 +21241,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>777.97</v>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>+1.580</t>
+        <v>777.67</v>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>-0.300</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -21264,15 +21264,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>776.39</v>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>777.97</v>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
+        <is>
+          <t>+1.580</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -21287,15 +21287,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>776.01</v>
+        <v>776.39</v>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>+0.660</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -21310,15 +21310,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>775.35</v>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>+0.700</t>
+        <v>776.01</v>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>+0.660</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -21333,15 +21333,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 06:35:56</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>774.65</v>
+        <v>775.35</v>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.700</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -21356,15 +21356,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 04:09:22</t>
+          <t>2026-09-03 06:35:56</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>774.64</v>
+        <v>774.65</v>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>-0.270</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -21379,15 +21379,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 04:09:22</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>774.91</v>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>+0.390</t>
+        <v>774.64</v>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -21402,15 +21402,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>774.52</v>
-      </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>+0.230</t>
+        <v>774.91</v>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -21425,15 +21425,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 17:58:25</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>774.29</v>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>774.52</v>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>+0.230</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -21448,15 +21448,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 17:58:25</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>774.36</v>
-      </c>
-      <c r="D84" s="16" t="inlineStr">
-        <is>
-          <t>-0.860</t>
+        <v>774.29</v>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -21471,15 +21471,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>774.36</v>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>-0.860</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -21494,15 +21494,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 02:48:49</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>774.87</v>
+        <v>775.22</v>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>-0.600</t>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -21517,15 +21517,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 02:48:49</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>775.47</v>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>774.87</v>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -21540,15 +21540,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>775.25</v>
+        <v>775.47</v>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>-1.030</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -21563,15 +21563,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>776.28</v>
+        <v>775.25</v>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>-0.280</t>
+          <t>-1.030</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -21586,15 +21586,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 09:25:49</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>776.5599999999999</v>
-      </c>
-      <c r="D90" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>776.28</v>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -21609,15 +21609,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 06:48:36</t>
+          <t>2026-09-01 09:25:49</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>776.58</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -21632,15 +21632,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 02:10:52</t>
+          <t>2026-09-01 06:48:36</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>776.63</v>
+        <v>776.58</v>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>+1.230</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -21655,15 +21655,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 02:10:52</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>775.4</v>
+        <v>776.63</v>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -21678,15 +21678,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>775.22</v>
+        <v>775.4</v>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>-0.700</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -21701,15 +21701,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 08:13:17</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>775.92</v>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.22</v>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -21724,15 +21724,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 08:13:17</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>775.85</v>
+        <v>775.92</v>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>-2.850</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -21747,15 +21747,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>778.7</v>
+        <v>775.85</v>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-2.850</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -21770,15 +21770,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>779.1</v>
+        <v>778.7</v>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -21793,15 +21793,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>778.72</v>
-      </c>
-      <c r="D99" s="11" t="inlineStr">
-        <is>
-          <t>-0.640</t>
+        <v>779.1</v>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -21816,15 +21816,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>779.36</v>
-      </c>
-      <c r="D100" s="16" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>778.72</v>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>-0.640</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -21839,15 +21839,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 04:13:31</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>779.5599999999999</v>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>779.36</v>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -21862,15 +21862,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 04:13:31</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>779.39</v>
+        <v>779.5599999999999</v>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -21885,15 +21885,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>779.6</v>
+        <v>779.39</v>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -21908,15 +21908,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>780.03</v>
-      </c>
-      <c r="D104" s="16" t="inlineStr">
-        <is>
-          <t>-0.120</t>
+        <v>779.6</v>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -21931,15 +21931,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 18:53:28</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>780.15</v>
+        <v>780.03</v>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -21954,15 +21954,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 18:53:28</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>780.62</v>
+        <v>780.15</v>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>+0.560</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -21977,15 +21977,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>780.0599999999999</v>
-      </c>
-      <c r="D107" s="11" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>780.62</v>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>+0.560</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -22000,15 +22000,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>780.17</v>
-      </c>
-      <c r="D108" s="16" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>780.0599999999999</v>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -22023,15 +22023,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>780.38</v>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>780.17</v>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -22046,15 +22046,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 10:07:59</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>780.36</v>
+        <v>780.38</v>
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -22069,15 +22069,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 07:52:24</t>
+          <t>2026-08-26 10:07:59</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>780.6</v>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>780.36</v>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -22092,15 +22092,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 01:49:35</t>
+          <t>2026-08-26 07:52:24</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>780.4299999999999</v>
-      </c>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>+0.080</t>
+        <v>780.6</v>
+      </c>
+      <c r="D112" s="16" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -22115,15 +22115,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 01:49:35</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>780.35</v>
+        <v>780.4299999999999</v>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -22138,15 +22138,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>780.3099999999999</v>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>+0.410</t>
+        <v>780.35</v>
+      </c>
+      <c r="D114" s="16" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -22161,15 +22161,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:05:53</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>779.9</v>
-      </c>
-      <c r="D115" s="11" t="inlineStr">
-        <is>
-          <t>-0.260</t>
+        <v>780.3099999999999</v>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>+0.410</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -22184,15 +22184,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 21:05:53</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>780.16</v>
-      </c>
-      <c r="D116" s="16" t="inlineStr">
-        <is>
-          <t>-0.230</t>
+        <v>779.9</v>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -22207,15 +22207,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>780.39</v>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>780.16</v>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>-0.230</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -22230,15 +22230,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>780.15</v>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>+0.540</t>
+        <v>780.39</v>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -22253,15 +22253,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:26</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>779.61</v>
-      </c>
-      <c r="D119" s="11" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>780.15</v>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>+0.540</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -22276,15 +22276,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:01:55</t>
+          <t>2026-08-25 15:51:26</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>779.65</v>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>779.61</v>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -22299,15 +22299,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 15:01:55</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>779.73</v>
+        <v>779.65</v>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -22322,15 +22322,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>780.11</v>
-      </c>
-      <c r="D122" s="16" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>779.73</v>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -22345,15 +22345,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>780.4</v>
-      </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>780.11</v>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -22368,15 +22368,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:57:56</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>780.3099999999999</v>
-      </c>
-      <c r="D124" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>780.4</v>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -22391,15 +22391,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 06:50:27</t>
+          <t>2026-08-25 09:57:56</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>780.1900000000001</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -22414,15 +22414,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 06:50:27</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>780.1799999999999</v>
+        <v>780.1900000000001</v>
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>-0.450</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -22437,15 +22437,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>780.63</v>
-      </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>780.1799999999999</v>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>-0.450</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -22460,15 +22460,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>780.17</v>
+        <v>780.63</v>
       </c>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -22483,15 +22483,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>780.61</v>
-      </c>
-      <c r="D129" s="9" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>780.17</v>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -22506,15 +22506,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>780.14</v>
+        <v>780.61</v>
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -22529,15 +22529,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>780.23</v>
+        <v>780.14</v>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>-0.530</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -22552,15 +22552,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>780.76</v>
-      </c>
-      <c r="D132" s="16" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>780.23</v>
+      </c>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -22575,15 +22575,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>780.91</v>
+        <v>780.76</v>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -22598,15 +22598,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>781.35</v>
-      </c>
-      <c r="D134" s="16" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>780.91</v>
+      </c>
+      <c r="D134" s="15" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -22621,15 +22621,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>781.38</v>
-      </c>
-      <c r="D135" s="9" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>781.35</v>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -22644,15 +22644,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>781.09</v>
+        <v>781.38</v>
       </c>
       <c r="D136" s="16" t="inlineStr">
         <is>
-          <t>-0.350</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -22667,15 +22667,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>781.4400000000001</v>
+        <v>781.09</v>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.350</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -22690,15 +22690,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>781.55</v>
+        <v>781.4400000000001</v>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -22713,15 +22713,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 09:42:15</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>781.23</v>
+        <v>781.55</v>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -22736,15 +22736,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 10:32:40</t>
+          <t>2026-08-24 09:42:15</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>781.01</v>
+        <v>781.23</v>
       </c>
       <c r="D140" s="16" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -22759,15 +22759,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 05:00:11</t>
+          <t>2026-08-22 10:32:40</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>781.11</v>
+        <v>781.01</v>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>-0.180</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -22782,15 +22782,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 02:00:51</t>
+          <t>2026-08-22 05:00:11</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>781.29</v>
-      </c>
-      <c r="D142" s="16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>781.11</v>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -22805,15 +22805,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-22 02:00:51</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>781.34</v>
-      </c>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>781.29</v>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -22828,15 +22828,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>780.79</v>
-      </c>
-      <c r="D144" s="15" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>781.34</v>
+      </c>
+      <c r="D144" s="16" t="inlineStr">
+        <is>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -22851,15 +22851,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>780.6799999999999</v>
-      </c>
-      <c r="D145" s="11" t="inlineStr">
-        <is>
-          <t>-0.610</t>
+        <v>780.79</v>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -22874,15 +22874,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>781.29</v>
-      </c>
-      <c r="D146" s="16" t="inlineStr">
-        <is>
-          <t>-1.420</t>
+        <v>780.6799999999999</v>
+      </c>
+      <c r="D146" s="15" t="inlineStr">
+        <is>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -22897,15 +22897,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>782.71</v>
+        <v>781.29</v>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-1.420</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -22920,15 +22920,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>782.95</v>
+        <v>782.71</v>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>+1.080</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -22943,15 +22943,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>781.87</v>
-      </c>
-      <c r="D149" s="11" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>782.95</v>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>+1.080</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -22966,15 +22966,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>782.25</v>
+        <v>781.87</v>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>+0.260</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -22989,15 +22989,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>781.99</v>
+        <v>782.25</v>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -23012,15 +23012,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>781.95</v>
+        <v>781.99</v>
       </c>
       <c r="D152" s="16" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -23035,15 +23035,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>781.99</v>
+        <v>781.95</v>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -23058,15 +23058,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>782.39</v>
+        <v>781.99</v>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>+0.360</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:13</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>782.03</v>
+        <v>782.39</v>
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>+0.400</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -23104,15 +23104,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 06:49:01</t>
+          <t>2026-08-21 09:10:13</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>781.63</v>
-      </c>
-      <c r="D156" s="15" t="inlineStr">
-        <is>
-          <t>+0.680</t>
+        <v>782.03</v>
+      </c>
+      <c r="D156" s="16" t="inlineStr">
+        <is>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -23127,15 +23127,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 06:49:01</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>780.95</v>
-      </c>
-      <c r="D157" s="11" t="inlineStr">
-        <is>
-          <t>-0.780</t>
+        <v>781.63</v>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -23150,15 +23150,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>781.73</v>
-      </c>
-      <c r="D158" s="16" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>780.95</v>
+      </c>
+      <c r="D158" s="15" t="inlineStr">
+        <is>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -23173,15 +23173,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>781.79</v>
+        <v>781.73</v>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -23196,15 +23196,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>782.1900000000001</v>
+        <v>781.79</v>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>+0.150</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -23219,15 +23219,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>782.04</v>
-      </c>
-      <c r="D161" s="11" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>782.1900000000001</v>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -23242,15 +23242,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>782.74</v>
+        <v>782.04</v>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -23265,15 +23265,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>782.42</v>
+        <v>782.74</v>
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -23288,15 +23288,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>781.95</v>
-      </c>
-      <c r="D164" s="15" t="inlineStr">
-        <is>
-          <t>+0.810</t>
+        <v>782.42</v>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -23311,15 +23311,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>781.14</v>
-      </c>
-      <c r="D165" s="11" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.95</v>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -23334,15 +23334,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>781.39</v>
+        <v>781.14</v>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -23357,15 +23357,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>781.2</v>
+        <v>781.39</v>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -23380,15 +23380,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>781.17</v>
+        <v>781.2</v>
       </c>
       <c r="D168" s="16" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -23403,15 +23403,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 10:06:13</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>781.42</v>
+        <v>781.17</v>
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 07:36:53</t>
+          <t>2026-08-20 10:06:13</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>781.79</v>
+        <v>781.42</v>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 06:33:42</t>
+          <t>2026-08-20 07:36:53</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>781.77</v>
+        <v>781.79</v>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 06:33:42</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>781.45</v>
-      </c>
-      <c r="D172" s="15" t="inlineStr">
-        <is>
-          <t>+0.850</t>
+        <v>781.77</v>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>780.6</v>
+        <v>781.45</v>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.850</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>780.12</v>
-      </c>
-      <c r="D174" s="15" t="inlineStr">
-        <is>
-          <t>+1.750</t>
+        <v>780.6</v>
+      </c>
+      <c r="D174" s="16" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>778.37</v>
+        <v>780.12</v>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>+1.750</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>778.09</v>
-      </c>
-      <c r="D176" s="15" t="inlineStr">
-        <is>
-          <t>+0.680</t>
+        <v>778.37</v>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -23587,15 +23587,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>777.41</v>
+        <v>778.09</v>
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -23610,15 +23610,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>777.3200000000001</v>
-      </c>
-      <c r="D178" s="15" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>777.41</v>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -23633,11 +23633,11 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>777.1</v>
+        <v>777.3200000000001</v>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
@@ -23656,15 +23656,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>776.88</v>
+        <v>777.1</v>
       </c>
       <c r="D180" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -23679,15 +23679,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>776.89</v>
-      </c>
-      <c r="D181" s="9" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>776.88</v>
+      </c>
+      <c r="D181" s="11" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -23702,15 +23702,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>776.84</v>
+        <v>776.89</v>
       </c>
       <c r="D182" s="16" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -23725,15 +23725,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 09:12:00</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.84</v>
+      </c>
+      <c r="D183" s="11" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -23748,15 +23748,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 09:12:00</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>776.72</v>
+        <v>776.9</v>
       </c>
       <c r="D184" s="16" t="inlineStr">
         <is>
-          <t>-0.460</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -23771,15 +23771,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>777.1799999999999</v>
-      </c>
-      <c r="D185" s="9" t="inlineStr">
-        <is>
-          <t>+0.630</t>
+        <v>776.72</v>
+      </c>
+      <c r="D185" s="11" t="inlineStr">
+        <is>
+          <t>-0.460</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -23794,15 +23794,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>776.55</v>
+        <v>777.1799999999999</v>
       </c>
       <c r="D186" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -23817,15 +23817,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:24</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>776.62</v>
-      </c>
-      <c r="D187" s="9" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>776.55</v>
+      </c>
+      <c r="D187" s="11" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -23840,15 +23840,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 17:58:24</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>776.53</v>
-      </c>
-      <c r="D188" s="15" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>776.62</v>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -23863,15 +23863,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>776.36</v>
-      </c>
-      <c r="D189" s="11" t="inlineStr">
-        <is>
-          <t>-0.160</t>
+        <v>776.53</v>
+      </c>
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -23886,15 +23886,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>776.52</v>
-      </c>
-      <c r="D190" s="16" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>776.36</v>
+      </c>
+      <c r="D190" s="15" t="inlineStr">
+        <is>
+          <t>-0.160</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -23909,15 +23909,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>776.53</v>
+        <v>776.52</v>
       </c>
       <c r="D191" s="11" t="inlineStr">
         <is>
-          <t>-0.390</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -23932,15 +23932,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>776.92</v>
+        <v>776.53</v>
       </c>
       <c r="D192" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -23955,15 +23955,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 10:04:24</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>776.8200000000001</v>
+        <v>776.92</v>
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -23978,15 +23978,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 07:54:32</t>
+          <t>2026-08-18 10:04:24</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>776.61</v>
+        <v>776.8200000000001</v>
       </c>
       <c r="D194" s="16" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -24001,15 +24001,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 05:48:09</t>
+          <t>2026-08-18 07:54:32</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>776.74</v>
-      </c>
-      <c r="D195" s="9" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.61</v>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -24024,15 +24024,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 05:48:09</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>776.5599999999999</v>
+        <v>776.74</v>
       </c>
       <c r="D196" s="16" t="inlineStr">
         <is>
-          <t>-0.600</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -24047,15 +24047,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>777.16</v>
-      </c>
-      <c r="D197" s="9" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>776.5599999999999</v>
+      </c>
+      <c r="D197" s="11" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -24070,15 +24070,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>776.8099999999999</v>
+        <v>777.16</v>
       </c>
       <c r="D198" s="16" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -24093,15 +24093,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:45</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>777.21</v>
+        <v>776.8099999999999</v>
       </c>
       <c r="D199" s="11" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -24116,15 +24116,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 21:10:45</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>777.4299999999999</v>
-      </c>
-      <c r="D200" s="16" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>777.21</v>
+      </c>
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -24139,15 +24139,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>777.52</v>
-      </c>
-      <c r="D201" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>777.4299999999999</v>
+      </c>
+      <c r="D201" s="11" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -24162,15 +24162,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>777.5</v>
-      </c>
-      <c r="D202" s="15" t="inlineStr">
-        <is>
-          <t>+0.370</t>
+        <v>777.52</v>
+      </c>
+      <c r="D202" s="16" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -24185,15 +24185,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>777.13</v>
+        <v>777.5</v>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.370</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -24208,15 +24208,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>777.04</v>
-      </c>
-      <c r="D204" s="15" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>777.13</v>
+      </c>
+      <c r="D204" s="16" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -24231,15 +24231,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D205" s="11" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.04</v>
+      </c>
+      <c r="D205" s="9" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -24254,15 +24254,15 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="D206" s="16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>776.9</v>
+      </c>
+      <c r="D206" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -24277,15 +24277,15 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>776.96</v>
-      </c>
-      <c r="D207" s="9" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>776.91</v>
+      </c>
+      <c r="D207" s="11" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -24300,15 +24300,15 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 09:21:39</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>776.84</v>
-      </c>
-      <c r="D208" s="15" t="inlineStr">
-        <is>
-          <t>+0.750</t>
+        <v>776.96</v>
+      </c>
+      <c r="D208" s="16" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -24323,15 +24323,15 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 09:21:39</t>
         </is>
       </c>
       <c r="C209" s="8" t="n">
-        <v>776.09</v>
-      </c>
-      <c r="D209" s="11" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>776.84</v>
+      </c>
+      <c r="D209" s="9" t="inlineStr">
+        <is>
+          <t>+0.750</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -24346,15 +24346,15 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>776.38</v>
+        <v>776.09</v>
       </c>
       <c r="D210" s="15" t="inlineStr">
         <is>
-          <t>+0.570</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -24369,15 +24369,15 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
-        <v>775.8099999999999</v>
+        <v>776.38</v>
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>+0.770</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -24392,15 +24392,15 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>775.04</v>
-      </c>
-      <c r="D212" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>775.8099999999999</v>
+      </c>
+      <c r="D212" s="16" t="inlineStr">
+        <is>
+          <t>+0.770</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -24415,15 +24415,15 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>774.92</v>
+        <v>775.04</v>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>+0.360</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -24438,15 +24438,15 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>774.5599999999999</v>
-      </c>
-      <c r="D214" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>774.92</v>
+      </c>
+      <c r="D214" s="16" t="inlineStr">
+        <is>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -24461,15 +24461,15 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>774.4400000000001</v>
-      </c>
-      <c r="D215" s="11" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>774.5599999999999</v>
+      </c>
+      <c r="D215" s="9" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -24484,15 +24484,15 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>774.46</v>
+        <v>774.4400000000001</v>
       </c>
       <c r="D216" s="15" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -24507,15 +24507,15 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
-        <v>774.25</v>
+        <v>774.46</v>
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>+0.310</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -24530,15 +24530,15 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 10:39:02</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>773.9400000000001</v>
-      </c>
-      <c r="D218" s="15" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>774.25</v>
+      </c>
+      <c r="D218" s="16" t="inlineStr">
+        <is>
+          <t>+0.310</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -24553,15 +24553,15 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 08:05:13</t>
+          <t>2026-08-14 10:39:02</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>773.9</v>
+        <v>773.9400000000001</v>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -24576,15 +24576,15 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 07:24:16</t>
+          <t>2026-08-14 08:05:13</t>
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>773.73</v>
-      </c>
-      <c r="D220" s="15" t="inlineStr">
-        <is>
-          <t>+0.200</t>
+        <v>773.9</v>
+      </c>
+      <c r="D220" s="16" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -24599,15 +24599,15 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 07:24:16</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>773.53</v>
-      </c>
-      <c r="D221" s="11" t="inlineStr">
-        <is>
-          <t>-0.790</t>
+        <v>773.73</v>
+      </c>
+      <c r="D221" s="9" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -24622,15 +24622,15 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>774.3200000000001</v>
+        <v>773.53</v>
       </c>
       <c r="D222" s="15" t="inlineStr">
         <is>
-          <t>+0.570</t>
+          <t>-0.790</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -24645,15 +24645,15 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>773.75</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -24668,15 +24668,15 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>773.7</v>
-      </c>
-      <c r="D224" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>773.75</v>
+      </c>
+      <c r="D224" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -24691,15 +24691,15 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>773.58</v>
+        <v>773.7</v>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>+0.250</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -24714,15 +24714,15 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>773.33</v>
+        <v>773.58</v>
       </c>
       <c r="D226" s="16" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -24737,15 +24737,15 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>773.39</v>
-      </c>
-      <c r="D227" s="9" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>773.33</v>
+      </c>
+      <c r="D227" s="11" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -24760,15 +24760,15 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C228" s="6" t="n">
-        <v>773.11</v>
+        <v>773.39</v>
       </c>
       <c r="D228" s="16" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -24783,15 +24783,15 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>773.24</v>
+        <v>773.11</v>
       </c>
       <c r="D229" s="11" t="inlineStr">
         <is>
-          <t>-0.340</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
@@ -24806,15 +24806,15 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>773.58</v>
-      </c>
-      <c r="D230" s="16" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>773.24</v>
+      </c>
+      <c r="D230" s="15" t="inlineStr">
+        <is>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -24829,15 +24829,15 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>773.64</v>
+        <v>773.58</v>
       </c>
       <c r="D231" s="11" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -24852,15 +24852,15 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C232" s="6" t="n">
-        <v>774.11</v>
-      </c>
-      <c r="D232" s="16" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>773.64</v>
+      </c>
+      <c r="D232" s="15" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -24875,15 +24875,15 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C233" s="8" t="n">
-        <v>774.3</v>
+        <v>774.11</v>
       </c>
       <c r="D233" s="11" t="inlineStr">
         <is>
-          <t>-0.740</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
@@ -24898,15 +24898,15 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C234" s="6" t="n">
-        <v>775.04</v>
+        <v>774.3</v>
       </c>
       <c r="D234" s="15" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>-0.740</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -24921,15 +24921,15 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>774.9</v>
+        <v>775.04</v>
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
@@ -24944,15 +24944,15 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C236" s="6" t="n">
-        <v>774.66</v>
-      </c>
-      <c r="D236" s="15" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>774.9</v>
+      </c>
+      <c r="D236" s="16" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -24967,15 +24967,15 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
-        <v>774.34</v>
+        <v>774.66</v>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
@@ -24990,15 +24990,15 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C238" s="6" t="n">
-        <v>774.15</v>
+        <v>774.34</v>
       </c>
       <c r="D238" s="16" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -25013,15 +25013,15 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 13:53:42</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
-        <v>774.25</v>
+        <v>774.15</v>
       </c>
       <c r="D239" s="11" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
@@ -25036,15 +25036,15 @@
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 13:53:42</t>
         </is>
       </c>
       <c r="C240" s="6" t="n">
-        <v>774.3200000000001</v>
-      </c>
-      <c r="D240" s="16" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>774.25</v>
+      </c>
+      <c r="D240" s="15" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -25059,15 +25059,15 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C241" s="8" t="n">
-        <v>774.74</v>
-      </c>
-      <c r="D241" s="9" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>774.3200000000001</v>
+      </c>
+      <c r="D241" s="11" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
@@ -25082,15 +25082,15 @@
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 01:28:47</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C242" s="6" t="n">
-        <v>774.5</v>
-      </c>
-      <c r="D242" s="15" t="inlineStr">
-        <is>
-          <t>+0.130</t>
+        <v>774.74</v>
+      </c>
+      <c r="D242" s="16" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -25105,15 +25105,15 @@
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 01:28:47</t>
         </is>
       </c>
       <c r="C243" s="8" t="n">
-        <v>774.37</v>
-      </c>
-      <c r="D243" s="11" t="inlineStr">
-        <is>
-          <t>-0.340</t>
+        <v>774.5</v>
+      </c>
+      <c r="D243" s="9" t="inlineStr">
+        <is>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
@@ -25128,15 +25128,15 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C244" s="6" t="n">
-        <v>774.71</v>
+        <v>774.37</v>
       </c>
       <c r="D244" s="15" t="inlineStr">
         <is>
-          <t>+1.160</t>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -25151,15 +25151,15 @@
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C245" s="8" t="n">
-        <v>773.55</v>
-      </c>
-      <c r="D245" s="11" t="inlineStr">
-        <is>
-          <t>-0.520</t>
+        <v>774.71</v>
+      </c>
+      <c r="D245" s="9" t="inlineStr">
+        <is>
+          <t>+1.160</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
@@ -25174,15 +25174,15 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C246" s="6" t="n">
-        <v>774.0700000000001</v>
-      </c>
-      <c r="D246" s="16" t="inlineStr">
-        <is>
-          <t>-0.690</t>
+        <v>773.55</v>
+      </c>
+      <c r="D246" s="15" t="inlineStr">
+        <is>
+          <t>-0.520</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
@@ -25197,15 +25197,15 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C247" s="8" t="n">
-        <v>774.76</v>
+        <v>774.0700000000001</v>
       </c>
       <c r="D247" s="11" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.690</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
@@ -25220,15 +25220,15 @@
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C248" s="6" t="n">
-        <v>775.3099999999999</v>
-      </c>
-      <c r="D248" s="16" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>774.76</v>
+      </c>
+      <c r="D248" s="15" t="inlineStr">
+        <is>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -25243,15 +25243,15 @@
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
-        <v>775.46</v>
+        <v>775.3099999999999</v>
       </c>
       <c r="D249" s="11" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
@@ -25266,15 +25266,15 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C250" s="6" t="n">
-        <v>775.84</v>
-      </c>
-      <c r="D250" s="16" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>775.46</v>
+      </c>
+      <c r="D250" s="15" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
@@ -25289,15 +25289,15 @@
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 08:05:33</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C251" s="8" t="n">
-        <v>775.9</v>
-      </c>
-      <c r="D251" s="9" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.84</v>
+      </c>
+      <c r="D251" s="11" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
@@ -25312,15 +25312,15 @@
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 08:05:33</t>
         </is>
       </c>
       <c r="C252" s="6" t="n">
-        <v>775.83</v>
-      </c>
-      <c r="D252" s="15" t="inlineStr">
-        <is>
-          <t>+0.630</t>
+        <v>775.9</v>
+      </c>
+      <c r="D252" s="16" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
@@ -25335,15 +25335,15 @@
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
-        <v>775.2</v>
-      </c>
-      <c r="D253" s="11" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>775.83</v>
+      </c>
+      <c r="D253" s="9" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
@@ -25358,15 +25358,15 @@
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C254" s="6" t="n">
-        <v>775.28</v>
+        <v>775.2</v>
       </c>
       <c r="D254" s="15" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
@@ -25381,15 +25381,15 @@
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C255" s="8" t="n">
-        <v>775.12</v>
+        <v>775.28</v>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
@@ -25404,13 +25404,13 @@
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C256" s="6" t="n">
-        <v>775.09</v>
-      </c>
-      <c r="D256" s="15" t="inlineStr">
+        <v>775.12</v>
+      </c>
+      <c r="D256" s="16" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -25427,15 +25427,15 @@
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 18:37:13</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C257" s="8" t="n">
-        <v>775.0599999999999</v>
+        <v>775.09</v>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
@@ -25450,15 +25450,15 @@
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 18:37:13</t>
         </is>
       </c>
       <c r="C258" s="6" t="n">
-        <v>774.58</v>
-      </c>
-      <c r="D258" s="15" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>775.0599999999999</v>
+      </c>
+      <c r="D258" s="16" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
@@ -25473,15 +25473,15 @@
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C259" s="8" t="n">
-        <v>774.29</v>
+        <v>774.58</v>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>+0.490</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
@@ -25496,15 +25496,15 @@
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C260" s="6" t="n">
-        <v>773.8</v>
+        <v>774.29</v>
       </c>
       <c r="D260" s="16" t="inlineStr">
         <is>
-          <t>-0.590</t>
+          <t>+0.490</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
@@ -25519,14 +25519,37 @@
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C261" s="8" t="n">
+        <v>773.8</v>
+      </c>
+      <c r="D261" s="11" t="inlineStr">
+        <is>
+          <t>-0.590</t>
+        </is>
+      </c>
+      <c r="E261" s="8" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="6" t="n">
+        <v>258</v>
+      </c>
+      <c r="B262" s="6" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C261" s="8" t="n">
+      <c r="C262" s="6" t="n">
         <v>774.39</v>
       </c>
-      <c r="D261" s="8" t="inlineStr"/>
-      <c r="E261" s="8" t="inlineStr">
+      <c r="D262" s="6" t="inlineStr"/>
+      <c r="E262" s="6" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>
@@ -25547,7 +25570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25567,7 +25590,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 668.13 | 最高: 673.240 | 最低: 667.650 | 总记录数: 202</t>
+          <t>最新价: 668.17 | 最高: 673.240 | 最低: 667.650 | 总记录数: 203</t>
         </is>
       </c>
     </row>
@@ -25604,15 +25627,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 23:32:15</t>
+          <t>2026-09-23 05:59:14</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>668.13</v>
+        <v>668.17</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -25627,15 +25650,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 19:17:55</t>
+          <t>2026-09-22 23:32:15</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>668.12</v>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>+0.330</t>
+        <v>668.13</v>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -25650,15 +25673,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00:07</t>
+          <t>2026-09-22 19:17:55</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>667.79</v>
+        <v>668.12</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>+0.330</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -25673,15 +25696,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 06:28:11</t>
+          <t>2026-09-22 14:00:07</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>667.65</v>
+        <v>667.79</v>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -25696,15 +25719,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 21:54:34</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>667.66</v>
+        <v>667.65</v>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -25719,15 +25742,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:24</t>
+          <t>2026-09-21 21:54:34</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>667.76</v>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>667.66</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -25742,15 +25765,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 07:12:19</t>
+          <t>2026-09-21 15:01:24</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>667.89</v>
+        <v>667.76</v>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -25765,15 +25788,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>668.03</v>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>667.89</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -25788,15 +25811,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>668.0599999999999</v>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>668.03</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -25811,15 +25834,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>667.89</v>
+        <v>668.0599999999999</v>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -25834,15 +25857,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>668.11</v>
+        <v>667.89</v>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>-0.630</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -25857,15 +25880,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>668.74</v>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>668.11</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>-0.630</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -25880,15 +25903,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>668.76</v>
+        <v>668.74</v>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -25903,15 +25926,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>668.95</v>
+        <v>668.76</v>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -25926,15 +25949,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>668.9400000000001</v>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>668.95</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -25949,15 +25972,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>669.03</v>
+        <v>668.9400000000001</v>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>+0.270</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -25972,15 +25995,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>668.76</v>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>669.03</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>+0.270</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -25995,15 +26018,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>668.77</v>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>668.76</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -26018,15 +26041,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>668.8200000000001</v>
+        <v>668.77</v>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>-0.280</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -26041,15 +26064,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>669.1</v>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>668.8200000000001</v>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -26064,15 +26087,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>669.29</v>
+        <v>669.1</v>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -26087,15 +26110,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>669.3099999999999</v>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>669.29</v>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -26110,15 +26133,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>669.39</v>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>669.3099999999999</v>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -26133,15 +26156,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>669.17</v>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>669.39</v>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -26156,15 +26179,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>669.02</v>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>669.17</v>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -26179,15 +26202,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>669.05</v>
+        <v>669.02</v>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -26202,11 +26225,11 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>668.95</v>
+        <v>669.05</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
@@ -26225,15 +26248,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>668.85</v>
+        <v>668.95</v>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -26248,15 +26271,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>668.87</v>
+        <v>668.85</v>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -26271,15 +26294,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>668.92</v>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>668.87</v>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -26294,15 +26317,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>669.09</v>
+        <v>668.92</v>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -26317,15 +26340,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>669.34</v>
+        <v>669.09</v>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -26340,15 +26363,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>669.33</v>
+        <v>669.34</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>+0.450</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -26363,15 +26386,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>668.88</v>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>669.33</v>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>+0.450</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -26386,15 +26409,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>668.76</v>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>668.88</v>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -26409,15 +26432,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>668.91</v>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>668.76</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -26432,15 +26455,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>668.97</v>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>668.91</v>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -26455,15 +26478,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>668.78</v>
+        <v>668.97</v>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -26478,15 +26501,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>668.95</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>668.78</v>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -26501,15 +26524,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>668.88</v>
+        <v>668.95</v>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>-0.260</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -26524,15 +26547,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>669.14</v>
+        <v>668.88</v>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -26547,15 +26570,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>669.16</v>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>669.14</v>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -26570,15 +26593,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>669.23</v>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>669.16</v>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -26593,15 +26616,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>669.2</v>
+        <v>669.23</v>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -26616,15 +26639,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>669.23</v>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>669.2</v>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -26639,15 +26662,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>669.22</v>
+        <v>669.23</v>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -26662,15 +26685,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>669.24</v>
+        <v>669.22</v>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -26685,15 +26708,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>669.3099999999999</v>
+        <v>669.24</v>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -26708,15 +26731,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>669.25</v>
+        <v>669.3099999999999</v>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -26731,15 +26754,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>669.2</v>
+        <v>669.25</v>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -26754,15 +26777,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>669.27</v>
+        <v>669.2</v>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>-0.510</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -26777,15 +26800,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>669.78</v>
-      </c>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>669.27</v>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>-0.510</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -26800,15 +26823,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>669.95</v>
+        <v>669.78</v>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -26823,15 +26846,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>669.96</v>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>669.95</v>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -26846,15 +26869,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>670.03</v>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>669.96</v>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -26869,15 +26892,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>669.9299999999999</v>
+        <v>670.03</v>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -26892,15 +26915,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>669.9400000000001</v>
+        <v>669.9299999999999</v>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -26915,15 +26938,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>670.04</v>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>669.9400000000001</v>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -26938,15 +26961,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>670.25</v>
+        <v>670.04</v>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -26961,15 +26984,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>670.38</v>
+        <v>670.25</v>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -26984,15 +27007,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>670.1900000000001</v>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.38</v>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -27007,15 +27030,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>670.2</v>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>670.1900000000001</v>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -27030,15 +27053,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>670.35</v>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>670.2</v>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -27053,15 +27076,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>670.24</v>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>670.35</v>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -27076,15 +27099,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>670.1</v>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>-0.120</t>
+        <v>670.24</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -27099,15 +27122,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>670.22</v>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>-0.920</t>
+        <v>670.1</v>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -27122,15 +27145,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>671.14</v>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>+0.930</t>
+        <v>670.22</v>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>-0.920</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -27145,15 +27168,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>670.21</v>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>671.14</v>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>+0.930</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -27168,15 +27191,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>670.11</v>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>670.21</v>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -27191,15 +27214,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>670.13</v>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>670.11</v>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -27214,15 +27237,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>670.24</v>
+        <v>670.13</v>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>-0.180</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -27237,15 +27260,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>670.42</v>
+        <v>670.24</v>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -27260,15 +27283,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>670.34</v>
+        <v>670.42</v>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>+0.150</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -27283,15 +27306,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>670.1900000000001</v>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>670.34</v>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -27306,15 +27329,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>670.1799999999999</v>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>670.1900000000001</v>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -27329,15 +27352,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>670.27</v>
+        <v>670.1799999999999</v>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -27352,15 +27375,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>670.22</v>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>670.27</v>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -27375,15 +27398,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>670.26</v>
+        <v>670.22</v>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -27398,15 +27421,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>670.16</v>
+        <v>670.26</v>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -27421,15 +27444,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>670.11</v>
-      </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>670.16</v>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -27444,15 +27467,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>670.1</v>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>670.11</v>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -27467,15 +27490,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>670.2</v>
-      </c>
-      <c r="D86" s="16" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>670.1</v>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -27490,15 +27513,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>670.4</v>
+        <v>670.2</v>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -27513,15 +27536,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>670.47</v>
-      </c>
-      <c r="D88" s="16" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.4</v>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -27536,15 +27559,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>670.48</v>
+        <v>670.47</v>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -27559,15 +27582,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>670.51</v>
+        <v>670.48</v>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -27582,15 +27605,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>670.3099999999999</v>
-      </c>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.51</v>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -27605,15 +27628,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>670.34</v>
-      </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.3099999999999</v>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -27628,15 +27651,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>670.35</v>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>670.34</v>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -27651,15 +27674,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>670.34</v>
+        <v>670.35</v>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -27674,15 +27697,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>670.4299999999999</v>
+        <v>670.34</v>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -27697,15 +27720,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>670.46</v>
+        <v>670.4299999999999</v>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -27720,15 +27743,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>670.4400000000001</v>
-      </c>
-      <c r="D97" s="11" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.46</v>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -27743,13 +27766,13 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>670.45</v>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
+        <v>670.4400000000001</v>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -27766,15 +27789,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>670.46</v>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>670.45</v>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -27789,15 +27812,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>670.4400000000001</v>
+        <v>670.46</v>
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -27812,15 +27835,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>670.45</v>
+        <v>670.4400000000001</v>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -27835,15 +27858,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>670.48</v>
+        <v>670.45</v>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -27858,15 +27881,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>670.45</v>
+        <v>670.48</v>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -27881,15 +27904,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>670.25</v>
+        <v>670.45</v>
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -27904,15 +27927,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>670.26</v>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>670.25</v>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -27927,13 +27950,13 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>670.23</v>
-      </c>
-      <c r="D106" s="15" t="inlineStr">
+        <v>670.26</v>
+      </c>
+      <c r="D106" s="16" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -27950,15 +27973,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>670.2</v>
+        <v>670.23</v>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -27973,15 +27996,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>670.1799999999999</v>
-      </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>670.2</v>
+      </c>
+      <c r="D108" s="16" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -27996,15 +28019,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>670.15</v>
-      </c>
-      <c r="D109" s="11" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.1799999999999</v>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -28019,15 +28042,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>670.1799999999999</v>
-      </c>
-      <c r="D110" s="16" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>670.15</v>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -28042,15 +28065,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>670.28</v>
+        <v>670.1799999999999</v>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -28065,15 +28088,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>670.29</v>
+        <v>670.28</v>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -28088,15 +28111,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>670.28</v>
-      </c>
-      <c r="D113" s="11" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.29</v>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -28111,15 +28134,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>670.3099999999999</v>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>-0.140</t>
+        <v>670.28</v>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -28134,15 +28157,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>670.45</v>
+        <v>670.3099999999999</v>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -28157,15 +28180,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>670.62</v>
+        <v>670.45</v>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -28180,15 +28203,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>670.5</v>
+        <v>670.62</v>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -28203,15 +28226,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>670.4400000000001</v>
+        <v>670.5</v>
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -28226,15 +28249,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>670.48</v>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>+0.080</t>
+        <v>670.4400000000001</v>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -28249,15 +28272,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>670.4</v>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>670.48</v>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -28272,15 +28295,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>670.26</v>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>670.4</v>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -28295,15 +28318,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>670.51</v>
-      </c>
-      <c r="D122" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>670.26</v>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -28318,15 +28341,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>670.53</v>
+        <v>670.51</v>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -28341,15 +28364,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 14:59:15</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>670.62</v>
+        <v>670.53</v>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -28364,15 +28387,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 14:59:15</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>670.5599999999999</v>
-      </c>
-      <c r="D125" s="11" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>670.62</v>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -28387,15 +28410,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>670.59</v>
+        <v>670.5599999999999</v>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -28410,15 +28433,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>670.52</v>
-      </c>
-      <c r="D127" s="11" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>670.59</v>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -28433,15 +28456,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>670.53</v>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>-0.530</t>
+        <v>670.52</v>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -28456,15 +28479,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>671.0599999999999</v>
+        <v>670.53</v>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -28479,15 +28502,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>671.0700000000001</v>
-      </c>
-      <c r="D130" s="16" t="inlineStr">
-        <is>
-          <t>-0.570</t>
+        <v>671.0599999999999</v>
+      </c>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -28502,15 +28525,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>671.64</v>
+        <v>671.0700000000001</v>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-0.570</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -28525,15 +28548,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>671.88</v>
-      </c>
-      <c r="D132" s="16" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>671.64</v>
+      </c>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -28548,15 +28571,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>671.91</v>
+        <v>671.88</v>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -28571,15 +28594,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>672.05</v>
+        <v>671.91</v>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -28594,15 +28617,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>671.87</v>
-      </c>
-      <c r="D135" s="11" t="inlineStr">
-        <is>
-          <t>-0.220</t>
+        <v>672.05</v>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -28617,15 +28640,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>672.09</v>
-      </c>
-      <c r="D136" s="16" t="inlineStr">
-        <is>
-          <t>-0.120</t>
+        <v>671.87</v>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -28640,15 +28663,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>672.21</v>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>672.09</v>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -28663,15 +28686,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 12:06:08</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>672.14</v>
+        <v>672.21</v>
       </c>
       <c r="D138" s="16" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -28686,15 +28709,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 12:06:08</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>672.2</v>
+        <v>672.14</v>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>-0.270</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -28709,15 +28732,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>672.47</v>
-      </c>
-      <c r="D140" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>672.2</v>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -28732,15 +28755,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>672.54</v>
-      </c>
-      <c r="D141" s="9" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.47</v>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -28755,15 +28778,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>672.53</v>
-      </c>
-      <c r="D142" s="15" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>672.54</v>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -28778,15 +28801,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>672.36</v>
-      </c>
-      <c r="D143" s="11" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>672.53</v>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -28801,15 +28824,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>672.37</v>
-      </c>
-      <c r="D144" s="16" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>672.36</v>
+      </c>
+      <c r="D144" s="15" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -28824,15 +28847,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>672.4</v>
+        <v>672.37</v>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -28847,15 +28870,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>672.54</v>
+        <v>672.4</v>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -28870,15 +28893,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>672.52</v>
+        <v>672.54</v>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -28893,15 +28916,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>672.41</v>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>+0.200</t>
+        <v>672.52</v>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -28916,15 +28939,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>672.21</v>
+        <v>672.41</v>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -28939,15 +28962,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>672.17</v>
-      </c>
-      <c r="D150" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>672.21</v>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -28962,15 +28985,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>672.14</v>
+        <v>672.17</v>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -28985,15 +29008,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>671.9400000000001</v>
+        <v>672.14</v>
       </c>
       <c r="D152" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -29008,15 +29031,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>671.96</v>
+        <v>671.9400000000001</v>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -29031,15 +29054,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>672.02</v>
-      </c>
-      <c r="D154" s="16" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>671.96</v>
+      </c>
+      <c r="D154" s="15" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -29054,15 +29077,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>672.22</v>
+        <v>672.02</v>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -29077,15 +29100,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>672.26</v>
-      </c>
-      <c r="D156" s="16" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>672.22</v>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -29100,15 +29123,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>672.36</v>
-      </c>
-      <c r="D157" s="9" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>672.26</v>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -29123,15 +29146,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>672.24</v>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.36</v>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -29146,15 +29169,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>672.23</v>
-      </c>
-      <c r="D159" s="11" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>672.24</v>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -29169,15 +29192,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>672.36</v>
+        <v>672.23</v>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -29192,15 +29215,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>672.26</v>
+        <v>672.36</v>
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -29215,15 +29238,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>672.24</v>
+        <v>672.26</v>
       </c>
       <c r="D162" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -29238,15 +29261,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>672.3099999999999</v>
-      </c>
-      <c r="D163" s="9" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.24</v>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -29261,15 +29284,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>672.3</v>
+        <v>672.3099999999999</v>
       </c>
       <c r="D164" s="16" t="inlineStr">
         <is>
-          <t>-0.170</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -29284,15 +29307,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>672.47</v>
+        <v>672.3</v>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -29307,15 +29330,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>672.5</v>
+        <v>672.47</v>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -29330,15 +29353,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>672.48</v>
-      </c>
-      <c r="D167" s="11" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>672.5</v>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -29353,15 +29376,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>672.54</v>
+        <v>672.48</v>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -29376,15 +29399,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>672.53</v>
+        <v>672.54</v>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -29399,15 +29422,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>672.35</v>
+        <v>672.53</v>
       </c>
       <c r="D170" s="16" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -29422,15 +29445,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>672.4299999999999</v>
+        <v>672.35</v>
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -29445,15 +29468,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>672.46</v>
-      </c>
-      <c r="D172" s="16" t="inlineStr">
-        <is>
-          <t>-0.170</t>
+        <v>672.4299999999999</v>
+      </c>
+      <c r="D172" s="15" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -29468,15 +29491,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>672.63</v>
-      </c>
-      <c r="D173" s="9" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>672.46</v>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>-0.170</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -29491,15 +29514,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>672.5700000000001</v>
-      </c>
-      <c r="D174" s="15" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>672.63</v>
+      </c>
+      <c r="D174" s="16" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -29514,15 +29537,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>672.55</v>
+        <v>672.5700000000001</v>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -29537,15 +29560,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>672.54</v>
-      </c>
-      <c r="D176" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>672.55</v>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -29560,15 +29583,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>672.51</v>
-      </c>
-      <c r="D177" s="11" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>672.54</v>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -29583,15 +29606,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>672.61</v>
+        <v>672.51</v>
       </c>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -29606,15 +29629,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>672.55</v>
+        <v>672.61</v>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -29629,15 +29652,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>672.5</v>
-      </c>
-      <c r="D180" s="15" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>672.55</v>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -29652,15 +29675,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>672.34</v>
+        <v>672.5</v>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -29675,15 +29698,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>672.33</v>
-      </c>
-      <c r="D182" s="15" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>672.34</v>
+      </c>
+      <c r="D182" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -29698,15 +29721,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>672.3</v>
-      </c>
-      <c r="D183" s="11" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>672.33</v>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -29721,15 +29744,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>672.41</v>
-      </c>
-      <c r="D184" s="16" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>672.3</v>
+      </c>
+      <c r="D184" s="15" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -29744,15 +29767,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>672.66</v>
+        <v>672.41</v>
       </c>
       <c r="D185" s="11" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -29767,15 +29790,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>672.78</v>
+        <v>672.66</v>
       </c>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -29790,15 +29813,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 12:26:44</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>672.76</v>
+        <v>672.78</v>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -29813,15 +29836,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 12:26:44</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>672.71</v>
-      </c>
-      <c r="D188" s="15" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>672.76</v>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -29836,15 +29859,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>672.67</v>
+        <v>672.71</v>
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -29859,15 +29882,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>672.59</v>
+        <v>672.67</v>
       </c>
       <c r="D190" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -29882,15 +29905,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>672.6</v>
+        <v>672.59</v>
       </c>
       <c r="D191" s="11" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -29905,15 +29928,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>672.8200000000001</v>
-      </c>
-      <c r="D192" s="16" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>672.6</v>
+      </c>
+      <c r="D192" s="15" t="inlineStr">
+        <is>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -29928,15 +29951,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>673.24</v>
-      </c>
-      <c r="D193" s="9" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>672.8200000000001</v>
+      </c>
+      <c r="D193" s="11" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -29951,15 +29974,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>672.9</v>
+        <v>673.24</v>
       </c>
       <c r="D194" s="16" t="inlineStr">
         <is>
-          <t>-0.140</t>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -29974,15 +29997,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>673.04</v>
-      </c>
-      <c r="D195" s="9" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>672.9</v>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>-0.140</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -29997,15 +30020,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>673.03</v>
-      </c>
-      <c r="D196" s="15" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>673.04</v>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -30020,15 +30043,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>672.79</v>
-      </c>
-      <c r="D197" s="11" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>673.03</v>
+      </c>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -30043,15 +30066,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>673.03</v>
+        <v>672.79</v>
       </c>
       <c r="D198" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -30066,11 +30089,11 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>673.02</v>
+        <v>673.03</v>
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
@@ -30089,15 +30112,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>673.01</v>
+        <v>673.02</v>
       </c>
       <c r="D200" s="16" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -30112,15 +30135,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>673.09</v>
+        <v>673.01</v>
       </c>
       <c r="D201" s="11" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -30135,15 +30158,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>673.11</v>
+        <v>673.09</v>
       </c>
       <c r="D202" s="15" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -30158,15 +30181,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>672.97</v>
+        <v>673.11</v>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -30181,15 +30204,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>672.87</v>
-      </c>
-      <c r="D204" s="15" t="inlineStr">
-        <is>
-          <t>+0.130</t>
+        <v>672.97</v>
+      </c>
+      <c r="D204" s="16" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -30204,15 +30227,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>672.74</v>
-      </c>
-      <c r="D205" s="11" t="inlineStr">
-        <is>
-          <t>-0.300</t>
+        <v>672.87</v>
+      </c>
+      <c r="D205" s="9" t="inlineStr">
+        <is>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -30227,14 +30250,37 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="n">
+        <v>672.74</v>
+      </c>
+      <c r="D206" s="15" t="inlineStr">
+        <is>
+          <t>-0.300</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="n">
+        <v>203</v>
+      </c>
+      <c r="B207" s="8" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C206" s="6" t="n">
+      <c r="C207" s="8" t="n">
         <v>673.04</v>
       </c>
-      <c r="D206" s="6" t="inlineStr"/>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="D207" s="8" t="inlineStr"/>
+      <c r="E207" s="8" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 20:15:40</t>
+          <t>更新时间: 2026-09-26 01:15:30</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>761.48</v>
+        <v>762.27</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25 20:15:35</t>
+          <t>2026-09-26 01:15:26</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E273"/>
+  <dimension ref="A1:E274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -20192,7 +20192,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 761.48 | 最高: 782.950 | 最低: 759.650 | 总记录数: 269</t>
+          <t>最新价: 762.27 | 最高: 782.950 | 最低: 759.650 | 总记录数: 270</t>
         </is>
       </c>
     </row>
@@ -20229,15 +20229,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25 20:15:35</t>
+          <t>2026-09-26 01:15:26</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>761.48</v>
+        <v>762.27</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>+1.200</t>
+          <t>+0.790</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -20252,15 +20252,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25 14:42:41</t>
+          <t>2026-09-25 20:15:35</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>760.28</v>
+        <v>761.48</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+1.200</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -20275,15 +20275,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25 01:40:29</t>
+          <t>2026-09-25 14:42:41</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>760.15</v>
+        <v>760.28</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>+0.500</t>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -20298,15 +20298,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 20:55:26</t>
+          <t>2026-09-25 01:40:29</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>759.65</v>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>-1.120</t>
+        <v>760.15</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>+0.500</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -20321,15 +20321,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 15:50:01</t>
+          <t>2026-09-24 20:55:26</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>760.77</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>+1.060</t>
+        <v>759.65</v>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>-1.120</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -20344,15 +20344,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 10:50:22</t>
+          <t>2026-09-24 15:50:01</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>759.71</v>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>760.77</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>+1.060</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -20367,15 +20367,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 07:56:20</t>
+          <t>2026-09-24 10:50:22</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>759.91</v>
+        <v>759.71</v>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -20390,15 +20390,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 02:27:02</t>
+          <t>2026-09-24 07:56:20</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>760.46</v>
+        <v>759.91</v>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -20413,15 +20413,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 22:21:19</t>
+          <t>2026-09-24 02:27:02</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>760.87</v>
+        <v>760.46</v>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>-1.520</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -20436,15 +20436,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 17:31:43</t>
+          <t>2026-09-23 22:21:19</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>762.39</v>
+        <v>760.87</v>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>-0.310</t>
+          <t>-1.520</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -20459,15 +20459,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 12:39:24</t>
+          <t>2026-09-23 17:31:43</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>762.7</v>
+        <v>762.39</v>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.310</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -20482,15 +20482,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 05:59:14</t>
+          <t>2026-09-23 12:39:24</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>762.89</v>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>762.7</v>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -20505,15 +20505,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 03:03:22</t>
+          <t>2026-09-23 05:59:14</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>762.41</v>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>-1.930</t>
+        <v>762.89</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -20528,15 +20528,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 23:32:15</t>
+          <t>2026-09-23 03:03:22</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>764.34</v>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>762.41</v>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>-1.930</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -20551,15 +20551,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 19:17:55</t>
+          <t>2026-09-22 23:32:15</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>764.09</v>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>-0.680</t>
+        <v>764.34</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -20574,15 +20574,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00:07</t>
+          <t>2026-09-22 19:17:55</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>764.77</v>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>+0.880</t>
+        <v>764.09</v>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>-0.680</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -20597,15 +20597,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 09:01:08</t>
+          <t>2026-09-22 14:00:07</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>763.89</v>
+        <v>764.77</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>+0.880</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -20620,15 +20620,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 06:28:11</t>
+          <t>2026-09-22 09:01:08</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>763.73</v>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>-0.670</t>
+        <v>763.89</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -20643,15 +20643,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 02:58:23</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>764.4</v>
+        <v>763.73</v>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>-0.750</t>
+          <t>-0.670</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -20666,15 +20666,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 21:54:34</t>
+          <t>2026-09-22 02:58:23</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>765.15</v>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>+0.510</t>
+        <v>764.4</v>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>-0.750</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -20689,15 +20689,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:24</t>
+          <t>2026-09-21 21:54:34</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>764.64</v>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>765.15</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>+0.510</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -20712,15 +20712,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 09:33:28</t>
+          <t>2026-09-21 15:01:24</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>765.11</v>
+        <v>764.64</v>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -20735,15 +20735,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 07:12:19</t>
+          <t>2026-09-21 09:33:28</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>765.54</v>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>+0.710</t>
+        <v>765.11</v>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -20758,15 +20758,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>764.83</v>
+        <v>765.54</v>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -20781,15 +20781,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>764.54</v>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>764.83</v>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -20804,15 +20804,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>764.62</v>
+        <v>764.54</v>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>-0.770</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -20827,15 +20827,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>765.39</v>
+        <v>764.62</v>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>-0.620</t>
+          <t>-0.770</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -20850,15 +20850,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:32:25</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>766.01</v>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>765.39</v>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>-0.620</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -20873,15 +20873,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 05:47:34</t>
+          <t>2026-09-18 09:32:25</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>765.63</v>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>766.01</v>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -20896,15 +20896,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 05:47:34</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>765.8200000000001</v>
+        <v>765.63</v>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>-1.020</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -20919,15 +20919,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>766.84</v>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>+1.260</t>
+        <v>765.8200000000001</v>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -20942,15 +20942,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>765.58</v>
+        <v>766.84</v>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>+0.340</t>
+          <t>+1.260</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -20965,15 +20965,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>765.24</v>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>765.58</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -20988,15 +20988,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 08:40:02</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>765.39</v>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>765.24</v>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -21011,15 +21011,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 08:40:02</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>765.05</v>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>-4.700</t>
+        <v>765.39</v>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -21034,15 +21034,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>769.75</v>
+        <v>765.05</v>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-4.700</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -21057,15 +21057,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>770.04</v>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>769.75</v>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -21080,15 +21080,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>769.95</v>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>-0.730</t>
+        <v>770.04</v>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -21103,15 +21103,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>770.6799999999999</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>769.95</v>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -21126,15 +21126,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 09:40:23</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>770.47</v>
+        <v>770.6799999999999</v>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -21149,15 +21149,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 07:41:58</t>
+          <t>2026-09-16 09:40:23</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>770.38</v>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>770.47</v>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -21172,15 +21172,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>770.8</v>
+        <v>770.38</v>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -21195,15 +21195,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>770.8200000000001</v>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>+0.400</t>
+        <v>770.8</v>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -21218,15 +21218,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>770.42</v>
+        <v>770.8200000000001</v>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -21241,15 +21241,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>770.24</v>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>770.42</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -21264,11 +21264,11 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>771.05</v>
+        <v>770.24</v>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
@@ -21287,15 +21287,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>771.86</v>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>+1.540</t>
+        <v>771.05</v>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -21310,15 +21310,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>770.3200000000001</v>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>771.86</v>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -21333,15 +21333,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>771.76</v>
+        <v>770.3200000000001</v>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>-2.140</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -21356,15 +21356,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12 05:00:53</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>773.9</v>
+        <v>771.76</v>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-2.140</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -21379,15 +21379,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15:57</t>
+          <t>2026-09-12 05:00:53</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>774.33</v>
+        <v>773.9</v>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>-0.730</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -21402,15 +21402,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-12 02:15:57</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>+1.400</t>
+        <v>774.33</v>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -21425,15 +21425,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>773.66</v>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>775.0599999999999</v>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>+1.400</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -21448,15 +21448,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>775.1</v>
+        <v>773.66</v>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>-0.500</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -21471,15 +21471,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 09:18:12</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>775.6</v>
+        <v>775.1</v>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.500</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -21494,15 +21494,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 09:18:12</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>776.01</v>
+        <v>775.6</v>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -21517,15 +21517,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>776.01</v>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -21540,15 +21540,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>775.83</v>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>776.38</v>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -21563,15 +21563,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>776.53</v>
+        <v>775.83</v>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -21586,15 +21586,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="D64" s="15" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.53</v>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -21609,15 +21609,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 06:08:04</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>776.7</v>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>776.91</v>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -21632,15 +21632,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 06:08:04</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>776.8</v>
+        <v>776.7</v>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -21655,15 +21655,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>777.27</v>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>+0.760</t>
+        <v>776.8</v>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -21678,15 +21678,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>776.51</v>
+        <v>777.27</v>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.760</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -21701,15 +21701,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>776.29</v>
+        <v>776.51</v>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>+0.390</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -21724,15 +21724,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>775.9</v>
+        <v>776.29</v>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -21747,15 +21747,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>775.58</v>
+        <v>775.9</v>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -21770,15 +21770,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>775.48</v>
-      </c>
-      <c r="D72" s="16" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>775.58</v>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -21793,15 +21793,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>776.29</v>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>775.48</v>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -21816,15 +21816,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 06:18:23</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>776.0700000000001</v>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>776.29</v>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -21839,15 +21839,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 06:18:23</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>776.54</v>
+        <v>776.0700000000001</v>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -21862,15 +21862,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>776.59</v>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>776.54</v>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -21885,15 +21885,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>776.13</v>
+        <v>776.59</v>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -21908,15 +21908,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>775.3200000000001</v>
-      </c>
-      <c r="D78" s="16" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>776.13</v>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -21931,15 +21931,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 08:56:04</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>775.6900000000001</v>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>775.3200000000001</v>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -21954,15 +21954,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 07:06:50</t>
+          <t>2026-09-07 08:56:04</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>775.63</v>
-      </c>
-      <c r="D80" s="16" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>775.6900000000001</v>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -21977,15 +21977,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-05 07:06:50</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>776.02</v>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>775.63</v>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -22000,15 +22000,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>775.76</v>
-      </c>
-      <c r="D82" s="16" t="inlineStr">
-        <is>
-          <t>-0.720</t>
+        <v>776.02</v>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -22023,15 +22023,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>776.48</v>
+        <v>775.76</v>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>-0.580</t>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -22046,15 +22046,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>777.0599999999999</v>
+        <v>776.48</v>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.580</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -22069,15 +22069,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 07:59:45</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>777.13</v>
+        <v>777.0599999999999</v>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>-0.540</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -22092,15 +22092,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 07:59:45</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>777.67</v>
+        <v>777.13</v>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>-0.300</t>
+          <t>-0.540</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -22115,15 +22115,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>777.97</v>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>+1.580</t>
+        <v>777.67</v>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>-0.300</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -22138,15 +22138,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>776.39</v>
+        <v>777.97</v>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>+1.580</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -22161,15 +22161,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>776.01</v>
+        <v>776.39</v>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>+0.660</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -22184,15 +22184,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>775.35</v>
+        <v>776.01</v>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>+0.700</t>
+          <t>+0.660</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -22207,15 +22207,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 06:35:56</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>774.65</v>
+        <v>775.35</v>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.700</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -22230,15 +22230,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 04:09:22</t>
+          <t>2026-09-03 06:35:56</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>774.64</v>
-      </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>-0.270</t>
+        <v>774.65</v>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -22253,15 +22253,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 04:09:22</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>774.91</v>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>+0.390</t>
+        <v>774.64</v>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -22276,15 +22276,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>774.52</v>
+        <v>774.91</v>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>+0.230</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -22299,15 +22299,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 17:58:25</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>774.29</v>
-      </c>
-      <c r="D95" s="11" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>774.52</v>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>+0.230</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -22322,15 +22322,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 17:58:25</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>774.36</v>
+        <v>774.29</v>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>-0.860</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -22345,15 +22345,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>774.36</v>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>-0.860</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -22368,15 +22368,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 02:48:49</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>774.87</v>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>775.22</v>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -22391,15 +22391,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 02:48:49</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>775.47</v>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>774.87</v>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -22414,15 +22414,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>775.25</v>
-      </c>
-      <c r="D100" s="16" t="inlineStr">
-        <is>
-          <t>-1.030</t>
+        <v>775.47</v>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -22437,15 +22437,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>776.28</v>
+        <v>775.25</v>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>-0.280</t>
+          <t>-1.030</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -22460,15 +22460,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 09:25:49</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>776.5599999999999</v>
+        <v>776.28</v>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -22483,15 +22483,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 06:48:36</t>
+          <t>2026-09-01 09:25:49</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>776.58</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -22506,15 +22506,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 02:10:52</t>
+          <t>2026-09-01 06:48:36</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>776.63</v>
-      </c>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>+1.230</t>
+        <v>776.58</v>
+      </c>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -22529,15 +22529,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 02:10:52</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>775.4</v>
+        <v>776.63</v>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -22552,15 +22552,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D106" s="16" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>775.4</v>
+      </c>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -22575,15 +22575,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 08:13:17</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>775.92</v>
-      </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.22</v>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -22598,15 +22598,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 08:13:17</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>775.85</v>
-      </c>
-      <c r="D108" s="16" t="inlineStr">
-        <is>
-          <t>-2.850</t>
+        <v>775.92</v>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -22621,15 +22621,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>778.7</v>
+        <v>775.85</v>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-2.850</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -22644,15 +22644,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>779.1</v>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>778.7</v>
+      </c>
+      <c r="D110" s="16" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -22667,15 +22667,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>778.72</v>
-      </c>
-      <c r="D111" s="11" t="inlineStr">
-        <is>
-          <t>-0.640</t>
+        <v>779.1</v>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -22690,15 +22690,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>779.36</v>
+        <v>778.72</v>
       </c>
       <c r="D112" s="16" t="inlineStr">
         <is>
-          <t>-0.200</t>
+          <t>-0.640</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -22713,15 +22713,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 04:13:31</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>779.5599999999999</v>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>779.36</v>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -22736,15 +22736,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 04:13:31</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>779.39</v>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>779.5599999999999</v>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -22759,15 +22759,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>779.6</v>
+        <v>779.39</v>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -22782,15 +22782,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>780.03</v>
+        <v>779.6</v>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -22805,15 +22805,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 18:53:28</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>780.15</v>
+        <v>780.03</v>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -22828,15 +22828,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 18:53:28</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>780.62</v>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>+0.560</t>
+        <v>780.15</v>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -22851,15 +22851,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>780.0599999999999</v>
-      </c>
-      <c r="D119" s="11" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>780.62</v>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>+0.560</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -22874,15 +22874,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>780.17</v>
+        <v>780.0599999999999</v>
       </c>
       <c r="D120" s="16" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -22897,15 +22897,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>780.38</v>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>780.17</v>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -22920,15 +22920,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 10:07:59</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>780.36</v>
-      </c>
-      <c r="D122" s="16" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>780.38</v>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -22943,15 +22943,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 07:52:24</t>
+          <t>2026-08-26 10:07:59</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>780.6</v>
-      </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>780.36</v>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -22966,15 +22966,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 01:49:35</t>
+          <t>2026-08-26 07:52:24</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>780.4299999999999</v>
+        <v>780.6</v>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -22989,15 +22989,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 01:49:35</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>780.35</v>
+        <v>780.4299999999999</v>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -23012,15 +23012,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>780.3099999999999</v>
+        <v>780.35</v>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>+0.410</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -23035,15 +23035,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:05:53</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>779.9</v>
-      </c>
-      <c r="D127" s="11" t="inlineStr">
-        <is>
-          <t>-0.260</t>
+        <v>780.3099999999999</v>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>+0.410</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -23058,15 +23058,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 21:05:53</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>780.16</v>
+        <v>779.9</v>
       </c>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>-0.230</t>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>780.39</v>
-      </c>
-      <c r="D129" s="9" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>780.16</v>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>-0.230</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -23104,15 +23104,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>780.15</v>
+        <v>780.39</v>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>+0.540</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -23127,15 +23127,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:26</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>779.61</v>
-      </c>
-      <c r="D131" s="11" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>780.15</v>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>+0.540</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -23150,15 +23150,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:01:55</t>
+          <t>2026-08-25 15:51:26</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>779.65</v>
+        <v>779.61</v>
       </c>
       <c r="D132" s="16" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -23173,15 +23173,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 15:01:55</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>779.73</v>
+        <v>779.65</v>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -23196,15 +23196,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>780.11</v>
+        <v>779.73</v>
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -23219,15 +23219,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>780.4</v>
-      </c>
-      <c r="D135" s="9" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>780.11</v>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -23242,15 +23242,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:57:56</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>780.3099999999999</v>
+        <v>780.4</v>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -23265,15 +23265,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 06:50:27</t>
+          <t>2026-08-25 09:57:56</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>780.1900000000001</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -23288,15 +23288,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 06:50:27</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>780.1799999999999</v>
-      </c>
-      <c r="D138" s="16" t="inlineStr">
-        <is>
-          <t>-0.450</t>
+        <v>780.1900000000001</v>
+      </c>
+      <c r="D138" s="15" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -23311,15 +23311,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>780.63</v>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>780.1799999999999</v>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>-0.450</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -23334,15 +23334,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>780.17</v>
-      </c>
-      <c r="D140" s="16" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.63</v>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -23357,15 +23357,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>780.61</v>
-      </c>
-      <c r="D141" s="9" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>780.17</v>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -23380,15 +23380,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>780.14</v>
-      </c>
-      <c r="D142" s="16" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>780.61</v>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -23403,15 +23403,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>780.23</v>
+        <v>780.14</v>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>-0.530</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>780.76</v>
+        <v>780.23</v>
       </c>
       <c r="D144" s="16" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>780.91</v>
+        <v>780.76</v>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>781.35</v>
+        <v>780.91</v>
       </c>
       <c r="D146" s="16" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>781.38</v>
-      </c>
-      <c r="D147" s="9" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>781.35</v>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>781.09</v>
-      </c>
-      <c r="D148" s="16" t="inlineStr">
-        <is>
-          <t>-0.350</t>
+        <v>781.38</v>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>781.4400000000001</v>
+        <v>781.09</v>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.350</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>781.55</v>
-      </c>
-      <c r="D150" s="15" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.4400000000001</v>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -23587,15 +23587,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 09:42:15</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>781.23</v>
+        <v>781.55</v>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -23610,15 +23610,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 10:32:40</t>
+          <t>2026-08-24 09:42:15</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>781.01</v>
-      </c>
-      <c r="D152" s="16" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>781.23</v>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -23633,15 +23633,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 05:00:11</t>
+          <t>2026-08-22 10:32:40</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>781.11</v>
+        <v>781.01</v>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>-0.180</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -23656,15 +23656,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 02:00:51</t>
+          <t>2026-08-22 05:00:11</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>781.29</v>
+        <v>781.11</v>
       </c>
       <c r="D154" s="16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -23679,15 +23679,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-22 02:00:51</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>781.34</v>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>781.29</v>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -23702,15 +23702,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>780.79</v>
+        <v>781.34</v>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -23725,15 +23725,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>780.6799999999999</v>
-      </c>
-      <c r="D157" s="11" t="inlineStr">
-        <is>
-          <t>-0.610</t>
+        <v>780.79</v>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -23748,15 +23748,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>781.29</v>
+        <v>780.6799999999999</v>
       </c>
       <c r="D158" s="16" t="inlineStr">
         <is>
-          <t>-1.420</t>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -23771,15 +23771,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>782.71</v>
+        <v>781.29</v>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-1.420</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -23794,15 +23794,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>782.95</v>
-      </c>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t>+1.080</t>
+        <v>782.71</v>
+      </c>
+      <c r="D160" s="16" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -23817,15 +23817,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>781.87</v>
-      </c>
-      <c r="D161" s="11" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>782.95</v>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>+1.080</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -23840,15 +23840,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>782.25</v>
-      </c>
-      <c r="D162" s="15" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>781.87</v>
+      </c>
+      <c r="D162" s="16" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -23863,15 +23863,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>781.99</v>
+        <v>782.25</v>
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -23886,15 +23886,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>781.95</v>
-      </c>
-      <c r="D164" s="16" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>781.99</v>
+      </c>
+      <c r="D164" s="15" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -23909,15 +23909,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>781.99</v>
+        <v>781.95</v>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -23932,15 +23932,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>782.39</v>
-      </c>
-      <c r="D166" s="15" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>781.99</v>
+      </c>
+      <c r="D166" s="16" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -23955,15 +23955,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:13</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>782.03</v>
+        <v>782.39</v>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>+0.400</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -23978,15 +23978,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 06:49:01</t>
+          <t>2026-08-21 09:10:13</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>781.63</v>
+        <v>782.03</v>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -24001,15 +24001,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 06:49:01</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>780.95</v>
-      </c>
-      <c r="D169" s="11" t="inlineStr">
-        <is>
-          <t>-0.780</t>
+        <v>781.63</v>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -24024,15 +24024,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>781.73</v>
+        <v>780.95</v>
       </c>
       <c r="D170" s="16" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -24047,15 +24047,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>781.79</v>
+        <v>781.73</v>
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -24070,15 +24070,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>782.1900000000001</v>
-      </c>
-      <c r="D172" s="15" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>781.79</v>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -24093,15 +24093,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>782.04</v>
-      </c>
-      <c r="D173" s="11" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>782.1900000000001</v>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -24116,15 +24116,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>782.74</v>
-      </c>
-      <c r="D174" s="15" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>782.04</v>
+      </c>
+      <c r="D174" s="16" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -24139,15 +24139,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>782.42</v>
+        <v>782.74</v>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -24162,15 +24162,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>781.95</v>
+        <v>782.42</v>
       </c>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -24185,15 +24185,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>781.14</v>
-      </c>
-      <c r="D177" s="11" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.95</v>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -24208,15 +24208,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>781.39</v>
-      </c>
-      <c r="D178" s="15" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>781.14</v>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -24231,15 +24231,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>781.2</v>
+        <v>781.39</v>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -24254,15 +24254,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>781.17</v>
-      </c>
-      <c r="D180" s="16" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.2</v>
+      </c>
+      <c r="D180" s="15" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -24277,15 +24277,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 10:06:13</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>781.42</v>
+        <v>781.17</v>
       </c>
       <c r="D181" s="11" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -24300,15 +24300,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 07:36:53</t>
+          <t>2026-08-20 10:06:13</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D182" s="15" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>781.42</v>
+      </c>
+      <c r="D182" s="16" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -24323,15 +24323,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 06:33:42</t>
+          <t>2026-08-20 07:36:53</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>781.77</v>
+        <v>781.79</v>
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -24346,15 +24346,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 06:33:42</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>781.45</v>
+        <v>781.77</v>
       </c>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>+0.850</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -24369,15 +24369,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>780.6</v>
+        <v>781.45</v>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.850</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -24392,15 +24392,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>780.12</v>
+        <v>780.6</v>
       </c>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>+1.750</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -24415,15 +24415,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>778.37</v>
+        <v>780.12</v>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>+1.750</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -24438,15 +24438,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>778.09</v>
+        <v>778.37</v>
       </c>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -24461,15 +24461,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>777.41</v>
+        <v>778.09</v>
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -24484,15 +24484,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>777.3200000000001</v>
+        <v>777.41</v>
       </c>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -24507,11 +24507,11 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>777.1</v>
+        <v>777.3200000000001</v>
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
@@ -24530,15 +24530,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>776.88</v>
-      </c>
-      <c r="D192" s="16" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.1</v>
+      </c>
+      <c r="D192" s="15" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -24553,15 +24553,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>776.89</v>
-      </c>
-      <c r="D193" s="9" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>776.88</v>
+      </c>
+      <c r="D193" s="11" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -24576,15 +24576,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>776.84</v>
-      </c>
-      <c r="D194" s="16" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>776.89</v>
+      </c>
+      <c r="D194" s="15" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -24599,15 +24599,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 09:12:00</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D195" s="9" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.84</v>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -24622,15 +24622,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 09:12:00</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>776.72</v>
-      </c>
-      <c r="D196" s="16" t="inlineStr">
-        <is>
-          <t>-0.460</t>
+        <v>776.9</v>
+      </c>
+      <c r="D196" s="15" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -24645,15 +24645,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>777.1799999999999</v>
-      </c>
-      <c r="D197" s="9" t="inlineStr">
-        <is>
-          <t>+0.630</t>
+        <v>776.72</v>
+      </c>
+      <c r="D197" s="11" t="inlineStr">
+        <is>
+          <t>-0.460</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -24668,15 +24668,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>776.55</v>
-      </c>
-      <c r="D198" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>777.1799999999999</v>
+      </c>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -24691,15 +24691,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:24</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>776.62</v>
-      </c>
-      <c r="D199" s="9" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>776.55</v>
+      </c>
+      <c r="D199" s="11" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -24714,15 +24714,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 17:58:24</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>776.53</v>
+        <v>776.62</v>
       </c>
       <c r="D200" s="15" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -24737,15 +24737,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>776.36</v>
-      </c>
-      <c r="D201" s="11" t="inlineStr">
-        <is>
-          <t>-0.160</t>
+        <v>776.53</v>
+      </c>
+      <c r="D201" s="9" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -24760,15 +24760,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>776.52</v>
+        <v>776.36</v>
       </c>
       <c r="D202" s="16" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.160</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -24783,15 +24783,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>776.53</v>
+        <v>776.52</v>
       </c>
       <c r="D203" s="11" t="inlineStr">
         <is>
-          <t>-0.390</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -24806,15 +24806,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>776.92</v>
-      </c>
-      <c r="D204" s="15" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>776.53</v>
+      </c>
+      <c r="D204" s="16" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -24829,15 +24829,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 10:04:24</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>776.8200000000001</v>
+        <v>776.92</v>
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -24852,15 +24852,15 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 07:54:32</t>
+          <t>2026-08-18 10:04:24</t>
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>776.61</v>
-      </c>
-      <c r="D206" s="16" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>776.8200000000001</v>
+      </c>
+      <c r="D206" s="15" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -24875,15 +24875,15 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 05:48:09</t>
+          <t>2026-08-18 07:54:32</t>
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>776.74</v>
-      </c>
-      <c r="D207" s="9" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.61</v>
+      </c>
+      <c r="D207" s="11" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -24898,15 +24898,15 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 05:48:09</t>
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>776.5599999999999</v>
-      </c>
-      <c r="D208" s="16" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>776.74</v>
+      </c>
+      <c r="D208" s="15" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -24921,15 +24921,15 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C209" s="8" t="n">
-        <v>777.16</v>
-      </c>
-      <c r="D209" s="9" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>776.5599999999999</v>
+      </c>
+      <c r="D209" s="11" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -24944,15 +24944,15 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>776.8099999999999</v>
-      </c>
-      <c r="D210" s="16" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>777.16</v>
+      </c>
+      <c r="D210" s="15" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -24967,15 +24967,15 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:45</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
-        <v>777.21</v>
+        <v>776.8099999999999</v>
       </c>
       <c r="D211" s="11" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -24990,15 +24990,15 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 21:10:45</t>
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>777.4299999999999</v>
+        <v>777.21</v>
       </c>
       <c r="D212" s="16" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -25013,15 +25013,15 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>777.52</v>
-      </c>
-      <c r="D213" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>777.4299999999999</v>
+      </c>
+      <c r="D213" s="11" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -25036,15 +25036,15 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>777.5</v>
+        <v>777.52</v>
       </c>
       <c r="D214" s="15" t="inlineStr">
         <is>
-          <t>+0.370</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -25059,15 +25059,15 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>777.13</v>
+        <v>777.5</v>
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.370</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -25082,15 +25082,15 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>777.04</v>
+        <v>777.13</v>
       </c>
       <c r="D216" s="15" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -25105,15 +25105,15 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D217" s="11" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.04</v>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -25128,15 +25128,15 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>776.91</v>
+        <v>776.9</v>
       </c>
       <c r="D218" s="16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -25151,15 +25151,15 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>776.96</v>
-      </c>
-      <c r="D219" s="9" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>776.91</v>
+      </c>
+      <c r="D219" s="11" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -25174,15 +25174,15 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 09:21:39</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>776.84</v>
+        <v>776.96</v>
       </c>
       <c r="D220" s="15" t="inlineStr">
         <is>
-          <t>+0.750</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -25197,15 +25197,15 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 09:21:39</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>776.09</v>
-      </c>
-      <c r="D221" s="11" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>776.84</v>
+      </c>
+      <c r="D221" s="9" t="inlineStr">
+        <is>
+          <t>+0.750</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -25220,15 +25220,15 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D222" s="15" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>776.09</v>
+      </c>
+      <c r="D222" s="16" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -25243,15 +25243,15 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>775.8099999999999</v>
+        <v>776.38</v>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>+0.770</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -25266,15 +25266,15 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>775.04</v>
+        <v>775.8099999999999</v>
       </c>
       <c r="D224" s="15" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.770</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -25289,15 +25289,15 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>774.92</v>
+        <v>775.04</v>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>+0.360</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -25312,15 +25312,15 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>774.5599999999999</v>
+        <v>774.92</v>
       </c>
       <c r="D226" s="15" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -25335,15 +25335,15 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>774.4400000000001</v>
-      </c>
-      <c r="D227" s="11" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>774.5599999999999</v>
+      </c>
+      <c r="D227" s="9" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -25358,15 +25358,15 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C228" s="6" t="n">
-        <v>774.46</v>
-      </c>
-      <c r="D228" s="15" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>774.4400000000001</v>
+      </c>
+      <c r="D228" s="16" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -25381,15 +25381,15 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>774.25</v>
+        <v>774.46</v>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>+0.310</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
@@ -25404,15 +25404,15 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 10:39:02</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>773.9400000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D230" s="15" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.310</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -25427,15 +25427,15 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 08:05:13</t>
+          <t>2026-08-14 10:39:02</t>
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>773.9</v>
+        <v>773.9400000000001</v>
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -25450,15 +25450,15 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 07:24:16</t>
+          <t>2026-08-14 08:05:13</t>
         </is>
       </c>
       <c r="C232" s="6" t="n">
-        <v>773.73</v>
+        <v>773.9</v>
       </c>
       <c r="D232" s="15" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -25473,15 +25473,15 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 07:24:16</t>
         </is>
       </c>
       <c r="C233" s="8" t="n">
-        <v>773.53</v>
-      </c>
-      <c r="D233" s="11" t="inlineStr">
-        <is>
-          <t>-0.790</t>
+        <v>773.73</v>
+      </c>
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
@@ -25496,15 +25496,15 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C234" s="6" t="n">
-        <v>774.3200000000001</v>
-      </c>
-      <c r="D234" s="15" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>773.53</v>
+      </c>
+      <c r="D234" s="16" t="inlineStr">
+        <is>
+          <t>-0.790</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -25519,15 +25519,15 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>773.75</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
@@ -25542,15 +25542,15 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C236" s="6" t="n">
-        <v>773.7</v>
+        <v>773.75</v>
       </c>
       <c r="D236" s="15" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -25565,15 +25565,15 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
-        <v>773.58</v>
+        <v>773.7</v>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>+0.250</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
@@ -25588,15 +25588,15 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C238" s="6" t="n">
-        <v>773.33</v>
-      </c>
-      <c r="D238" s="16" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>773.58</v>
+      </c>
+      <c r="D238" s="15" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -25611,15 +25611,15 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
-        <v>773.39</v>
-      </c>
-      <c r="D239" s="9" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>773.33</v>
+      </c>
+      <c r="D239" s="11" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
@@ -25634,15 +25634,15 @@
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C240" s="6" t="n">
-        <v>773.11</v>
-      </c>
-      <c r="D240" s="16" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>773.39</v>
+      </c>
+      <c r="D240" s="15" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -25657,15 +25657,15 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C241" s="8" t="n">
-        <v>773.24</v>
+        <v>773.11</v>
       </c>
       <c r="D241" s="11" t="inlineStr">
         <is>
-          <t>-0.340</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
@@ -25680,15 +25680,15 @@
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C242" s="6" t="n">
-        <v>773.58</v>
+        <v>773.24</v>
       </c>
       <c r="D242" s="16" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -25703,15 +25703,15 @@
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C243" s="8" t="n">
-        <v>773.64</v>
+        <v>773.58</v>
       </c>
       <c r="D243" s="11" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
@@ -25726,15 +25726,15 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C244" s="6" t="n">
-        <v>774.11</v>
+        <v>773.64</v>
       </c>
       <c r="D244" s="16" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -25749,15 +25749,15 @@
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C245" s="8" t="n">
-        <v>774.3</v>
+        <v>774.11</v>
       </c>
       <c r="D245" s="11" t="inlineStr">
         <is>
-          <t>-0.740</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
@@ -25772,15 +25772,15 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C246" s="6" t="n">
-        <v>775.04</v>
-      </c>
-      <c r="D246" s="15" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>774.3</v>
+      </c>
+      <c r="D246" s="16" t="inlineStr">
+        <is>
+          <t>-0.740</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
@@ -25795,15 +25795,15 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C247" s="8" t="n">
-        <v>774.9</v>
+        <v>775.04</v>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
@@ -25818,15 +25818,15 @@
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C248" s="6" t="n">
-        <v>774.66</v>
+        <v>774.9</v>
       </c>
       <c r="D248" s="15" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -25841,15 +25841,15 @@
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
-        <v>774.34</v>
+        <v>774.66</v>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
@@ -25864,15 +25864,15 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C250" s="6" t="n">
-        <v>774.15</v>
-      </c>
-      <c r="D250" s="16" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>774.34</v>
+      </c>
+      <c r="D250" s="15" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
@@ -25887,15 +25887,15 @@
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 13:53:42</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C251" s="8" t="n">
-        <v>774.25</v>
+        <v>774.15</v>
       </c>
       <c r="D251" s="11" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
@@ -25910,15 +25910,15 @@
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 13:53:42</t>
         </is>
       </c>
       <c r="C252" s="6" t="n">
-        <v>774.3200000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D252" s="16" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
@@ -25933,15 +25933,15 @@
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
-        <v>774.74</v>
-      </c>
-      <c r="D253" s="9" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>774.3200000000001</v>
+      </c>
+      <c r="D253" s="11" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
@@ -25956,15 +25956,15 @@
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 01:28:47</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C254" s="6" t="n">
-        <v>774.5</v>
+        <v>774.74</v>
       </c>
       <c r="D254" s="15" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
@@ -25979,15 +25979,15 @@
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 01:28:47</t>
         </is>
       </c>
       <c r="C255" s="8" t="n">
-        <v>774.37</v>
-      </c>
-      <c r="D255" s="11" t="inlineStr">
-        <is>
-          <t>-0.340</t>
+        <v>774.5</v>
+      </c>
+      <c r="D255" s="9" t="inlineStr">
+        <is>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
@@ -26002,15 +26002,15 @@
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C256" s="6" t="n">
-        <v>774.71</v>
-      </c>
-      <c r="D256" s="15" t="inlineStr">
-        <is>
-          <t>+1.160</t>
+        <v>774.37</v>
+      </c>
+      <c r="D256" s="16" t="inlineStr">
+        <is>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
@@ -26025,15 +26025,15 @@
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C257" s="8" t="n">
-        <v>773.55</v>
-      </c>
-      <c r="D257" s="11" t="inlineStr">
-        <is>
-          <t>-0.520</t>
+        <v>774.71</v>
+      </c>
+      <c r="D257" s="9" t="inlineStr">
+        <is>
+          <t>+1.160</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
@@ -26048,15 +26048,15 @@
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C258" s="6" t="n">
-        <v>774.0700000000001</v>
+        <v>773.55</v>
       </c>
       <c r="D258" s="16" t="inlineStr">
         <is>
-          <t>-0.690</t>
+          <t>-0.520</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
@@ -26071,15 +26071,15 @@
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C259" s="8" t="n">
-        <v>774.76</v>
+        <v>774.0700000000001</v>
       </c>
       <c r="D259" s="11" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.690</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
@@ -26094,15 +26094,15 @@
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C260" s="6" t="n">
-        <v>775.3099999999999</v>
+        <v>774.76</v>
       </c>
       <c r="D260" s="16" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
@@ -26117,15 +26117,15 @@
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C261" s="8" t="n">
-        <v>775.46</v>
+        <v>775.3099999999999</v>
       </c>
       <c r="D261" s="11" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
@@ -26140,15 +26140,15 @@
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C262" s="6" t="n">
-        <v>775.84</v>
+        <v>775.46</v>
       </c>
       <c r="D262" s="16" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
@@ -26163,15 +26163,15 @@
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 08:05:33</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C263" s="8" t="n">
-        <v>775.9</v>
-      </c>
-      <c r="D263" s="9" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.84</v>
+      </c>
+      <c r="D263" s="11" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
@@ -26186,15 +26186,15 @@
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 08:05:33</t>
         </is>
       </c>
       <c r="C264" s="6" t="n">
-        <v>775.83</v>
+        <v>775.9</v>
       </c>
       <c r="D264" s="15" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E264" s="6" t="inlineStr">
@@ -26209,15 +26209,15 @@
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C265" s="8" t="n">
-        <v>775.2</v>
-      </c>
-      <c r="D265" s="11" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>775.83</v>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
@@ -26232,15 +26232,15 @@
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C266" s="6" t="n">
-        <v>775.28</v>
-      </c>
-      <c r="D266" s="15" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>775.2</v>
+      </c>
+      <c r="D266" s="16" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E266" s="6" t="inlineStr">
@@ -26255,15 +26255,15 @@
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C267" s="8" t="n">
-        <v>775.12</v>
+        <v>775.28</v>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
@@ -26278,11 +26278,11 @@
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C268" s="6" t="n">
-        <v>775.09</v>
+        <v>775.12</v>
       </c>
       <c r="D268" s="15" t="inlineStr">
         <is>
@@ -26301,15 +26301,15 @@
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 18:37:13</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C269" s="8" t="n">
-        <v>775.0599999999999</v>
+        <v>775.09</v>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
@@ -26324,15 +26324,15 @@
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 18:37:13</t>
         </is>
       </c>
       <c r="C270" s="6" t="n">
-        <v>774.58</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D270" s="15" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E270" s="6" t="inlineStr">
@@ -26347,15 +26347,15 @@
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C271" s="8" t="n">
-        <v>774.29</v>
+        <v>774.58</v>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>+0.490</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
@@ -26370,15 +26370,15 @@
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C272" s="6" t="n">
-        <v>773.8</v>
-      </c>
-      <c r="D272" s="16" t="inlineStr">
-        <is>
-          <t>-0.590</t>
+        <v>774.29</v>
+      </c>
+      <c r="D272" s="15" t="inlineStr">
+        <is>
+          <t>+0.490</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
@@ -26393,14 +26393,37 @@
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C273" s="8" t="n">
+        <v>773.8</v>
+      </c>
+      <c r="D273" s="11" t="inlineStr">
+        <is>
+          <t>-0.590</t>
+        </is>
+      </c>
+      <c r="E273" s="8" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="B274" s="6" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C273" s="8" t="n">
+      <c r="C274" s="6" t="n">
         <v>774.39</v>
       </c>
-      <c r="D273" s="8" t="inlineStr"/>
-      <c r="E273" s="8" t="inlineStr">
+      <c r="D274" s="6" t="inlineStr"/>
+      <c r="E274" s="6" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 01:15:30</t>
+          <t>更新时间: 2026-09-26 04:30:55</t>
         </is>
       </c>
     </row>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>762.27</v>
+        <v>761.5700000000001</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26 01:15:26</t>
+          <t>2026-09-26 04:30:49</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E274"/>
+  <dimension ref="A1:E275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -20192,7 +20192,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 762.27 | 最高: 782.950 | 最低: 759.650 | 总记录数: 270</t>
+          <t>最新价: 761.57 | 最高: 782.950 | 最低: 759.650 | 总记录数: 271</t>
         </is>
       </c>
     </row>
@@ -20229,15 +20229,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26 01:15:26</t>
+          <t>2026-09-26 04:30:49</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>762.27</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>+0.790</t>
+        <v>761.5700000000001</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -20252,15 +20252,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25 20:15:35</t>
+          <t>2026-09-26 01:15:26</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>761.48</v>
+        <v>762.27</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>+1.200</t>
+          <t>+0.790</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -20275,15 +20275,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25 14:42:41</t>
+          <t>2026-09-25 20:15:35</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>760.28</v>
+        <v>761.48</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+1.200</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -20298,15 +20298,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25 01:40:29</t>
+          <t>2026-09-25 14:42:41</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>760.15</v>
+        <v>760.28</v>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>+0.500</t>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -20321,15 +20321,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 20:55:26</t>
+          <t>2026-09-25 01:40:29</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>759.65</v>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>-1.120</t>
+        <v>760.15</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>+0.500</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -20344,15 +20344,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 15:50:01</t>
+          <t>2026-09-24 20:55:26</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>760.77</v>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>+1.060</t>
+        <v>759.65</v>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>-1.120</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -20367,15 +20367,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 10:50:22</t>
+          <t>2026-09-24 15:50:01</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>759.71</v>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>760.77</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>+1.060</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -20390,15 +20390,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 07:56:20</t>
+          <t>2026-09-24 10:50:22</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>759.91</v>
+        <v>759.71</v>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -20413,15 +20413,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 02:27:02</t>
+          <t>2026-09-24 07:56:20</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>760.46</v>
+        <v>759.91</v>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -20436,15 +20436,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 22:21:19</t>
+          <t>2026-09-24 02:27:02</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>760.87</v>
+        <v>760.46</v>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>-1.520</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -20459,15 +20459,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 17:31:43</t>
+          <t>2026-09-23 22:21:19</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>762.39</v>
+        <v>760.87</v>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>-0.310</t>
+          <t>-1.520</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -20482,15 +20482,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 12:39:24</t>
+          <t>2026-09-23 17:31:43</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>762.7</v>
+        <v>762.39</v>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.310</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -20505,15 +20505,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 05:59:14</t>
+          <t>2026-09-23 12:39:24</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>762.89</v>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>762.7</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -20528,15 +20528,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 03:03:22</t>
+          <t>2026-09-23 05:59:14</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>762.41</v>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>-1.930</t>
+        <v>762.89</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -20551,15 +20551,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 23:32:15</t>
+          <t>2026-09-23 03:03:22</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>764.34</v>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>762.41</v>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>-1.930</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -20574,15 +20574,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 19:17:55</t>
+          <t>2026-09-22 23:32:15</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>764.09</v>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>-0.680</t>
+        <v>764.34</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -20597,15 +20597,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00:07</t>
+          <t>2026-09-22 19:17:55</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>764.77</v>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>+0.880</t>
+        <v>764.09</v>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>-0.680</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -20620,15 +20620,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 09:01:08</t>
+          <t>2026-09-22 14:00:07</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>763.89</v>
+        <v>764.77</v>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>+0.880</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -20643,15 +20643,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 06:28:11</t>
+          <t>2026-09-22 09:01:08</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>763.73</v>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>-0.670</t>
+        <v>763.89</v>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -20666,15 +20666,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 02:58:23</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>764.4</v>
+        <v>763.73</v>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>-0.750</t>
+          <t>-0.670</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -20689,15 +20689,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 21:54:34</t>
+          <t>2026-09-22 02:58:23</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>765.15</v>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>+0.510</t>
+        <v>764.4</v>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>-0.750</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -20712,15 +20712,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:24</t>
+          <t>2026-09-21 21:54:34</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>764.64</v>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>765.15</v>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>+0.510</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -20735,15 +20735,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 09:33:28</t>
+          <t>2026-09-21 15:01:24</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>765.11</v>
+        <v>764.64</v>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -20758,15 +20758,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 07:12:19</t>
+          <t>2026-09-21 09:33:28</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>765.54</v>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>+0.710</t>
+        <v>765.11</v>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -20781,15 +20781,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>764.83</v>
+        <v>765.54</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -20804,15 +20804,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>764.54</v>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>764.83</v>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -20827,15 +20827,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>764.62</v>
+        <v>764.54</v>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>-0.770</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -20850,15 +20850,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>765.39</v>
+        <v>764.62</v>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>-0.620</t>
+          <t>-0.770</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -20873,15 +20873,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:32:25</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>766.01</v>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>765.39</v>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>-0.620</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -20896,15 +20896,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 05:47:34</t>
+          <t>2026-09-18 09:32:25</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>765.63</v>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>766.01</v>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -20919,15 +20919,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 05:47:34</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>765.8200000000001</v>
+        <v>765.63</v>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>-1.020</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -20942,15 +20942,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>766.84</v>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>+1.260</t>
+        <v>765.8200000000001</v>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -20965,15 +20965,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>765.58</v>
+        <v>766.84</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>+0.340</t>
+          <t>+1.260</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -20988,15 +20988,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>765.24</v>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>765.58</v>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -21011,15 +21011,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 08:40:02</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>765.39</v>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>765.24</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -21034,15 +21034,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 08:40:02</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>765.05</v>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>-4.700</t>
+        <v>765.39</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -21057,15 +21057,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>769.75</v>
+        <v>765.05</v>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-4.700</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -21080,15 +21080,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>770.04</v>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>769.75</v>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -21103,15 +21103,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>769.95</v>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>-0.730</t>
+        <v>770.04</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -21126,15 +21126,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>770.6799999999999</v>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>769.95</v>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -21149,15 +21149,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:40:23</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>770.47</v>
+        <v>770.6799999999999</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -21172,15 +21172,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 07:41:58</t>
+          <t>2026-09-16 09:40:23</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>770.38</v>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>770.47</v>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -21195,15 +21195,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>770.8</v>
+        <v>770.38</v>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -21218,15 +21218,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>770.8200000000001</v>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>+0.400</t>
+        <v>770.8</v>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -21241,15 +21241,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>770.42</v>
+        <v>770.8200000000001</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -21264,15 +21264,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>770.24</v>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>770.42</v>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -21287,11 +21287,11 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>771.05</v>
+        <v>770.24</v>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
@@ -21310,15 +21310,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>771.86</v>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>+1.540</t>
+        <v>771.05</v>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -21333,15 +21333,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>770.3200000000001</v>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>771.86</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -21356,15 +21356,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>771.76</v>
+        <v>770.3200000000001</v>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>-2.140</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -21379,15 +21379,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12 05:00:53</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>773.9</v>
+        <v>771.76</v>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-2.140</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -21402,15 +21402,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15:57</t>
+          <t>2026-09-12 05:00:53</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>774.33</v>
+        <v>773.9</v>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>-0.730</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -21425,15 +21425,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-12 02:15:57</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>+1.400</t>
+        <v>774.33</v>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -21448,15 +21448,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>773.66</v>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>775.0599999999999</v>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>+1.400</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -21471,15 +21471,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>775.1</v>
+        <v>773.66</v>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>-0.500</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -21494,15 +21494,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:18:12</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>775.6</v>
+        <v>775.1</v>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.500</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -21517,15 +21517,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 09:18:12</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>776.01</v>
+        <v>775.6</v>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -21540,15 +21540,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>776.01</v>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -21563,15 +21563,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>775.83</v>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>776.38</v>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -21586,15 +21586,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>776.53</v>
+        <v>775.83</v>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -21609,15 +21609,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.53</v>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -21632,15 +21632,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 06:08:04</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>776.7</v>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>776.91</v>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -21655,15 +21655,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 06:08:04</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>776.8</v>
+        <v>776.7</v>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -21678,15 +21678,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>777.27</v>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>+0.760</t>
+        <v>776.8</v>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -21701,15 +21701,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>776.51</v>
+        <v>777.27</v>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.760</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -21724,15 +21724,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>776.29</v>
+        <v>776.51</v>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>+0.390</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -21747,15 +21747,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>775.9</v>
+        <v>776.29</v>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -21770,15 +21770,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>775.58</v>
+        <v>775.9</v>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -21793,15 +21793,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>775.48</v>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>775.58</v>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -21816,15 +21816,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>776.29</v>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>775.48</v>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -21839,15 +21839,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 06:18:23</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>776.0700000000001</v>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>776.29</v>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -21862,15 +21862,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 06:18:23</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>776.54</v>
+        <v>776.0700000000001</v>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -21885,15 +21885,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>776.59</v>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>776.54</v>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -21908,15 +21908,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>776.13</v>
+        <v>776.59</v>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -21931,15 +21931,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>775.3200000000001</v>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>776.13</v>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -21954,15 +21954,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 08:56:04</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>775.6900000000001</v>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>775.3200000000001</v>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -21977,15 +21977,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 07:06:50</t>
+          <t>2026-09-07 08:56:04</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>775.63</v>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>775.6900000000001</v>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -22000,15 +22000,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-05 07:06:50</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>776.02</v>
-      </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>775.63</v>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -22023,15 +22023,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>775.76</v>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>-0.720</t>
+        <v>776.02</v>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -22046,15 +22046,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>776.48</v>
+        <v>775.76</v>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>-0.580</t>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -22069,15 +22069,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>777.0599999999999</v>
+        <v>776.48</v>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.580</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -22092,15 +22092,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 07:59:45</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>777.13</v>
+        <v>777.0599999999999</v>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>-0.540</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -22115,15 +22115,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 07:59:45</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>777.67</v>
+        <v>777.13</v>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>-0.300</t>
+          <t>-0.540</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -22138,15 +22138,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>777.97</v>
-      </c>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>+1.580</t>
+        <v>777.67</v>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>-0.300</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -22161,15 +22161,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>776.39</v>
+        <v>777.97</v>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>+1.580</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -22184,15 +22184,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>776.01</v>
+        <v>776.39</v>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>+0.660</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -22207,15 +22207,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>775.35</v>
+        <v>776.01</v>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>+0.700</t>
+          <t>+0.660</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -22230,15 +22230,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 06:35:56</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>774.65</v>
+        <v>775.35</v>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.700</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -22253,15 +22253,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 04:09:22</t>
+          <t>2026-09-03 06:35:56</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>774.64</v>
-      </c>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>-0.270</t>
+        <v>774.65</v>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -22276,15 +22276,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 04:09:22</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>774.91</v>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>+0.390</t>
+        <v>774.64</v>
+      </c>
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -22299,15 +22299,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>774.52</v>
+        <v>774.91</v>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>+0.230</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -22322,15 +22322,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 17:58:25</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>774.29</v>
-      </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>774.52</v>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>+0.230</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -22345,15 +22345,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 17:58:25</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>774.36</v>
+        <v>774.29</v>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>-0.860</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -22368,15 +22368,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D98" s="15" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>774.36</v>
+      </c>
+      <c r="D98" s="16" t="inlineStr">
+        <is>
+          <t>-0.860</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -22391,15 +22391,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 02:48:49</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>774.87</v>
-      </c>
-      <c r="D99" s="11" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>775.22</v>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -22414,15 +22414,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 02:48:49</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>775.47</v>
-      </c>
-      <c r="D100" s="15" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>774.87</v>
+      </c>
+      <c r="D100" s="16" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -22437,15 +22437,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>775.25</v>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>-1.030</t>
+        <v>775.47</v>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -22460,15 +22460,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>776.28</v>
+        <v>775.25</v>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>-0.280</t>
+          <t>-1.030</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -22483,15 +22483,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 09:25:49</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>776.5599999999999</v>
+        <v>776.28</v>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -22506,15 +22506,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 06:48:36</t>
+          <t>2026-09-01 09:25:49</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>776.58</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -22529,15 +22529,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 02:10:52</t>
+          <t>2026-09-01 06:48:36</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>776.63</v>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>+1.230</t>
+        <v>776.58</v>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -22552,15 +22552,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 02:10:52</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>775.4</v>
+        <v>776.63</v>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -22575,15 +22575,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D107" s="11" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>775.4</v>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -22598,15 +22598,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 08:13:17</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>775.92</v>
-      </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.22</v>
+      </c>
+      <c r="D108" s="16" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -22621,15 +22621,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 08:13:17</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>775.85</v>
-      </c>
-      <c r="D109" s="11" t="inlineStr">
-        <is>
-          <t>-2.850</t>
+        <v>775.92</v>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -22644,15 +22644,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>778.7</v>
+        <v>775.85</v>
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-2.850</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -22667,15 +22667,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>779.1</v>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>778.7</v>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -22690,15 +22690,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>778.72</v>
-      </c>
-      <c r="D112" s="16" t="inlineStr">
-        <is>
-          <t>-0.640</t>
+        <v>779.1</v>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -22713,15 +22713,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>779.36</v>
+        <v>778.72</v>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>-0.200</t>
+          <t>-0.640</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -22736,15 +22736,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 04:13:31</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>779.5599999999999</v>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>779.36</v>
+      </c>
+      <c r="D114" s="16" t="inlineStr">
+        <is>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -22759,15 +22759,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 04:13:31</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>779.39</v>
-      </c>
-      <c r="D115" s="11" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>779.5599999999999</v>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -22782,15 +22782,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>779.6</v>
+        <v>779.39</v>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -22805,15 +22805,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>780.03</v>
+        <v>779.6</v>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -22828,15 +22828,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 18:53:28</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>780.15</v>
+        <v>780.03</v>
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -22851,15 +22851,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 18:53:28</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>780.62</v>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>+0.560</t>
+        <v>780.15</v>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -22874,15 +22874,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>780.0599999999999</v>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>780.62</v>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>+0.560</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -22897,15 +22897,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>780.17</v>
+        <v>780.0599999999999</v>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -22920,15 +22920,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>780.38</v>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>780.17</v>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -22943,15 +22943,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 10:07:59</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>780.36</v>
-      </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>780.38</v>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -22966,15 +22966,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 07:52:24</t>
+          <t>2026-08-26 10:07:59</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>780.6</v>
-      </c>
-      <c r="D124" s="15" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>780.36</v>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -22989,15 +22989,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 01:49:35</t>
+          <t>2026-08-26 07:52:24</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>780.4299999999999</v>
+        <v>780.6</v>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -23012,15 +23012,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 01:49:35</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>780.35</v>
+        <v>780.4299999999999</v>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -23035,15 +23035,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.35</v>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>+0.410</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -23058,15 +23058,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:05:53</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>779.9</v>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>-0.260</t>
+        <v>780.3099999999999</v>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>+0.410</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 21:05:53</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>780.16</v>
+        <v>779.9</v>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>-0.230</t>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -23104,15 +23104,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>780.39</v>
-      </c>
-      <c r="D130" s="15" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>780.16</v>
+      </c>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>-0.230</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -23127,15 +23127,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>780.15</v>
+        <v>780.39</v>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>+0.540</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -23150,15 +23150,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:26</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>779.61</v>
-      </c>
-      <c r="D132" s="16" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>780.15</v>
+      </c>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t>+0.540</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -23173,15 +23173,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:01:55</t>
+          <t>2026-08-25 15:51:26</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>779.65</v>
+        <v>779.61</v>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -23196,15 +23196,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 15:01:55</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>779.73</v>
+        <v>779.65</v>
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -23219,15 +23219,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>780.11</v>
+        <v>779.73</v>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -23242,15 +23242,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>780.4</v>
-      </c>
-      <c r="D136" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>780.11</v>
+      </c>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -23265,15 +23265,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:57:56</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.4</v>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -23288,15 +23288,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 06:50:27</t>
+          <t>2026-08-25 09:57:56</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>780.1900000000001</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -23311,15 +23311,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 06:50:27</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>780.1799999999999</v>
-      </c>
-      <c r="D139" s="11" t="inlineStr">
-        <is>
-          <t>-0.450</t>
+        <v>780.1900000000001</v>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -23334,15 +23334,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>780.63</v>
-      </c>
-      <c r="D140" s="15" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>780.1799999999999</v>
+      </c>
+      <c r="D140" s="16" t="inlineStr">
+        <is>
+          <t>-0.450</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -23357,15 +23357,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>780.17</v>
-      </c>
-      <c r="D141" s="11" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.63</v>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -23380,15 +23380,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>780.61</v>
-      </c>
-      <c r="D142" s="15" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>780.17</v>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -23403,15 +23403,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>780.14</v>
-      </c>
-      <c r="D143" s="11" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>780.61</v>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>780.23</v>
+        <v>780.14</v>
       </c>
       <c r="D144" s="16" t="inlineStr">
         <is>
-          <t>-0.530</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>780.76</v>
+        <v>780.23</v>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>780.91</v>
+        <v>780.76</v>
       </c>
       <c r="D146" s="16" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>781.35</v>
+        <v>780.91</v>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>781.38</v>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>781.35</v>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>781.09</v>
-      </c>
-      <c r="D149" s="11" t="inlineStr">
-        <is>
-          <t>-0.350</t>
+        <v>781.38</v>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>781.4400000000001</v>
+        <v>781.09</v>
       </c>
       <c r="D150" s="16" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.350</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -23587,15 +23587,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>781.55</v>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.4400000000001</v>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -23610,15 +23610,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 09:42:15</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>781.23</v>
+        <v>781.55</v>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -23633,15 +23633,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 10:32:40</t>
+          <t>2026-08-24 09:42:15</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>781.01</v>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>781.23</v>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -23656,15 +23656,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 05:00:11</t>
+          <t>2026-08-22 10:32:40</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>781.11</v>
+        <v>781.01</v>
       </c>
       <c r="D154" s="16" t="inlineStr">
         <is>
-          <t>-0.180</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -23679,15 +23679,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 02:00:51</t>
+          <t>2026-08-22 05:00:11</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>781.29</v>
+        <v>781.11</v>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -23702,15 +23702,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-22 02:00:51</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>781.34</v>
-      </c>
-      <c r="D156" s="15" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>781.29</v>
+      </c>
+      <c r="D156" s="16" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -23725,15 +23725,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>780.79</v>
+        <v>781.34</v>
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -23748,15 +23748,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>780.6799999999999</v>
-      </c>
-      <c r="D158" s="16" t="inlineStr">
-        <is>
-          <t>-0.610</t>
+        <v>780.79</v>
+      </c>
+      <c r="D158" s="15" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -23771,15 +23771,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>781.29</v>
+        <v>780.6799999999999</v>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>-1.420</t>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -23794,15 +23794,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>782.71</v>
+        <v>781.29</v>
       </c>
       <c r="D160" s="16" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-1.420</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -23817,15 +23817,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>782.95</v>
-      </c>
-      <c r="D161" s="9" t="inlineStr">
-        <is>
-          <t>+1.080</t>
+        <v>782.71</v>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -23840,15 +23840,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>781.87</v>
-      </c>
-      <c r="D162" s="16" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>782.95</v>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>+1.080</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -23863,15 +23863,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>782.25</v>
-      </c>
-      <c r="D163" s="9" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>781.87</v>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -23886,15 +23886,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>781.99</v>
+        <v>782.25</v>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -23909,15 +23909,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>781.95</v>
-      </c>
-      <c r="D165" s="11" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>781.99</v>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -23932,15 +23932,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>781.99</v>
+        <v>781.95</v>
       </c>
       <c r="D166" s="16" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -23955,15 +23955,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>782.39</v>
-      </c>
-      <c r="D167" s="9" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>781.99</v>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -23978,15 +23978,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:13</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>782.03</v>
+        <v>782.39</v>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>+0.400</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -24001,15 +24001,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 06:49:01</t>
+          <t>2026-08-21 09:10:13</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>781.63</v>
+        <v>782.03</v>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -24024,15 +24024,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 06:49:01</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>780.95</v>
-      </c>
-      <c r="D170" s="16" t="inlineStr">
-        <is>
-          <t>-0.780</t>
+        <v>781.63</v>
+      </c>
+      <c r="D170" s="15" t="inlineStr">
+        <is>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -24047,15 +24047,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>781.73</v>
+        <v>780.95</v>
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -24070,15 +24070,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>781.79</v>
+        <v>781.73</v>
       </c>
       <c r="D172" s="16" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -24093,15 +24093,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>782.1900000000001</v>
-      </c>
-      <c r="D173" s="9" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>781.79</v>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -24116,15 +24116,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>782.04</v>
-      </c>
-      <c r="D174" s="16" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>782.1900000000001</v>
+      </c>
+      <c r="D174" s="15" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -24139,15 +24139,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>782.74</v>
-      </c>
-      <c r="D175" s="9" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>782.04</v>
+      </c>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -24162,15 +24162,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>782.42</v>
+        <v>782.74</v>
       </c>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -24185,15 +24185,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>781.95</v>
+        <v>782.42</v>
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -24208,15 +24208,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>781.14</v>
-      </c>
-      <c r="D178" s="16" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.95</v>
+      </c>
+      <c r="D178" s="15" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -24231,15 +24231,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>781.39</v>
-      </c>
-      <c r="D179" s="9" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>781.14</v>
+      </c>
+      <c r="D179" s="11" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -24254,15 +24254,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>781.2</v>
+        <v>781.39</v>
       </c>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -24277,15 +24277,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>781.17</v>
-      </c>
-      <c r="D181" s="11" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.2</v>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -24300,15 +24300,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 10:06:13</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>781.42</v>
+        <v>781.17</v>
       </c>
       <c r="D182" s="16" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -24323,15 +24323,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 07:36:53</t>
+          <t>2026-08-20 10:06:13</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>781.42</v>
+      </c>
+      <c r="D183" s="11" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -24346,15 +24346,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 06:33:42</t>
+          <t>2026-08-20 07:36:53</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>781.77</v>
+        <v>781.79</v>
       </c>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -24369,15 +24369,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 06:33:42</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>781.45</v>
+        <v>781.77</v>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>+0.850</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -24392,15 +24392,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>780.6</v>
+        <v>781.45</v>
       </c>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.850</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -24415,15 +24415,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>780.12</v>
+        <v>780.6</v>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>+1.750</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -24438,15 +24438,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>778.37</v>
+        <v>780.12</v>
       </c>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>+1.750</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -24461,15 +24461,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>778.09</v>
+        <v>778.37</v>
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -24484,15 +24484,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>777.41</v>
+        <v>778.09</v>
       </c>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -24507,15 +24507,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>777.3200000000001</v>
+        <v>777.41</v>
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -24530,11 +24530,11 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>777.1</v>
+        <v>777.3200000000001</v>
       </c>
       <c r="D192" s="15" t="inlineStr">
         <is>
@@ -24553,15 +24553,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>776.88</v>
-      </c>
-      <c r="D193" s="11" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.1</v>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -24576,15 +24576,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>776.89</v>
-      </c>
-      <c r="D194" s="15" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>776.88</v>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -24599,15 +24599,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>776.84</v>
-      </c>
-      <c r="D195" s="11" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>776.89</v>
+      </c>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -24622,15 +24622,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 09:12:00</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D196" s="15" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.84</v>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -24645,15 +24645,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 09:12:00</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>776.72</v>
-      </c>
-      <c r="D197" s="11" t="inlineStr">
-        <is>
-          <t>-0.460</t>
+        <v>776.9</v>
+      </c>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -24668,15 +24668,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>777.1799999999999</v>
-      </c>
-      <c r="D198" s="15" t="inlineStr">
-        <is>
-          <t>+0.630</t>
+        <v>776.72</v>
+      </c>
+      <c r="D198" s="16" t="inlineStr">
+        <is>
+          <t>-0.460</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -24691,15 +24691,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>776.55</v>
-      </c>
-      <c r="D199" s="11" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>777.1799999999999</v>
+      </c>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -24714,15 +24714,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:24</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>776.62</v>
-      </c>
-      <c r="D200" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>776.55</v>
+      </c>
+      <c r="D200" s="16" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -24737,15 +24737,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 17:58:24</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>776.53</v>
+        <v>776.62</v>
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -24760,15 +24760,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>776.36</v>
-      </c>
-      <c r="D202" s="16" t="inlineStr">
-        <is>
-          <t>-0.160</t>
+        <v>776.53</v>
+      </c>
+      <c r="D202" s="15" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -24783,15 +24783,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>776.52</v>
+        <v>776.36</v>
       </c>
       <c r="D203" s="11" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.160</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -24806,15 +24806,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>776.53</v>
+        <v>776.52</v>
       </c>
       <c r="D204" s="16" t="inlineStr">
         <is>
-          <t>-0.390</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -24829,15 +24829,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>776.92</v>
-      </c>
-      <c r="D205" s="9" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>776.53</v>
+      </c>
+      <c r="D205" s="11" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -24852,15 +24852,15 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 10:04:24</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>776.8200000000001</v>
+        <v>776.92</v>
       </c>
       <c r="D206" s="15" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -24875,15 +24875,15 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 07:54:32</t>
+          <t>2026-08-18 10:04:24</t>
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>776.61</v>
-      </c>
-      <c r="D207" s="11" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>776.8200000000001</v>
+      </c>
+      <c r="D207" s="9" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -24898,15 +24898,15 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 05:48:09</t>
+          <t>2026-08-18 07:54:32</t>
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>776.74</v>
-      </c>
-      <c r="D208" s="15" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.61</v>
+      </c>
+      <c r="D208" s="16" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -24921,15 +24921,15 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 05:48:09</t>
         </is>
       </c>
       <c r="C209" s="8" t="n">
-        <v>776.5599999999999</v>
-      </c>
-      <c r="D209" s="11" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>776.74</v>
+      </c>
+      <c r="D209" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -24944,15 +24944,15 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>777.16</v>
-      </c>
-      <c r="D210" s="15" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>776.5599999999999</v>
+      </c>
+      <c r="D210" s="16" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -24967,15 +24967,15 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
-        <v>776.8099999999999</v>
-      </c>
-      <c r="D211" s="11" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>777.16</v>
+      </c>
+      <c r="D211" s="9" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -24990,15 +24990,15 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:45</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>777.21</v>
+        <v>776.8099999999999</v>
       </c>
       <c r="D212" s="16" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -25013,15 +25013,15 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 21:10:45</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>777.4299999999999</v>
+        <v>777.21</v>
       </c>
       <c r="D213" s="11" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -25036,15 +25036,15 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>777.52</v>
-      </c>
-      <c r="D214" s="15" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>777.4299999999999</v>
+      </c>
+      <c r="D214" s="16" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -25059,15 +25059,15 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>777.5</v>
+        <v>777.52</v>
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>+0.370</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -25082,15 +25082,15 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>777.13</v>
+        <v>777.5</v>
       </c>
       <c r="D216" s="15" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.370</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -25105,15 +25105,15 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
-        <v>777.04</v>
+        <v>777.13</v>
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -25128,15 +25128,15 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D218" s="16" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.04</v>
+      </c>
+      <c r="D218" s="15" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -25151,15 +25151,15 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>776.91</v>
+        <v>776.9</v>
       </c>
       <c r="D219" s="11" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -25174,15 +25174,15 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>776.96</v>
-      </c>
-      <c r="D220" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>776.91</v>
+      </c>
+      <c r="D220" s="16" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -25197,15 +25197,15 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 09:21:39</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>776.84</v>
+        <v>776.96</v>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>+0.750</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -25220,15 +25220,15 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 09:21:39</t>
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>776.09</v>
-      </c>
-      <c r="D222" s="16" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>776.84</v>
+      </c>
+      <c r="D222" s="15" t="inlineStr">
+        <is>
+          <t>+0.750</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -25243,15 +25243,15 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>776.09</v>
+      </c>
+      <c r="D223" s="11" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -25266,15 +25266,15 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>775.8099999999999</v>
+        <v>776.38</v>
       </c>
       <c r="D224" s="15" t="inlineStr">
         <is>
-          <t>+0.770</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -25289,15 +25289,15 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>775.04</v>
+        <v>775.8099999999999</v>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.770</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -25312,15 +25312,15 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>774.92</v>
+        <v>775.04</v>
       </c>
       <c r="D226" s="15" t="inlineStr">
         <is>
-          <t>+0.360</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -25335,15 +25335,15 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>774.5599999999999</v>
+        <v>774.92</v>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -25358,15 +25358,15 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C228" s="6" t="n">
-        <v>774.4400000000001</v>
-      </c>
-      <c r="D228" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>774.5599999999999</v>
+      </c>
+      <c r="D228" s="15" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -25381,15 +25381,15 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>774.46</v>
-      </c>
-      <c r="D229" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>774.4400000000001</v>
+      </c>
+      <c r="D229" s="11" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
@@ -25404,15 +25404,15 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>774.25</v>
+        <v>774.46</v>
       </c>
       <c r="D230" s="15" t="inlineStr">
         <is>
-          <t>+0.310</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -25427,15 +25427,15 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 10:39:02</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>773.9400000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.310</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -25450,15 +25450,15 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 08:05:13</t>
+          <t>2026-08-14 10:39:02</t>
         </is>
       </c>
       <c r="C232" s="6" t="n">
-        <v>773.9</v>
+        <v>773.9400000000001</v>
       </c>
       <c r="D232" s="15" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -25473,15 +25473,15 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 07:24:16</t>
+          <t>2026-08-14 08:05:13</t>
         </is>
       </c>
       <c r="C233" s="8" t="n">
-        <v>773.73</v>
+        <v>773.9</v>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
@@ -25496,15 +25496,15 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 07:24:16</t>
         </is>
       </c>
       <c r="C234" s="6" t="n">
-        <v>773.53</v>
-      </c>
-      <c r="D234" s="16" t="inlineStr">
-        <is>
-          <t>-0.790</t>
+        <v>773.73</v>
+      </c>
+      <c r="D234" s="15" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -25519,15 +25519,15 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>774.3200000000001</v>
-      </c>
-      <c r="D235" s="9" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>773.53</v>
+      </c>
+      <c r="D235" s="11" t="inlineStr">
+        <is>
+          <t>-0.790</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
@@ -25542,15 +25542,15 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C236" s="6" t="n">
-        <v>773.75</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="D236" s="15" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -25565,15 +25565,15 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
-        <v>773.7</v>
+        <v>773.75</v>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
@@ -25588,15 +25588,15 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C238" s="6" t="n">
-        <v>773.58</v>
+        <v>773.7</v>
       </c>
       <c r="D238" s="15" t="inlineStr">
         <is>
-          <t>+0.250</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -25611,15 +25611,15 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
-        <v>773.33</v>
-      </c>
-      <c r="D239" s="11" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>773.58</v>
+      </c>
+      <c r="D239" s="9" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
@@ -25634,15 +25634,15 @@
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C240" s="6" t="n">
-        <v>773.39</v>
-      </c>
-      <c r="D240" s="15" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>773.33</v>
+      </c>
+      <c r="D240" s="16" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -25657,15 +25657,15 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C241" s="8" t="n">
-        <v>773.11</v>
-      </c>
-      <c r="D241" s="11" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>773.39</v>
+      </c>
+      <c r="D241" s="9" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
@@ -25680,15 +25680,15 @@
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C242" s="6" t="n">
-        <v>773.24</v>
+        <v>773.11</v>
       </c>
       <c r="D242" s="16" t="inlineStr">
         <is>
-          <t>-0.340</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -25703,15 +25703,15 @@
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C243" s="8" t="n">
-        <v>773.58</v>
+        <v>773.24</v>
       </c>
       <c r="D243" s="11" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
@@ -25726,15 +25726,15 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C244" s="6" t="n">
-        <v>773.64</v>
+        <v>773.58</v>
       </c>
       <c r="D244" s="16" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -25749,15 +25749,15 @@
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C245" s="8" t="n">
-        <v>774.11</v>
+        <v>773.64</v>
       </c>
       <c r="D245" s="11" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
@@ -25772,15 +25772,15 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C246" s="6" t="n">
-        <v>774.3</v>
+        <v>774.11</v>
       </c>
       <c r="D246" s="16" t="inlineStr">
         <is>
-          <t>-0.740</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
@@ -25795,15 +25795,15 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C247" s="8" t="n">
-        <v>775.04</v>
-      </c>
-      <c r="D247" s="9" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>774.3</v>
+      </c>
+      <c r="D247" s="11" t="inlineStr">
+        <is>
+          <t>-0.740</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
@@ -25818,15 +25818,15 @@
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C248" s="6" t="n">
-        <v>774.9</v>
+        <v>775.04</v>
       </c>
       <c r="D248" s="15" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -25841,15 +25841,15 @@
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
-        <v>774.66</v>
+        <v>774.9</v>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
@@ -25864,15 +25864,15 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C250" s="6" t="n">
-        <v>774.34</v>
+        <v>774.66</v>
       </c>
       <c r="D250" s="15" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
@@ -25887,15 +25887,15 @@
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C251" s="8" t="n">
-        <v>774.15</v>
-      </c>
-      <c r="D251" s="11" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>774.34</v>
+      </c>
+      <c r="D251" s="9" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
@@ -25910,15 +25910,15 @@
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 13:53:42</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C252" s="6" t="n">
-        <v>774.25</v>
+        <v>774.15</v>
       </c>
       <c r="D252" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
@@ -25933,15 +25933,15 @@
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 13:53:42</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
-        <v>774.3200000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D253" s="11" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
@@ -25956,15 +25956,15 @@
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C254" s="6" t="n">
-        <v>774.74</v>
-      </c>
-      <c r="D254" s="15" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>774.3200000000001</v>
+      </c>
+      <c r="D254" s="16" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
@@ -25979,15 +25979,15 @@
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 01:28:47</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C255" s="8" t="n">
-        <v>774.5</v>
+        <v>774.74</v>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
@@ -26002,15 +26002,15 @@
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 01:28:47</t>
         </is>
       </c>
       <c r="C256" s="6" t="n">
-        <v>774.37</v>
-      </c>
-      <c r="D256" s="16" t="inlineStr">
-        <is>
-          <t>-0.340</t>
+        <v>774.5</v>
+      </c>
+      <c r="D256" s="15" t="inlineStr">
+        <is>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
@@ -26025,15 +26025,15 @@
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C257" s="8" t="n">
-        <v>774.71</v>
-      </c>
-      <c r="D257" s="9" t="inlineStr">
-        <is>
-          <t>+1.160</t>
+        <v>774.37</v>
+      </c>
+      <c r="D257" s="11" t="inlineStr">
+        <is>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
@@ -26048,15 +26048,15 @@
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C258" s="6" t="n">
-        <v>773.55</v>
-      </c>
-      <c r="D258" s="16" t="inlineStr">
-        <is>
-          <t>-0.520</t>
+        <v>774.71</v>
+      </c>
+      <c r="D258" s="15" t="inlineStr">
+        <is>
+          <t>+1.160</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
@@ -26071,15 +26071,15 @@
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C259" s="8" t="n">
-        <v>774.0700000000001</v>
+        <v>773.55</v>
       </c>
       <c r="D259" s="11" t="inlineStr">
         <is>
-          <t>-0.690</t>
+          <t>-0.520</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
@@ -26094,15 +26094,15 @@
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C260" s="6" t="n">
-        <v>774.76</v>
+        <v>774.0700000000001</v>
       </c>
       <c r="D260" s="16" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.690</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
@@ -26117,15 +26117,15 @@
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C261" s="8" t="n">
-        <v>775.3099999999999</v>
+        <v>774.76</v>
       </c>
       <c r="D261" s="11" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
@@ -26140,15 +26140,15 @@
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C262" s="6" t="n">
-        <v>775.46</v>
+        <v>775.3099999999999</v>
       </c>
       <c r="D262" s="16" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
@@ -26163,15 +26163,15 @@
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C263" s="8" t="n">
-        <v>775.84</v>
+        <v>775.46</v>
       </c>
       <c r="D263" s="11" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
@@ -26186,15 +26186,15 @@
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 08:05:33</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C264" s="6" t="n">
-        <v>775.9</v>
-      </c>
-      <c r="D264" s="15" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.84</v>
+      </c>
+      <c r="D264" s="16" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E264" s="6" t="inlineStr">
@@ -26209,15 +26209,15 @@
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 08:05:33</t>
         </is>
       </c>
       <c r="C265" s="8" t="n">
-        <v>775.83</v>
+        <v>775.9</v>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
@@ -26232,15 +26232,15 @@
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C266" s="6" t="n">
-        <v>775.2</v>
-      </c>
-      <c r="D266" s="16" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>775.83</v>
+      </c>
+      <c r="D266" s="15" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E266" s="6" t="inlineStr">
@@ -26255,15 +26255,15 @@
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C267" s="8" t="n">
-        <v>775.28</v>
-      </c>
-      <c r="D267" s="9" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>775.2</v>
+      </c>
+      <c r="D267" s="11" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
@@ -26278,15 +26278,15 @@
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C268" s="6" t="n">
-        <v>775.12</v>
+        <v>775.28</v>
       </c>
       <c r="D268" s="15" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E268" s="6" t="inlineStr">
@@ -26301,11 +26301,11 @@
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C269" s="8" t="n">
-        <v>775.09</v>
+        <v>775.12</v>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
@@ -26324,15 +26324,15 @@
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 18:37:13</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C270" s="6" t="n">
-        <v>775.0599999999999</v>
+        <v>775.09</v>
       </c>
       <c r="D270" s="15" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E270" s="6" t="inlineStr">
@@ -26347,15 +26347,15 @@
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 18:37:13</t>
         </is>
       </c>
       <c r="C271" s="8" t="n">
-        <v>774.58</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
@@ -26370,15 +26370,15 @@
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C272" s="6" t="n">
-        <v>774.29</v>
+        <v>774.58</v>
       </c>
       <c r="D272" s="15" t="inlineStr">
         <is>
-          <t>+0.490</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
@@ -26393,15 +26393,15 @@
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C273" s="8" t="n">
-        <v>773.8</v>
-      </c>
-      <c r="D273" s="11" t="inlineStr">
-        <is>
-          <t>-0.590</t>
+        <v>774.29</v>
+      </c>
+      <c r="D273" s="9" t="inlineStr">
+        <is>
+          <t>+0.490</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
@@ -26416,14 +26416,37 @@
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C274" s="6" t="n">
+        <v>773.8</v>
+      </c>
+      <c r="D274" s="16" t="inlineStr">
+        <is>
+          <t>-0.590</t>
+        </is>
+      </c>
+      <c r="E274" s="6" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="8" t="n">
+        <v>271</v>
+      </c>
+      <c r="B275" s="8" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C274" s="6" t="n">
+      <c r="C275" s="8" t="n">
         <v>774.39</v>
       </c>
-      <c r="D274" s="6" t="inlineStr"/>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="D275" s="8" t="inlineStr"/>
+      <c r="E275" s="8" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 07:27:58</t>
+          <t>更新时间: 2026-09-26 09:48:15</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 09:48:15</t>
+          <t>更新时间: 2026-09-26 14:41:11</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 14:41:11</t>
+          <t>更新时间: 2026-09-26 19:47:05</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 19:47:05</t>
+          <t>更新时间: 2026-09-26 23:07:40</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 23:07:40</t>
+          <t>更新时间: 2026-09-27 02:33:26</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 02:33:26</t>
+          <t>更新时间: 2026-09-27 05:27:34</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 05:27:34</t>
+          <t>更新时间: 2026-09-27 07:44:40</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 07:44:40</t>
+          <t>更新时间: 2026-09-27 09:50:20</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 09:50:20</t>
+          <t>更新时间: 2026-09-27 15:11:55</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 15:11:55</t>
+          <t>更新时间: 2026-09-27 21:00:58</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 21:00:58</t>
+          <t>更新时间: 2026-09-28 01:38:53</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 01:38:53</t>
+          <t>更新时间: 2026-09-28 04:22:42</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 07:24:15</t>
+          <t>更新时间: 2026-10-03 10:08:06</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 10:08:06</t>
+          <t>更新时间: 2026-10-03 16:01:57</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 16:01:57</t>
+          <t>更新时间: 2026-10-03 21:17:05</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 21:17:05</t>
+          <t>更新时间: 2026-10-04 01:19:09</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 01:19:09</t>
+          <t>更新时间: 2026-10-04 04:00:25</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 04:00:25</t>
+          <t>更新时间: 2026-10-04 06:45:09</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 06:45:09</t>
+          <t>更新时间: 2026-10-04 10:00:11</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 10:00:11</t>
+          <t>更新时间: 2026-10-04 16:14:40</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 16:14:40</t>
+          <t>更新时间: 2026-10-04 22:05:29</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 22:05:29</t>
+          <t>更新时间: 2026-10-05 02:06:19</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 02:06:19</t>
+          <t>更新时间: 2026-10-05 05:16:49</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -185,10 +185,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 05:16:49</t>
+          <t>更新时间: 2026-10-05 07:58:30</t>
         </is>
       </c>
     </row>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>751.58</v>
+        <v>751.75</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03 07:24:10</t>
+          <t>2026-10-05 07:58:26</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E299"/>
+  <dimension ref="A1:E300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -21043,7 +21043,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 751.58 | 最高: 782.950 | 最低: 750.700 | 总记录数: 295</t>
+          <t>最新价: 751.75 | 最高: 782.950 | 最低: 750.700 | 总记录数: 296</t>
         </is>
       </c>
     </row>
@@ -21080,15 +21080,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 07:24:10</t>
+          <t>2026-10-05 07:58:26</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>751.58</v>
+        <v>751.75</v>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>+0.430</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -21103,15 +21103,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03 03:54:13</t>
+          <t>2026-10-03 07:24:10</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>751.15</v>
+        <v>751.58</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-2.800</t>
+          <t>+0.430</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -21126,15 +21126,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02 23:05:32</t>
+          <t>2026-10-03 03:54:13</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>753.95</v>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>+1.310</t>
+        <v>751.15</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>-2.800</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -21149,15 +21149,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02 16:50:38</t>
+          <t>2026-10-02 23:05:32</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>752.64</v>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>+1.940</t>
+        <v>753.95</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>+1.310</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -21172,15 +21172,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02 10:28:43</t>
+          <t>2026-10-02 16:50:38</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>750.7</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>752.64</v>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>+1.940</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -21195,15 +21195,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02 03:52:14</t>
+          <t>2026-10-02 10:28:43</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>750.8099999999999</v>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>-3.460</t>
+        <v>750.7</v>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -21218,15 +21218,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01 22:45:56</t>
+          <t>2026-10-02 03:52:14</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>754.27</v>
+        <v>750.8099999999999</v>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>-1.430</t>
+          <t>-3.460</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -21241,15 +21241,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01 15:40:31</t>
+          <t>2026-10-01 22:45:56</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>755.7</v>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>-0.970</t>
+        <v>754.27</v>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>-1.430</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -21264,15 +21264,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01 09:30:52</t>
+          <t>2026-10-01 15:40:31</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>756.67</v>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>755.7</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>-0.970</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -21287,15 +21287,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01 06:35:22</t>
+          <t>2026-10-01 09:30:52</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>756.61</v>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>756.67</v>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -21310,15 +21310,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01 02:37:20</t>
+          <t>2026-10-01 06:35:22</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>756.5</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>-1.520</t>
+        <v>756.61</v>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -21333,15 +21333,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30 21:52:18</t>
+          <t>2026-10-01 02:37:20</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>758.02</v>
+        <v>756.5</v>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>+1.070</t>
+          <t>-1.520</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -21356,15 +21356,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30 15:18:20</t>
+          <t>2026-09-30 21:52:18</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>756.95</v>
+        <v>758.02</v>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>+1.070</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -21379,15 +21379,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30 09:33:06</t>
+          <t>2026-09-30 15:18:20</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>756.48</v>
+        <v>756.95</v>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>-0.490</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -21402,15 +21402,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30 06:39:24</t>
+          <t>2026-09-30 09:33:06</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>756.97</v>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>+1.820</t>
+        <v>756.48</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>-0.490</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -21425,15 +21425,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30 02:44:52</t>
+          <t>2026-09-30 06:39:24</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>755.15</v>
+        <v>756.97</v>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>-1.720</t>
+          <t>+1.820</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -21448,15 +21448,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 21:24:10</t>
+          <t>2026-09-30 02:44:52</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>756.87</v>
+        <v>755.15</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>-1.250</t>
+          <t>-1.720</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -21471,15 +21471,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29 14:50:03</t>
+          <t>2026-09-29 21:24:10</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>758.12</v>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>-1.140</t>
+        <v>756.87</v>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>-1.250</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -21494,15 +21494,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 09:07:04</t>
+          <t>2026-09-29 14:50:03</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>759.26</v>
+        <v>758.12</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-1.140</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -21517,15 +21517,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29 05:25:52</t>
+          <t>2026-09-29 09:07:04</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>759.3200000000001</v>
+        <v>759.26</v>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -21540,15 +21540,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28 23:53:17</t>
+          <t>2026-09-29 05:25:52</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>759.21</v>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>-1.020</t>
+        <v>759.3200000000001</v>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -21563,15 +21563,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-28 15:35:28</t>
+          <t>2026-09-28 23:53:17</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>760.23</v>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>-0.480</t>
+        <v>759.21</v>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -21586,15 +21586,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28 07:09:27</t>
+          <t>2026-09-28 15:35:28</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>760.71</v>
+        <v>760.23</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>-1.020</t>
+          <t>-0.480</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -21609,15 +21609,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26 07:27:54</t>
+          <t>2026-09-28 07:09:27</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>761.73</v>
+        <v>760.71</v>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -21632,15 +21632,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26 04:30:49</t>
+          <t>2026-09-26 07:27:54</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>761.5700000000001</v>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>761.73</v>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -21655,15 +21655,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26 01:15:26</t>
+          <t>2026-09-26 04:30:49</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>762.27</v>
+        <v>761.5700000000001</v>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>+0.790</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -21678,15 +21678,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25 20:15:35</t>
+          <t>2026-09-26 01:15:26</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>761.48</v>
+        <v>762.27</v>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>+1.200</t>
+          <t>+0.790</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -21701,15 +21701,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25 14:42:41</t>
+          <t>2026-09-25 20:15:35</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>760.28</v>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>+0.130</t>
+        <v>761.48</v>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>+1.200</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -21724,15 +21724,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25 01:40:29</t>
+          <t>2026-09-25 14:42:41</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>760.15</v>
+        <v>760.28</v>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>+0.500</t>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -21747,15 +21747,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 20:55:26</t>
+          <t>2026-09-25 01:40:29</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>759.65</v>
+        <v>760.15</v>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-1.120</t>
+          <t>+0.500</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -21770,15 +21770,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 15:50:01</t>
+          <t>2026-09-24 20:55:26</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>760.77</v>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>+1.060</t>
+        <v>759.65</v>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>-1.120</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -21793,15 +21793,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 10:50:22</t>
+          <t>2026-09-24 15:50:01</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>759.71</v>
+        <v>760.77</v>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>-0.200</t>
+          <t>+1.060</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -21816,15 +21816,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 07:56:20</t>
+          <t>2026-09-24 10:50:22</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>759.91</v>
+        <v>759.71</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -21839,15 +21839,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 02:27:02</t>
+          <t>2026-09-24 07:56:20</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>760.46</v>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>-0.410</t>
+        <v>759.91</v>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -21862,15 +21862,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 22:21:19</t>
+          <t>2026-09-24 02:27:02</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>760.87</v>
+        <v>760.46</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>-1.520</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -21885,15 +21885,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 17:31:43</t>
+          <t>2026-09-23 22:21:19</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>762.39</v>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>-0.310</t>
+        <v>760.87</v>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>-1.520</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -21908,15 +21908,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 12:39:24</t>
+          <t>2026-09-23 17:31:43</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>762.7</v>
+        <v>762.39</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.310</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -21931,15 +21931,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 05:59:14</t>
+          <t>2026-09-23 12:39:24</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>762.89</v>
+        <v>762.7</v>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -21954,15 +21954,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 03:03:22</t>
+          <t>2026-09-23 05:59:14</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>762.41</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>-1.930</t>
+        <v>762.89</v>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -21977,15 +21977,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 23:32:15</t>
+          <t>2026-09-23 03:03:22</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>764.34</v>
+        <v>762.41</v>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>+0.250</t>
+          <t>-1.930</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -22000,15 +22000,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 19:17:55</t>
+          <t>2026-09-22 23:32:15</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>764.09</v>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>-0.680</t>
+        <v>764.34</v>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -22023,15 +22023,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00:07</t>
+          <t>2026-09-22 19:17:55</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>764.77</v>
+        <v>764.09</v>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>+0.880</t>
+          <t>-0.680</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -22046,15 +22046,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 09:01:08</t>
+          <t>2026-09-22 14:00:07</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>763.89</v>
+        <v>764.77</v>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>+0.880</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -22069,15 +22069,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 06:28:11</t>
+          <t>2026-09-22 09:01:08</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>763.73</v>
+        <v>763.89</v>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>-0.670</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -22092,15 +22092,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 02:58:23</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>764.4</v>
+        <v>763.73</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>-0.750</t>
+          <t>-0.670</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -22115,15 +22115,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 21:54:34</t>
+          <t>2026-09-22 02:58:23</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>765.15</v>
+        <v>764.4</v>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>+0.510</t>
+          <t>-0.750</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -22138,15 +22138,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:24</t>
+          <t>2026-09-21 21:54:34</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>764.64</v>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>765.15</v>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>+0.510</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -22161,15 +22161,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 09:33:28</t>
+          <t>2026-09-21 15:01:24</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>765.11</v>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>-0.430</t>
+        <v>764.64</v>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -22184,15 +22184,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 07:12:19</t>
+          <t>2026-09-21 09:33:28</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>765.54</v>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>+0.710</t>
+        <v>765.11</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -22207,15 +22207,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>764.83</v>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>765.54</v>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -22230,15 +22230,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>764.54</v>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>764.83</v>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -22253,15 +22253,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>764.62</v>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>-0.770</t>
+        <v>764.54</v>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -22276,15 +22276,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>765.39</v>
+        <v>764.62</v>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>-0.620</t>
+          <t>-0.770</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -22299,15 +22299,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:32:25</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>766.01</v>
+        <v>765.39</v>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>-0.620</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -22322,15 +22322,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 05:47:34</t>
+          <t>2026-09-18 09:32:25</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>765.63</v>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>766.01</v>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -22345,15 +22345,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 05:47:34</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>765.8200000000001</v>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>-1.020</t>
+        <v>765.63</v>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -22368,15 +22368,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>766.84</v>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>+1.260</t>
+        <v>765.8200000000001</v>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -22391,15 +22391,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>765.58</v>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>766.84</v>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>+1.260</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -22414,15 +22414,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>765.24</v>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>765.58</v>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -22437,15 +22437,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 08:40:02</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>765.39</v>
+        <v>765.24</v>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>+0.340</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -22460,15 +22460,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 08:40:02</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>765.05</v>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>-4.700</t>
+        <v>765.39</v>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -22483,15 +22483,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>769.75</v>
-      </c>
-      <c r="D66" s="15" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>765.05</v>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>-4.700</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -22506,15 +22506,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>770.04</v>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>769.75</v>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -22529,15 +22529,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>769.95</v>
+        <v>770.04</v>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>-0.730</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -22552,15 +22552,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>770.6799999999999</v>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>769.95</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -22575,15 +22575,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 09:40:23</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>770.47</v>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>770.6799999999999</v>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -22598,15 +22598,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 07:41:58</t>
+          <t>2026-09-16 09:40:23</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>770.38</v>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>770.47</v>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -22621,15 +22621,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>770.8</v>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>770.38</v>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -22644,15 +22644,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>770.8200000000001</v>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>+0.400</t>
+        <v>770.8</v>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -22667,15 +22667,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>770.42</v>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>770.8200000000001</v>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -22690,15 +22690,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>770.24</v>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>770.42</v>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -22713,13 +22713,13 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>771.05</v>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
+        <v>770.24</v>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>-0.810</t>
         </is>
@@ -22736,15 +22736,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>771.86</v>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>+1.540</t>
+        <v>771.05</v>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -22759,15 +22759,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>770.3200000000001</v>
+        <v>771.86</v>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>-1.440</t>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -22782,15 +22782,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>771.76</v>
+        <v>770.3200000000001</v>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>-2.140</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -22805,15 +22805,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12 05:00:53</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>773.9</v>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>-0.430</t>
+        <v>771.76</v>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>-2.140</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -22828,15 +22828,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15:57</t>
+          <t>2026-09-12 05:00:53</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>774.33</v>
+        <v>773.9</v>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>-0.730</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -22851,15 +22851,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-12 02:15:57</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>775.0599999999999</v>
+        <v>774.33</v>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>+1.400</t>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -22874,15 +22874,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>773.66</v>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>775.0599999999999</v>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>+1.400</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -22897,15 +22897,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>775.1</v>
-      </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>-0.500</t>
+        <v>773.66</v>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -22920,15 +22920,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 09:18:12</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>775.6</v>
+        <v>775.1</v>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.500</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -22943,15 +22943,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 09:18:12</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>776.01</v>
-      </c>
-      <c r="D86" s="15" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>775.6</v>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -22966,15 +22966,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>776.01</v>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -22989,15 +22989,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>775.83</v>
+        <v>776.38</v>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>-0.700</t>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -23012,15 +23012,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>776.53</v>
+        <v>775.83</v>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -23035,15 +23035,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>776.91</v>
+        <v>776.53</v>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -23058,15 +23058,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 06:08:04</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>776.7</v>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>776.91</v>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 06:08:04</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>776.8</v>
-      </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>776.7</v>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -23104,15 +23104,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>777.27</v>
-      </c>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>+0.760</t>
+        <v>776.8</v>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -23127,15 +23127,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>776.51</v>
-      </c>
-      <c r="D94" s="16" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>777.27</v>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>+0.760</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -23150,15 +23150,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>776.29</v>
+        <v>776.51</v>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>+0.390</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -23173,15 +23173,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>775.9</v>
-      </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>776.29</v>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -23196,15 +23196,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>775.58</v>
+        <v>775.9</v>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -23219,15 +23219,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>775.48</v>
+        <v>775.58</v>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>-0.810</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -23242,15 +23242,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>776.29</v>
-      </c>
-      <c r="D99" s="11" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>775.48</v>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -23265,15 +23265,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 06:18:23</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>776.0700000000001</v>
+        <v>776.29</v>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -23288,15 +23288,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 06:18:23</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>776.54</v>
+        <v>776.0700000000001</v>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -23311,15 +23311,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>776.59</v>
+        <v>776.54</v>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>+0.460</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -23334,15 +23334,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>776.13</v>
+        <v>776.59</v>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -23357,15 +23357,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>775.3200000000001</v>
+        <v>776.13</v>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -23380,15 +23380,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 08:56:04</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>775.6900000000001</v>
-      </c>
-      <c r="D105" s="11" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>775.3200000000001</v>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -23403,15 +23403,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 07:06:50</t>
+          <t>2026-09-07 08:56:04</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>775.63</v>
+        <v>775.6900000000001</v>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>-0.390</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-05 07:06:50</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>776.02</v>
-      </c>
-      <c r="D107" s="11" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>775.63</v>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>775.76</v>
+        <v>776.02</v>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>-0.720</t>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>776.48</v>
+        <v>775.76</v>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>-0.580</t>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>777.0599999999999</v>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>776.48</v>
+      </c>
+      <c r="D110" s="16" t="inlineStr">
+        <is>
+          <t>-0.580</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 07:59:45</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>777.13</v>
+        <v>777.0599999999999</v>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>-0.540</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 07:59:45</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>777.67</v>
-      </c>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>-0.300</t>
+        <v>777.13</v>
+      </c>
+      <c r="D112" s="16" t="inlineStr">
+        <is>
+          <t>-0.540</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>777.97</v>
-      </c>
-      <c r="D113" s="11" t="inlineStr">
-        <is>
-          <t>+1.580</t>
+        <v>777.67</v>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>-0.300</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -23587,15 +23587,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>776.39</v>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>777.97</v>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>+1.580</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -23610,15 +23610,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>776.01</v>
+        <v>776.39</v>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>+0.660</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -23633,15 +23633,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>775.35</v>
-      </c>
-      <c r="D116" s="16" t="inlineStr">
-        <is>
-          <t>+0.700</t>
+        <v>776.01</v>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>+0.660</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -23656,15 +23656,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 06:35:56</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>774.65</v>
+        <v>775.35</v>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.700</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -23679,15 +23679,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 04:09:22</t>
+          <t>2026-09-03 06:35:56</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>774.64</v>
+        <v>774.65</v>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>-0.270</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -23702,15 +23702,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 04:09:22</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>774.91</v>
-      </c>
-      <c r="D119" s="11" t="inlineStr">
-        <is>
-          <t>+0.390</t>
+        <v>774.64</v>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -23725,15 +23725,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>774.52</v>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>+0.230</t>
+        <v>774.91</v>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -23748,15 +23748,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 17:58:25</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>774.29</v>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>774.52</v>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>+0.230</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -23771,15 +23771,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 17:58:25</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>774.36</v>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>-0.860</t>
+        <v>774.29</v>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -23794,15 +23794,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>774.36</v>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>-0.860</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -23817,15 +23817,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 02:48:49</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>774.87</v>
+        <v>775.22</v>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>-0.600</t>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -23840,15 +23840,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 02:48:49</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>775.47</v>
-      </c>
-      <c r="D125" s="11" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>774.87</v>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -23863,15 +23863,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>775.25</v>
+        <v>775.47</v>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>-1.030</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -23886,15 +23886,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>776.28</v>
+        <v>775.25</v>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>-0.280</t>
+          <t>-1.030</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -23909,15 +23909,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 09:25:49</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>776.5599999999999</v>
-      </c>
-      <c r="D128" s="15" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>776.28</v>
+      </c>
+      <c r="D128" s="16" t="inlineStr">
+        <is>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -23932,15 +23932,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 06:48:36</t>
+          <t>2026-09-01 09:25:49</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>776.58</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -23955,15 +23955,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 02:10:52</t>
+          <t>2026-09-01 06:48:36</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>776.63</v>
+        <v>776.58</v>
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>+1.230</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -23978,15 +23978,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 02:10:52</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>775.4</v>
+        <v>776.63</v>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -24001,15 +24001,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>775.22</v>
+        <v>775.4</v>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>-0.700</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -24024,15 +24024,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 08:13:17</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>775.92</v>
-      </c>
-      <c r="D133" s="11" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.22</v>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -24047,15 +24047,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 08:13:17</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>775.85</v>
+        <v>775.92</v>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>-2.850</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -24070,15 +24070,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>778.7</v>
+        <v>775.85</v>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-2.850</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -24093,15 +24093,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>779.1</v>
+        <v>778.7</v>
       </c>
       <c r="D136" s="16" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -24116,15 +24116,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>778.72</v>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>-0.640</t>
+        <v>779.1</v>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -24139,15 +24139,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>779.36</v>
-      </c>
-      <c r="D138" s="15" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>778.72</v>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>-0.640</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -24162,15 +24162,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 04:13:31</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>779.5599999999999</v>
-      </c>
-      <c r="D139" s="11" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>779.36</v>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -24185,15 +24185,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 04:13:31</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>779.39</v>
+        <v>779.5599999999999</v>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -24208,15 +24208,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>779.6</v>
+        <v>779.39</v>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -24231,15 +24231,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>780.03</v>
-      </c>
-      <c r="D142" s="15" t="inlineStr">
-        <is>
-          <t>-0.120</t>
+        <v>779.6</v>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -24254,15 +24254,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 18:53:28</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>780.15</v>
+        <v>780.03</v>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -24277,15 +24277,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 18:53:28</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>780.62</v>
+        <v>780.15</v>
       </c>
       <c r="D144" s="16" t="inlineStr">
         <is>
-          <t>+0.560</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -24300,15 +24300,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>780.0599999999999</v>
-      </c>
-      <c r="D145" s="9" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>780.62</v>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>+0.560</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -24323,15 +24323,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>780.17</v>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>780.0599999999999</v>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -24346,15 +24346,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>780.38</v>
-      </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>780.17</v>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -24369,15 +24369,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 10:07:59</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>780.36</v>
+        <v>780.38</v>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -24392,15 +24392,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 07:52:24</t>
+          <t>2026-08-26 10:07:59</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>780.6</v>
-      </c>
-      <c r="D149" s="11" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>780.36</v>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -24415,15 +24415,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 01:49:35</t>
+          <t>2026-08-26 07:52:24</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>780.4299999999999</v>
-      </c>
-      <c r="D150" s="16" t="inlineStr">
-        <is>
-          <t>+0.080</t>
+        <v>780.6</v>
+      </c>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -24438,15 +24438,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 01:49:35</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>780.35</v>
+        <v>780.4299999999999</v>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -24461,15 +24461,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>780.3099999999999</v>
-      </c>
-      <c r="D152" s="16" t="inlineStr">
-        <is>
-          <t>+0.410</t>
+        <v>780.35</v>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -24484,15 +24484,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:05:53</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>779.9</v>
-      </c>
-      <c r="D153" s="9" t="inlineStr">
-        <is>
-          <t>-0.260</t>
+        <v>780.3099999999999</v>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>+0.410</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -24507,15 +24507,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 21:05:53</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>780.16</v>
-      </c>
-      <c r="D154" s="15" t="inlineStr">
-        <is>
-          <t>-0.230</t>
+        <v>779.9</v>
+      </c>
+      <c r="D154" s="16" t="inlineStr">
+        <is>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -24530,15 +24530,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>780.39</v>
-      </c>
-      <c r="D155" s="11" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>780.16</v>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>-0.230</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -24553,15 +24553,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>780.15</v>
-      </c>
-      <c r="D156" s="16" t="inlineStr">
-        <is>
-          <t>+0.540</t>
+        <v>780.39</v>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -24576,15 +24576,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:26</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>779.61</v>
-      </c>
-      <c r="D157" s="9" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>780.15</v>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>+0.540</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -24599,15 +24599,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:01:55</t>
+          <t>2026-08-25 15:51:26</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>779.65</v>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>779.61</v>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -24622,15 +24622,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 15:01:55</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>779.73</v>
+        <v>779.65</v>
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -24645,15 +24645,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>780.11</v>
-      </c>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>779.73</v>
+      </c>
+      <c r="D160" s="16" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -24668,15 +24668,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>780.4</v>
-      </c>
-      <c r="D161" s="11" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>780.11</v>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -24691,15 +24691,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:57:56</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>780.3099999999999</v>
-      </c>
-      <c r="D162" s="16" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>780.4</v>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -24714,15 +24714,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 06:50:27</t>
+          <t>2026-08-25 09:57:56</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>780.1900000000001</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -24737,15 +24737,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 06:50:27</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>780.1799999999999</v>
+        <v>780.1900000000001</v>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>-0.450</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -24760,15 +24760,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>780.63</v>
-      </c>
-      <c r="D165" s="11" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>780.1799999999999</v>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>-0.450</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -24783,15 +24783,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>780.17</v>
+        <v>780.63</v>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -24806,15 +24806,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>780.61</v>
-      </c>
-      <c r="D167" s="11" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>780.17</v>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -24829,15 +24829,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>780.14</v>
+        <v>780.61</v>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -24852,15 +24852,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>780.23</v>
+        <v>780.14</v>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>-0.530</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -24875,15 +24875,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>780.76</v>
-      </c>
-      <c r="D170" s="15" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>780.23</v>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -24898,15 +24898,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>780.91</v>
+        <v>780.76</v>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -24921,15 +24921,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>781.35</v>
-      </c>
-      <c r="D172" s="15" t="inlineStr">
-        <is>
-          <t>-0.030</t>
+        <v>780.91</v>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -24944,15 +24944,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>781.38</v>
-      </c>
-      <c r="D173" s="11" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>781.35</v>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -24967,15 +24967,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>781.09</v>
+        <v>781.38</v>
       </c>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>-0.350</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -24990,15 +24990,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>781.4400000000001</v>
+        <v>781.09</v>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.350</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -25013,15 +25013,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>781.55</v>
+        <v>781.4400000000001</v>
       </c>
       <c r="D176" s="16" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -25036,15 +25036,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 09:42:15</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>781.23</v>
+        <v>781.55</v>
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -25059,15 +25059,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 10:32:40</t>
+          <t>2026-08-24 09:42:15</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>781.01</v>
+        <v>781.23</v>
       </c>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -25082,15 +25082,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 05:00:11</t>
+          <t>2026-08-22 10:32:40</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>781.11</v>
+        <v>781.01</v>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>-0.180</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -25105,15 +25105,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 02:00:51</t>
+          <t>2026-08-22 05:00:11</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>781.29</v>
-      </c>
-      <c r="D180" s="15" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>781.11</v>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -25128,15 +25128,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-22 02:00:51</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>781.34</v>
-      </c>
-      <c r="D181" s="11" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>781.29</v>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -25151,15 +25151,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>780.79</v>
-      </c>
-      <c r="D182" s="16" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>781.34</v>
+      </c>
+      <c r="D182" s="15" t="inlineStr">
+        <is>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -25174,15 +25174,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>780.6799999999999</v>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
-        <is>
-          <t>-0.610</t>
+        <v>780.79</v>
+      </c>
+      <c r="D183" s="11" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -25197,15 +25197,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>781.29</v>
-      </c>
-      <c r="D184" s="15" t="inlineStr">
-        <is>
-          <t>-1.420</t>
+        <v>780.6799999999999</v>
+      </c>
+      <c r="D184" s="16" t="inlineStr">
+        <is>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -25220,15 +25220,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>782.71</v>
+        <v>781.29</v>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-1.420</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -25243,15 +25243,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>782.95</v>
+        <v>782.71</v>
       </c>
       <c r="D186" s="16" t="inlineStr">
         <is>
-          <t>+1.080</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -25266,15 +25266,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>781.87</v>
-      </c>
-      <c r="D187" s="9" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>782.95</v>
+      </c>
+      <c r="D187" s="11" t="inlineStr">
+        <is>
+          <t>+1.080</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -25289,15 +25289,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>782.25</v>
+        <v>781.87</v>
       </c>
       <c r="D188" s="16" t="inlineStr">
         <is>
-          <t>+0.260</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -25312,15 +25312,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>781.99</v>
+        <v>782.25</v>
       </c>
       <c r="D189" s="11" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -25335,15 +25335,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>781.95</v>
+        <v>781.99</v>
       </c>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -25358,15 +25358,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>781.99</v>
+        <v>781.95</v>
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -25381,15 +25381,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>782.39</v>
+        <v>781.99</v>
       </c>
       <c r="D192" s="16" t="inlineStr">
         <is>
-          <t>+0.360</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -25404,15 +25404,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:13</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>782.03</v>
+        <v>782.39</v>
       </c>
       <c r="D193" s="11" t="inlineStr">
         <is>
-          <t>+0.400</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -25427,15 +25427,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 06:49:01</t>
+          <t>2026-08-21 09:10:13</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>781.63</v>
-      </c>
-      <c r="D194" s="16" t="inlineStr">
-        <is>
-          <t>+0.680</t>
+        <v>782.03</v>
+      </c>
+      <c r="D194" s="15" t="inlineStr">
+        <is>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -25450,15 +25450,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 06:49:01</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>780.95</v>
-      </c>
-      <c r="D195" s="9" t="inlineStr">
-        <is>
-          <t>-0.780</t>
+        <v>781.63</v>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -25473,15 +25473,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>781.73</v>
-      </c>
-      <c r="D196" s="15" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>780.95</v>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -25496,15 +25496,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>781.79</v>
+        <v>781.73</v>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -25519,15 +25519,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>782.1900000000001</v>
+        <v>781.79</v>
       </c>
       <c r="D198" s="16" t="inlineStr">
         <is>
-          <t>+0.150</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -25542,15 +25542,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>782.04</v>
-      </c>
-      <c r="D199" s="9" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>782.1900000000001</v>
+      </c>
+      <c r="D199" s="11" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -25565,15 +25565,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>782.74</v>
+        <v>782.04</v>
       </c>
       <c r="D200" s="16" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -25588,15 +25588,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>782.42</v>
+        <v>782.74</v>
       </c>
       <c r="D201" s="11" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -25611,15 +25611,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>781.95</v>
-      </c>
-      <c r="D202" s="16" t="inlineStr">
-        <is>
-          <t>+0.810</t>
+        <v>782.42</v>
+      </c>
+      <c r="D202" s="15" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -25634,15 +25634,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>781.14</v>
-      </c>
-      <c r="D203" s="9" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.95</v>
+      </c>
+      <c r="D203" s="11" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -25657,15 +25657,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>781.39</v>
+        <v>781.14</v>
       </c>
       <c r="D204" s="16" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -25680,15 +25680,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>781.2</v>
+        <v>781.39</v>
       </c>
       <c r="D205" s="11" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -25703,15 +25703,15 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>781.17</v>
+        <v>781.2</v>
       </c>
       <c r="D206" s="15" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -25726,15 +25726,15 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 10:06:13</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>781.42</v>
+        <v>781.17</v>
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -25749,15 +25749,15 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 07:36:53</t>
+          <t>2026-08-20 10:06:13</t>
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>781.79</v>
+        <v>781.42</v>
       </c>
       <c r="D208" s="16" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -25772,15 +25772,15 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 06:33:42</t>
+          <t>2026-08-20 07:36:53</t>
         </is>
       </c>
       <c r="C209" s="8" t="n">
-        <v>781.77</v>
+        <v>781.79</v>
       </c>
       <c r="D209" s="11" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -25795,15 +25795,15 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 06:33:42</t>
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>781.45</v>
-      </c>
-      <c r="D210" s="16" t="inlineStr">
-        <is>
-          <t>+0.850</t>
+        <v>781.77</v>
+      </c>
+      <c r="D210" s="15" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -25818,15 +25818,15 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
-        <v>780.6</v>
+        <v>781.45</v>
       </c>
       <c r="D211" s="11" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.850</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -25841,15 +25841,15 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>780.12</v>
-      </c>
-      <c r="D212" s="16" t="inlineStr">
-        <is>
-          <t>+1.750</t>
+        <v>780.6</v>
+      </c>
+      <c r="D212" s="15" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -25864,15 +25864,15 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>778.37</v>
+        <v>780.12</v>
       </c>
       <c r="D213" s="11" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>+1.750</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -25887,15 +25887,15 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>778.09</v>
-      </c>
-      <c r="D214" s="16" t="inlineStr">
-        <is>
-          <t>+0.680</t>
+        <v>778.37</v>
+      </c>
+      <c r="D214" s="15" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -25910,15 +25910,15 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>777.41</v>
+        <v>778.09</v>
       </c>
       <c r="D215" s="11" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -25933,15 +25933,15 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>777.3200000000001</v>
-      </c>
-      <c r="D216" s="16" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>777.41</v>
+      </c>
+      <c r="D216" s="15" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -25956,11 +25956,11 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
-        <v>777.1</v>
+        <v>777.3200000000001</v>
       </c>
       <c r="D217" s="11" t="inlineStr">
         <is>
@@ -25979,15 +25979,15 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>776.88</v>
+        <v>777.1</v>
       </c>
       <c r="D218" s="15" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -26002,15 +26002,15 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>776.89</v>
-      </c>
-      <c r="D219" s="11" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>776.88</v>
+      </c>
+      <c r="D219" s="9" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -26025,15 +26025,15 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>776.84</v>
+        <v>776.89</v>
       </c>
       <c r="D220" s="15" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -26048,15 +26048,15 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 09:12:00</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D221" s="11" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.84</v>
+      </c>
+      <c r="D221" s="9" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -26071,15 +26071,15 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 09:12:00</t>
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>776.72</v>
+        <v>776.9</v>
       </c>
       <c r="D222" s="15" t="inlineStr">
         <is>
-          <t>-0.460</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -26094,15 +26094,15 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>777.1799999999999</v>
-      </c>
-      <c r="D223" s="11" t="inlineStr">
-        <is>
-          <t>+0.630</t>
+        <v>776.72</v>
+      </c>
+      <c r="D223" s="9" t="inlineStr">
+        <is>
+          <t>-0.460</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -26117,15 +26117,15 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>776.55</v>
+        <v>777.1799999999999</v>
       </c>
       <c r="D224" s="15" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -26140,15 +26140,15 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:24</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>776.62</v>
-      </c>
-      <c r="D225" s="11" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>776.55</v>
+      </c>
+      <c r="D225" s="9" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -26163,15 +26163,15 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 17:58:24</t>
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>776.53</v>
-      </c>
-      <c r="D226" s="16" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>776.62</v>
+      </c>
+      <c r="D226" s="15" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -26186,15 +26186,15 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>776.36</v>
-      </c>
-      <c r="D227" s="9" t="inlineStr">
-        <is>
-          <t>-0.160</t>
+        <v>776.53</v>
+      </c>
+      <c r="D227" s="11" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -26209,15 +26209,15 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C228" s="6" t="n">
-        <v>776.52</v>
-      </c>
-      <c r="D228" s="15" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>776.36</v>
+      </c>
+      <c r="D228" s="16" t="inlineStr">
+        <is>
+          <t>-0.160</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -26232,15 +26232,15 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>776.53</v>
+        <v>776.52</v>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>-0.390</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
@@ -26255,15 +26255,15 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>776.92</v>
+        <v>776.53</v>
       </c>
       <c r="D230" s="16" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -26278,15 +26278,15 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 10:04:24</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>776.8200000000001</v>
+        <v>776.92</v>
       </c>
       <c r="D231" s="11" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -26301,15 +26301,15 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 07:54:32</t>
+          <t>2026-08-18 10:04:24</t>
         </is>
       </c>
       <c r="C232" s="6" t="n">
-        <v>776.61</v>
+        <v>776.8200000000001</v>
       </c>
       <c r="D232" s="15" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -26324,15 +26324,15 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 05:48:09</t>
+          <t>2026-08-18 07:54:32</t>
         </is>
       </c>
       <c r="C233" s="8" t="n">
-        <v>776.74</v>
-      </c>
-      <c r="D233" s="11" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.61</v>
+      </c>
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
@@ -26347,15 +26347,15 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 05:48:09</t>
         </is>
       </c>
       <c r="C234" s="6" t="n">
-        <v>776.5599999999999</v>
+        <v>776.74</v>
       </c>
       <c r="D234" s="15" t="inlineStr">
         <is>
-          <t>-0.600</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -26370,15 +26370,15 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>777.16</v>
-      </c>
-      <c r="D235" s="11" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>776.5599999999999</v>
+      </c>
+      <c r="D235" s="9" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
@@ -26393,15 +26393,15 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C236" s="6" t="n">
-        <v>776.8099999999999</v>
+        <v>777.16</v>
       </c>
       <c r="D236" s="15" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -26416,15 +26416,15 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:45</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
-        <v>777.21</v>
+        <v>776.8099999999999</v>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
@@ -26439,15 +26439,15 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 21:10:45</t>
         </is>
       </c>
       <c r="C238" s="6" t="n">
-        <v>777.4299999999999</v>
-      </c>
-      <c r="D238" s="15" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>777.21</v>
+      </c>
+      <c r="D238" s="16" t="inlineStr">
+        <is>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -26462,15 +26462,15 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
-        <v>777.52</v>
-      </c>
-      <c r="D239" s="11" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>777.4299999999999</v>
+      </c>
+      <c r="D239" s="9" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
@@ -26485,15 +26485,15 @@
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C240" s="6" t="n">
-        <v>777.5</v>
-      </c>
-      <c r="D240" s="16" t="inlineStr">
-        <is>
-          <t>+0.370</t>
+        <v>777.52</v>
+      </c>
+      <c r="D240" s="15" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -26508,15 +26508,15 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C241" s="8" t="n">
-        <v>777.13</v>
+        <v>777.5</v>
       </c>
       <c r="D241" s="11" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.370</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
@@ -26531,15 +26531,15 @@
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C242" s="6" t="n">
-        <v>777.04</v>
-      </c>
-      <c r="D242" s="16" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>777.13</v>
+      </c>
+      <c r="D242" s="15" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -26554,15 +26554,15 @@
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C243" s="8" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D243" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.04</v>
+      </c>
+      <c r="D243" s="11" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
@@ -26577,15 +26577,15 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C244" s="6" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="D244" s="15" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>776.9</v>
+      </c>
+      <c r="D244" s="16" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -26600,15 +26600,15 @@
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C245" s="8" t="n">
-        <v>776.96</v>
-      </c>
-      <c r="D245" s="11" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>776.91</v>
+      </c>
+      <c r="D245" s="9" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
@@ -26623,15 +26623,15 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 09:21:39</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C246" s="6" t="n">
-        <v>776.84</v>
-      </c>
-      <c r="D246" s="16" t="inlineStr">
-        <is>
-          <t>+0.750</t>
+        <v>776.96</v>
+      </c>
+      <c r="D246" s="15" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
@@ -26646,15 +26646,15 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 09:21:39</t>
         </is>
       </c>
       <c r="C247" s="8" t="n">
-        <v>776.09</v>
-      </c>
-      <c r="D247" s="9" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>776.84</v>
+      </c>
+      <c r="D247" s="11" t="inlineStr">
+        <is>
+          <t>+0.750</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
@@ -26669,15 +26669,15 @@
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C248" s="6" t="n">
-        <v>776.38</v>
+        <v>776.09</v>
       </c>
       <c r="D248" s="16" t="inlineStr">
         <is>
-          <t>+0.570</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -26692,15 +26692,15 @@
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
-        <v>775.8099999999999</v>
+        <v>776.38</v>
       </c>
       <c r="D249" s="11" t="inlineStr">
         <is>
-          <t>+0.770</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
@@ -26715,15 +26715,15 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C250" s="6" t="n">
-        <v>775.04</v>
-      </c>
-      <c r="D250" s="16" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>775.8099999999999</v>
+      </c>
+      <c r="D250" s="15" t="inlineStr">
+        <is>
+          <t>+0.770</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
@@ -26738,15 +26738,15 @@
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C251" s="8" t="n">
-        <v>774.92</v>
+        <v>775.04</v>
       </c>
       <c r="D251" s="11" t="inlineStr">
         <is>
-          <t>+0.360</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
@@ -26761,15 +26761,15 @@
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C252" s="6" t="n">
-        <v>774.5599999999999</v>
-      </c>
-      <c r="D252" s="16" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>774.92</v>
+      </c>
+      <c r="D252" s="15" t="inlineStr">
+        <is>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
@@ -26784,15 +26784,15 @@
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
-        <v>774.4400000000001</v>
-      </c>
-      <c r="D253" s="9" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>774.5599999999999</v>
+      </c>
+      <c r="D253" s="11" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
@@ -26807,15 +26807,15 @@
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C254" s="6" t="n">
-        <v>774.46</v>
+        <v>774.4400000000001</v>
       </c>
       <c r="D254" s="16" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
@@ -26830,15 +26830,15 @@
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C255" s="8" t="n">
-        <v>774.25</v>
+        <v>774.46</v>
       </c>
       <c r="D255" s="11" t="inlineStr">
         <is>
-          <t>+0.310</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
@@ -26853,15 +26853,15 @@
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 10:39:02</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C256" s="6" t="n">
-        <v>773.9400000000001</v>
-      </c>
-      <c r="D256" s="16" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>774.25</v>
+      </c>
+      <c r="D256" s="15" t="inlineStr">
+        <is>
+          <t>+0.310</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
@@ -26876,15 +26876,15 @@
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 08:05:13</t>
+          <t>2026-08-14 10:39:02</t>
         </is>
       </c>
       <c r="C257" s="8" t="n">
-        <v>773.9</v>
+        <v>773.9400000000001</v>
       </c>
       <c r="D257" s="11" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
@@ -26899,15 +26899,15 @@
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 07:24:16</t>
+          <t>2026-08-14 08:05:13</t>
         </is>
       </c>
       <c r="C258" s="6" t="n">
-        <v>773.73</v>
-      </c>
-      <c r="D258" s="16" t="inlineStr">
-        <is>
-          <t>+0.200</t>
+        <v>773.9</v>
+      </c>
+      <c r="D258" s="15" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
@@ -26922,15 +26922,15 @@
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 07:24:16</t>
         </is>
       </c>
       <c r="C259" s="8" t="n">
-        <v>773.53</v>
-      </c>
-      <c r="D259" s="9" t="inlineStr">
-        <is>
-          <t>-0.790</t>
+        <v>773.73</v>
+      </c>
+      <c r="D259" s="11" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
@@ -26945,15 +26945,15 @@
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C260" s="6" t="n">
-        <v>774.3200000000001</v>
+        <v>773.53</v>
       </c>
       <c r="D260" s="16" t="inlineStr">
         <is>
-          <t>+0.570</t>
+          <t>-0.790</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
@@ -26968,15 +26968,15 @@
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C261" s="8" t="n">
-        <v>773.75</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="D261" s="11" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
@@ -26991,15 +26991,15 @@
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C262" s="6" t="n">
-        <v>773.7</v>
-      </c>
-      <c r="D262" s="16" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>773.75</v>
+      </c>
+      <c r="D262" s="15" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
@@ -27014,15 +27014,15 @@
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C263" s="8" t="n">
-        <v>773.58</v>
+        <v>773.7</v>
       </c>
       <c r="D263" s="11" t="inlineStr">
         <is>
-          <t>+0.250</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
@@ -27037,15 +27037,15 @@
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C264" s="6" t="n">
-        <v>773.33</v>
+        <v>773.58</v>
       </c>
       <c r="D264" s="15" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E264" s="6" t="inlineStr">
@@ -27060,15 +27060,15 @@
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C265" s="8" t="n">
-        <v>773.39</v>
-      </c>
-      <c r="D265" s="11" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>773.33</v>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
@@ -27083,15 +27083,15 @@
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C266" s="6" t="n">
-        <v>773.11</v>
+        <v>773.39</v>
       </c>
       <c r="D266" s="15" t="inlineStr">
         <is>
-          <t>-0.130</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E266" s="6" t="inlineStr">
@@ -27106,15 +27106,15 @@
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C267" s="8" t="n">
-        <v>773.24</v>
+        <v>773.11</v>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>-0.340</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
@@ -27129,15 +27129,15 @@
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C268" s="6" t="n">
-        <v>773.58</v>
-      </c>
-      <c r="D268" s="15" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>773.24</v>
+      </c>
+      <c r="D268" s="16" t="inlineStr">
+        <is>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E268" s="6" t="inlineStr">
@@ -27152,15 +27152,15 @@
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C269" s="8" t="n">
-        <v>773.64</v>
+        <v>773.58</v>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
@@ -27175,15 +27175,15 @@
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C270" s="6" t="n">
-        <v>774.11</v>
-      </c>
-      <c r="D270" s="15" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>773.64</v>
+      </c>
+      <c r="D270" s="16" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E270" s="6" t="inlineStr">
@@ -27198,15 +27198,15 @@
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C271" s="8" t="n">
-        <v>774.3</v>
+        <v>774.11</v>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>-0.740</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
@@ -27221,15 +27221,15 @@
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C272" s="6" t="n">
-        <v>775.04</v>
+        <v>774.3</v>
       </c>
       <c r="D272" s="16" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>-0.740</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
@@ -27244,15 +27244,15 @@
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C273" s="8" t="n">
-        <v>774.9</v>
+        <v>775.04</v>
       </c>
       <c r="D273" s="11" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
@@ -27267,15 +27267,15 @@
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C274" s="6" t="n">
-        <v>774.66</v>
-      </c>
-      <c r="D274" s="16" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>774.9</v>
+      </c>
+      <c r="D274" s="15" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
@@ -27290,15 +27290,15 @@
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C275" s="8" t="n">
-        <v>774.34</v>
+        <v>774.66</v>
       </c>
       <c r="D275" s="11" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
@@ -27313,15 +27313,15 @@
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C276" s="6" t="n">
-        <v>774.15</v>
+        <v>774.34</v>
       </c>
       <c r="D276" s="15" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
@@ -27336,15 +27336,15 @@
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 13:53:42</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C277" s="8" t="n">
-        <v>774.25</v>
+        <v>774.15</v>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
@@ -27359,15 +27359,15 @@
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 13:53:42</t>
         </is>
       </c>
       <c r="C278" s="6" t="n">
-        <v>774.3200000000001</v>
-      </c>
-      <c r="D278" s="15" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>774.25</v>
+      </c>
+      <c r="D278" s="16" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
@@ -27382,15 +27382,15 @@
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C279" s="8" t="n">
-        <v>774.74</v>
-      </c>
-      <c r="D279" s="11" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>774.3200000000001</v>
+      </c>
+      <c r="D279" s="9" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
@@ -27405,15 +27405,15 @@
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 01:28:47</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C280" s="6" t="n">
-        <v>774.5</v>
-      </c>
-      <c r="D280" s="16" t="inlineStr">
-        <is>
-          <t>+0.130</t>
+        <v>774.74</v>
+      </c>
+      <c r="D280" s="15" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E280" s="6" t="inlineStr">
@@ -27428,15 +27428,15 @@
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 01:28:47</t>
         </is>
       </c>
       <c r="C281" s="8" t="n">
-        <v>774.37</v>
-      </c>
-      <c r="D281" s="9" t="inlineStr">
-        <is>
-          <t>-0.340</t>
+        <v>774.5</v>
+      </c>
+      <c r="D281" s="11" t="inlineStr">
+        <is>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
@@ -27451,15 +27451,15 @@
       </c>
       <c r="B282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C282" s="6" t="n">
-        <v>774.71</v>
+        <v>774.37</v>
       </c>
       <c r="D282" s="16" t="inlineStr">
         <is>
-          <t>+1.160</t>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
@@ -27474,15 +27474,15 @@
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C283" s="8" t="n">
-        <v>773.55</v>
-      </c>
-      <c r="D283" s="9" t="inlineStr">
-        <is>
-          <t>-0.520</t>
+        <v>774.71</v>
+      </c>
+      <c r="D283" s="11" t="inlineStr">
+        <is>
+          <t>+1.160</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
@@ -27497,15 +27497,15 @@
       </c>
       <c r="B284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C284" s="6" t="n">
-        <v>774.0700000000001</v>
-      </c>
-      <c r="D284" s="15" t="inlineStr">
-        <is>
-          <t>-0.690</t>
+        <v>773.55</v>
+      </c>
+      <c r="D284" s="16" t="inlineStr">
+        <is>
+          <t>-0.520</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
@@ -27520,15 +27520,15 @@
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C285" s="8" t="n">
-        <v>774.76</v>
+        <v>774.0700000000001</v>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.690</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
@@ -27543,15 +27543,15 @@
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C286" s="6" t="n">
-        <v>775.3099999999999</v>
-      </c>
-      <c r="D286" s="15" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>774.76</v>
+      </c>
+      <c r="D286" s="16" t="inlineStr">
+        <is>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
@@ -27566,15 +27566,15 @@
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C287" s="8" t="n">
-        <v>775.46</v>
+        <v>775.3099999999999</v>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
@@ -27589,15 +27589,15 @@
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C288" s="6" t="n">
-        <v>775.84</v>
-      </c>
-      <c r="D288" s="15" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>775.46</v>
+      </c>
+      <c r="D288" s="16" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
@@ -27612,15 +27612,15 @@
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 08:05:33</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C289" s="8" t="n">
-        <v>775.9</v>
-      </c>
-      <c r="D289" s="11" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.84</v>
+      </c>
+      <c r="D289" s="9" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
@@ -27635,15 +27635,15 @@
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 08:05:33</t>
         </is>
       </c>
       <c r="C290" s="6" t="n">
-        <v>775.83</v>
-      </c>
-      <c r="D290" s="16" t="inlineStr">
-        <is>
-          <t>+0.630</t>
+        <v>775.9</v>
+      </c>
+      <c r="D290" s="15" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
@@ -27658,15 +27658,15 @@
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C291" s="8" t="n">
-        <v>775.2</v>
-      </c>
-      <c r="D291" s="9" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>775.83</v>
+      </c>
+      <c r="D291" s="11" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
@@ -27681,15 +27681,15 @@
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C292" s="6" t="n">
-        <v>775.28</v>
+        <v>775.2</v>
       </c>
       <c r="D292" s="16" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
@@ -27704,15 +27704,15 @@
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C293" s="8" t="n">
-        <v>775.12</v>
+        <v>775.28</v>
       </c>
       <c r="D293" s="11" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
@@ -27727,13 +27727,13 @@
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C294" s="6" t="n">
-        <v>775.09</v>
-      </c>
-      <c r="D294" s="16" t="inlineStr">
+        <v>775.12</v>
+      </c>
+      <c r="D294" s="15" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -27750,15 +27750,15 @@
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 18:37:13</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C295" s="8" t="n">
-        <v>775.0599999999999</v>
+        <v>775.09</v>
       </c>
       <c r="D295" s="11" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
@@ -27773,15 +27773,15 @@
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 18:37:13</t>
         </is>
       </c>
       <c r="C296" s="6" t="n">
-        <v>774.58</v>
-      </c>
-      <c r="D296" s="16" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>775.0599999999999</v>
+      </c>
+      <c r="D296" s="15" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E296" s="6" t="inlineStr">
@@ -27796,15 +27796,15 @@
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C297" s="8" t="n">
-        <v>774.29</v>
+        <v>774.58</v>
       </c>
       <c r="D297" s="11" t="inlineStr">
         <is>
-          <t>+0.490</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
@@ -27819,15 +27819,15 @@
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C298" s="6" t="n">
-        <v>773.8</v>
+        <v>774.29</v>
       </c>
       <c r="D298" s="15" t="inlineStr">
         <is>
-          <t>-0.590</t>
+          <t>+0.490</t>
         </is>
       </c>
       <c r="E298" s="6" t="inlineStr">
@@ -27842,14 +27842,37 @@
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C299" s="8" t="n">
+        <v>773.8</v>
+      </c>
+      <c r="D299" s="9" t="inlineStr">
+        <is>
+          <t>-0.590</t>
+        </is>
+      </c>
+      <c r="E299" s="8" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="6" t="n">
+        <v>296</v>
+      </c>
+      <c r="B300" s="6" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C299" s="8" t="n">
+      <c r="C300" s="6" t="n">
         <v>774.39</v>
       </c>
-      <c r="D299" s="8" t="inlineStr"/>
-      <c r="E299" s="8" t="inlineStr">
+      <c r="D300" s="6" t="inlineStr"/>
+      <c r="E300" s="6" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>
@@ -27956,7 +27979,7 @@
       <c r="C6" s="6" t="n">
         <v>669.72</v>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>+0.490</t>
         </is>
@@ -28002,7 +28025,7 @@
       <c r="C8" s="6" t="n">
         <v>668.73</v>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>+0.140</t>
         </is>
@@ -28048,7 +28071,7 @@
       <c r="C10" s="6" t="n">
         <v>668.45</v>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>-0.350</t>
         </is>
@@ -28094,7 +28117,7 @@
       <c r="C12" s="6" t="n">
         <v>668.47</v>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>-0.240</t>
         </is>
@@ -28140,7 +28163,7 @@
       <c r="C14" s="6" t="n">
         <v>669.23</v>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>-0.110</t>
         </is>
@@ -28186,7 +28209,7 @@
       <c r="C16" s="6" t="n">
         <v>669.48</v>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>-0.450</t>
         </is>
@@ -28232,7 +28255,7 @@
       <c r="C18" s="6" t="n">
         <v>669.4299999999999</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -28278,7 +28301,7 @@
       <c r="C20" s="6" t="n">
         <v>669.41</v>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>+0.230</t>
         </is>
@@ -28324,7 +28347,7 @@
       <c r="C22" s="6" t="n">
         <v>669.24</v>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>+0.380</t>
         </is>
@@ -28370,7 +28393,7 @@
       <c r="C24" s="6" t="n">
         <v>668.79</v>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>+0.180</t>
         </is>
@@ -28416,7 +28439,7 @@
       <c r="C26" s="6" t="n">
         <v>668.17</v>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>+0.040</t>
         </is>
@@ -28462,7 +28485,7 @@
       <c r="C28" s="6" t="n">
         <v>668.12</v>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>+0.330</t>
         </is>
@@ -28508,7 +28531,7 @@
       <c r="C30" s="6" t="n">
         <v>667.65</v>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -28554,7 +28577,7 @@
       <c r="C32" s="6" t="n">
         <v>667.76</v>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>-0.130</t>
         </is>
@@ -28600,7 +28623,7 @@
       <c r="C34" s="6" t="n">
         <v>668.03</v>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -28646,7 +28669,7 @@
       <c r="C36" s="6" t="n">
         <v>667.89</v>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>-0.220</t>
         </is>
@@ -28692,7 +28715,7 @@
       <c r="C38" s="6" t="n">
         <v>668.74</v>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -28738,7 +28761,7 @@
       <c r="C40" s="6" t="n">
         <v>668.95</v>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -28784,7 +28807,7 @@
       <c r="C42" s="6" t="n">
         <v>669.03</v>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>+0.270</t>
         </is>
@@ -28830,7 +28853,7 @@
       <c r="C44" s="6" t="n">
         <v>668.77</v>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>-0.050</t>
         </is>
@@ -28876,7 +28899,7 @@
       <c r="C46" s="6" t="n">
         <v>669.1</v>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>-0.190</t>
         </is>
@@ -28922,7 +28945,7 @@
       <c r="C48" s="6" t="n">
         <v>669.3099999999999</v>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>-0.080</t>
         </is>
@@ -28968,7 +28991,7 @@
       <c r="C50" s="6" t="n">
         <v>669.17</v>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>+0.150</t>
         </is>
@@ -29014,7 +29037,7 @@
       <c r="C52" s="6" t="n">
         <v>669.05</v>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -29060,7 +29083,7 @@
       <c r="C54" s="6" t="n">
         <v>668.85</v>
       </c>
-      <c r="D54" s="15" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -29106,7 +29129,7 @@
       <c r="C56" s="6" t="n">
         <v>668.92</v>
       </c>
-      <c r="D56" s="15" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
@@ -29152,7 +29175,7 @@
       <c r="C58" s="6" t="n">
         <v>669.34</v>
       </c>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -29198,7 +29221,7 @@
       <c r="C60" s="6" t="n">
         <v>668.88</v>
       </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="D60" s="15" t="inlineStr">
         <is>
           <t>+0.120</t>
         </is>
@@ -29244,7 +29267,7 @@
       <c r="C62" s="6" t="n">
         <v>668.91</v>
       </c>
-      <c r="D62" s="15" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>-0.060</t>
         </is>
@@ -29290,7 +29313,7 @@
       <c r="C64" s="6" t="n">
         <v>668.78</v>
       </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
@@ -29336,7 +29359,7 @@
       <c r="C66" s="6" t="n">
         <v>668.88</v>
       </c>
-      <c r="D66" s="15" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>-0.260</t>
         </is>
@@ -29382,7 +29405,7 @@
       <c r="C68" s="6" t="n">
         <v>669.16</v>
       </c>
-      <c r="D68" s="15" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -29428,7 +29451,7 @@
       <c r="C70" s="6" t="n">
         <v>669.2</v>
       </c>
-      <c r="D70" s="15" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -29474,7 +29497,7 @@
       <c r="C72" s="6" t="n">
         <v>669.22</v>
       </c>
-      <c r="D72" s="15" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -29520,7 +29543,7 @@
       <c r="C74" s="6" t="n">
         <v>669.3099999999999</v>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="D74" s="15" t="inlineStr">
         <is>
           <t>+0.060</t>
         </is>
@@ -29566,7 +29589,7 @@
       <c r="C76" s="6" t="n">
         <v>669.2</v>
       </c>
-      <c r="D76" s="15" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -29612,7 +29635,7 @@
       <c r="C78" s="6" t="n">
         <v>669.78</v>
       </c>
-      <c r="D78" s="15" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
@@ -29658,7 +29681,7 @@
       <c r="C80" s="6" t="n">
         <v>669.96</v>
       </c>
-      <c r="D80" s="15" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -29704,7 +29727,7 @@
       <c r="C82" s="6" t="n">
         <v>669.9299999999999</v>
       </c>
-      <c r="D82" s="15" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -29750,7 +29773,7 @@
       <c r="C84" s="6" t="n">
         <v>670.04</v>
       </c>
-      <c r="D84" s="15" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
         <is>
           <t>-0.210</t>
         </is>
@@ -29796,7 +29819,7 @@
       <c r="C86" s="6" t="n">
         <v>670.38</v>
       </c>
-      <c r="D86" s="16" t="inlineStr">
+      <c r="D86" s="15" t="inlineStr">
         <is>
           <t>+0.190</t>
         </is>
@@ -29842,7 +29865,7 @@
       <c r="C88" s="6" t="n">
         <v>670.2</v>
       </c>
-      <c r="D88" s="15" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>-0.150</t>
         </is>
@@ -29888,7 +29911,7 @@
       <c r="C90" s="6" t="n">
         <v>670.24</v>
       </c>
-      <c r="D90" s="16" t="inlineStr">
+      <c r="D90" s="15" t="inlineStr">
         <is>
           <t>+0.140</t>
         </is>
@@ -29934,7 +29957,7 @@
       <c r="C92" s="6" t="n">
         <v>670.22</v>
       </c>
-      <c r="D92" s="15" t="inlineStr">
+      <c r="D92" s="16" t="inlineStr">
         <is>
           <t>-0.920</t>
         </is>
@@ -29980,7 +30003,7 @@
       <c r="C94" s="6" t="n">
         <v>670.21</v>
       </c>
-      <c r="D94" s="16" t="inlineStr">
+      <c r="D94" s="15" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -30026,7 +30049,7 @@
       <c r="C96" s="6" t="n">
         <v>670.13</v>
       </c>
-      <c r="D96" s="15" t="inlineStr">
+      <c r="D96" s="16" t="inlineStr">
         <is>
           <t>-0.110</t>
         </is>
@@ -30072,7 +30095,7 @@
       <c r="C98" s="6" t="n">
         <v>670.42</v>
       </c>
-      <c r="D98" s="16" t="inlineStr">
+      <c r="D98" s="15" t="inlineStr">
         <is>
           <t>+0.080</t>
         </is>
@@ -30118,7 +30141,7 @@
       <c r="C100" s="6" t="n">
         <v>670.1900000000001</v>
       </c>
-      <c r="D100" s="16" t="inlineStr">
+      <c r="D100" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -30164,7 +30187,7 @@
       <c r="C102" s="6" t="n">
         <v>670.27</v>
       </c>
-      <c r="D102" s="16" t="inlineStr">
+      <c r="D102" s="15" t="inlineStr">
         <is>
           <t>+0.050</t>
         </is>
@@ -30210,7 +30233,7 @@
       <c r="C104" s="6" t="n">
         <v>670.26</v>
       </c>
-      <c r="D104" s="16" t="inlineStr">
+      <c r="D104" s="15" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -30256,7 +30279,7 @@
       <c r="C106" s="6" t="n">
         <v>670.11</v>
       </c>
-      <c r="D106" s="16" t="inlineStr">
+      <c r="D106" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -30302,7 +30325,7 @@
       <c r="C108" s="6" t="n">
         <v>670.2</v>
       </c>
-      <c r="D108" s="15" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
         <is>
           <t>-0.200</t>
         </is>
@@ -30348,7 +30371,7 @@
       <c r="C110" s="6" t="n">
         <v>670.47</v>
       </c>
-      <c r="D110" s="15" t="inlineStr">
+      <c r="D110" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -30394,7 +30417,7 @@
       <c r="C112" s="6" t="n">
         <v>670.51</v>
       </c>
-      <c r="D112" s="16" t="inlineStr">
+      <c r="D112" s="15" t="inlineStr">
         <is>
           <t>+0.200</t>
         </is>
@@ -30440,7 +30463,7 @@
       <c r="C114" s="6" t="n">
         <v>670.34</v>
       </c>
-      <c r="D114" s="15" t="inlineStr">
+      <c r="D114" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -30486,7 +30509,7 @@
       <c r="C116" s="6" t="n">
         <v>670.34</v>
       </c>
-      <c r="D116" s="15" t="inlineStr">
+      <c r="D116" s="16" t="inlineStr">
         <is>
           <t>-0.090</t>
         </is>
@@ -30532,7 +30555,7 @@
       <c r="C118" s="6" t="n">
         <v>670.46</v>
       </c>
-      <c r="D118" s="16" t="inlineStr">
+      <c r="D118" s="15" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -30578,7 +30601,7 @@
       <c r="C120" s="6" t="n">
         <v>670.45</v>
       </c>
-      <c r="D120" s="15" t="inlineStr">
+      <c r="D120" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -30624,7 +30647,7 @@
       <c r="C122" s="6" t="n">
         <v>670.4400000000001</v>
       </c>
-      <c r="D122" s="15" t="inlineStr">
+      <c r="D122" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -30670,7 +30693,7 @@
       <c r="C124" s="6" t="n">
         <v>670.48</v>
       </c>
-      <c r="D124" s="16" t="inlineStr">
+      <c r="D124" s="15" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -30716,7 +30739,7 @@
       <c r="C126" s="6" t="n">
         <v>670.25</v>
       </c>
-      <c r="D126" s="15" t="inlineStr">
+      <c r="D126" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -30762,7 +30785,7 @@
       <c r="C128" s="6" t="n">
         <v>670.23</v>
       </c>
-      <c r="D128" s="16" t="inlineStr">
+      <c r="D128" s="15" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -30808,7 +30831,7 @@
       <c r="C130" s="6" t="n">
         <v>670.1799999999999</v>
       </c>
-      <c r="D130" s="16" t="inlineStr">
+      <c r="D130" s="15" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -30854,7 +30877,7 @@
       <c r="C132" s="6" t="n">
         <v>670.1799999999999</v>
       </c>
-      <c r="D132" s="15" t="inlineStr">
+      <c r="D132" s="16" t="inlineStr">
         <is>
           <t>-0.100</t>
         </is>
@@ -30900,7 +30923,7 @@
       <c r="C134" s="6" t="n">
         <v>670.29</v>
       </c>
-      <c r="D134" s="16" t="inlineStr">
+      <c r="D134" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -30946,7 +30969,7 @@
       <c r="C136" s="6" t="n">
         <v>670.3099999999999</v>
       </c>
-      <c r="D136" s="15" t="inlineStr">
+      <c r="D136" s="16" t="inlineStr">
         <is>
           <t>-0.140</t>
         </is>
@@ -30992,7 +31015,7 @@
       <c r="C138" s="6" t="n">
         <v>670.62</v>
       </c>
-      <c r="D138" s="16" t="inlineStr">
+      <c r="D138" s="15" t="inlineStr">
         <is>
           <t>+0.120</t>
         </is>
@@ -31038,7 +31061,7 @@
       <c r="C140" s="6" t="n">
         <v>670.4400000000001</v>
       </c>
-      <c r="D140" s="15" t="inlineStr">
+      <c r="D140" s="16" t="inlineStr">
         <is>
           <t>-0.040</t>
         </is>
@@ -31084,7 +31107,7 @@
       <c r="C142" s="6" t="n">
         <v>670.4</v>
       </c>
-      <c r="D142" s="16" t="inlineStr">
+      <c r="D142" s="15" t="inlineStr">
         <is>
           <t>+0.140</t>
         </is>
@@ -31130,7 +31153,7 @@
       <c r="C144" s="6" t="n">
         <v>670.51</v>
       </c>
-      <c r="D144" s="15" t="inlineStr">
+      <c r="D144" s="16" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -31176,7 +31199,7 @@
       <c r="C146" s="6" t="n">
         <v>670.62</v>
       </c>
-      <c r="D146" s="16" t="inlineStr">
+      <c r="D146" s="15" t="inlineStr">
         <is>
           <t>+0.060</t>
         </is>
@@ -31222,7 +31245,7 @@
       <c r="C148" s="6" t="n">
         <v>670.59</v>
       </c>
-      <c r="D148" s="16" t="inlineStr">
+      <c r="D148" s="15" t="inlineStr">
         <is>
           <t>+0.070</t>
         </is>
@@ -31268,7 +31291,7 @@
       <c r="C150" s="6" t="n">
         <v>670.53</v>
       </c>
-      <c r="D150" s="15" t="inlineStr">
+      <c r="D150" s="16" t="inlineStr">
         <is>
           <t>-0.530</t>
         </is>
@@ -31314,7 +31337,7 @@
       <c r="C152" s="6" t="n">
         <v>671.0700000000001</v>
       </c>
-      <c r="D152" s="15" t="inlineStr">
+      <c r="D152" s="16" t="inlineStr">
         <is>
           <t>-0.570</t>
         </is>
@@ -31360,7 +31383,7 @@
       <c r="C154" s="6" t="n">
         <v>671.88</v>
       </c>
-      <c r="D154" s="15" t="inlineStr">
+      <c r="D154" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -31406,7 +31429,7 @@
       <c r="C156" s="6" t="n">
         <v>672.05</v>
       </c>
-      <c r="D156" s="16" t="inlineStr">
+      <c r="D156" s="15" t="inlineStr">
         <is>
           <t>+0.180</t>
         </is>
@@ -31452,7 +31475,7 @@
       <c r="C158" s="6" t="n">
         <v>672.09</v>
       </c>
-      <c r="D158" s="15" t="inlineStr">
+      <c r="D158" s="16" t="inlineStr">
         <is>
           <t>-0.120</t>
         </is>
@@ -31498,7 +31521,7 @@
       <c r="C160" s="6" t="n">
         <v>672.14</v>
       </c>
-      <c r="D160" s="15" t="inlineStr">
+      <c r="D160" s="16" t="inlineStr">
         <is>
           <t>-0.060</t>
         </is>
@@ -31544,7 +31567,7 @@
       <c r="C162" s="6" t="n">
         <v>672.47</v>
       </c>
-      <c r="D162" s="15" t="inlineStr">
+      <c r="D162" s="16" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -31590,7 +31613,7 @@
       <c r="C164" s="6" t="n">
         <v>672.53</v>
       </c>
-      <c r="D164" s="16" t="inlineStr">
+      <c r="D164" s="15" t="inlineStr">
         <is>
           <t>+0.170</t>
         </is>
@@ -31636,7 +31659,7 @@
       <c r="C166" s="6" t="n">
         <v>672.37</v>
       </c>
-      <c r="D166" s="15" t="inlineStr">
+      <c r="D166" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -31682,7 +31705,7 @@
       <c r="C168" s="6" t="n">
         <v>672.54</v>
       </c>
-      <c r="D168" s="16" t="inlineStr">
+      <c r="D168" s="15" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -31728,7 +31751,7 @@
       <c r="C170" s="6" t="n">
         <v>672.41</v>
       </c>
-      <c r="D170" s="16" t="inlineStr">
+      <c r="D170" s="15" t="inlineStr">
         <is>
           <t>+0.200</t>
         </is>
@@ -31774,7 +31797,7 @@
       <c r="C172" s="6" t="n">
         <v>672.17</v>
       </c>
-      <c r="D172" s="16" t="inlineStr">
+      <c r="D172" s="15" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -31820,7 +31843,7 @@
       <c r="C174" s="6" t="n">
         <v>671.9400000000001</v>
       </c>
-      <c r="D174" s="15" t="inlineStr">
+      <c r="D174" s="16" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -31866,7 +31889,7 @@
       <c r="C176" s="6" t="n">
         <v>672.02</v>
       </c>
-      <c r="D176" s="15" t="inlineStr">
+      <c r="D176" s="16" t="inlineStr">
         <is>
           <t>-0.200</t>
         </is>
@@ -31912,7 +31935,7 @@
       <c r="C178" s="6" t="n">
         <v>672.26</v>
       </c>
-      <c r="D178" s="15" t="inlineStr">
+      <c r="D178" s="16" t="inlineStr">
         <is>
           <t>-0.100</t>
         </is>
@@ -31958,7 +31981,7 @@
       <c r="C180" s="6" t="n">
         <v>672.24</v>
       </c>
-      <c r="D180" s="16" t="inlineStr">
+      <c r="D180" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -32004,7 +32027,7 @@
       <c r="C182" s="6" t="n">
         <v>672.36</v>
       </c>
-      <c r="D182" s="16" t="inlineStr">
+      <c r="D182" s="15" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -32050,7 +32073,7 @@
       <c r="C184" s="6" t="n">
         <v>672.24</v>
       </c>
-      <c r="D184" s="15" t="inlineStr">
+      <c r="D184" s="16" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -32096,7 +32119,7 @@
       <c r="C186" s="6" t="n">
         <v>672.3</v>
       </c>
-      <c r="D186" s="15" t="inlineStr">
+      <c r="D186" s="16" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
@@ -32142,7 +32165,7 @@
       <c r="C188" s="6" t="n">
         <v>672.5</v>
       </c>
-      <c r="D188" s="16" t="inlineStr">
+      <c r="D188" s="15" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -32188,7 +32211,7 @@
       <c r="C190" s="6" t="n">
         <v>672.54</v>
       </c>
-      <c r="D190" s="16" t="inlineStr">
+      <c r="D190" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -32234,7 +32257,7 @@
       <c r="C192" s="6" t="n">
         <v>672.35</v>
       </c>
-      <c r="D192" s="15" t="inlineStr">
+      <c r="D192" s="16" t="inlineStr">
         <is>
           <t>-0.080</t>
         </is>
@@ -32280,7 +32303,7 @@
       <c r="C194" s="6" t="n">
         <v>672.46</v>
       </c>
-      <c r="D194" s="15" t="inlineStr">
+      <c r="D194" s="16" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
@@ -32326,7 +32349,7 @@
       <c r="C196" s="6" t="n">
         <v>672.5700000000001</v>
       </c>
-      <c r="D196" s="16" t="inlineStr">
+      <c r="D196" s="15" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -32372,7 +32395,7 @@
       <c r="C198" s="6" t="n">
         <v>672.54</v>
       </c>
-      <c r="D198" s="16" t="inlineStr">
+      <c r="D198" s="15" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -32418,7 +32441,7 @@
       <c r="C200" s="6" t="n">
         <v>672.61</v>
       </c>
-      <c r="D200" s="16" t="inlineStr">
+      <c r="D200" s="15" t="inlineStr">
         <is>
           <t>+0.060</t>
         </is>
@@ -32464,7 +32487,7 @@
       <c r="C202" s="6" t="n">
         <v>672.5</v>
       </c>
-      <c r="D202" s="16" t="inlineStr">
+      <c r="D202" s="15" t="inlineStr">
         <is>
           <t>+0.160</t>
         </is>
@@ -32510,7 +32533,7 @@
       <c r="C204" s="6" t="n">
         <v>672.33</v>
       </c>
-      <c r="D204" s="16" t="inlineStr">
+      <c r="D204" s="15" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -32556,7 +32579,7 @@
       <c r="C206" s="6" t="n">
         <v>672.41</v>
       </c>
-      <c r="D206" s="15" t="inlineStr">
+      <c r="D206" s="16" t="inlineStr">
         <is>
           <t>-0.250</t>
         </is>
@@ -32602,7 +32625,7 @@
       <c r="C208" s="6" t="n">
         <v>672.78</v>
       </c>
-      <c r="D208" s="16" t="inlineStr">
+      <c r="D208" s="15" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -32648,7 +32671,7 @@
       <c r="C210" s="6" t="n">
         <v>672.71</v>
       </c>
-      <c r="D210" s="16" t="inlineStr">
+      <c r="D210" s="15" t="inlineStr">
         <is>
           <t>+0.040</t>
         </is>
@@ -32694,7 +32717,7 @@
       <c r="C212" s="6" t="n">
         <v>672.59</v>
       </c>
-      <c r="D212" s="15" t="inlineStr">
+      <c r="D212" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -32740,7 +32763,7 @@
       <c r="C214" s="6" t="n">
         <v>672.8200000000001</v>
       </c>
-      <c r="D214" s="15" t="inlineStr">
+      <c r="D214" s="16" t="inlineStr">
         <is>
           <t>-0.420</t>
         </is>
@@ -32786,7 +32809,7 @@
       <c r="C216" s="6" t="n">
         <v>672.9</v>
       </c>
-      <c r="D216" s="15" t="inlineStr">
+      <c r="D216" s="16" t="inlineStr">
         <is>
           <t>-0.140</t>
         </is>
@@ -32832,7 +32855,7 @@
       <c r="C218" s="6" t="n">
         <v>673.03</v>
       </c>
-      <c r="D218" s="16" t="inlineStr">
+      <c r="D218" s="15" t="inlineStr">
         <is>
           <t>+0.240</t>
         </is>
@@ -32878,7 +32901,7 @@
       <c r="C220" s="6" t="n">
         <v>673.03</v>
       </c>
-      <c r="D220" s="16" t="inlineStr">
+      <c r="D220" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -32924,7 +32947,7 @@
       <c r="C222" s="6" t="n">
         <v>673.01</v>
       </c>
-      <c r="D222" s="15" t="inlineStr">
+      <c r="D222" s="16" t="inlineStr">
         <is>
           <t>-0.080</t>
         </is>
@@ -32970,7 +32993,7 @@
       <c r="C224" s="6" t="n">
         <v>673.11</v>
       </c>
-      <c r="D224" s="16" t="inlineStr">
+      <c r="D224" s="15" t="inlineStr">
         <is>
           <t>+0.140</t>
         </is>
@@ -33016,7 +33039,7 @@
       <c r="C226" s="6" t="n">
         <v>672.87</v>
       </c>
-      <c r="D226" s="16" t="inlineStr">
+      <c r="D226" s="15" t="inlineStr">
         <is>
           <t>+0.130</t>
         </is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 23:55:30</t>
+          <t>更新时间: 2026-10-08 04:55:41</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>746.39</v>
+        <v>747.61</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 23:55:26</t>
+          <t>2026-10-08 04:55:36</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E311"/>
+  <dimension ref="A1:E312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -21411,7 +21411,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 746.39 | 最高: 782.950 | 最低: 746.390 | 总记录数: 307</t>
+          <t>最新价: 747.61 | 最高: 782.950 | 最低: 746.390 | 总记录数: 308</t>
         </is>
       </c>
     </row>
@@ -21448,15 +21448,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07 23:55:26</t>
+          <t>2026-10-08 04:55:36</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>746.39</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>-3.090</t>
+        <v>747.61</v>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>+1.220</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -21471,15 +21471,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 16:54:58</t>
+          <t>2026-10-07 23:55:26</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>749.48</v>
+        <v>746.39</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-1.210</t>
+          <t>-3.090</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -21494,15 +21494,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07 10:22:51</t>
+          <t>2026-10-07 16:54:58</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>750.6900000000001</v>
+        <v>749.48</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>-1.090</t>
+          <t>-1.210</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -21517,15 +21517,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 07:12:13</t>
+          <t>2026-10-07 10:22:51</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>751.78</v>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>750.6900000000001</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>-1.090</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -21540,15 +21540,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07 03:32:01</t>
+          <t>2026-10-07 07:12:13</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>751.53</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>751.78</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -21563,15 +21563,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06 22:12:22</t>
+          <t>2026-10-07 03:32:01</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>751.97</v>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>+3.510</t>
+        <v>751.53</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -21586,15 +21586,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06 15:13:54</t>
+          <t>2026-10-06 22:12:22</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>748.46</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>-0.720</t>
+        <v>751.97</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>+3.510</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -21609,15 +21609,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06 08:58:12</t>
+          <t>2026-10-06 15:13:54</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>749.1799999999999</v>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>+0.620</t>
+        <v>748.46</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -21632,15 +21632,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06 03:50:37</t>
+          <t>2026-10-06 08:58:12</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>748.5599999999999</v>
+        <v>749.1799999999999</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>+0.710</t>
+          <t>+0.620</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -21655,15 +21655,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-05 19:45:53</t>
+          <t>2026-10-06 03:50:37</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>747.85</v>
+        <v>748.5599999999999</v>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>+1.230</t>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -21678,15 +21678,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05 12:29:35</t>
+          <t>2026-10-05 19:45:53</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>746.62</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>-5.130</t>
+        <v>747.85</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -21701,15 +21701,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-05 07:58:26</t>
+          <t>2026-10-05 12:29:35</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>751.75</v>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>746.62</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>-5.130</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -21724,15 +21724,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 07:24:10</t>
+          <t>2026-10-05 07:58:26</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>751.58</v>
+        <v>751.75</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>+0.430</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -21747,15 +21747,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03 03:54:13</t>
+          <t>2026-10-03 07:24:10</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>751.15</v>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>-2.800</t>
+        <v>751.58</v>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>+0.430</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -21770,15 +21770,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02 23:05:32</t>
+          <t>2026-10-03 03:54:13</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>753.95</v>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>+1.310</t>
+        <v>751.15</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>-2.800</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -21793,15 +21793,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02 16:50:38</t>
+          <t>2026-10-02 23:05:32</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>752.64</v>
+        <v>753.95</v>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>+1.940</t>
+          <t>+1.310</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -21816,15 +21816,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02 10:28:43</t>
+          <t>2026-10-02 16:50:38</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>750.7</v>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>752.64</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>+1.940</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -21839,15 +21839,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02 03:52:14</t>
+          <t>2026-10-02 10:28:43</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>750.8099999999999</v>
+        <v>750.7</v>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-3.460</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -21862,15 +21862,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01 22:45:56</t>
+          <t>2026-10-02 03:52:14</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>754.27</v>
+        <v>750.8099999999999</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>-1.430</t>
+          <t>-3.460</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -21885,15 +21885,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01 15:40:31</t>
+          <t>2026-10-01 22:45:56</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>755.7</v>
+        <v>754.27</v>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>-0.970</t>
+          <t>-1.430</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -21908,15 +21908,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01 09:30:52</t>
+          <t>2026-10-01 15:40:31</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>756.67</v>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>755.7</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>-0.970</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -21931,15 +21931,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01 06:35:22</t>
+          <t>2026-10-01 09:30:52</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>756.61</v>
+        <v>756.67</v>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -21954,15 +21954,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01 02:37:20</t>
+          <t>2026-10-01 06:35:22</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>756.5</v>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>-1.520</t>
+        <v>756.61</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -21977,15 +21977,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30 21:52:18</t>
+          <t>2026-10-01 02:37:20</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>758.02</v>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>+1.070</t>
+        <v>756.5</v>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>-1.520</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -22000,15 +22000,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30 15:18:20</t>
+          <t>2026-09-30 21:52:18</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>756.95</v>
+        <v>758.02</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>+1.070</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -22023,15 +22023,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30 09:33:06</t>
+          <t>2026-09-30 15:18:20</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>756.48</v>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>-0.490</t>
+        <v>756.95</v>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -22046,15 +22046,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30 06:39:24</t>
+          <t>2026-09-30 09:33:06</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>756.97</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>+1.820</t>
+        <v>756.48</v>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>-0.490</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -22069,15 +22069,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30 02:44:52</t>
+          <t>2026-09-30 06:39:24</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>755.15</v>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>-1.720</t>
+        <v>756.97</v>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>+1.820</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -22092,15 +22092,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 21:24:10</t>
+          <t>2026-09-30 02:44:52</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>756.87</v>
+        <v>755.15</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>-1.250</t>
+          <t>-1.720</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -22115,15 +22115,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29 14:50:03</t>
+          <t>2026-09-29 21:24:10</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>758.12</v>
+        <v>756.87</v>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-1.140</t>
+          <t>-1.250</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -22138,15 +22138,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 09:07:04</t>
+          <t>2026-09-29 14:50:03</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>759.26</v>
+        <v>758.12</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-1.140</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -22161,15 +22161,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29 05:25:52</t>
+          <t>2026-09-29 09:07:04</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>759.3200000000001</v>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>759.26</v>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -22184,15 +22184,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28 23:53:17</t>
+          <t>2026-09-29 05:25:52</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>759.21</v>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>-1.020</t>
+        <v>759.3200000000001</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -22207,15 +22207,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-28 15:35:28</t>
+          <t>2026-09-28 23:53:17</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>760.23</v>
+        <v>759.21</v>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>-0.480</t>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -22230,15 +22230,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28 07:09:27</t>
+          <t>2026-09-28 15:35:28</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>760.71</v>
+        <v>760.23</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>-1.020</t>
+          <t>-0.480</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -22253,15 +22253,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26 07:27:54</t>
+          <t>2026-09-28 07:09:27</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>761.73</v>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>760.71</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -22276,15 +22276,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26 04:30:49</t>
+          <t>2026-09-26 07:27:54</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>761.5700000000001</v>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>761.73</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -22299,15 +22299,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26 01:15:26</t>
+          <t>2026-09-26 04:30:49</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>762.27</v>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>+0.790</t>
+        <v>761.5700000000001</v>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -22322,15 +22322,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25 20:15:35</t>
+          <t>2026-09-26 01:15:26</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>761.48</v>
+        <v>762.27</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>+1.200</t>
+          <t>+0.790</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -22345,15 +22345,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25 14:42:41</t>
+          <t>2026-09-25 20:15:35</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>760.28</v>
+        <v>761.48</v>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+1.200</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -22368,15 +22368,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25 01:40:29</t>
+          <t>2026-09-25 14:42:41</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>760.15</v>
+        <v>760.28</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>+0.500</t>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -22391,15 +22391,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 20:55:26</t>
+          <t>2026-09-25 01:40:29</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>759.65</v>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>-1.120</t>
+        <v>760.15</v>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>+0.500</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -22414,15 +22414,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 15:50:01</t>
+          <t>2026-09-24 20:55:26</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>760.77</v>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>+1.060</t>
+        <v>759.65</v>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>-1.120</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -22437,15 +22437,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 10:50:22</t>
+          <t>2026-09-24 15:50:01</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>759.71</v>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>760.77</v>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>+1.060</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -22460,15 +22460,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 07:56:20</t>
+          <t>2026-09-24 10:50:22</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>759.91</v>
+        <v>759.71</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -22483,15 +22483,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 02:27:02</t>
+          <t>2026-09-24 07:56:20</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>760.46</v>
+        <v>759.91</v>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -22506,15 +22506,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 22:21:19</t>
+          <t>2026-09-24 02:27:02</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>760.87</v>
+        <v>760.46</v>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>-1.520</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -22529,15 +22529,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 17:31:43</t>
+          <t>2026-09-23 22:21:19</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>762.39</v>
+        <v>760.87</v>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>-0.310</t>
+          <t>-1.520</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -22552,15 +22552,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 12:39:24</t>
+          <t>2026-09-23 17:31:43</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>762.7</v>
+        <v>762.39</v>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.310</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -22575,15 +22575,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 05:59:14</t>
+          <t>2026-09-23 12:39:24</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>762.89</v>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>762.7</v>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -22598,15 +22598,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 03:03:22</t>
+          <t>2026-09-23 05:59:14</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>762.41</v>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>-1.930</t>
+        <v>762.89</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -22621,15 +22621,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 23:32:15</t>
+          <t>2026-09-23 03:03:22</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>764.34</v>
-      </c>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>762.41</v>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>-1.930</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -22644,15 +22644,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 19:17:55</t>
+          <t>2026-09-22 23:32:15</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>764.09</v>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>-0.680</t>
+        <v>764.34</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -22667,15 +22667,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00:07</t>
+          <t>2026-09-22 19:17:55</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>764.77</v>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>+0.880</t>
+        <v>764.09</v>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>-0.680</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -22690,15 +22690,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 09:01:08</t>
+          <t>2026-09-22 14:00:07</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>763.89</v>
+        <v>764.77</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>+0.880</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -22713,15 +22713,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 06:28:11</t>
+          <t>2026-09-22 09:01:08</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>763.73</v>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>-0.670</t>
+        <v>763.89</v>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -22736,15 +22736,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 02:58:23</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>764.4</v>
+        <v>763.73</v>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>-0.750</t>
+          <t>-0.670</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -22759,15 +22759,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 21:54:34</t>
+          <t>2026-09-22 02:58:23</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>765.15</v>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>+0.510</t>
+        <v>764.4</v>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>-0.750</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -22782,15 +22782,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:24</t>
+          <t>2026-09-21 21:54:34</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>764.64</v>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>765.15</v>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>+0.510</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -22805,15 +22805,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 09:33:28</t>
+          <t>2026-09-21 15:01:24</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>765.11</v>
+        <v>764.64</v>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -22828,15 +22828,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 07:12:19</t>
+          <t>2026-09-21 09:33:28</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>765.54</v>
-      </c>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t>+0.710</t>
+        <v>765.11</v>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -22851,15 +22851,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>764.83</v>
+        <v>765.54</v>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -22874,15 +22874,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>764.54</v>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>764.83</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -22897,15 +22897,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>764.62</v>
+        <v>764.54</v>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>-0.770</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -22920,15 +22920,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>765.39</v>
+        <v>764.62</v>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>-0.620</t>
+          <t>-0.770</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -22943,15 +22943,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:32:25</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>766.01</v>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>765.39</v>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>-0.620</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -22966,15 +22966,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 05:47:34</t>
+          <t>2026-09-18 09:32:25</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>765.63</v>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>766.01</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -22989,15 +22989,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 05:47:34</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>765.8200000000001</v>
+        <v>765.63</v>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>-1.020</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -23012,15 +23012,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>766.84</v>
-      </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t>+1.260</t>
+        <v>765.8200000000001</v>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -23035,15 +23035,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>765.58</v>
+        <v>766.84</v>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>+0.340</t>
+          <t>+1.260</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -23058,15 +23058,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>765.24</v>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>765.58</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 08:40:02</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>765.39</v>
-      </c>
-      <c r="D76" s="16" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>765.24</v>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -23104,15 +23104,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 08:40:02</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>765.05</v>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>-4.700</t>
+        <v>765.39</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -23127,15 +23127,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>769.75</v>
+        <v>765.05</v>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-4.700</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -23150,15 +23150,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>770.04</v>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>769.75</v>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -23173,15 +23173,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>769.95</v>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>-0.730</t>
+        <v>770.04</v>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -23196,15 +23196,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>770.6799999999999</v>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>769.95</v>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -23219,15 +23219,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 09:40:23</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>770.47</v>
+        <v>770.6799999999999</v>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -23242,15 +23242,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 07:41:58</t>
+          <t>2026-09-16 09:40:23</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>770.38</v>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>770.47</v>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -23265,15 +23265,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>770.8</v>
+        <v>770.38</v>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -23288,15 +23288,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>770.8200000000001</v>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>+0.400</t>
+        <v>770.8</v>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -23311,15 +23311,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>770.42</v>
+        <v>770.8200000000001</v>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -23334,15 +23334,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>770.24</v>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>770.42</v>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -23357,11 +23357,11 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>771.05</v>
+        <v>770.24</v>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
@@ -23380,15 +23380,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>771.86</v>
-      </c>
-      <c r="D89" s="12" t="inlineStr">
-        <is>
-          <t>+1.540</t>
+        <v>771.05</v>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -23403,15 +23403,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>770.3200000000001</v>
-      </c>
-      <c r="D90" s="15" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>771.86</v>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>771.76</v>
+        <v>770.3200000000001</v>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>-2.140</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12 05:00:53</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>773.9</v>
+        <v>771.76</v>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-2.140</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15:57</t>
+          <t>2026-09-12 05:00:53</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>774.33</v>
+        <v>773.9</v>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>-0.730</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-12 02:15:57</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D94" s="16" t="inlineStr">
-        <is>
-          <t>+1.400</t>
+        <v>774.33</v>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>773.66</v>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>775.0599999999999</v>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>+1.400</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>775.1</v>
+        <v>773.66</v>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>-0.500</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 09:18:12</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>775.6</v>
+        <v>775.1</v>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.500</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -23587,15 +23587,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 09:18:12</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>776.01</v>
+        <v>775.6</v>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -23610,15 +23610,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>776.01</v>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -23633,15 +23633,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>775.83</v>
-      </c>
-      <c r="D100" s="15" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>776.38</v>
+      </c>
+      <c r="D100" s="16" t="inlineStr">
+        <is>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -23656,15 +23656,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>776.53</v>
+        <v>775.83</v>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -23679,15 +23679,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="D102" s="16" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.53</v>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -23702,15 +23702,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 06:08:04</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>776.7</v>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>776.91</v>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -23725,15 +23725,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 06:08:04</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>776.8</v>
+        <v>776.7</v>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -23748,15 +23748,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>777.27</v>
-      </c>
-      <c r="D105" s="12" t="inlineStr">
-        <is>
-          <t>+0.760</t>
+        <v>776.8</v>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -23771,15 +23771,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>776.51</v>
+        <v>777.27</v>
       </c>
       <c r="D106" s="16" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.760</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -23794,15 +23794,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>776.29</v>
+        <v>776.51</v>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>+0.390</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -23817,15 +23817,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>775.9</v>
+        <v>776.29</v>
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -23840,15 +23840,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>775.58</v>
+        <v>775.9</v>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -23863,15 +23863,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>775.48</v>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>775.58</v>
+      </c>
+      <c r="D110" s="16" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -23886,15 +23886,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>776.29</v>
-      </c>
-      <c r="D111" s="12" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>775.48</v>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -23909,15 +23909,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 06:18:23</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>776.0700000000001</v>
-      </c>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>776.29</v>
+      </c>
+      <c r="D112" s="16" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -23932,15 +23932,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 06:18:23</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>776.54</v>
+        <v>776.0700000000001</v>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -23955,15 +23955,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>776.59</v>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>776.54</v>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -23978,15 +23978,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>776.13</v>
+        <v>776.59</v>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -24001,15 +24001,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>775.3200000000001</v>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>776.13</v>
+      </c>
+      <c r="D116" s="16" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -24024,15 +24024,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 08:56:04</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>775.6900000000001</v>
-      </c>
-      <c r="D117" s="12" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>775.3200000000001</v>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -24047,15 +24047,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 07:06:50</t>
+          <t>2026-09-07 08:56:04</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>775.63</v>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>775.6900000000001</v>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -24070,15 +24070,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-05 07:06:50</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>776.02</v>
-      </c>
-      <c r="D119" s="12" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>775.63</v>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -24093,15 +24093,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>775.76</v>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>-0.720</t>
+        <v>776.02</v>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -24116,15 +24116,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>776.48</v>
+        <v>775.76</v>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>-0.580</t>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -24139,15 +24139,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>777.0599999999999</v>
+        <v>776.48</v>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.580</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -24162,15 +24162,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 07:59:45</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>777.13</v>
+        <v>777.0599999999999</v>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>-0.540</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -24185,15 +24185,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 07:59:45</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>777.67</v>
+        <v>777.13</v>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>-0.300</t>
+          <t>-0.540</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -24208,15 +24208,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>777.97</v>
-      </c>
-      <c r="D125" s="12" t="inlineStr">
-        <is>
-          <t>+1.580</t>
+        <v>777.67</v>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>-0.300</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -24231,15 +24231,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>776.39</v>
+        <v>777.97</v>
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>+1.580</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -24254,15 +24254,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>776.01</v>
+        <v>776.39</v>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>+0.660</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -24277,15 +24277,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>775.35</v>
+        <v>776.01</v>
       </c>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>+0.700</t>
+          <t>+0.660</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -24300,15 +24300,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 06:35:56</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>774.65</v>
+        <v>775.35</v>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.700</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -24323,15 +24323,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 04:09:22</t>
+          <t>2026-09-03 06:35:56</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>774.64</v>
-      </c>
-      <c r="D130" s="15" t="inlineStr">
-        <is>
-          <t>-0.270</t>
+        <v>774.65</v>
+      </c>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -24346,15 +24346,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 04:09:22</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>774.91</v>
-      </c>
-      <c r="D131" s="12" t="inlineStr">
-        <is>
-          <t>+0.390</t>
+        <v>774.64</v>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -24369,15 +24369,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>774.52</v>
+        <v>774.91</v>
       </c>
       <c r="D132" s="16" t="inlineStr">
         <is>
-          <t>+0.230</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -24392,15 +24392,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 17:58:25</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>774.29</v>
-      </c>
-      <c r="D133" s="9" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>774.52</v>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>+0.230</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -24415,15 +24415,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 17:58:25</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>774.36</v>
+        <v>774.29</v>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>-0.860</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -24438,15 +24438,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D135" s="12" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>774.36</v>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>-0.860</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -24461,15 +24461,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 02:48:49</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>774.87</v>
-      </c>
-      <c r="D136" s="15" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>775.22</v>
+      </c>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -24484,15 +24484,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 02:48:49</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>775.47</v>
-      </c>
-      <c r="D137" s="12" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>774.87</v>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -24507,15 +24507,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>775.25</v>
-      </c>
-      <c r="D138" s="15" t="inlineStr">
-        <is>
-          <t>-1.030</t>
+        <v>775.47</v>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -24530,15 +24530,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>776.28</v>
+        <v>775.25</v>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>-0.280</t>
+          <t>-1.030</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -24553,15 +24553,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 09:25:49</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>776.5599999999999</v>
+        <v>776.28</v>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -24576,15 +24576,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 06:48:36</t>
+          <t>2026-09-01 09:25:49</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>776.58</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -24599,15 +24599,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 02:10:52</t>
+          <t>2026-09-01 06:48:36</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>776.63</v>
-      </c>
-      <c r="D142" s="16" t="inlineStr">
-        <is>
-          <t>+1.230</t>
+        <v>776.58</v>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -24622,15 +24622,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 02:10:52</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>775.4</v>
+        <v>776.63</v>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -24645,15 +24645,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D144" s="15" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>775.4</v>
+      </c>
+      <c r="D144" s="16" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -24668,15 +24668,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 08:13:17</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>775.92</v>
-      </c>
-      <c r="D145" s="12" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.22</v>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -24691,15 +24691,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 08:13:17</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>775.85</v>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>-2.850</t>
+        <v>775.92</v>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -24714,15 +24714,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>778.7</v>
+        <v>775.85</v>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-2.850</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -24737,15 +24737,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>779.1</v>
-      </c>
-      <c r="D148" s="16" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>778.7</v>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -24760,15 +24760,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>778.72</v>
-      </c>
-      <c r="D149" s="9" t="inlineStr">
-        <is>
-          <t>-0.640</t>
+        <v>779.1</v>
+      </c>
+      <c r="D149" s="12" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -24783,15 +24783,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>779.36</v>
+        <v>778.72</v>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>-0.200</t>
+          <t>-0.640</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -24806,15 +24806,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 04:13:31</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>779.5599999999999</v>
-      </c>
-      <c r="D151" s="12" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>779.36</v>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -24829,15 +24829,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 04:13:31</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>779.39</v>
-      </c>
-      <c r="D152" s="15" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>779.5599999999999</v>
+      </c>
+      <c r="D152" s="16" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -24852,15 +24852,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>779.6</v>
+        <v>779.39</v>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -24875,15 +24875,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>780.03</v>
+        <v>779.6</v>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -24898,15 +24898,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 18:53:28</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>780.15</v>
+        <v>780.03</v>
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -24921,15 +24921,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 18:53:28</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>780.62</v>
-      </c>
-      <c r="D156" s="16" t="inlineStr">
-        <is>
-          <t>+0.560</t>
+        <v>780.15</v>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -24944,15 +24944,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>780.0599999999999</v>
-      </c>
-      <c r="D157" s="9" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>780.62</v>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
+        <is>
+          <t>+0.560</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -24967,15 +24967,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>780.17</v>
+        <v>780.0599999999999</v>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -24990,15 +24990,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>780.38</v>
-      </c>
-      <c r="D159" s="12" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>780.17</v>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -25013,15 +25013,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 10:07:59</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>780.36</v>
-      </c>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>780.38</v>
+      </c>
+      <c r="D160" s="16" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -25036,15 +25036,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 07:52:24</t>
+          <t>2026-08-26 10:07:59</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>780.6</v>
-      </c>
-      <c r="D161" s="12" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>780.36</v>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -25059,15 +25059,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 01:49:35</t>
+          <t>2026-08-26 07:52:24</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>780.4299999999999</v>
+        <v>780.6</v>
       </c>
       <c r="D162" s="16" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -25082,15 +25082,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 01:49:35</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>780.35</v>
+        <v>780.4299999999999</v>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -25105,15 +25105,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>780.3099999999999</v>
+        <v>780.35</v>
       </c>
       <c r="D164" s="16" t="inlineStr">
         <is>
-          <t>+0.410</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -25128,15 +25128,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:05:53</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>779.9</v>
-      </c>
-      <c r="D165" s="9" t="inlineStr">
-        <is>
-          <t>-0.260</t>
+        <v>780.3099999999999</v>
+      </c>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>+0.410</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -25151,15 +25151,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 21:05:53</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>780.16</v>
+        <v>779.9</v>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>-0.230</t>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -25174,15 +25174,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>780.39</v>
-      </c>
-      <c r="D167" s="12" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>780.16</v>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>-0.230</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -25197,15 +25197,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>780.15</v>
+        <v>780.39</v>
       </c>
       <c r="D168" s="16" t="inlineStr">
         <is>
-          <t>+0.540</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -25220,15 +25220,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:26</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>779.61</v>
-      </c>
-      <c r="D169" s="9" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>780.15</v>
+      </c>
+      <c r="D169" s="12" t="inlineStr">
+        <is>
+          <t>+0.540</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -25243,15 +25243,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:01:55</t>
+          <t>2026-08-25 15:51:26</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>779.65</v>
+        <v>779.61</v>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -25266,15 +25266,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 15:01:55</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>779.73</v>
+        <v>779.65</v>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -25289,15 +25289,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>780.11</v>
+        <v>779.73</v>
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -25312,15 +25312,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>780.4</v>
-      </c>
-      <c r="D173" s="12" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>780.11</v>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -25335,15 +25335,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:57:56</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>780.3099999999999</v>
+        <v>780.4</v>
       </c>
       <c r="D174" s="16" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -25358,15 +25358,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 06:50:27</t>
+          <t>2026-08-25 09:57:56</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>780.1900000000001</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -25381,15 +25381,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 06:50:27</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>780.1799999999999</v>
-      </c>
-      <c r="D176" s="15" t="inlineStr">
-        <is>
-          <t>-0.450</t>
+        <v>780.1900000000001</v>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -25404,15 +25404,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>780.63</v>
-      </c>
-      <c r="D177" s="12" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>780.1799999999999</v>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>-0.450</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -25427,15 +25427,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>780.17</v>
-      </c>
-      <c r="D178" s="15" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.63</v>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -25450,15 +25450,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>780.61</v>
-      </c>
-      <c r="D179" s="12" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>780.17</v>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -25473,15 +25473,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>780.14</v>
-      </c>
-      <c r="D180" s="15" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>780.61</v>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -25496,15 +25496,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>780.23</v>
+        <v>780.14</v>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>-0.530</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -25519,15 +25519,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>780.76</v>
+        <v>780.23</v>
       </c>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -25542,15 +25542,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>780.91</v>
+        <v>780.76</v>
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -25565,15 +25565,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>781.35</v>
+        <v>780.91</v>
       </c>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -25588,15 +25588,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>781.38</v>
-      </c>
-      <c r="D185" s="12" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>781.35</v>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -25611,15 +25611,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>781.09</v>
-      </c>
-      <c r="D186" s="15" t="inlineStr">
-        <is>
-          <t>-0.350</t>
+        <v>781.38</v>
+      </c>
+      <c r="D186" s="16" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -25634,15 +25634,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>781.4400000000001</v>
+        <v>781.09</v>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.350</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -25657,15 +25657,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>781.55</v>
-      </c>
-      <c r="D188" s="16" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.4400000000001</v>
+      </c>
+      <c r="D188" s="15" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -25680,15 +25680,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 09:42:15</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>781.23</v>
+        <v>781.55</v>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -25703,15 +25703,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 10:32:40</t>
+          <t>2026-08-24 09:42:15</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>781.01</v>
-      </c>
-      <c r="D190" s="15" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>781.23</v>
+      </c>
+      <c r="D190" s="16" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -25726,15 +25726,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 05:00:11</t>
+          <t>2026-08-22 10:32:40</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>781.11</v>
+        <v>781.01</v>
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>-0.180</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -25749,15 +25749,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 02:00:51</t>
+          <t>2026-08-22 05:00:11</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>781.29</v>
+        <v>781.11</v>
       </c>
       <c r="D192" s="15" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -25772,15 +25772,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-22 02:00:51</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>781.34</v>
-      </c>
-      <c r="D193" s="12" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>781.29</v>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -25795,15 +25795,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>780.79</v>
+        <v>781.34</v>
       </c>
       <c r="D194" s="16" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -25818,15 +25818,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>780.6799999999999</v>
-      </c>
-      <c r="D195" s="9" t="inlineStr">
-        <is>
-          <t>-0.610</t>
+        <v>780.79</v>
+      </c>
+      <c r="D195" s="12" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -25841,15 +25841,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>781.29</v>
+        <v>780.6799999999999</v>
       </c>
       <c r="D196" s="15" t="inlineStr">
         <is>
-          <t>-1.420</t>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -25864,15 +25864,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>782.71</v>
+        <v>781.29</v>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-1.420</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -25887,15 +25887,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>782.95</v>
-      </c>
-      <c r="D198" s="16" t="inlineStr">
-        <is>
-          <t>+1.080</t>
+        <v>782.71</v>
+      </c>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -25910,15 +25910,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>781.87</v>
-      </c>
-      <c r="D199" s="9" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>782.95</v>
+      </c>
+      <c r="D199" s="12" t="inlineStr">
+        <is>
+          <t>+1.080</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -25933,15 +25933,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>782.25</v>
-      </c>
-      <c r="D200" s="16" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>781.87</v>
+      </c>
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -25956,15 +25956,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>781.99</v>
+        <v>782.25</v>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -25979,15 +25979,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>781.95</v>
-      </c>
-      <c r="D202" s="15" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>781.99</v>
+      </c>
+      <c r="D202" s="16" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -26002,15 +26002,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>781.99</v>
+        <v>781.95</v>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -26025,15 +26025,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>782.39</v>
-      </c>
-      <c r="D204" s="16" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>781.99</v>
+      </c>
+      <c r="D204" s="15" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -26048,15 +26048,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:13</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>782.03</v>
+        <v>782.39</v>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>+0.400</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -26071,15 +26071,15 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 06:49:01</t>
+          <t>2026-08-21 09:10:13</t>
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>781.63</v>
+        <v>782.03</v>
       </c>
       <c r="D206" s="16" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -26094,15 +26094,15 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 06:49:01</t>
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>780.95</v>
-      </c>
-      <c r="D207" s="9" t="inlineStr">
-        <is>
-          <t>-0.780</t>
+        <v>781.63</v>
+      </c>
+      <c r="D207" s="12" t="inlineStr">
+        <is>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -26117,15 +26117,15 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>781.73</v>
+        <v>780.95</v>
       </c>
       <c r="D208" s="15" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -26140,15 +26140,15 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C209" s="8" t="n">
-        <v>781.79</v>
+        <v>781.73</v>
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -26163,15 +26163,15 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>782.1900000000001</v>
-      </c>
-      <c r="D210" s="16" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>781.79</v>
+      </c>
+      <c r="D210" s="15" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -26186,15 +26186,15 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
-        <v>782.04</v>
-      </c>
-      <c r="D211" s="9" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>782.1900000000001</v>
+      </c>
+      <c r="D211" s="12" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -26209,15 +26209,15 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>782.74</v>
-      </c>
-      <c r="D212" s="16" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>782.04</v>
+      </c>
+      <c r="D212" s="15" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -26232,15 +26232,15 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>782.42</v>
+        <v>782.74</v>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -26255,15 +26255,15 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>781.95</v>
+        <v>782.42</v>
       </c>
       <c r="D214" s="16" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -26278,15 +26278,15 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>781.14</v>
-      </c>
-      <c r="D215" s="9" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.95</v>
+      </c>
+      <c r="D215" s="12" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -26301,15 +26301,15 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>781.39</v>
-      </c>
-      <c r="D216" s="16" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>781.14</v>
+      </c>
+      <c r="D216" s="15" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -26324,15 +26324,15 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
-        <v>781.2</v>
+        <v>781.39</v>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -26347,15 +26347,15 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>781.17</v>
-      </c>
-      <c r="D218" s="15" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.2</v>
+      </c>
+      <c r="D218" s="16" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -26370,15 +26370,15 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 10:06:13</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>781.42</v>
+        <v>781.17</v>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -26393,15 +26393,15 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 07:36:53</t>
+          <t>2026-08-20 10:06:13</t>
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D220" s="16" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>781.42</v>
+      </c>
+      <c r="D220" s="15" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -26416,15 +26416,15 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 06:33:42</t>
+          <t>2026-08-20 07:36:53</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>781.77</v>
+        <v>781.79</v>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -26439,15 +26439,15 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 06:33:42</t>
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>781.45</v>
+        <v>781.77</v>
       </c>
       <c r="D222" s="16" t="inlineStr">
         <is>
-          <t>+0.850</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -26462,15 +26462,15 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>780.6</v>
+        <v>781.45</v>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.850</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -26485,15 +26485,15 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>780.12</v>
+        <v>780.6</v>
       </c>
       <c r="D224" s="16" t="inlineStr">
         <is>
-          <t>+1.750</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -26508,15 +26508,15 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>778.37</v>
+        <v>780.12</v>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>+1.750</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -26531,15 +26531,15 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>778.09</v>
+        <v>778.37</v>
       </c>
       <c r="D226" s="16" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -26554,15 +26554,15 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>777.41</v>
+        <v>778.09</v>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -26577,15 +26577,15 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C228" s="6" t="n">
-        <v>777.3200000000001</v>
+        <v>777.41</v>
       </c>
       <c r="D228" s="16" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -26600,11 +26600,11 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>777.1</v>
+        <v>777.3200000000001</v>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
@@ -26623,15 +26623,15 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>776.88</v>
-      </c>
-      <c r="D230" s="15" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.1</v>
+      </c>
+      <c r="D230" s="16" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -26646,15 +26646,15 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>776.89</v>
-      </c>
-      <c r="D231" s="12" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>776.88</v>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -26669,15 +26669,15 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C232" s="6" t="n">
-        <v>776.84</v>
-      </c>
-      <c r="D232" s="15" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>776.89</v>
+      </c>
+      <c r="D232" s="16" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -26692,15 +26692,15 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 09:12:00</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C233" s="8" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D233" s="12" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.84</v>
+      </c>
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
@@ -26715,15 +26715,15 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 09:12:00</t>
         </is>
       </c>
       <c r="C234" s="6" t="n">
-        <v>776.72</v>
-      </c>
-      <c r="D234" s="15" t="inlineStr">
-        <is>
-          <t>-0.460</t>
+        <v>776.9</v>
+      </c>
+      <c r="D234" s="16" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -26738,15 +26738,15 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>777.1799999999999</v>
-      </c>
-      <c r="D235" s="12" t="inlineStr">
-        <is>
-          <t>+0.630</t>
+        <v>776.72</v>
+      </c>
+      <c r="D235" s="9" t="inlineStr">
+        <is>
+          <t>-0.460</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
@@ -26761,15 +26761,15 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C236" s="6" t="n">
-        <v>776.55</v>
-      </c>
-      <c r="D236" s="15" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>777.1799999999999</v>
+      </c>
+      <c r="D236" s="16" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -26784,15 +26784,15 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:24</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
-        <v>776.62</v>
-      </c>
-      <c r="D237" s="12" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>776.55</v>
+      </c>
+      <c r="D237" s="9" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
@@ -26807,15 +26807,15 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 17:58:24</t>
         </is>
       </c>
       <c r="C238" s="6" t="n">
-        <v>776.53</v>
+        <v>776.62</v>
       </c>
       <c r="D238" s="16" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -26830,15 +26830,15 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
-        <v>776.36</v>
-      </c>
-      <c r="D239" s="9" t="inlineStr">
-        <is>
-          <t>-0.160</t>
+        <v>776.53</v>
+      </c>
+      <c r="D239" s="12" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
@@ -26853,15 +26853,15 @@
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C240" s="6" t="n">
-        <v>776.52</v>
+        <v>776.36</v>
       </c>
       <c r="D240" s="15" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.160</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -26876,15 +26876,15 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C241" s="8" t="n">
-        <v>776.53</v>
+        <v>776.52</v>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>-0.390</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
@@ -26899,15 +26899,15 @@
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C242" s="6" t="n">
-        <v>776.92</v>
-      </c>
-      <c r="D242" s="16" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>776.53</v>
+      </c>
+      <c r="D242" s="15" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -26922,15 +26922,15 @@
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 10:04:24</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C243" s="8" t="n">
-        <v>776.8200000000001</v>
+        <v>776.92</v>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
@@ -26945,15 +26945,15 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 07:54:32</t>
+          <t>2026-08-18 10:04:24</t>
         </is>
       </c>
       <c r="C244" s="6" t="n">
-        <v>776.61</v>
-      </c>
-      <c r="D244" s="15" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>776.8200000000001</v>
+      </c>
+      <c r="D244" s="16" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -26968,15 +26968,15 @@
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 05:48:09</t>
+          <t>2026-08-18 07:54:32</t>
         </is>
       </c>
       <c r="C245" s="8" t="n">
-        <v>776.74</v>
-      </c>
-      <c r="D245" s="12" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.61</v>
+      </c>
+      <c r="D245" s="9" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
@@ -26991,15 +26991,15 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 05:48:09</t>
         </is>
       </c>
       <c r="C246" s="6" t="n">
-        <v>776.5599999999999</v>
-      </c>
-      <c r="D246" s="15" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>776.74</v>
+      </c>
+      <c r="D246" s="16" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
@@ -27014,15 +27014,15 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C247" s="8" t="n">
-        <v>777.16</v>
-      </c>
-      <c r="D247" s="12" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>776.5599999999999</v>
+      </c>
+      <c r="D247" s="9" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
@@ -27037,15 +27037,15 @@
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C248" s="6" t="n">
-        <v>776.8099999999999</v>
-      </c>
-      <c r="D248" s="15" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>777.16</v>
+      </c>
+      <c r="D248" s="16" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -27060,15 +27060,15 @@
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:45</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
-        <v>777.21</v>
+        <v>776.8099999999999</v>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
@@ -27083,15 +27083,15 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 21:10:45</t>
         </is>
       </c>
       <c r="C250" s="6" t="n">
-        <v>777.4299999999999</v>
+        <v>777.21</v>
       </c>
       <c r="D250" s="15" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
@@ -27106,15 +27106,15 @@
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C251" s="8" t="n">
-        <v>777.52</v>
-      </c>
-      <c r="D251" s="12" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>777.4299999999999</v>
+      </c>
+      <c r="D251" s="9" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
@@ -27129,15 +27129,15 @@
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C252" s="6" t="n">
-        <v>777.5</v>
+        <v>777.52</v>
       </c>
       <c r="D252" s="16" t="inlineStr">
         <is>
-          <t>+0.370</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
@@ -27152,15 +27152,15 @@
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
-        <v>777.13</v>
+        <v>777.5</v>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.370</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
@@ -27175,15 +27175,15 @@
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C254" s="6" t="n">
-        <v>777.04</v>
+        <v>777.13</v>
       </c>
       <c r="D254" s="16" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
@@ -27198,15 +27198,15 @@
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C255" s="8" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D255" s="9" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.04</v>
+      </c>
+      <c r="D255" s="12" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
@@ -27221,15 +27221,15 @@
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C256" s="6" t="n">
-        <v>776.91</v>
+        <v>776.9</v>
       </c>
       <c r="D256" s="15" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
@@ -27244,15 +27244,15 @@
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C257" s="8" t="n">
-        <v>776.96</v>
-      </c>
-      <c r="D257" s="12" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>776.91</v>
+      </c>
+      <c r="D257" s="9" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
@@ -27267,15 +27267,15 @@
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 09:21:39</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C258" s="6" t="n">
-        <v>776.84</v>
+        <v>776.96</v>
       </c>
       <c r="D258" s="16" t="inlineStr">
         <is>
-          <t>+0.750</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
@@ -27290,15 +27290,15 @@
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 09:21:39</t>
         </is>
       </c>
       <c r="C259" s="8" t="n">
-        <v>776.09</v>
-      </c>
-      <c r="D259" s="9" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>776.84</v>
+      </c>
+      <c r="D259" s="12" t="inlineStr">
+        <is>
+          <t>+0.750</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
@@ -27313,15 +27313,15 @@
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C260" s="6" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D260" s="16" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>776.09</v>
+      </c>
+      <c r="D260" s="15" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
@@ -27336,15 +27336,15 @@
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C261" s="8" t="n">
-        <v>775.8099999999999</v>
+        <v>776.38</v>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>+0.770</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
@@ -27359,15 +27359,15 @@
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C262" s="6" t="n">
-        <v>775.04</v>
+        <v>775.8099999999999</v>
       </c>
       <c r="D262" s="16" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.770</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
@@ -27382,15 +27382,15 @@
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C263" s="8" t="n">
-        <v>774.92</v>
+        <v>775.04</v>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>+0.360</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
@@ -27405,15 +27405,15 @@
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C264" s="6" t="n">
-        <v>774.5599999999999</v>
+        <v>774.92</v>
       </c>
       <c r="D264" s="16" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E264" s="6" t="inlineStr">
@@ -27428,15 +27428,15 @@
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C265" s="8" t="n">
-        <v>774.4400000000001</v>
-      </c>
-      <c r="D265" s="9" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>774.5599999999999</v>
+      </c>
+      <c r="D265" s="12" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
@@ -27451,15 +27451,15 @@
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C266" s="6" t="n">
-        <v>774.46</v>
-      </c>
-      <c r="D266" s="16" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>774.4400000000001</v>
+      </c>
+      <c r="D266" s="15" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E266" s="6" t="inlineStr">
@@ -27474,15 +27474,15 @@
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C267" s="8" t="n">
-        <v>774.25</v>
+        <v>774.46</v>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>+0.310</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
@@ -27497,15 +27497,15 @@
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 10:39:02</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C268" s="6" t="n">
-        <v>773.9400000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D268" s="16" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.310</t>
         </is>
       </c>
       <c r="E268" s="6" t="inlineStr">
@@ -27520,15 +27520,15 @@
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 08:05:13</t>
+          <t>2026-08-14 10:39:02</t>
         </is>
       </c>
       <c r="C269" s="8" t="n">
-        <v>773.9</v>
+        <v>773.9400000000001</v>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
@@ -27543,15 +27543,15 @@
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 07:24:16</t>
+          <t>2026-08-14 08:05:13</t>
         </is>
       </c>
       <c r="C270" s="6" t="n">
-        <v>773.73</v>
+        <v>773.9</v>
       </c>
       <c r="D270" s="16" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E270" s="6" t="inlineStr">
@@ -27566,15 +27566,15 @@
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 07:24:16</t>
         </is>
       </c>
       <c r="C271" s="8" t="n">
-        <v>773.53</v>
-      </c>
-      <c r="D271" s="9" t="inlineStr">
-        <is>
-          <t>-0.790</t>
+        <v>773.73</v>
+      </c>
+      <c r="D271" s="12" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
@@ -27589,15 +27589,15 @@
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C272" s="6" t="n">
-        <v>774.3200000000001</v>
-      </c>
-      <c r="D272" s="16" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>773.53</v>
+      </c>
+      <c r="D272" s="15" t="inlineStr">
+        <is>
+          <t>-0.790</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
@@ -27612,15 +27612,15 @@
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C273" s="8" t="n">
-        <v>773.75</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
@@ -27635,15 +27635,15 @@
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C274" s="6" t="n">
-        <v>773.7</v>
+        <v>773.75</v>
       </c>
       <c r="D274" s="16" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
@@ -27658,15 +27658,15 @@
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C275" s="8" t="n">
-        <v>773.58</v>
+        <v>773.7</v>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>+0.250</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
@@ -27681,15 +27681,15 @@
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C276" s="6" t="n">
-        <v>773.33</v>
-      </c>
-      <c r="D276" s="15" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>773.58</v>
+      </c>
+      <c r="D276" s="16" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
@@ -27704,15 +27704,15 @@
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C277" s="8" t="n">
-        <v>773.39</v>
-      </c>
-      <c r="D277" s="12" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>773.33</v>
+      </c>
+      <c r="D277" s="9" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
@@ -27727,15 +27727,15 @@
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C278" s="6" t="n">
-        <v>773.11</v>
-      </c>
-      <c r="D278" s="15" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>773.39</v>
+      </c>
+      <c r="D278" s="16" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
@@ -27750,15 +27750,15 @@
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C279" s="8" t="n">
-        <v>773.24</v>
+        <v>773.11</v>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>-0.340</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
@@ -27773,15 +27773,15 @@
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C280" s="6" t="n">
-        <v>773.58</v>
+        <v>773.24</v>
       </c>
       <c r="D280" s="15" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E280" s="6" t="inlineStr">
@@ -27796,15 +27796,15 @@
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C281" s="8" t="n">
-        <v>773.64</v>
+        <v>773.58</v>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
@@ -27819,15 +27819,15 @@
       </c>
       <c r="B282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C282" s="6" t="n">
-        <v>774.11</v>
+        <v>773.64</v>
       </c>
       <c r="D282" s="15" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
@@ -27842,15 +27842,15 @@
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C283" s="8" t="n">
-        <v>774.3</v>
+        <v>774.11</v>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>-0.740</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
@@ -27865,15 +27865,15 @@
       </c>
       <c r="B284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C284" s="6" t="n">
-        <v>775.04</v>
-      </c>
-      <c r="D284" s="16" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>774.3</v>
+      </c>
+      <c r="D284" s="15" t="inlineStr">
+        <is>
+          <t>-0.740</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
@@ -27888,15 +27888,15 @@
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C285" s="8" t="n">
-        <v>774.9</v>
+        <v>775.04</v>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
@@ -27911,15 +27911,15 @@
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C286" s="6" t="n">
-        <v>774.66</v>
+        <v>774.9</v>
       </c>
       <c r="D286" s="16" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
@@ -27934,15 +27934,15 @@
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C287" s="8" t="n">
-        <v>774.34</v>
+        <v>774.66</v>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
@@ -27957,15 +27957,15 @@
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C288" s="6" t="n">
-        <v>774.15</v>
-      </c>
-      <c r="D288" s="15" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>774.34</v>
+      </c>
+      <c r="D288" s="16" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
@@ -27980,15 +27980,15 @@
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 13:53:42</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C289" s="8" t="n">
-        <v>774.25</v>
+        <v>774.15</v>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
@@ -28003,15 +28003,15 @@
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 13:53:42</t>
         </is>
       </c>
       <c r="C290" s="6" t="n">
-        <v>774.3200000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D290" s="15" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
@@ -28026,15 +28026,15 @@
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C291" s="8" t="n">
-        <v>774.74</v>
-      </c>
-      <c r="D291" s="12" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>774.3200000000001</v>
+      </c>
+      <c r="D291" s="9" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
@@ -28049,15 +28049,15 @@
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 01:28:47</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C292" s="6" t="n">
-        <v>774.5</v>
+        <v>774.74</v>
       </c>
       <c r="D292" s="16" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
@@ -28072,15 +28072,15 @@
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 01:28:47</t>
         </is>
       </c>
       <c r="C293" s="8" t="n">
-        <v>774.37</v>
-      </c>
-      <c r="D293" s="9" t="inlineStr">
-        <is>
-          <t>-0.340</t>
+        <v>774.5</v>
+      </c>
+      <c r="D293" s="12" t="inlineStr">
+        <is>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
@@ -28095,15 +28095,15 @@
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C294" s="6" t="n">
-        <v>774.71</v>
-      </c>
-      <c r="D294" s="16" t="inlineStr">
-        <is>
-          <t>+1.160</t>
+        <v>774.37</v>
+      </c>
+      <c r="D294" s="15" t="inlineStr">
+        <is>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E294" s="6" t="inlineStr">
@@ -28118,15 +28118,15 @@
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C295" s="8" t="n">
-        <v>773.55</v>
-      </c>
-      <c r="D295" s="9" t="inlineStr">
-        <is>
-          <t>-0.520</t>
+        <v>774.71</v>
+      </c>
+      <c r="D295" s="12" t="inlineStr">
+        <is>
+          <t>+1.160</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
@@ -28141,15 +28141,15 @@
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C296" s="6" t="n">
-        <v>774.0700000000001</v>
+        <v>773.55</v>
       </c>
       <c r="D296" s="15" t="inlineStr">
         <is>
-          <t>-0.690</t>
+          <t>-0.520</t>
         </is>
       </c>
       <c r="E296" s="6" t="inlineStr">
@@ -28164,15 +28164,15 @@
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C297" s="8" t="n">
-        <v>774.76</v>
+        <v>774.0700000000001</v>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.690</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
@@ -28187,15 +28187,15 @@
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C298" s="6" t="n">
-        <v>775.3099999999999</v>
+        <v>774.76</v>
       </c>
       <c r="D298" s="15" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E298" s="6" t="inlineStr">
@@ -28210,15 +28210,15 @@
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C299" s="8" t="n">
-        <v>775.46</v>
+        <v>775.3099999999999</v>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
@@ -28233,15 +28233,15 @@
       </c>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C300" s="6" t="n">
-        <v>775.84</v>
+        <v>775.46</v>
       </c>
       <c r="D300" s="15" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E300" s="6" t="inlineStr">
@@ -28256,15 +28256,15 @@
       </c>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 08:05:33</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C301" s="8" t="n">
-        <v>775.9</v>
-      </c>
-      <c r="D301" s="12" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.84</v>
+      </c>
+      <c r="D301" s="9" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
@@ -28279,15 +28279,15 @@
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 08:05:33</t>
         </is>
       </c>
       <c r="C302" s="6" t="n">
-        <v>775.83</v>
+        <v>775.9</v>
       </c>
       <c r="D302" s="16" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E302" s="6" t="inlineStr">
@@ -28302,15 +28302,15 @@
       </c>
       <c r="B303" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C303" s="8" t="n">
-        <v>775.2</v>
-      </c>
-      <c r="D303" s="9" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>775.83</v>
+      </c>
+      <c r="D303" s="12" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
@@ -28325,15 +28325,15 @@
       </c>
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C304" s="6" t="n">
-        <v>775.28</v>
-      </c>
-      <c r="D304" s="16" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>775.2</v>
+      </c>
+      <c r="D304" s="15" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E304" s="6" t="inlineStr">
@@ -28348,15 +28348,15 @@
       </c>
       <c r="B305" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C305" s="8" t="n">
-        <v>775.12</v>
+        <v>775.28</v>
       </c>
       <c r="D305" s="12" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
@@ -28371,11 +28371,11 @@
       </c>
       <c r="B306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C306" s="6" t="n">
-        <v>775.09</v>
+        <v>775.12</v>
       </c>
       <c r="D306" s="16" t="inlineStr">
         <is>
@@ -28394,15 +28394,15 @@
       </c>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 18:37:13</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C307" s="8" t="n">
-        <v>775.0599999999999</v>
+        <v>775.09</v>
       </c>
       <c r="D307" s="12" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
@@ -28417,15 +28417,15 @@
       </c>
       <c r="B308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 18:37:13</t>
         </is>
       </c>
       <c r="C308" s="6" t="n">
-        <v>774.58</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D308" s="16" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E308" s="6" t="inlineStr">
@@ -28440,15 +28440,15 @@
       </c>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C309" s="8" t="n">
-        <v>774.29</v>
+        <v>774.58</v>
       </c>
       <c r="D309" s="12" t="inlineStr">
         <is>
-          <t>+0.490</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
@@ -28463,15 +28463,15 @@
       </c>
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C310" s="6" t="n">
-        <v>773.8</v>
-      </c>
-      <c r="D310" s="15" t="inlineStr">
-        <is>
-          <t>-0.590</t>
+        <v>774.29</v>
+      </c>
+      <c r="D310" s="16" t="inlineStr">
+        <is>
+          <t>+0.490</t>
         </is>
       </c>
       <c r="E310" s="6" t="inlineStr">
@@ -28486,14 +28486,37 @@
       </c>
       <c r="B311" s="8" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C311" s="8" t="n">
+        <v>773.8</v>
+      </c>
+      <c r="D311" s="9" t="inlineStr">
+        <is>
+          <t>-0.590</t>
+        </is>
+      </c>
+      <c r="E311" s="8" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="6" t="n">
+        <v>308</v>
+      </c>
+      <c r="B312" s="6" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C311" s="8" t="n">
+      <c r="C312" s="6" t="n">
         <v>774.39</v>
       </c>
-      <c r="D311" s="8" t="inlineStr"/>
-      <c r="E311" s="8" t="inlineStr">
+      <c r="D312" s="6" t="inlineStr"/>
+      <c r="E312" s="6" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 05:51:06</t>
+          <t>更新时间: 2026-10-10 09:19:19</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 21:46:51</t>
+          <t>更新时间: 2026-10-11 02:03:25</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 02:03:25</t>
+          <t>更新时间: 2026-10-11 05:32:54</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 05:32:54</t>
+          <t>更新时间: 2026-10-11 08:24:27</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 08:24:27</t>
+          <t>更新时间: 2026-10-11 14:03:56</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 14:03:56</t>
+          <t>更新时间: 2026-10-11 20:38:45</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 20:38:45</t>
+          <t>更新时间: 2026-10-12 01:46:35</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 01:46:35</t>
+          <t>更新时间: 2026-10-12 05:04:40</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -185,10 +185,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-15 03:31:02</t>
+          <t>更新时间: 2026-10-15 06:32:18</t>
         </is>
       </c>
     </row>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>743.3200000000001</v>
+        <v>743.3</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 03:30:59</t>
+          <t>2026-10-15 06:32:13</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E334"/>
+  <dimension ref="A1:E335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -22446,7 +22446,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 743.32 | 最高: 782.950 | 最低: 741.220 | 总记录数: 330</t>
+          <t>最新价: 743.30 | 最高: 782.950 | 最低: 741.220 | 总记录数: 331</t>
         </is>
       </c>
     </row>
@@ -22483,15 +22483,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-10-15 03:30:59</t>
+          <t>2026-10-15 06:32:13</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>743.3200000000001</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>+2.100</t>
+        <v>743.3</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -22506,15 +22506,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 23:23:31</t>
+          <t>2026-10-15 03:30:59</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>741.22</v>
+        <v>743.3200000000001</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-4.140</t>
+          <t>+2.100</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -22529,15 +22529,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14 18:30:58</t>
+          <t>2026-10-14 23:23:31</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>745.36</v>
+        <v>741.22</v>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>-0.820</t>
+          <t>-4.140</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -22552,15 +22552,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 13:30:58</t>
+          <t>2026-10-14 18:30:58</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>746.1799999999999</v>
+        <v>745.36</v>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>-0.820</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -22575,15 +22575,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14 08:52:22</t>
+          <t>2026-10-14 13:30:58</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>746.04</v>
+        <v>746.1799999999999</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -22598,15 +22598,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 05:57:42</t>
+          <t>2026-10-14 08:52:22</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>745.83</v>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>746.04</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -22621,15 +22621,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14 01:42:57</t>
+          <t>2026-10-14 05:57:42</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>745.37</v>
+        <v>745.83</v>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>+0.520</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -22644,15 +22644,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 18:28:00</t>
+          <t>2026-10-14 01:42:57</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>744.85</v>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>+0.810</t>
+        <v>745.37</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>+0.520</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -22667,15 +22667,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13 11:09:04</t>
+          <t>2026-10-13 18:28:00</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>744.04</v>
+        <v>744.85</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>+1.170</t>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -22690,15 +22690,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 06:35:47</t>
+          <t>2026-10-13 11:09:04</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>742.87</v>
+        <v>744.04</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-1.330</t>
+          <t>+1.170</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -22713,15 +22713,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12 23:41:57</t>
+          <t>2026-10-13 06:35:47</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>744.2</v>
+        <v>742.87</v>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>-1.920</t>
+          <t>-1.330</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -22736,15 +22736,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 14:18:12</t>
+          <t>2026-10-12 23:41:57</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>746.12</v>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>-0.430</t>
+        <v>744.2</v>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>-1.920</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -22759,15 +22759,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12 08:27:33</t>
+          <t>2026-10-12 14:18:12</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>746.55</v>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>+0.640</t>
+        <v>746.12</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -22782,15 +22782,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 05:51:00</t>
+          <t>2026-10-12 08:27:33</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>745.91</v>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>+0.590</t>
+        <v>746.55</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>+0.640</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -22805,15 +22805,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10 01:31:35</t>
+          <t>2026-10-10 05:51:00</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>745.3200000000001</v>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>-1.300</t>
+        <v>745.91</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>+0.590</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -22828,15 +22828,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 19:31:18</t>
+          <t>2026-10-10 01:31:35</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>746.62</v>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>-1.510</t>
+        <v>745.3200000000001</v>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>-1.300</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -22851,15 +22851,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09 12:43:45</t>
+          <t>2026-10-09 19:31:18</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>748.13</v>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>746.62</v>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>-1.510</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -22874,15 +22874,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 07:57:46</t>
+          <t>2026-10-09 12:43:45</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>747.85</v>
+        <v>748.13</v>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-0.330</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -22897,15 +22897,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09 03:43:29</t>
+          <t>2026-10-09 07:57:46</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>748.1799999999999</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>+1.990</t>
+        <v>747.85</v>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>-0.330</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -22920,15 +22920,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 21:59:30</t>
+          <t>2026-10-09 03:43:29</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>746.1900000000001</v>
+        <v>748.1799999999999</v>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>-0.780</t>
+          <t>+1.990</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -22943,15 +22943,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08 14:38:03</t>
+          <t>2026-10-08 21:59:30</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>746.97</v>
+        <v>746.1900000000001</v>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>-0.820</t>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -22966,15 +22966,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 08:38:58</t>
+          <t>2026-10-08 14:38:03</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>747.79</v>
+        <v>746.97</v>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.820</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -22989,15 +22989,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08 04:55:36</t>
+          <t>2026-10-08 08:38:58</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>747.61</v>
+        <v>747.79</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>+1.220</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -23012,15 +23012,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 23:55:26</t>
+          <t>2026-10-08 04:55:36</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>746.39</v>
+        <v>747.61</v>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>-3.090</t>
+          <t>+1.220</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -23035,15 +23035,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07 16:54:58</t>
+          <t>2026-10-07 23:55:26</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>749.48</v>
+        <v>746.39</v>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>-1.210</t>
+          <t>-3.090</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -23058,15 +23058,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 10:22:51</t>
+          <t>2026-10-07 16:54:58</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>750.6900000000001</v>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>-1.090</t>
+        <v>749.48</v>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>-1.210</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07 07:12:13</t>
+          <t>2026-10-07 10:22:51</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>751.78</v>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>750.6900000000001</v>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>-1.090</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -23104,15 +23104,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 03:32:01</t>
+          <t>2026-10-07 07:12:13</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>751.53</v>
+        <v>751.78</v>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -23127,15 +23127,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06 22:12:22</t>
+          <t>2026-10-07 03:32:01</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>751.97</v>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>+3.510</t>
+        <v>751.53</v>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -23150,15 +23150,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06 15:13:54</t>
+          <t>2026-10-06 22:12:22</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>748.46</v>
+        <v>751.97</v>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-0.720</t>
+          <t>+3.510</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -23173,15 +23173,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06 08:58:12</t>
+          <t>2026-10-06 15:13:54</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>749.1799999999999</v>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>+0.620</t>
+        <v>748.46</v>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -23196,15 +23196,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06 03:50:37</t>
+          <t>2026-10-06 08:58:12</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>748.5599999999999</v>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>+0.710</t>
+        <v>749.1799999999999</v>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>+0.620</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -23219,15 +23219,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05 19:45:53</t>
+          <t>2026-10-06 03:50:37</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>747.85</v>
+        <v>748.5599999999999</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>+1.230</t>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -23242,15 +23242,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-10-05 12:29:35</t>
+          <t>2026-10-05 19:45:53</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>746.62</v>
+        <v>747.85</v>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>-5.130</t>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -23265,15 +23265,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05 07:58:26</t>
+          <t>2026-10-05 12:29:35</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>751.75</v>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>746.62</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>-5.130</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -23288,15 +23288,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03 07:24:10</t>
+          <t>2026-10-05 07:58:26</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>751.58</v>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>+0.430</t>
+        <v>751.75</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -23311,15 +23311,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 03:54:13</t>
+          <t>2026-10-03 07:24:10</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>751.15</v>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>-2.800</t>
+        <v>751.58</v>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>+0.430</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -23334,15 +23334,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02 23:05:32</t>
+          <t>2026-10-03 03:54:13</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>753.95</v>
+        <v>751.15</v>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>+1.310</t>
+          <t>-2.800</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -23357,15 +23357,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02 16:50:38</t>
+          <t>2026-10-02 23:05:32</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>752.64</v>
+        <v>753.95</v>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>+1.940</t>
+          <t>+1.310</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -23380,15 +23380,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02 10:28:43</t>
+          <t>2026-10-02 16:50:38</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>750.7</v>
+        <v>752.64</v>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>+1.940</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -23403,15 +23403,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02 03:52:14</t>
+          <t>2026-10-02 10:28:43</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>750.8099999999999</v>
+        <v>750.7</v>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>-3.460</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01 22:45:56</t>
+          <t>2026-10-02 03:52:14</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>754.27</v>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>-1.430</t>
+        <v>750.8099999999999</v>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>-3.460</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01 15:40:31</t>
+          <t>2026-10-01 22:45:56</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>755.7</v>
+        <v>754.27</v>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>-0.970</t>
+          <t>-1.430</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01 09:30:52</t>
+          <t>2026-10-01 15:40:31</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>756.67</v>
+        <v>755.7</v>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.970</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01 06:35:22</t>
+          <t>2026-10-01 09:30:52</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>756.61</v>
+        <v>756.67</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01 02:37:20</t>
+          <t>2026-10-01 06:35:22</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>756.5</v>
+        <v>756.61</v>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>-1.520</t>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30 21:52:18</t>
+          <t>2026-10-01 02:37:20</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>758.02</v>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>+1.070</t>
+        <v>756.5</v>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>-1.520</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30 15:18:20</t>
+          <t>2026-09-30 21:52:18</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>756.95</v>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>758.02</v>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>+1.070</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -23587,15 +23587,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30 09:33:06</t>
+          <t>2026-09-30 15:18:20</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>756.48</v>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>-0.490</t>
+        <v>756.95</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -23610,15 +23610,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30 06:39:24</t>
+          <t>2026-09-30 09:33:06</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>756.97</v>
+        <v>756.48</v>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>+1.820</t>
+          <t>-0.490</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -23633,15 +23633,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30 02:44:52</t>
+          <t>2026-09-30 06:39:24</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>755.15</v>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>-1.720</t>
+        <v>756.97</v>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>+1.820</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -23656,15 +23656,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29 21:24:10</t>
+          <t>2026-09-30 02:44:52</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>756.87</v>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>-1.250</t>
+        <v>755.15</v>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>-1.720</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -23679,15 +23679,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 14:50:03</t>
+          <t>2026-09-29 21:24:10</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>758.12</v>
+        <v>756.87</v>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>-1.140</t>
+          <t>-1.250</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -23702,15 +23702,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29 09:07:04</t>
+          <t>2026-09-29 14:50:03</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>759.26</v>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>758.12</v>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>-1.140</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -23725,15 +23725,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 05:25:52</t>
+          <t>2026-09-29 09:07:04</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>759.3200000000001</v>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>759.26</v>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -23748,15 +23748,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-28 23:53:17</t>
+          <t>2026-09-29 05:25:52</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>759.21</v>
+        <v>759.3200000000001</v>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>-1.020</t>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -23771,15 +23771,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28 15:35:28</t>
+          <t>2026-09-28 23:53:17</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>760.23</v>
+        <v>759.21</v>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>-0.480</t>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -23794,15 +23794,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-28 07:09:27</t>
+          <t>2026-09-28 15:35:28</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>760.71</v>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>-1.020</t>
+        <v>760.23</v>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>-0.480</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -23817,15 +23817,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26 07:27:54</t>
+          <t>2026-09-28 07:09:27</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>761.73</v>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>760.71</v>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -23840,15 +23840,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26 04:30:49</t>
+          <t>2026-09-26 07:27:54</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>761.5700000000001</v>
+        <v>761.73</v>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>-0.700</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -23863,15 +23863,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26 01:15:26</t>
+          <t>2026-09-26 04:30:49</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>762.27</v>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>+0.790</t>
+        <v>761.5700000000001</v>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -23886,15 +23886,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25 20:15:35</t>
+          <t>2026-09-26 01:15:26</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>761.48</v>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>+1.200</t>
+        <v>762.27</v>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>+0.790</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -23909,15 +23909,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25 14:42:41</t>
+          <t>2026-09-25 20:15:35</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>760.28</v>
+        <v>761.48</v>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+1.200</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -23932,15 +23932,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25 01:40:29</t>
+          <t>2026-09-25 14:42:41</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>760.15</v>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
-        <is>
-          <t>+0.500</t>
+        <v>760.28</v>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -23955,15 +23955,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 20:55:26</t>
+          <t>2026-09-25 01:40:29</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>759.65</v>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>-1.120</t>
+        <v>760.15</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>+0.500</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -23978,15 +23978,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 15:50:01</t>
+          <t>2026-09-24 20:55:26</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>760.77</v>
+        <v>759.65</v>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>+1.060</t>
+          <t>-1.120</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -24001,15 +24001,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 10:50:22</t>
+          <t>2026-09-24 15:50:01</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>759.71</v>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>760.77</v>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>+1.060</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -24024,15 +24024,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 07:56:20</t>
+          <t>2026-09-24 10:50:22</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>759.91</v>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>-0.550</t>
+        <v>759.71</v>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -24047,15 +24047,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 02:27:02</t>
+          <t>2026-09-24 07:56:20</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>760.46</v>
+        <v>759.91</v>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -24070,15 +24070,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 22:21:19</t>
+          <t>2026-09-24 02:27:02</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>760.87</v>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
-        <is>
-          <t>-1.520</t>
+        <v>760.46</v>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -24093,15 +24093,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 17:31:43</t>
+          <t>2026-09-23 22:21:19</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>762.39</v>
+        <v>760.87</v>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>-0.310</t>
+          <t>-1.520</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -24116,15 +24116,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 12:39:24</t>
+          <t>2026-09-23 17:31:43</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>762.7</v>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>762.39</v>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
+        <is>
+          <t>-0.310</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -24139,15 +24139,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 05:59:14</t>
+          <t>2026-09-23 12:39:24</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>762.89</v>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>762.7</v>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -24162,15 +24162,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 03:03:22</t>
+          <t>2026-09-23 05:59:14</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>762.41</v>
+        <v>762.89</v>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>-1.930</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -24185,15 +24185,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 23:32:15</t>
+          <t>2026-09-23 03:03:22</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>764.34</v>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>762.41</v>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>-1.930</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -24208,15 +24208,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 19:17:55</t>
+          <t>2026-09-22 23:32:15</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>764.09</v>
+        <v>764.34</v>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>-0.680</t>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -24231,15 +24231,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00:07</t>
+          <t>2026-09-22 19:17:55</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>764.77</v>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>+0.880</t>
+        <v>764.09</v>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>-0.680</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -24254,15 +24254,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 09:01:08</t>
+          <t>2026-09-22 14:00:07</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>763.89</v>
-      </c>
-      <c r="D82" s="16" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>764.77</v>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>+0.880</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -24277,15 +24277,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 06:28:11</t>
+          <t>2026-09-22 09:01:08</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>763.73</v>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>-0.670</t>
+        <v>763.89</v>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -24300,15 +24300,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 02:58:23</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>764.4</v>
-      </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>-0.750</t>
+        <v>763.73</v>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>-0.670</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -24323,15 +24323,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 21:54:34</t>
+          <t>2026-09-22 02:58:23</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>765.15</v>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>+0.510</t>
+        <v>764.4</v>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>-0.750</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -24346,15 +24346,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:24</t>
+          <t>2026-09-21 21:54:34</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>764.64</v>
+        <v>765.15</v>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>+0.510</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -24369,15 +24369,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 09:33:28</t>
+          <t>2026-09-21 15:01:24</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>765.11</v>
+        <v>764.64</v>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -24392,15 +24392,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 07:12:19</t>
+          <t>2026-09-21 09:33:28</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>765.54</v>
+        <v>765.11</v>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>+0.710</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -24415,15 +24415,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>764.83</v>
+        <v>765.54</v>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -24438,15 +24438,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>764.54</v>
+        <v>764.83</v>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -24461,15 +24461,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>764.62</v>
+        <v>764.54</v>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>-0.770</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -24484,15 +24484,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>765.39</v>
-      </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>-0.620</t>
+        <v>764.62</v>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>-0.770</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -24507,15 +24507,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:32:25</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>766.01</v>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>765.39</v>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>-0.620</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -24530,15 +24530,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 05:47:34</t>
+          <t>2026-09-18 09:32:25</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>765.63</v>
+        <v>766.01</v>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -24553,15 +24553,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 05:47:34</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>765.8200000000001</v>
+        <v>765.63</v>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>-1.020</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -24576,15 +24576,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>766.84</v>
+        <v>765.8200000000001</v>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>+1.260</t>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -24599,15 +24599,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>765.58</v>
+        <v>766.84</v>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>+0.340</t>
+          <t>+1.260</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -24622,15 +24622,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>765.24</v>
+        <v>765.58</v>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -24645,15 +24645,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 08:40:02</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>765.39</v>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>765.24</v>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -24668,15 +24668,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 08:40:02</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>765.05</v>
+        <v>765.39</v>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>-4.700</t>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -24691,15 +24691,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>769.75</v>
+        <v>765.05</v>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-4.700</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -24714,15 +24714,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>770.04</v>
+        <v>769.75</v>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -24737,15 +24737,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>769.95</v>
-      </c>
-      <c r="D103" s="11" t="inlineStr">
-        <is>
-          <t>-0.730</t>
+        <v>770.04</v>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -24760,15 +24760,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>770.6799999999999</v>
+        <v>769.95</v>
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -24783,15 +24783,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:40:23</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>770.47</v>
+        <v>770.6799999999999</v>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -24806,15 +24806,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 07:41:58</t>
+          <t>2026-09-16 09:40:23</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>770.38</v>
+        <v>770.47</v>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -24829,15 +24829,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>770.8</v>
+        <v>770.38</v>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -24852,15 +24852,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>770.8200000000001</v>
+        <v>770.8</v>
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>+0.400</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -24875,15 +24875,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>770.42</v>
+        <v>770.8200000000001</v>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -24898,15 +24898,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>770.24</v>
+        <v>770.42</v>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>-0.810</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -24921,11 +24921,11 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>771.05</v>
+        <v>770.24</v>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
@@ -24944,15 +24944,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>771.86</v>
+        <v>771.05</v>
       </c>
       <c r="D112" s="16" t="inlineStr">
         <is>
-          <t>+1.540</t>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -24967,15 +24967,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>770.3200000000001</v>
-      </c>
-      <c r="D113" s="11" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>771.86</v>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -24990,15 +24990,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>771.76</v>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>-2.140</t>
+        <v>770.3200000000001</v>
+      </c>
+      <c r="D114" s="16" t="inlineStr">
+        <is>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -25013,15 +25013,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12 05:00:53</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>773.9</v>
+        <v>771.76</v>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-2.140</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -25036,15 +25036,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15:57</t>
+          <t>2026-09-12 05:00:53</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>774.33</v>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>-0.730</t>
+        <v>773.9</v>
+      </c>
+      <c r="D116" s="16" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -25059,15 +25059,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-12 02:15:57</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>+1.400</t>
+        <v>774.33</v>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -25082,15 +25082,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>773.66</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>-1.440</t>
+          <t>+1.400</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -25105,15 +25105,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>775.1</v>
+        <v>773.66</v>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>-0.500</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -25128,15 +25128,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:18:12</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>775.6</v>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>-0.410</t>
+        <v>775.1</v>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>-0.500</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -25151,15 +25151,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 09:18:12</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>776.01</v>
+        <v>775.6</v>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -25174,15 +25174,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>776.38</v>
+        <v>776.01</v>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>+0.550</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -25197,15 +25197,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>775.83</v>
-      </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>776.38</v>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -25220,15 +25220,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>776.53</v>
-      </c>
-      <c r="D124" s="15" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>775.83</v>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -25243,15 +25243,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="D125" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.53</v>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -25266,15 +25266,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 06:08:04</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>776.7</v>
+        <v>776.91</v>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>-0.100</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -25289,15 +25289,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 06:08:04</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>776.8</v>
+        <v>776.7</v>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -25312,15 +25312,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>777.27</v>
+        <v>776.8</v>
       </c>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>+0.760</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -25335,15 +25335,15 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>776.51</v>
+        <v>777.27</v>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.760</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -25358,15 +25358,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>776.29</v>
-      </c>
-      <c r="D130" s="16" t="inlineStr">
-        <is>
-          <t>+0.390</t>
+        <v>776.51</v>
+      </c>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -25381,15 +25381,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>775.9</v>
+        <v>776.29</v>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -25404,15 +25404,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>775.58</v>
-      </c>
-      <c r="D132" s="16" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>775.9</v>
+      </c>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -25427,15 +25427,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>775.48</v>
-      </c>
-      <c r="D133" s="11" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>775.58</v>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -25450,15 +25450,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>776.29</v>
+        <v>775.48</v>
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -25473,15 +25473,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 06:18:23</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>776.0700000000001</v>
-      </c>
-      <c r="D135" s="11" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>776.29</v>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -25496,15 +25496,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 06:18:23</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>776.54</v>
-      </c>
-      <c r="D136" s="15" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>776.0700000000001</v>
+      </c>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -25519,15 +25519,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>776.59</v>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>776.54</v>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -25542,15 +25542,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>776.13</v>
-      </c>
-      <c r="D138" s="16" t="inlineStr">
-        <is>
-          <t>+0.810</t>
+        <v>776.59</v>
+      </c>
+      <c r="D138" s="15" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -25565,15 +25565,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>775.3200000000001</v>
-      </c>
-      <c r="D139" s="11" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>776.13</v>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -25588,15 +25588,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 08:56:04</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>775.6900000000001</v>
+        <v>775.3200000000001</v>
       </c>
       <c r="D140" s="16" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -25611,15 +25611,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 07:06:50</t>
+          <t>2026-09-07 08:56:04</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>775.63</v>
-      </c>
-      <c r="D141" s="11" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>775.6900000000001</v>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -25634,15 +25634,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-05 07:06:50</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>776.02</v>
+        <v>775.63</v>
       </c>
       <c r="D142" s="16" t="inlineStr">
         <is>
-          <t>+0.260</t>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -25657,15 +25657,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>775.76</v>
-      </c>
-      <c r="D143" s="11" t="inlineStr">
-        <is>
-          <t>-0.720</t>
+        <v>776.02</v>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -25680,15 +25680,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>776.48</v>
-      </c>
-      <c r="D144" s="15" t="inlineStr">
-        <is>
-          <t>-0.580</t>
+        <v>775.76</v>
+      </c>
+      <c r="D144" s="16" t="inlineStr">
+        <is>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -25703,15 +25703,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>777.0599999999999</v>
+        <v>776.48</v>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.580</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -25726,15 +25726,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 07:59:45</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>777.13</v>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>-0.540</t>
+        <v>777.0599999999999</v>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -25749,15 +25749,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 07:59:45</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>777.67</v>
+        <v>777.13</v>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>-0.300</t>
+          <t>-0.540</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -25772,15 +25772,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>777.97</v>
+        <v>777.67</v>
       </c>
       <c r="D148" s="16" t="inlineStr">
         <is>
-          <t>+1.580</t>
+          <t>-0.300</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -25795,15 +25795,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>776.39</v>
+        <v>777.97</v>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>+1.580</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -25818,15 +25818,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>776.01</v>
-      </c>
-      <c r="D150" s="16" t="inlineStr">
-        <is>
-          <t>+0.660</t>
+        <v>776.39</v>
+      </c>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -25841,15 +25841,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>775.35</v>
+        <v>776.01</v>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>+0.700</t>
+          <t>+0.660</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -25864,15 +25864,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 06:35:56</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>774.65</v>
-      </c>
-      <c r="D152" s="16" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>775.35</v>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>+0.700</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -25887,15 +25887,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 04:09:22</t>
+          <t>2026-09-03 06:35:56</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>774.64</v>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>-0.270</t>
+        <v>774.65</v>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -25910,15 +25910,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 04:09:22</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>774.91</v>
+        <v>774.64</v>
       </c>
       <c r="D154" s="16" t="inlineStr">
         <is>
-          <t>+0.390</t>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -25933,15 +25933,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>774.52</v>
+        <v>774.91</v>
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>+0.230</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -25956,15 +25956,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 17:58:25</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>774.29</v>
+        <v>774.52</v>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.230</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -25979,15 +25979,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 17:58:25</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>774.36</v>
+        <v>774.29</v>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>-0.860</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -26002,15 +26002,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>775.22</v>
+        <v>774.36</v>
       </c>
       <c r="D158" s="16" t="inlineStr">
         <is>
-          <t>+0.350</t>
+          <t>-0.860</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -26025,15 +26025,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 02:48:49</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>774.87</v>
-      </c>
-      <c r="D159" s="11" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>775.22</v>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -26048,15 +26048,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 02:48:49</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>775.47</v>
+        <v>774.87</v>
       </c>
       <c r="D160" s="16" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -26071,15 +26071,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>775.25</v>
-      </c>
-      <c r="D161" s="11" t="inlineStr">
-        <is>
-          <t>-1.030</t>
+        <v>775.47</v>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -26094,15 +26094,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>776.28</v>
-      </c>
-      <c r="D162" s="15" t="inlineStr">
-        <is>
-          <t>-0.280</t>
+        <v>775.25</v>
+      </c>
+      <c r="D162" s="16" t="inlineStr">
+        <is>
+          <t>-1.030</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -26117,15 +26117,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 09:25:49</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>776.5599999999999</v>
+        <v>776.28</v>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -26140,15 +26140,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 06:48:36</t>
+          <t>2026-09-01 09:25:49</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>776.58</v>
-      </c>
-      <c r="D164" s="15" t="inlineStr">
-        <is>
-          <t>-0.050</t>
+        <v>776.5599999999999</v>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -26163,15 +26163,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 02:10:52</t>
+          <t>2026-09-01 06:48:36</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>776.63</v>
-      </c>
-      <c r="D165" s="9" t="inlineStr">
-        <is>
-          <t>+1.230</t>
+        <v>776.58</v>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -26186,15 +26186,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 02:10:52</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>775.4</v>
-      </c>
-      <c r="D166" s="16" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.63</v>
+      </c>
+      <c r="D166" s="15" t="inlineStr">
+        <is>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -26209,15 +26209,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D167" s="11" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>775.4</v>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -26232,15 +26232,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 08:13:17</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>775.92</v>
+        <v>775.22</v>
       </c>
       <c r="D168" s="16" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -26255,15 +26255,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 08:13:17</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>775.85</v>
-      </c>
-      <c r="D169" s="11" t="inlineStr">
-        <is>
-          <t>-2.850</t>
+        <v>775.92</v>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -26278,15 +26278,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>778.7</v>
-      </c>
-      <c r="D170" s="15" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>775.85</v>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t>-2.850</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -26301,15 +26301,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>779.1</v>
-      </c>
-      <c r="D171" s="9" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>778.7</v>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -26324,15 +26324,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>778.72</v>
+        <v>779.1</v>
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>-0.640</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -26347,15 +26347,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>779.36</v>
+        <v>778.72</v>
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>-0.200</t>
+          <t>-0.640</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -26370,15 +26370,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 04:13:31</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>779.5599999999999</v>
+        <v>779.36</v>
       </c>
       <c r="D174" s="16" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -26393,15 +26393,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 04:13:31</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>779.39</v>
-      </c>
-      <c r="D175" s="11" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>779.5599999999999</v>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -26416,15 +26416,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>779.6</v>
-      </c>
-      <c r="D176" s="15" t="inlineStr">
-        <is>
-          <t>-0.430</t>
+        <v>779.39</v>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -26439,15 +26439,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>780.03</v>
+        <v>779.6</v>
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -26462,15 +26462,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 18:53:28</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>780.15</v>
-      </c>
-      <c r="D178" s="15" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>780.03</v>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -26485,15 +26485,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 18:53:28</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>780.62</v>
-      </c>
-      <c r="D179" s="9" t="inlineStr">
-        <is>
-          <t>+0.560</t>
+        <v>780.15</v>
+      </c>
+      <c r="D179" s="11" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -26508,15 +26508,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>780.0599999999999</v>
+        <v>780.62</v>
       </c>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>+0.560</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -26531,15 +26531,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>780.17</v>
+        <v>780.0599999999999</v>
       </c>
       <c r="D181" s="11" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -26554,15 +26554,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>780.38</v>
+        <v>780.17</v>
       </c>
       <c r="D182" s="16" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -26577,15 +26577,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 10:07:59</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>780.36</v>
-      </c>
-      <c r="D183" s="11" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>780.38</v>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -26600,15 +26600,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 07:52:24</t>
+          <t>2026-08-26 10:07:59</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>780.6</v>
+        <v>780.36</v>
       </c>
       <c r="D184" s="16" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -26623,15 +26623,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 01:49:35</t>
+          <t>2026-08-26 07:52:24</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>780.4299999999999</v>
+        <v>780.6</v>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -26646,15 +26646,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 01:49:35</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>780.35</v>
-      </c>
-      <c r="D186" s="16" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>780.4299999999999</v>
+      </c>
+      <c r="D186" s="15" t="inlineStr">
+        <is>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -26669,15 +26669,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.35</v>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>+0.410</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -26692,15 +26692,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:05:53</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>779.9</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>-0.260</t>
+          <t>+0.410</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -26715,15 +26715,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 21:05:53</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>780.16</v>
+        <v>779.9</v>
       </c>
       <c r="D189" s="11" t="inlineStr">
         <is>
-          <t>-0.230</t>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -26738,15 +26738,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>780.39</v>
+        <v>780.16</v>
       </c>
       <c r="D190" s="16" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>-0.230</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -26761,15 +26761,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>780.15</v>
+        <v>780.39</v>
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>+0.540</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -26784,15 +26784,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:26</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>779.61</v>
+        <v>780.15</v>
       </c>
       <c r="D192" s="15" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.540</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -26807,15 +26807,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:01:55</t>
+          <t>2026-08-25 15:51:26</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>779.65</v>
+        <v>779.61</v>
       </c>
       <c r="D193" s="11" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -26830,15 +26830,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 15:01:55</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>779.73</v>
-      </c>
-      <c r="D194" s="15" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>779.65</v>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -26853,15 +26853,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>780.11</v>
+        <v>779.73</v>
       </c>
       <c r="D195" s="11" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -26876,15 +26876,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>780.4</v>
+        <v>780.11</v>
       </c>
       <c r="D196" s="16" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -26899,15 +26899,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:57:56</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.4</v>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -26922,15 +26922,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 06:50:27</t>
+          <t>2026-08-25 09:57:56</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>780.1900000000001</v>
-      </c>
-      <c r="D198" s="16" t="inlineStr">
-        <is>
-          <t>+0.010</t>
+        <v>780.3099999999999</v>
+      </c>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -26945,15 +26945,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 06:50:27</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>780.1799999999999</v>
-      </c>
-      <c r="D199" s="11" t="inlineStr">
-        <is>
-          <t>-0.450</t>
+        <v>780.1900000000001</v>
+      </c>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -26968,15 +26968,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>780.63</v>
+        <v>780.1799999999999</v>
       </c>
       <c r="D200" s="16" t="inlineStr">
         <is>
-          <t>+0.460</t>
+          <t>-0.450</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -26991,15 +26991,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>780.17</v>
-      </c>
-      <c r="D201" s="11" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.63</v>
+      </c>
+      <c r="D201" s="9" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -27014,15 +27014,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>780.61</v>
+        <v>780.17</v>
       </c>
       <c r="D202" s="16" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -27037,15 +27037,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>780.14</v>
-      </c>
-      <c r="D203" s="11" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>780.61</v>
+      </c>
+      <c r="D203" s="9" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -27060,15 +27060,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>780.23</v>
-      </c>
-      <c r="D204" s="15" t="inlineStr">
-        <is>
-          <t>-0.530</t>
+        <v>780.14</v>
+      </c>
+      <c r="D204" s="16" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -27083,15 +27083,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>780.76</v>
+        <v>780.23</v>
       </c>
       <c r="D205" s="11" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -27106,15 +27106,15 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>780.91</v>
-      </c>
-      <c r="D206" s="15" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.76</v>
+      </c>
+      <c r="D206" s="16" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -27129,15 +27129,15 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>781.35</v>
+        <v>780.91</v>
       </c>
       <c r="D207" s="11" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -27152,15 +27152,15 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>781.38</v>
+        <v>781.35</v>
       </c>
       <c r="D208" s="16" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -27175,15 +27175,15 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C209" s="8" t="n">
-        <v>781.09</v>
-      </c>
-      <c r="D209" s="11" t="inlineStr">
-        <is>
-          <t>-0.350</t>
+        <v>781.38</v>
+      </c>
+      <c r="D209" s="9" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -27198,15 +27198,15 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>781.4400000000001</v>
-      </c>
-      <c r="D210" s="15" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>781.09</v>
+      </c>
+      <c r="D210" s="16" t="inlineStr">
+        <is>
+          <t>-0.350</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -27221,15 +27221,15 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
-        <v>781.55</v>
-      </c>
-      <c r="D211" s="9" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.4400000000001</v>
+      </c>
+      <c r="D211" s="11" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -27244,15 +27244,15 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 09:42:15</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>781.23</v>
-      </c>
-      <c r="D212" s="16" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>781.55</v>
+      </c>
+      <c r="D212" s="15" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -27267,15 +27267,15 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 10:32:40</t>
+          <t>2026-08-24 09:42:15</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>781.01</v>
-      </c>
-      <c r="D213" s="11" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>781.23</v>
+      </c>
+      <c r="D213" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -27290,15 +27290,15 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 05:00:11</t>
+          <t>2026-08-22 10:32:40</t>
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>781.11</v>
-      </c>
-      <c r="D214" s="15" t="inlineStr">
-        <is>
-          <t>-0.180</t>
+        <v>781.01</v>
+      </c>
+      <c r="D214" s="16" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -27313,15 +27313,15 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 02:00:51</t>
+          <t>2026-08-22 05:00:11</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>781.29</v>
+        <v>781.11</v>
       </c>
       <c r="D215" s="11" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -27336,15 +27336,15 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-22 02:00:51</t>
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>781.34</v>
+        <v>781.29</v>
       </c>
       <c r="D216" s="16" t="inlineStr">
         <is>
-          <t>+0.550</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -27359,15 +27359,15 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
-        <v>780.79</v>
+        <v>781.34</v>
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -27382,15 +27382,15 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>780.6799999999999</v>
+        <v>780.79</v>
       </c>
       <c r="D218" s="15" t="inlineStr">
         <is>
-          <t>-0.610</t>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -27405,15 +27405,15 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>781.29</v>
+        <v>780.6799999999999</v>
       </c>
       <c r="D219" s="11" t="inlineStr">
         <is>
-          <t>-1.420</t>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -27428,15 +27428,15 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>782.71</v>
-      </c>
-      <c r="D220" s="15" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>781.29</v>
+      </c>
+      <c r="D220" s="16" t="inlineStr">
+        <is>
+          <t>-1.420</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -27451,15 +27451,15 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>782.95</v>
-      </c>
-      <c r="D221" s="9" t="inlineStr">
-        <is>
-          <t>+1.080</t>
+        <v>782.71</v>
+      </c>
+      <c r="D221" s="11" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -27474,15 +27474,15 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>781.87</v>
+        <v>782.95</v>
       </c>
       <c r="D222" s="15" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>+1.080</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -27497,15 +27497,15 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>782.25</v>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>781.87</v>
+      </c>
+      <c r="D223" s="11" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -27520,15 +27520,15 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>781.99</v>
-      </c>
-      <c r="D224" s="16" t="inlineStr">
-        <is>
-          <t>+0.040</t>
+        <v>782.25</v>
+      </c>
+      <c r="D224" s="15" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -27543,15 +27543,15 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>781.95</v>
-      </c>
-      <c r="D225" s="11" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>781.99</v>
+      </c>
+      <c r="D225" s="9" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -27566,15 +27566,15 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>781.99</v>
-      </c>
-      <c r="D226" s="15" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>781.95</v>
+      </c>
+      <c r="D226" s="16" t="inlineStr">
+        <is>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -27589,15 +27589,15 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>782.39</v>
-      </c>
-      <c r="D227" s="9" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>781.99</v>
+      </c>
+      <c r="D227" s="11" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -27612,15 +27612,15 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:13</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C228" s="6" t="n">
-        <v>782.03</v>
-      </c>
-      <c r="D228" s="16" t="inlineStr">
-        <is>
-          <t>+0.400</t>
+        <v>782.39</v>
+      </c>
+      <c r="D228" s="15" t="inlineStr">
+        <is>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -27635,15 +27635,15 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 06:49:01</t>
+          <t>2026-08-21 09:10:13</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>781.63</v>
+        <v>782.03</v>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
@@ -27658,15 +27658,15 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 06:49:01</t>
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>780.95</v>
+        <v>781.63</v>
       </c>
       <c r="D230" s="15" t="inlineStr">
         <is>
-          <t>-0.780</t>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -27681,15 +27681,15 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>781.73</v>
+        <v>780.95</v>
       </c>
       <c r="D231" s="11" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -27704,15 +27704,15 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C232" s="6" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D232" s="15" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>781.73</v>
+      </c>
+      <c r="D232" s="16" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -27727,15 +27727,15 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C233" s="8" t="n">
-        <v>782.1900000000001</v>
-      </c>
-      <c r="D233" s="9" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>781.79</v>
+      </c>
+      <c r="D233" s="11" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
@@ -27750,15 +27750,15 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C234" s="6" t="n">
-        <v>782.04</v>
+        <v>782.1900000000001</v>
       </c>
       <c r="D234" s="15" t="inlineStr">
         <is>
-          <t>-0.700</t>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -27773,15 +27773,15 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>782.74</v>
-      </c>
-      <c r="D235" s="9" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>782.04</v>
+      </c>
+      <c r="D235" s="11" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
@@ -27796,15 +27796,15 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C236" s="6" t="n">
-        <v>782.42</v>
-      </c>
-      <c r="D236" s="16" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>782.74</v>
+      </c>
+      <c r="D236" s="15" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -27819,15 +27819,15 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
-        <v>781.95</v>
+        <v>782.42</v>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
@@ -27842,15 +27842,15 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C238" s="6" t="n">
-        <v>781.14</v>
+        <v>781.95</v>
       </c>
       <c r="D238" s="15" t="inlineStr">
         <is>
-          <t>-0.250</t>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -27865,15 +27865,15 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
-        <v>781.39</v>
-      </c>
-      <c r="D239" s="9" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>781.14</v>
+      </c>
+      <c r="D239" s="11" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
@@ -27888,15 +27888,15 @@
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C240" s="6" t="n">
-        <v>781.2</v>
-      </c>
-      <c r="D240" s="16" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>781.39</v>
+      </c>
+      <c r="D240" s="15" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -27911,15 +27911,15 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C241" s="8" t="n">
-        <v>781.17</v>
-      </c>
-      <c r="D241" s="11" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.2</v>
+      </c>
+      <c r="D241" s="9" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
@@ -27934,15 +27934,15 @@
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 10:06:13</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C242" s="6" t="n">
-        <v>781.42</v>
-      </c>
-      <c r="D242" s="15" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>781.17</v>
+      </c>
+      <c r="D242" s="16" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -27957,15 +27957,15 @@
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 07:36:53</t>
+          <t>2026-08-20 10:06:13</t>
         </is>
       </c>
       <c r="C243" s="8" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D243" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>781.42</v>
+      </c>
+      <c r="D243" s="11" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
@@ -27980,15 +27980,15 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 06:33:42</t>
+          <t>2026-08-20 07:36:53</t>
         </is>
       </c>
       <c r="C244" s="6" t="n">
-        <v>781.77</v>
-      </c>
-      <c r="D244" s="16" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.79</v>
+      </c>
+      <c r="D244" s="15" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -28003,15 +28003,15 @@
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 06:33:42</t>
         </is>
       </c>
       <c r="C245" s="8" t="n">
-        <v>781.45</v>
+        <v>781.77</v>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>+0.850</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
@@ -28026,15 +28026,15 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C246" s="6" t="n">
-        <v>780.6</v>
-      </c>
-      <c r="D246" s="16" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>781.45</v>
+      </c>
+      <c r="D246" s="15" t="inlineStr">
+        <is>
+          <t>+0.850</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
@@ -28049,15 +28049,15 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C247" s="8" t="n">
-        <v>780.12</v>
+        <v>780.6</v>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>+1.750</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
@@ -28072,15 +28072,15 @@
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C248" s="6" t="n">
-        <v>778.37</v>
-      </c>
-      <c r="D248" s="16" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>780.12</v>
+      </c>
+      <c r="D248" s="15" t="inlineStr">
+        <is>
+          <t>+1.750</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -28095,15 +28095,15 @@
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
-        <v>778.09</v>
+        <v>778.37</v>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
@@ -28118,15 +28118,15 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C250" s="6" t="n">
-        <v>777.41</v>
-      </c>
-      <c r="D250" s="16" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>778.09</v>
+      </c>
+      <c r="D250" s="15" t="inlineStr">
+        <is>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
@@ -28141,15 +28141,15 @@
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C251" s="8" t="n">
-        <v>777.3200000000001</v>
+        <v>777.41</v>
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
@@ -28164,13 +28164,13 @@
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C252" s="6" t="n">
-        <v>777.1</v>
-      </c>
-      <c r="D252" s="16" t="inlineStr">
+        <v>777.3200000000001</v>
+      </c>
+      <c r="D252" s="15" t="inlineStr">
         <is>
           <t>+0.220</t>
         </is>
@@ -28187,15 +28187,15 @@
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
-        <v>776.88</v>
-      </c>
-      <c r="D253" s="11" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.1</v>
+      </c>
+      <c r="D253" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
@@ -28210,15 +28210,15 @@
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C254" s="6" t="n">
-        <v>776.89</v>
+        <v>776.88</v>
       </c>
       <c r="D254" s="16" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
@@ -28233,15 +28233,15 @@
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C255" s="8" t="n">
-        <v>776.84</v>
-      </c>
-      <c r="D255" s="11" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>776.89</v>
+      </c>
+      <c r="D255" s="9" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
@@ -28256,15 +28256,15 @@
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 09:12:00</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C256" s="6" t="n">
-        <v>776.9</v>
+        <v>776.84</v>
       </c>
       <c r="D256" s="16" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
@@ -28279,15 +28279,15 @@
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 09:12:00</t>
         </is>
       </c>
       <c r="C257" s="8" t="n">
-        <v>776.72</v>
-      </c>
-      <c r="D257" s="11" t="inlineStr">
-        <is>
-          <t>-0.460</t>
+        <v>776.9</v>
+      </c>
+      <c r="D257" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
@@ -28302,15 +28302,15 @@
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C258" s="6" t="n">
-        <v>777.1799999999999</v>
+        <v>776.72</v>
       </c>
       <c r="D258" s="16" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>-0.460</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
@@ -28325,15 +28325,15 @@
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C259" s="8" t="n">
-        <v>776.55</v>
-      </c>
-      <c r="D259" s="11" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>777.1799999999999</v>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
@@ -28348,15 +28348,15 @@
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:24</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C260" s="6" t="n">
-        <v>776.62</v>
+        <v>776.55</v>
       </c>
       <c r="D260" s="16" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
@@ -28371,15 +28371,15 @@
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 17:58:24</t>
         </is>
       </c>
       <c r="C261" s="8" t="n">
-        <v>776.53</v>
+        <v>776.62</v>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
@@ -28394,15 +28394,15 @@
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C262" s="6" t="n">
-        <v>776.36</v>
+        <v>776.53</v>
       </c>
       <c r="D262" s="15" t="inlineStr">
         <is>
-          <t>-0.160</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
@@ -28417,15 +28417,15 @@
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C263" s="8" t="n">
-        <v>776.52</v>
+        <v>776.36</v>
       </c>
       <c r="D263" s="11" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.160</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
@@ -28440,15 +28440,15 @@
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C264" s="6" t="n">
-        <v>776.53</v>
-      </c>
-      <c r="D264" s="15" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>776.52</v>
+      </c>
+      <c r="D264" s="16" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E264" s="6" t="inlineStr">
@@ -28463,15 +28463,15 @@
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C265" s="8" t="n">
-        <v>776.92</v>
-      </c>
-      <c r="D265" s="9" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>776.53</v>
+      </c>
+      <c r="D265" s="11" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
@@ -28486,15 +28486,15 @@
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 10:04:24</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C266" s="6" t="n">
-        <v>776.8200000000001</v>
-      </c>
-      <c r="D266" s="16" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.92</v>
+      </c>
+      <c r="D266" s="15" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E266" s="6" t="inlineStr">
@@ -28509,15 +28509,15 @@
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 07:54:32</t>
+          <t>2026-08-18 10:04:24</t>
         </is>
       </c>
       <c r="C267" s="8" t="n">
-        <v>776.61</v>
-      </c>
-      <c r="D267" s="11" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>776.8200000000001</v>
+      </c>
+      <c r="D267" s="9" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
@@ -28532,15 +28532,15 @@
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 05:48:09</t>
+          <t>2026-08-18 07:54:32</t>
         </is>
       </c>
       <c r="C268" s="6" t="n">
-        <v>776.74</v>
+        <v>776.61</v>
       </c>
       <c r="D268" s="16" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E268" s="6" t="inlineStr">
@@ -28555,15 +28555,15 @@
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 05:48:09</t>
         </is>
       </c>
       <c r="C269" s="8" t="n">
-        <v>776.5599999999999</v>
-      </c>
-      <c r="D269" s="11" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>776.74</v>
+      </c>
+      <c r="D269" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
@@ -28578,15 +28578,15 @@
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C270" s="6" t="n">
-        <v>777.16</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="D270" s="16" t="inlineStr">
         <is>
-          <t>+0.350</t>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E270" s="6" t="inlineStr">
@@ -28601,15 +28601,15 @@
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C271" s="8" t="n">
-        <v>776.8099999999999</v>
-      </c>
-      <c r="D271" s="11" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>777.16</v>
+      </c>
+      <c r="D271" s="9" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
@@ -28624,15 +28624,15 @@
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:45</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C272" s="6" t="n">
-        <v>777.21</v>
-      </c>
-      <c r="D272" s="15" t="inlineStr">
-        <is>
-          <t>-0.220</t>
+        <v>776.8099999999999</v>
+      </c>
+      <c r="D272" s="16" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
@@ -28647,15 +28647,15 @@
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 21:10:45</t>
         </is>
       </c>
       <c r="C273" s="8" t="n">
-        <v>777.4299999999999</v>
+        <v>777.21</v>
       </c>
       <c r="D273" s="11" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
@@ -28670,15 +28670,15 @@
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C274" s="6" t="n">
-        <v>777.52</v>
+        <v>777.4299999999999</v>
       </c>
       <c r="D274" s="16" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
@@ -28693,15 +28693,15 @@
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C275" s="8" t="n">
-        <v>777.5</v>
+        <v>777.52</v>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>+0.370</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
@@ -28716,15 +28716,15 @@
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C276" s="6" t="n">
-        <v>777.13</v>
-      </c>
-      <c r="D276" s="16" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>777.5</v>
+      </c>
+      <c r="D276" s="15" t="inlineStr">
+        <is>
+          <t>+0.370</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
@@ -28739,15 +28739,15 @@
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C277" s="8" t="n">
-        <v>777.04</v>
+        <v>777.13</v>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
@@ -28762,15 +28762,15 @@
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C278" s="6" t="n">
-        <v>776.9</v>
+        <v>777.04</v>
       </c>
       <c r="D278" s="15" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
@@ -28785,15 +28785,15 @@
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C279" s="8" t="n">
-        <v>776.91</v>
+        <v>776.9</v>
       </c>
       <c r="D279" s="11" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
@@ -28808,15 +28808,15 @@
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C280" s="6" t="n">
-        <v>776.96</v>
+        <v>776.91</v>
       </c>
       <c r="D280" s="16" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E280" s="6" t="inlineStr">
@@ -28831,15 +28831,15 @@
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 09:21:39</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C281" s="8" t="n">
-        <v>776.84</v>
+        <v>776.96</v>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>+0.750</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
@@ -28854,15 +28854,15 @@
       </c>
       <c r="B282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 09:21:39</t>
         </is>
       </c>
       <c r="C282" s="6" t="n">
-        <v>776.09</v>
+        <v>776.84</v>
       </c>
       <c r="D282" s="15" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>+0.750</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
@@ -28877,15 +28877,15 @@
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C283" s="8" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D283" s="9" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>776.09</v>
+      </c>
+      <c r="D283" s="11" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
@@ -28900,15 +28900,15 @@
       </c>
       <c r="B284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C284" s="6" t="n">
-        <v>775.8099999999999</v>
-      </c>
-      <c r="D284" s="16" t="inlineStr">
-        <is>
-          <t>+0.770</t>
+        <v>776.38</v>
+      </c>
+      <c r="D284" s="15" t="inlineStr">
+        <is>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
@@ -28923,15 +28923,15 @@
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C285" s="8" t="n">
-        <v>775.04</v>
+        <v>775.8099999999999</v>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.770</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
@@ -28946,15 +28946,15 @@
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C286" s="6" t="n">
-        <v>774.92</v>
-      </c>
-      <c r="D286" s="16" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>775.04</v>
+      </c>
+      <c r="D286" s="15" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
@@ -28969,15 +28969,15 @@
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C287" s="8" t="n">
-        <v>774.5599999999999</v>
+        <v>774.92</v>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
@@ -28992,15 +28992,15 @@
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C288" s="6" t="n">
-        <v>774.4400000000001</v>
+        <v>774.5599999999999</v>
       </c>
       <c r="D288" s="15" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
@@ -29015,15 +29015,15 @@
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C289" s="8" t="n">
-        <v>774.46</v>
-      </c>
-      <c r="D289" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>774.4400000000001</v>
+      </c>
+      <c r="D289" s="11" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
@@ -29038,15 +29038,15 @@
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C290" s="6" t="n">
-        <v>774.25</v>
-      </c>
-      <c r="D290" s="16" t="inlineStr">
-        <is>
-          <t>+0.310</t>
+        <v>774.46</v>
+      </c>
+      <c r="D290" s="15" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
@@ -29061,15 +29061,15 @@
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 10:39:02</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C291" s="8" t="n">
-        <v>773.9400000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.310</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
@@ -29084,15 +29084,15 @@
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 08:05:13</t>
+          <t>2026-08-14 10:39:02</t>
         </is>
       </c>
       <c r="C292" s="6" t="n">
-        <v>773.9</v>
-      </c>
-      <c r="D292" s="16" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>773.9400000000001</v>
+      </c>
+      <c r="D292" s="15" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
@@ -29107,15 +29107,15 @@
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 07:24:16</t>
+          <t>2026-08-14 08:05:13</t>
         </is>
       </c>
       <c r="C293" s="8" t="n">
-        <v>773.73</v>
+        <v>773.9</v>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
@@ -29130,15 +29130,15 @@
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 07:24:16</t>
         </is>
       </c>
       <c r="C294" s="6" t="n">
-        <v>773.53</v>
+        <v>773.73</v>
       </c>
       <c r="D294" s="15" t="inlineStr">
         <is>
-          <t>-0.790</t>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E294" s="6" t="inlineStr">
@@ -29153,15 +29153,15 @@
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C295" s="8" t="n">
-        <v>774.3200000000001</v>
-      </c>
-      <c r="D295" s="9" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>773.53</v>
+      </c>
+      <c r="D295" s="11" t="inlineStr">
+        <is>
+          <t>-0.790</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
@@ -29176,15 +29176,15 @@
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C296" s="6" t="n">
-        <v>773.75</v>
-      </c>
-      <c r="D296" s="16" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>774.3200000000001</v>
+      </c>
+      <c r="D296" s="15" t="inlineStr">
+        <is>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E296" s="6" t="inlineStr">
@@ -29199,15 +29199,15 @@
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C297" s="8" t="n">
-        <v>773.7</v>
+        <v>773.75</v>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
@@ -29222,15 +29222,15 @@
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C298" s="6" t="n">
-        <v>773.58</v>
-      </c>
-      <c r="D298" s="16" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>773.7</v>
+      </c>
+      <c r="D298" s="15" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E298" s="6" t="inlineStr">
@@ -29245,15 +29245,15 @@
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C299" s="8" t="n">
-        <v>773.33</v>
-      </c>
-      <c r="D299" s="11" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>773.58</v>
+      </c>
+      <c r="D299" s="9" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
@@ -29268,15 +29268,15 @@
       </c>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C300" s="6" t="n">
-        <v>773.39</v>
+        <v>773.33</v>
       </c>
       <c r="D300" s="16" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E300" s="6" t="inlineStr">
@@ -29291,15 +29291,15 @@
       </c>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C301" s="8" t="n">
-        <v>773.11</v>
-      </c>
-      <c r="D301" s="11" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>773.39</v>
+      </c>
+      <c r="D301" s="9" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
@@ -29314,15 +29314,15 @@
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C302" s="6" t="n">
-        <v>773.24</v>
-      </c>
-      <c r="D302" s="15" t="inlineStr">
-        <is>
-          <t>-0.340</t>
+        <v>773.11</v>
+      </c>
+      <c r="D302" s="16" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E302" s="6" t="inlineStr">
@@ -29337,15 +29337,15 @@
       </c>
       <c r="B303" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C303" s="8" t="n">
-        <v>773.58</v>
+        <v>773.24</v>
       </c>
       <c r="D303" s="11" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
@@ -29360,15 +29360,15 @@
       </c>
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C304" s="6" t="n">
-        <v>773.64</v>
-      </c>
-      <c r="D304" s="15" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>773.58</v>
+      </c>
+      <c r="D304" s="16" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E304" s="6" t="inlineStr">
@@ -29383,15 +29383,15 @@
       </c>
       <c r="B305" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C305" s="8" t="n">
-        <v>774.11</v>
+        <v>773.64</v>
       </c>
       <c r="D305" s="11" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
@@ -29406,15 +29406,15 @@
       </c>
       <c r="B306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C306" s="6" t="n">
-        <v>774.3</v>
-      </c>
-      <c r="D306" s="15" t="inlineStr">
-        <is>
-          <t>-0.740</t>
+        <v>774.11</v>
+      </c>
+      <c r="D306" s="16" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E306" s="6" t="inlineStr">
@@ -29429,15 +29429,15 @@
       </c>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C307" s="8" t="n">
-        <v>775.04</v>
-      </c>
-      <c r="D307" s="9" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>774.3</v>
+      </c>
+      <c r="D307" s="11" t="inlineStr">
+        <is>
+          <t>-0.740</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
@@ -29452,15 +29452,15 @@
       </c>
       <c r="B308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C308" s="6" t="n">
-        <v>774.9</v>
-      </c>
-      <c r="D308" s="16" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>775.04</v>
+      </c>
+      <c r="D308" s="15" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E308" s="6" t="inlineStr">
@@ -29475,15 +29475,15 @@
       </c>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C309" s="8" t="n">
-        <v>774.66</v>
+        <v>774.9</v>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
@@ -29498,15 +29498,15 @@
       </c>
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C310" s="6" t="n">
-        <v>774.34</v>
-      </c>
-      <c r="D310" s="16" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>774.66</v>
+      </c>
+      <c r="D310" s="15" t="inlineStr">
+        <is>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E310" s="6" t="inlineStr">
@@ -29521,15 +29521,15 @@
       </c>
       <c r="B311" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C311" s="8" t="n">
-        <v>774.15</v>
-      </c>
-      <c r="D311" s="11" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>774.34</v>
+      </c>
+      <c r="D311" s="9" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
@@ -29544,15 +29544,15 @@
       </c>
       <c r="B312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 13:53:42</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C312" s="6" t="n">
-        <v>774.25</v>
-      </c>
-      <c r="D312" s="15" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>774.15</v>
+      </c>
+      <c r="D312" s="16" t="inlineStr">
+        <is>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E312" s="6" t="inlineStr">
@@ -29567,15 +29567,15 @@
       </c>
       <c r="B313" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 13:53:42</t>
         </is>
       </c>
       <c r="C313" s="8" t="n">
-        <v>774.3200000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D313" s="11" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E313" s="8" t="inlineStr">
@@ -29590,15 +29590,15 @@
       </c>
       <c r="B314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C314" s="6" t="n">
-        <v>774.74</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="D314" s="16" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E314" s="6" t="inlineStr">
@@ -29613,15 +29613,15 @@
       </c>
       <c r="B315" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 01:28:47</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C315" s="8" t="n">
-        <v>774.5</v>
+        <v>774.74</v>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E315" s="8" t="inlineStr">
@@ -29636,15 +29636,15 @@
       </c>
       <c r="B316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 01:28:47</t>
         </is>
       </c>
       <c r="C316" s="6" t="n">
-        <v>774.37</v>
+        <v>774.5</v>
       </c>
       <c r="D316" s="15" t="inlineStr">
         <is>
-          <t>-0.340</t>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E316" s="6" t="inlineStr">
@@ -29659,15 +29659,15 @@
       </c>
       <c r="B317" s="8" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C317" s="8" t="n">
-        <v>774.71</v>
-      </c>
-      <c r="D317" s="9" t="inlineStr">
-        <is>
-          <t>+1.160</t>
+        <v>774.37</v>
+      </c>
+      <c r="D317" s="11" t="inlineStr">
+        <is>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E317" s="8" t="inlineStr">
@@ -29682,15 +29682,15 @@
       </c>
       <c r="B318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C318" s="6" t="n">
-        <v>773.55</v>
+        <v>774.71</v>
       </c>
       <c r="D318" s="15" t="inlineStr">
         <is>
-          <t>-0.520</t>
+          <t>+1.160</t>
         </is>
       </c>
       <c r="E318" s="6" t="inlineStr">
@@ -29705,15 +29705,15 @@
       </c>
       <c r="B319" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C319" s="8" t="n">
-        <v>774.0700000000001</v>
+        <v>773.55</v>
       </c>
       <c r="D319" s="11" t="inlineStr">
         <is>
-          <t>-0.690</t>
+          <t>-0.520</t>
         </is>
       </c>
       <c r="E319" s="8" t="inlineStr">
@@ -29728,15 +29728,15 @@
       </c>
       <c r="B320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C320" s="6" t="n">
-        <v>774.76</v>
-      </c>
-      <c r="D320" s="15" t="inlineStr">
-        <is>
-          <t>-0.550</t>
+        <v>774.0700000000001</v>
+      </c>
+      <c r="D320" s="16" t="inlineStr">
+        <is>
+          <t>-0.690</t>
         </is>
       </c>
       <c r="E320" s="6" t="inlineStr">
@@ -29751,15 +29751,15 @@
       </c>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C321" s="8" t="n">
-        <v>775.3099999999999</v>
+        <v>774.76</v>
       </c>
       <c r="D321" s="11" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E321" s="8" t="inlineStr">
@@ -29774,15 +29774,15 @@
       </c>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C322" s="6" t="n">
-        <v>775.46</v>
-      </c>
-      <c r="D322" s="15" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>775.3099999999999</v>
+      </c>
+      <c r="D322" s="16" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E322" s="6" t="inlineStr">
@@ -29797,15 +29797,15 @@
       </c>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C323" s="8" t="n">
-        <v>775.84</v>
+        <v>775.46</v>
       </c>
       <c r="D323" s="11" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E323" s="8" t="inlineStr">
@@ -29820,15 +29820,15 @@
       </c>
       <c r="B324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 08:05:33</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C324" s="6" t="n">
-        <v>775.9</v>
+        <v>775.84</v>
       </c>
       <c r="D324" s="16" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E324" s="6" t="inlineStr">
@@ -29843,15 +29843,15 @@
       </c>
       <c r="B325" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 08:05:33</t>
         </is>
       </c>
       <c r="C325" s="8" t="n">
-        <v>775.83</v>
+        <v>775.9</v>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E325" s="8" t="inlineStr">
@@ -29866,15 +29866,15 @@
       </c>
       <c r="B326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C326" s="6" t="n">
-        <v>775.2</v>
+        <v>775.83</v>
       </c>
       <c r="D326" s="15" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E326" s="6" t="inlineStr">
@@ -29889,15 +29889,15 @@
       </c>
       <c r="B327" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C327" s="8" t="n">
-        <v>775.28</v>
-      </c>
-      <c r="D327" s="9" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>775.2</v>
+      </c>
+      <c r="D327" s="11" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
@@ -29912,15 +29912,15 @@
       </c>
       <c r="B328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C328" s="6" t="n">
-        <v>775.12</v>
-      </c>
-      <c r="D328" s="16" t="inlineStr">
-        <is>
-          <t>+0.030</t>
+        <v>775.28</v>
+      </c>
+      <c r="D328" s="15" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E328" s="6" t="inlineStr">
@@ -29935,11 +29935,11 @@
       </c>
       <c r="B329" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C329" s="8" t="n">
-        <v>775.09</v>
+        <v>775.12</v>
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
@@ -29958,15 +29958,15 @@
       </c>
       <c r="B330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 18:37:13</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C330" s="6" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D330" s="16" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>775.09</v>
+      </c>
+      <c r="D330" s="15" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E330" s="6" t="inlineStr">
@@ -29981,15 +29981,15 @@
       </c>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 18:37:13</t>
         </is>
       </c>
       <c r="C331" s="8" t="n">
-        <v>774.58</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
@@ -30004,15 +30004,15 @@
       </c>
       <c r="B332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C332" s="6" t="n">
-        <v>774.29</v>
-      </c>
-      <c r="D332" s="16" t="inlineStr">
-        <is>
-          <t>+0.490</t>
+        <v>774.58</v>
+      </c>
+      <c r="D332" s="15" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E332" s="6" t="inlineStr">
@@ -30027,15 +30027,15 @@
       </c>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C333" s="8" t="n">
-        <v>773.8</v>
-      </c>
-      <c r="D333" s="11" t="inlineStr">
-        <is>
-          <t>-0.590</t>
+        <v>774.29</v>
+      </c>
+      <c r="D333" s="9" t="inlineStr">
+        <is>
+          <t>+0.490</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
@@ -30050,14 +30050,37 @@
       </c>
       <c r="B334" s="6" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C334" s="6" t="n">
+        <v>773.8</v>
+      </c>
+      <c r="D334" s="16" t="inlineStr">
+        <is>
+          <t>-0.590</t>
+        </is>
+      </c>
+      <c r="E334" s="6" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="8" t="n">
+        <v>331</v>
+      </c>
+      <c r="B335" s="8" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C334" s="6" t="n">
+      <c r="C335" s="8" t="n">
         <v>774.39</v>
       </c>
-      <c r="D334" s="6" t="inlineStr"/>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="D335" s="8" t="inlineStr"/>
+      <c r="E335" s="8" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>
@@ -30164,7 +30187,7 @@
       <c r="C6" s="6" t="n">
         <v>667.97</v>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>+0.570</t>
         </is>
@@ -30210,7 +30233,7 @@
       <c r="C8" s="6" t="n">
         <v>667.3099999999999</v>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>-0.060</t>
         </is>
@@ -30256,7 +30279,7 @@
       <c r="C10" s="6" t="n">
         <v>667.38</v>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>-0.210</t>
         </is>
@@ -30302,7 +30325,7 @@
       <c r="C12" s="6" t="n">
         <v>667.51</v>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -30348,7 +30371,7 @@
       <c r="C14" s="6" t="n">
         <v>667.4</v>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -30394,7 +30417,7 @@
       <c r="C16" s="6" t="n">
         <v>667.35</v>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>-0.480</t>
         </is>
@@ -30440,7 +30463,7 @@
       <c r="C18" s="6" t="n">
         <v>668.48</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>-0.050</t>
         </is>
@@ -30486,7 +30509,7 @@
       <c r="C20" s="6" t="n">
         <v>668.45</v>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -30532,7 +30555,7 @@
       <c r="C22" s="6" t="n">
         <v>669.12</v>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>-0.600</t>
         </is>
@@ -30578,7 +30601,7 @@
       <c r="C24" s="6" t="n">
         <v>669.23</v>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>+0.500</t>
         </is>
@@ -30624,7 +30647,7 @@
       <c r="C26" s="6" t="n">
         <v>668.59</v>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>+0.140</t>
         </is>
@@ -30670,7 +30693,7 @@
       <c r="C28" s="6" t="n">
         <v>668.8</v>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>+0.330</t>
         </is>
@@ -30716,7 +30739,7 @@
       <c r="C30" s="6" t="n">
         <v>668.71</v>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>-0.520</t>
         </is>
@@ -30762,7 +30785,7 @@
       <c r="C32" s="6" t="n">
         <v>669.34</v>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>-0.140</t>
         </is>
@@ -30808,7 +30831,7 @@
       <c r="C34" s="6" t="n">
         <v>669.9299999999999</v>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>+0.500</t>
         </is>
@@ -30854,7 +30877,7 @@
       <c r="C36" s="6" t="n">
         <v>669.46</v>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>+0.050</t>
         </is>
@@ -30900,7 +30923,7 @@
       <c r="C38" s="6" t="n">
         <v>669.1799999999999</v>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>-0.060</t>
         </is>
@@ -30946,7 +30969,7 @@
       <c r="C40" s="6" t="n">
         <v>668.86</v>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>+0.070</t>
         </is>
@@ -30992,7 +31015,7 @@
       <c r="C42" s="6" t="n">
         <v>668.61</v>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>+0.440</t>
         </is>
@@ -31038,7 +31061,7 @@
       <c r="C44" s="6" t="n">
         <v>668.13</v>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -31084,7 +31107,7 @@
       <c r="C46" s="6" t="n">
         <v>667.79</v>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>+0.140</t>
         </is>
@@ -31130,7 +31153,7 @@
       <c r="C48" s="6" t="n">
         <v>667.66</v>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>-0.100</t>
         </is>
@@ -31176,7 +31199,7 @@
       <c r="C50" s="6" t="n">
         <v>667.89</v>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>-0.140</t>
         </is>
@@ -31222,7 +31245,7 @@
       <c r="C52" s="6" t="n">
         <v>668.0599999999999</v>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>+0.170</t>
         </is>
@@ -31268,7 +31291,7 @@
       <c r="C54" s="6" t="n">
         <v>668.11</v>
       </c>
-      <c r="D54" s="15" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>-0.630</t>
         </is>
@@ -31314,7 +31337,7 @@
       <c r="C56" s="6" t="n">
         <v>668.76</v>
       </c>
-      <c r="D56" s="15" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>-0.190</t>
         </is>
@@ -31360,7 +31383,7 @@
       <c r="C58" s="6" t="n">
         <v>668.9400000000001</v>
       </c>
-      <c r="D58" s="15" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>-0.090</t>
         </is>
@@ -31406,7 +31429,7 @@
       <c r="C60" s="6" t="n">
         <v>668.76</v>
       </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -31452,7 +31475,7 @@
       <c r="C62" s="6" t="n">
         <v>668.8200000000001</v>
       </c>
-      <c r="D62" s="15" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>-0.280</t>
         </is>
@@ -31498,7 +31521,7 @@
       <c r="C64" s="6" t="n">
         <v>669.29</v>
       </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -31544,7 +31567,7 @@
       <c r="C66" s="6" t="n">
         <v>669.39</v>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D66" s="15" t="inlineStr">
         <is>
           <t>+0.220</t>
         </is>
@@ -31590,7 +31613,7 @@
       <c r="C68" s="6" t="n">
         <v>669.02</v>
       </c>
-      <c r="D68" s="15" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -31636,7 +31659,7 @@
       <c r="C70" s="6" t="n">
         <v>668.95</v>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="D70" s="15" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -31682,7 +31705,7 @@
       <c r="C72" s="6" t="n">
         <v>668.87</v>
       </c>
-      <c r="D72" s="15" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>-0.050</t>
         </is>
@@ -31728,7 +31751,7 @@
       <c r="C74" s="6" t="n">
         <v>669.09</v>
       </c>
-      <c r="D74" s="15" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>-0.250</t>
         </is>
@@ -31774,7 +31797,7 @@
       <c r="C76" s="6" t="n">
         <v>669.33</v>
       </c>
-      <c r="D76" s="16" t="inlineStr">
+      <c r="D76" s="15" t="inlineStr">
         <is>
           <t>+0.450</t>
         </is>
@@ -31820,7 +31843,7 @@
       <c r="C78" s="6" t="n">
         <v>668.76</v>
       </c>
-      <c r="D78" s="15" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>-0.150</t>
         </is>
@@ -31866,7 +31889,7 @@
       <c r="C80" s="6" t="n">
         <v>668.97</v>
       </c>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="D80" s="15" t="inlineStr">
         <is>
           <t>+0.190</t>
         </is>
@@ -31912,7 +31935,7 @@
       <c r="C82" s="6" t="n">
         <v>668.95</v>
       </c>
-      <c r="D82" s="16" t="inlineStr">
+      <c r="D82" s="15" t="inlineStr">
         <is>
           <t>+0.070</t>
         </is>
@@ -31958,7 +31981,7 @@
       <c r="C84" s="6" t="n">
         <v>669.14</v>
       </c>
-      <c r="D84" s="15" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -32004,7 +32027,7 @@
       <c r="C86" s="6" t="n">
         <v>669.23</v>
       </c>
-      <c r="D86" s="16" t="inlineStr">
+      <c r="D86" s="15" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -32050,7 +32073,7 @@
       <c r="C88" s="6" t="n">
         <v>669.23</v>
       </c>
-      <c r="D88" s="16" t="inlineStr">
+      <c r="D88" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -32096,7 +32119,7 @@
       <c r="C90" s="6" t="n">
         <v>669.24</v>
       </c>
-      <c r="D90" s="15" t="inlineStr">
+      <c r="D90" s="16" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -32142,7 +32165,7 @@
       <c r="C92" s="6" t="n">
         <v>669.25</v>
       </c>
-      <c r="D92" s="16" t="inlineStr">
+      <c r="D92" s="15" t="inlineStr">
         <is>
           <t>+0.050</t>
         </is>
@@ -32188,7 +32211,7 @@
       <c r="C94" s="6" t="n">
         <v>669.27</v>
       </c>
-      <c r="D94" s="15" t="inlineStr">
+      <c r="D94" s="16" t="inlineStr">
         <is>
           <t>-0.510</t>
         </is>
@@ -32234,7 +32257,7 @@
       <c r="C96" s="6" t="n">
         <v>669.95</v>
       </c>
-      <c r="D96" s="15" t="inlineStr">
+      <c r="D96" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -32280,7 +32303,7 @@
       <c r="C98" s="6" t="n">
         <v>670.03</v>
       </c>
-      <c r="D98" s="16" t="inlineStr">
+      <c r="D98" s="15" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -32326,7 +32349,7 @@
       <c r="C100" s="6" t="n">
         <v>669.9400000000001</v>
       </c>
-      <c r="D100" s="15" t="inlineStr">
+      <c r="D100" s="16" t="inlineStr">
         <is>
           <t>-0.100</t>
         </is>
@@ -32372,7 +32395,7 @@
       <c r="C102" s="6" t="n">
         <v>670.25</v>
       </c>
-      <c r="D102" s="15" t="inlineStr">
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>-0.130</t>
         </is>
@@ -32418,7 +32441,7 @@
       <c r="C104" s="6" t="n">
         <v>670.1900000000001</v>
       </c>
-      <c r="D104" s="15" t="inlineStr">
+      <c r="D104" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -32464,7 +32487,7 @@
       <c r="C106" s="6" t="n">
         <v>670.35</v>
       </c>
-      <c r="D106" s="16" t="inlineStr">
+      <c r="D106" s="15" t="inlineStr">
         <is>
           <t>+0.110</t>
         </is>
@@ -32510,7 +32533,7 @@
       <c r="C108" s="6" t="n">
         <v>670.1</v>
       </c>
-      <c r="D108" s="15" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
         <is>
           <t>-0.120</t>
         </is>
@@ -32556,7 +32579,7 @@
       <c r="C110" s="6" t="n">
         <v>671.14</v>
       </c>
-      <c r="D110" s="16" t="inlineStr">
+      <c r="D110" s="15" t="inlineStr">
         <is>
           <t>+0.930</t>
         </is>
@@ -32602,7 +32625,7 @@
       <c r="C112" s="6" t="n">
         <v>670.11</v>
       </c>
-      <c r="D112" s="15" t="inlineStr">
+      <c r="D112" s="16" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -32648,7 +32671,7 @@
       <c r="C114" s="6" t="n">
         <v>670.24</v>
       </c>
-      <c r="D114" s="15" t="inlineStr">
+      <c r="D114" s="16" t="inlineStr">
         <is>
           <t>-0.180</t>
         </is>
@@ -32694,7 +32717,7 @@
       <c r="C116" s="6" t="n">
         <v>670.34</v>
       </c>
-      <c r="D116" s="16" t="inlineStr">
+      <c r="D116" s="15" t="inlineStr">
         <is>
           <t>+0.150</t>
         </is>
@@ -32740,7 +32763,7 @@
       <c r="C118" s="6" t="n">
         <v>670.1799999999999</v>
       </c>
-      <c r="D118" s="15" t="inlineStr">
+      <c r="D118" s="16" t="inlineStr">
         <is>
           <t>-0.090</t>
         </is>
@@ -32786,7 +32809,7 @@
       <c r="C120" s="6" t="n">
         <v>670.22</v>
       </c>
-      <c r="D120" s="15" t="inlineStr">
+      <c r="D120" s="16" t="inlineStr">
         <is>
           <t>-0.040</t>
         </is>
@@ -32832,7 +32855,7 @@
       <c r="C122" s="6" t="n">
         <v>670.16</v>
       </c>
-      <c r="D122" s="16" t="inlineStr">
+      <c r="D122" s="15" t="inlineStr">
         <is>
           <t>+0.050</t>
         </is>
@@ -32878,7 +32901,7 @@
       <c r="C124" s="6" t="n">
         <v>670.1</v>
       </c>
-      <c r="D124" s="15" t="inlineStr">
+      <c r="D124" s="16" t="inlineStr">
         <is>
           <t>-0.100</t>
         </is>
@@ -32924,7 +32947,7 @@
       <c r="C126" s="6" t="n">
         <v>670.4</v>
       </c>
-      <c r="D126" s="15" t="inlineStr">
+      <c r="D126" s="16" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
@@ -32970,7 +32993,7 @@
       <c r="C128" s="6" t="n">
         <v>670.48</v>
       </c>
-      <c r="D128" s="15" t="inlineStr">
+      <c r="D128" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -33016,7 +33039,7 @@
       <c r="C130" s="6" t="n">
         <v>670.3099999999999</v>
       </c>
-      <c r="D130" s="15" t="inlineStr">
+      <c r="D130" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -33062,7 +33085,7 @@
       <c r="C132" s="6" t="n">
         <v>670.35</v>
       </c>
-      <c r="D132" s="16" t="inlineStr">
+      <c r="D132" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -33108,7 +33131,7 @@
       <c r="C134" s="6" t="n">
         <v>670.4299999999999</v>
       </c>
-      <c r="D134" s="15" t="inlineStr">
+      <c r="D134" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -33154,7 +33177,7 @@
       <c r="C136" s="6" t="n">
         <v>670.4400000000001</v>
       </c>
-      <c r="D136" s="15" t="inlineStr">
+      <c r="D136" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -33200,7 +33223,7 @@
       <c r="C138" s="6" t="n">
         <v>670.46</v>
       </c>
-      <c r="D138" s="16" t="inlineStr">
+      <c r="D138" s="15" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -33246,7 +33269,7 @@
       <c r="C140" s="6" t="n">
         <v>670.45</v>
       </c>
-      <c r="D140" s="15" t="inlineStr">
+      <c r="D140" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -33292,7 +33315,7 @@
       <c r="C142" s="6" t="n">
         <v>670.45</v>
       </c>
-      <c r="D142" s="16" t="inlineStr">
+      <c r="D142" s="15" t="inlineStr">
         <is>
           <t>+0.200</t>
         </is>
@@ -33338,7 +33361,7 @@
       <c r="C144" s="6" t="n">
         <v>670.26</v>
       </c>
-      <c r="D144" s="16" t="inlineStr">
+      <c r="D144" s="15" t="inlineStr">
         <is>
           <t>+0.030</t>
         </is>
@@ -33384,7 +33407,7 @@
       <c r="C146" s="6" t="n">
         <v>670.2</v>
       </c>
-      <c r="D146" s="16" t="inlineStr">
+      <c r="D146" s="15" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -33430,7 +33453,7 @@
       <c r="C148" s="6" t="n">
         <v>670.15</v>
       </c>
-      <c r="D148" s="15" t="inlineStr">
+      <c r="D148" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -33476,7 +33499,7 @@
       <c r="C150" s="6" t="n">
         <v>670.28</v>
       </c>
-      <c r="D150" s="15" t="inlineStr">
+      <c r="D150" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -33522,7 +33545,7 @@
       <c r="C152" s="6" t="n">
         <v>670.28</v>
       </c>
-      <c r="D152" s="15" t="inlineStr">
+      <c r="D152" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -33568,7 +33591,7 @@
       <c r="C154" s="6" t="n">
         <v>670.45</v>
       </c>
-      <c r="D154" s="15" t="inlineStr">
+      <c r="D154" s="16" t="inlineStr">
         <is>
           <t>-0.170</t>
         </is>
@@ -33614,7 +33637,7 @@
       <c r="C156" s="6" t="n">
         <v>670.5</v>
       </c>
-      <c r="D156" s="16" t="inlineStr">
+      <c r="D156" s="15" t="inlineStr">
         <is>
           <t>+0.060</t>
         </is>
@@ -33660,7 +33683,7 @@
       <c r="C158" s="6" t="n">
         <v>670.48</v>
       </c>
-      <c r="D158" s="16" t="inlineStr">
+      <c r="D158" s="15" t="inlineStr">
         <is>
           <t>+0.080</t>
         </is>
@@ -33706,7 +33729,7 @@
       <c r="C160" s="6" t="n">
         <v>670.26</v>
       </c>
-      <c r="D160" s="15" t="inlineStr">
+      <c r="D160" s="16" t="inlineStr">
         <is>
           <t>-0.250</t>
         </is>
@@ -33752,7 +33775,7 @@
       <c r="C162" s="6" t="n">
         <v>670.53</v>
       </c>
-      <c r="D162" s="15" t="inlineStr">
+      <c r="D162" s="16" t="inlineStr">
         <is>
           <t>-0.090</t>
         </is>
@@ -33798,7 +33821,7 @@
       <c r="C164" s="6" t="n">
         <v>670.5599999999999</v>
       </c>
-      <c r="D164" s="15" t="inlineStr">
+      <c r="D164" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -33844,7 +33867,7 @@
       <c r="C166" s="6" t="n">
         <v>670.52</v>
       </c>
-      <c r="D166" s="15" t="inlineStr">
+      <c r="D166" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -33890,7 +33913,7 @@
       <c r="C168" s="6" t="n">
         <v>671.0599999999999</v>
       </c>
-      <c r="D168" s="15" t="inlineStr">
+      <c r="D168" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -33936,7 +33959,7 @@
       <c r="C170" s="6" t="n">
         <v>671.64</v>
       </c>
-      <c r="D170" s="15" t="inlineStr">
+      <c r="D170" s="16" t="inlineStr">
         <is>
           <t>-0.240</t>
         </is>
@@ -33982,7 +34005,7 @@
       <c r="C172" s="6" t="n">
         <v>671.91</v>
       </c>
-      <c r="D172" s="15" t="inlineStr">
+      <c r="D172" s="16" t="inlineStr">
         <is>
           <t>-0.140</t>
         </is>
@@ -34028,7 +34051,7 @@
       <c r="C174" s="6" t="n">
         <v>671.87</v>
       </c>
-      <c r="D174" s="15" t="inlineStr">
+      <c r="D174" s="16" t="inlineStr">
         <is>
           <t>-0.220</t>
         </is>
@@ -34074,7 +34097,7 @@
       <c r="C176" s="6" t="n">
         <v>672.21</v>
       </c>
-      <c r="D176" s="16" t="inlineStr">
+      <c r="D176" s="15" t="inlineStr">
         <is>
           <t>+0.070</t>
         </is>
@@ -34120,7 +34143,7 @@
       <c r="C178" s="6" t="n">
         <v>672.2</v>
       </c>
-      <c r="D178" s="15" t="inlineStr">
+      <c r="D178" s="16" t="inlineStr">
         <is>
           <t>-0.270</t>
         </is>
@@ -34166,7 +34189,7 @@
       <c r="C180" s="6" t="n">
         <v>672.54</v>
       </c>
-      <c r="D180" s="16" t="inlineStr">
+      <c r="D180" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -34212,7 +34235,7 @@
       <c r="C182" s="6" t="n">
         <v>672.36</v>
       </c>
-      <c r="D182" s="15" t="inlineStr">
+      <c r="D182" s="16" t="inlineStr">
         <is>
           <t>-0.010</t>
         </is>
@@ -34258,7 +34281,7 @@
       <c r="C184" s="6" t="n">
         <v>672.4</v>
       </c>
-      <c r="D184" s="15" t="inlineStr">
+      <c r="D184" s="16" t="inlineStr">
         <is>
           <t>-0.140</t>
         </is>
@@ -34304,7 +34327,7 @@
       <c r="C186" s="6" t="n">
         <v>672.52</v>
       </c>
-      <c r="D186" s="16" t="inlineStr">
+      <c r="D186" s="15" t="inlineStr">
         <is>
           <t>+0.110</t>
         </is>
@@ -34350,7 +34373,7 @@
       <c r="C188" s="6" t="n">
         <v>672.21</v>
       </c>
-      <c r="D188" s="16" t="inlineStr">
+      <c r="D188" s="15" t="inlineStr">
         <is>
           <t>+0.040</t>
         </is>
@@ -34396,7 +34419,7 @@
       <c r="C190" s="6" t="n">
         <v>672.14</v>
       </c>
-      <c r="D190" s="16" t="inlineStr">
+      <c r="D190" s="15" t="inlineStr">
         <is>
           <t>+0.200</t>
         </is>
@@ -34442,7 +34465,7 @@
       <c r="C192" s="6" t="n">
         <v>671.96</v>
       </c>
-      <c r="D192" s="15" t="inlineStr">
+      <c r="D192" s="16" t="inlineStr">
         <is>
           <t>-0.060</t>
         </is>
@@ -34488,7 +34511,7 @@
       <c r="C194" s="6" t="n">
         <v>672.22</v>
       </c>
-      <c r="D194" s="15" t="inlineStr">
+      <c r="D194" s="16" t="inlineStr">
         <is>
           <t>-0.040</t>
         </is>
@@ -34534,7 +34557,7 @@
       <c r="C196" s="6" t="n">
         <v>672.36</v>
       </c>
-      <c r="D196" s="16" t="inlineStr">
+      <c r="D196" s="15" t="inlineStr">
         <is>
           <t>+0.120</t>
         </is>
@@ -34580,7 +34603,7 @@
       <c r="C198" s="6" t="n">
         <v>672.23</v>
       </c>
-      <c r="D198" s="15" t="inlineStr">
+      <c r="D198" s="16" t="inlineStr">
         <is>
           <t>-0.130</t>
         </is>
@@ -34626,7 +34649,7 @@
       <c r="C200" s="6" t="n">
         <v>672.26</v>
       </c>
-      <c r="D200" s="16" t="inlineStr">
+      <c r="D200" s="15" t="inlineStr">
         <is>
           <t>+0.020</t>
         </is>
@@ -34672,7 +34695,7 @@
       <c r="C202" s="6" t="n">
         <v>672.3099999999999</v>
       </c>
-      <c r="D202" s="16" t="inlineStr">
+      <c r="D202" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -34718,7 +34741,7 @@
       <c r="C204" s="6" t="n">
         <v>672.47</v>
       </c>
-      <c r="D204" s="15" t="inlineStr">
+      <c r="D204" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -34764,7 +34787,7 @@
       <c r="C206" s="6" t="n">
         <v>672.48</v>
       </c>
-      <c r="D206" s="15" t="inlineStr">
+      <c r="D206" s="16" t="inlineStr">
         <is>
           <t>-0.060</t>
         </is>
@@ -34810,7 +34833,7 @@
       <c r="C208" s="6" t="n">
         <v>672.53</v>
       </c>
-      <c r="D208" s="16" t="inlineStr">
+      <c r="D208" s="15" t="inlineStr">
         <is>
           <t>+0.180</t>
         </is>
@@ -34856,7 +34879,7 @@
       <c r="C210" s="6" t="n">
         <v>672.4299999999999</v>
       </c>
-      <c r="D210" s="15" t="inlineStr">
+      <c r="D210" s="16" t="inlineStr">
         <is>
           <t>-0.030</t>
         </is>
@@ -34902,7 +34925,7 @@
       <c r="C212" s="6" t="n">
         <v>672.63</v>
       </c>
-      <c r="D212" s="16" t="inlineStr">
+      <c r="D212" s="15" t="inlineStr">
         <is>
           <t>+0.060</t>
         </is>
@@ -34948,7 +34971,7 @@
       <c r="C214" s="6" t="n">
         <v>672.55</v>
       </c>
-      <c r="D214" s="16" t="inlineStr">
+      <c r="D214" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -34994,7 +35017,7 @@
       <c r="C216" s="6" t="n">
         <v>672.51</v>
       </c>
-      <c r="D216" s="15" t="inlineStr">
+      <c r="D216" s="16" t="inlineStr">
         <is>
           <t>-0.100</t>
         </is>
@@ -35040,7 +35063,7 @@
       <c r="C218" s="6" t="n">
         <v>672.55</v>
       </c>
-      <c r="D218" s="16" t="inlineStr">
+      <c r="D218" s="15" t="inlineStr">
         <is>
           <t>+0.050</t>
         </is>
@@ -35086,7 +35109,7 @@
       <c r="C220" s="6" t="n">
         <v>672.34</v>
       </c>
-      <c r="D220" s="16" t="inlineStr">
+      <c r="D220" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -35132,7 +35155,7 @@
       <c r="C222" s="6" t="n">
         <v>672.3</v>
       </c>
-      <c r="D222" s="15" t="inlineStr">
+      <c r="D222" s="16" t="inlineStr">
         <is>
           <t>-0.110</t>
         </is>
@@ -35178,7 +35201,7 @@
       <c r="C224" s="6" t="n">
         <v>672.66</v>
       </c>
-      <c r="D224" s="15" t="inlineStr">
+      <c r="D224" s="16" t="inlineStr">
         <is>
           <t>-0.120</t>
         </is>
@@ -35224,7 +35247,7 @@
       <c r="C226" s="6" t="n">
         <v>672.76</v>
       </c>
-      <c r="D226" s="16" t="inlineStr">
+      <c r="D226" s="15" t="inlineStr">
         <is>
           <t>+0.050</t>
         </is>
@@ -35270,7 +35293,7 @@
       <c r="C228" s="6" t="n">
         <v>672.67</v>
       </c>
-      <c r="D228" s="16" t="inlineStr">
+      <c r="D228" s="15" t="inlineStr">
         <is>
           <t>+0.080</t>
         </is>
@@ -35316,7 +35339,7 @@
       <c r="C230" s="6" t="n">
         <v>672.6</v>
       </c>
-      <c r="D230" s="15" t="inlineStr">
+      <c r="D230" s="16" t="inlineStr">
         <is>
           <t>-0.220</t>
         </is>
@@ -35362,7 +35385,7 @@
       <c r="C232" s="6" t="n">
         <v>673.24</v>
       </c>
-      <c r="D232" s="16" t="inlineStr">
+      <c r="D232" s="15" t="inlineStr">
         <is>
           <t>+0.340</t>
         </is>
@@ -35408,7 +35431,7 @@
       <c r="C234" s="6" t="n">
         <v>673.04</v>
       </c>
-      <c r="D234" s="16" t="inlineStr">
+      <c r="D234" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -35454,7 +35477,7 @@
       <c r="C236" s="6" t="n">
         <v>672.79</v>
       </c>
-      <c r="D236" s="15" t="inlineStr">
+      <c r="D236" s="16" t="inlineStr">
         <is>
           <t>-0.240</t>
         </is>
@@ -35500,7 +35523,7 @@
       <c r="C238" s="6" t="n">
         <v>673.02</v>
       </c>
-      <c r="D238" s="16" t="inlineStr">
+      <c r="D238" s="15" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
@@ -35546,7 +35569,7 @@
       <c r="C240" s="6" t="n">
         <v>673.09</v>
       </c>
-      <c r="D240" s="15" t="inlineStr">
+      <c r="D240" s="16" t="inlineStr">
         <is>
           <t>-0.020</t>
         </is>
@@ -35592,7 +35615,7 @@
       <c r="C242" s="6" t="n">
         <v>672.97</v>
       </c>
-      <c r="D242" s="16" t="inlineStr">
+      <c r="D242" s="15" t="inlineStr">
         <is>
           <t>+0.100</t>
         </is>
@@ -35638,7 +35661,7 @@
       <c r="C244" s="6" t="n">
         <v>672.74</v>
       </c>
-      <c r="D244" s="15" t="inlineStr">
+      <c r="D244" s="16" t="inlineStr">
         <is>
           <t>-0.300</t>
         </is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-17 08:28:08</t>
+          <t>更新时间: 2026-10-17 12:49:43</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-17 12:49:43</t>
+          <t>更新时间: 2026-10-17 16:51:51</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-17 16:51:51</t>
+          <t>更新时间: 2026-10-17 20:29:38</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-17 20:29:38</t>
+          <t>更新时间: 2026-10-17 23:50:07</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-17 23:50:07</t>
+          <t>更新时间: 2026-10-18 01:58:24</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 01:58:24</t>
+          <t>更新时间: 2026-10-18 04:13:33</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 04:13:33</t>
+          <t>更新时间: 2026-10-18 06:19:13</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 06:19:13</t>
+          <t>更新时间: 2026-10-18 08:06:00</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 08:06:00</t>
+          <t>更新时间: 2026-10-18 12:21:13</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 12:21:13</t>
+          <t>更新时间: 2026-10-18 16:55:53</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 16:55:53</t>
+          <t>更新时间: 2026-10-18 20:55:18</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 20:55:18</t>
+          <t>更新时间: 2026-10-19 00:16:12</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-19 00:16:12</t>
+          <t>更新时间: 2026-10-19 02:40:03</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-19 02:40:03</t>
+          <t>更新时间: 2026-10-19 05:01:59</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-19 05:01:59</t>
+          <t>更新时间: 2026-10-19 06:58:49</t>
         </is>
       </c>
     </row>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-20 05:38:34</t>
+          <t>更新时间: 2026-10-20 08:37:42</t>
         </is>
       </c>
     </row>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>745.3</v>
+        <v>745.77</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 05:38:30</t>
+          <t>2026-10-20 08:37:37</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E352"/>
+  <dimension ref="A1:E353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23205,7 +23205,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 745.30 | 最高: 782.950 | 最低: 741.220 | 总记录数: 348</t>
+          <t>最新价: 745.77 | 最高: 782.950 | 最低: 741.220 | 总记录数: 349</t>
         </is>
       </c>
     </row>
@@ -23242,15 +23242,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20 05:38:30</t>
+          <t>2026-10-20 08:37:37</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>745.3</v>
+        <v>745.77</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -23265,15 +23265,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 01:25:07</t>
+          <t>2026-10-20 05:38:30</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>745.14</v>
+        <v>745.3</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -23288,15 +23288,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 19:02:37</t>
+          <t>2026-10-20 01:25:07</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>745.02</v>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>-1.730</t>
+        <v>745.14</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -23311,15 +23311,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 13:25:49</t>
+          <t>2026-10-19 19:02:37</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>746.75</v>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>745.02</v>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>-1.730</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -23334,15 +23334,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19 08:53:37</t>
+          <t>2026-10-19 13:25:49</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>746.64</v>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>-1.150</t>
+        <v>746.75</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -23357,15 +23357,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 08:28:03</t>
+          <t>2026-10-19 08:53:37</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>747.79</v>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>+1.500</t>
+        <v>746.64</v>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>-1.150</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -23380,15 +23380,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-17 03:43:23</t>
+          <t>2026-10-17 08:28:03</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>746.29</v>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>747.79</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>+1.500</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -23403,15 +23403,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 00:48:26</t>
+          <t>2026-10-17 03:43:23</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>746.66</v>
+        <v>746.29</v>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>-2.250</t>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16 20:23:43</t>
+          <t>2026-10-17 00:48:26</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>748.91</v>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>+2.020</t>
+        <v>746.66</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>-2.250</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 15:12:09</t>
+          <t>2026-10-16 20:23:43</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>746.89</v>
+        <v>748.91</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>+2.020</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:14:29</t>
+          <t>2026-10-16 15:12:09</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>746.65</v>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>746.89</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 07:54:32</t>
+          <t>2026-10-16 10:14:29</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>746.89</v>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>+0.710</t>
+        <v>746.65</v>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>2026-10-16 02:42:45</t>
+          <t>2026-10-16 07:54:32</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>746.1799999999999</v>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>746.89</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 22:51:56</t>
+          <t>2026-10-16 02:42:45</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>746.3099999999999</v>
+        <v>746.1799999999999</v>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>-1.240</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2026-10-15 18:02:39</t>
+          <t>2026-10-15 22:51:56</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>747.55</v>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>+0.530</t>
+        <v>746.3099999999999</v>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>-1.240</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -23587,15 +23587,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 13:18:14</t>
+          <t>2026-10-15 18:02:39</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>747.02</v>
+        <v>747.55</v>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>+2.980</t>
+          <t>+0.530</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -23610,15 +23610,15 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>2026-10-15 08:47:10</t>
+          <t>2026-10-15 13:18:14</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>744.04</v>
+        <v>747.02</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>+0.740</t>
+          <t>+2.980</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -23633,15 +23633,15 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 06:32:13</t>
+          <t>2026-10-15 08:47:10</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>743.3</v>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>744.04</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>+0.740</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -23656,15 +23656,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-10-15 03:30:59</t>
+          <t>2026-10-15 06:32:13</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>743.3200000000001</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>+2.100</t>
+        <v>743.3</v>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -23679,15 +23679,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 23:23:31</t>
+          <t>2026-10-15 03:30:59</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>741.22</v>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>-4.140</t>
+        <v>743.3200000000001</v>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>+2.100</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -23702,15 +23702,15 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14 18:30:58</t>
+          <t>2026-10-14 23:23:31</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>745.36</v>
+        <v>741.22</v>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>-0.820</t>
+          <t>-4.140</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -23725,15 +23725,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 13:30:58</t>
+          <t>2026-10-14 18:30:58</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>746.1799999999999</v>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>745.36</v>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>-0.820</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -23748,15 +23748,15 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14 08:52:22</t>
+          <t>2026-10-14 13:30:58</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>746.04</v>
+        <v>746.1799999999999</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -23771,15 +23771,15 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 05:57:42</t>
+          <t>2026-10-14 08:52:22</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>745.83</v>
+        <v>746.04</v>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>+0.460</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -23794,15 +23794,15 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2026-10-14 01:42:57</t>
+          <t>2026-10-14 05:57:42</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>745.37</v>
+        <v>745.83</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>+0.520</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -23817,15 +23817,15 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 18:28:00</t>
+          <t>2026-10-14 01:42:57</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>744.85</v>
+        <v>745.37</v>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.520</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -23840,15 +23840,15 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-13 11:09:04</t>
+          <t>2026-10-13 18:28:00</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>744.04</v>
+        <v>744.85</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>+1.170</t>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -23863,15 +23863,15 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 06:35:47</t>
+          <t>2026-10-13 11:09:04</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>742.87</v>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>-1.330</t>
+        <v>744.04</v>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>+1.170</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -23886,15 +23886,15 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12 23:41:57</t>
+          <t>2026-10-13 06:35:47</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>744.2</v>
+        <v>742.87</v>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>-1.920</t>
+          <t>-1.330</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -23909,15 +23909,15 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 14:18:12</t>
+          <t>2026-10-12 23:41:57</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>746.12</v>
+        <v>744.2</v>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-1.920</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -23932,15 +23932,15 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2026-10-12 08:27:33</t>
+          <t>2026-10-12 14:18:12</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>746.55</v>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>+0.640</t>
+        <v>746.12</v>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -23955,15 +23955,15 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 05:51:00</t>
+          <t>2026-10-12 08:27:33</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>745.91</v>
+        <v>746.55</v>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>+0.590</t>
+          <t>+0.640</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -23978,15 +23978,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-10-10 01:31:35</t>
+          <t>2026-10-10 05:51:00</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>745.3200000000001</v>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>-1.300</t>
+        <v>745.91</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>+0.590</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -24001,15 +24001,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 19:31:18</t>
+          <t>2026-10-10 01:31:35</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>746.62</v>
+        <v>745.3200000000001</v>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>-1.510</t>
+          <t>-1.300</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -24024,15 +24024,15 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09 12:43:45</t>
+          <t>2026-10-09 19:31:18</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>748.13</v>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>746.62</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>-1.510</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -24047,15 +24047,15 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 07:57:46</t>
+          <t>2026-10-09 12:43:45</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>747.85</v>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>-0.330</t>
+        <v>748.13</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -24070,15 +24070,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09 03:43:29</t>
+          <t>2026-10-09 07:57:46</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>748.1799999999999</v>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>+1.990</t>
+        <v>747.85</v>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>-0.330</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -24093,15 +24093,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 21:59:30</t>
+          <t>2026-10-09 03:43:29</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>746.1900000000001</v>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>-0.780</t>
+        <v>748.1799999999999</v>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>+1.990</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -24116,15 +24116,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08 14:38:03</t>
+          <t>2026-10-08 21:59:30</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>746.97</v>
+        <v>746.1900000000001</v>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>-0.820</t>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -24139,15 +24139,15 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 08:38:58</t>
+          <t>2026-10-08 14:38:03</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>747.79</v>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>746.97</v>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>-0.820</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -24162,15 +24162,15 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2026-10-08 04:55:36</t>
+          <t>2026-10-08 08:38:58</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>747.61</v>
+        <v>747.79</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>+1.220</t>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -24185,15 +24185,15 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 23:55:26</t>
+          <t>2026-10-08 04:55:36</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>746.39</v>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>-3.090</t>
+        <v>747.61</v>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>+1.220</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -24208,15 +24208,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07 16:54:58</t>
+          <t>2026-10-07 23:55:26</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>749.48</v>
+        <v>746.39</v>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>-1.210</t>
+          <t>-3.090</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -24231,15 +24231,15 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 10:22:51</t>
+          <t>2026-10-07 16:54:58</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>750.6900000000001</v>
+        <v>749.48</v>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>-1.090</t>
+          <t>-1.210</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -24254,15 +24254,15 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07 07:12:13</t>
+          <t>2026-10-07 10:22:51</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>751.78</v>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>750.6900000000001</v>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>-1.090</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -24277,15 +24277,15 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 03:32:01</t>
+          <t>2026-10-07 07:12:13</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>751.53</v>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>751.78</v>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -24300,15 +24300,15 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06 22:12:22</t>
+          <t>2026-10-07 03:32:01</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>751.97</v>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>+3.510</t>
+        <v>751.53</v>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -24323,15 +24323,15 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06 15:13:54</t>
+          <t>2026-10-06 22:12:22</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>748.46</v>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>-0.720</t>
+        <v>751.97</v>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>+3.510</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -24346,15 +24346,15 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2026-10-06 08:58:12</t>
+          <t>2026-10-06 15:13:54</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>749.1799999999999</v>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>+0.620</t>
+        <v>748.46</v>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -24369,15 +24369,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06 03:50:37</t>
+          <t>2026-10-06 08:58:12</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>748.5599999999999</v>
+        <v>749.1799999999999</v>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>+0.710</t>
+          <t>+0.620</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -24392,15 +24392,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05 19:45:53</t>
+          <t>2026-10-06 03:50:37</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>747.85</v>
+        <v>748.5599999999999</v>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>+1.230</t>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -24415,15 +24415,15 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>2026-10-05 12:29:35</t>
+          <t>2026-10-05 19:45:53</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>746.62</v>
-      </c>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>-5.130</t>
+        <v>747.85</v>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -24438,15 +24438,15 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>2026-10-05 07:58:26</t>
+          <t>2026-10-05 12:29:35</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>751.75</v>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>746.62</v>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>-5.130</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -24461,15 +24461,15 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2026-10-03 07:24:10</t>
+          <t>2026-10-05 07:58:26</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>751.58</v>
+        <v>751.75</v>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>+0.430</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -24484,15 +24484,15 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 03:54:13</t>
+          <t>2026-10-03 07:24:10</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>751.15</v>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>-2.800</t>
+        <v>751.58</v>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>+0.430</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -24507,15 +24507,15 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02 23:05:32</t>
+          <t>2026-10-03 03:54:13</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>753.95</v>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>+1.310</t>
+        <v>751.15</v>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>-2.800</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -24530,15 +24530,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02 16:50:38</t>
+          <t>2026-10-02 23:05:32</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>752.64</v>
+        <v>753.95</v>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>+1.940</t>
+          <t>+1.310</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -24553,15 +24553,15 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02 10:28:43</t>
+          <t>2026-10-02 16:50:38</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>750.7</v>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>752.64</v>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>+1.940</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -24576,15 +24576,15 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>2026-10-02 03:52:14</t>
+          <t>2026-10-02 10:28:43</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>750.8099999999999</v>
+        <v>750.7</v>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>-3.460</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -24599,15 +24599,15 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01 22:45:56</t>
+          <t>2026-10-02 03:52:14</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>754.27</v>
+        <v>750.8099999999999</v>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>-1.430</t>
+          <t>-3.460</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -24622,15 +24622,15 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01 15:40:31</t>
+          <t>2026-10-01 22:45:56</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>755.7</v>
+        <v>754.27</v>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>-0.970</t>
+          <t>-1.430</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -24645,15 +24645,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01 09:30:52</t>
+          <t>2026-10-01 15:40:31</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>756.67</v>
-      </c>
-      <c r="D66" s="15" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>755.7</v>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>-0.970</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -24668,15 +24668,15 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01 06:35:22</t>
+          <t>2026-10-01 09:30:52</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>756.61</v>
+        <v>756.67</v>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -24691,15 +24691,15 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01 02:37:20</t>
+          <t>2026-10-01 06:35:22</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>756.5</v>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
-        <is>
-          <t>-1.520</t>
+        <v>756.61</v>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -24714,15 +24714,15 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30 21:52:18</t>
+          <t>2026-10-01 02:37:20</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>758.02</v>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>+1.070</t>
+        <v>756.5</v>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>-1.520</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -24737,15 +24737,15 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30 15:18:20</t>
+          <t>2026-09-30 21:52:18</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>756.95</v>
+        <v>758.02</v>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>+1.070</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -24760,15 +24760,15 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30 09:33:06</t>
+          <t>2026-09-30 15:18:20</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>756.48</v>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>-0.490</t>
+        <v>756.95</v>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -24783,15 +24783,15 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30 06:39:24</t>
+          <t>2026-09-30 09:33:06</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>756.97</v>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>+1.820</t>
+        <v>756.48</v>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>-0.490</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -24806,15 +24806,15 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30 02:44:52</t>
+          <t>2026-09-30 06:39:24</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>755.15</v>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>-1.720</t>
+        <v>756.97</v>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>+1.820</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -24829,15 +24829,15 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29 21:24:10</t>
+          <t>2026-09-30 02:44:52</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>756.87</v>
+        <v>755.15</v>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>-1.250</t>
+          <t>-1.720</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -24852,15 +24852,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 14:50:03</t>
+          <t>2026-09-29 21:24:10</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>758.12</v>
+        <v>756.87</v>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>-1.140</t>
+          <t>-1.250</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -24875,15 +24875,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29 09:07:04</t>
+          <t>2026-09-29 14:50:03</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>759.26</v>
+        <v>758.12</v>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-1.140</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -24898,15 +24898,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 05:25:52</t>
+          <t>2026-09-29 09:07:04</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>759.3200000000001</v>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>+0.110</t>
+        <v>759.26</v>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -24921,15 +24921,15 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>2026-09-28 23:53:17</t>
+          <t>2026-09-29 05:25:52</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>759.21</v>
-      </c>
-      <c r="D78" s="16" t="inlineStr">
-        <is>
-          <t>-1.020</t>
+        <v>759.3200000000001</v>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -24944,15 +24944,15 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2026-09-28 15:35:28</t>
+          <t>2026-09-28 23:53:17</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>760.23</v>
+        <v>759.21</v>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>-0.480</t>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -24967,15 +24967,15 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>2026-09-28 07:09:27</t>
+          <t>2026-09-28 15:35:28</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>760.71</v>
+        <v>760.23</v>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>-1.020</t>
+          <t>-0.480</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -24990,15 +24990,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26 07:27:54</t>
+          <t>2026-09-28 07:09:27</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>761.73</v>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>760.71</v>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -25013,15 +25013,15 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26 04:30:49</t>
+          <t>2026-09-26 07:27:54</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>761.5700000000001</v>
-      </c>
-      <c r="D82" s="16" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>761.73</v>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -25036,15 +25036,15 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26 01:15:26</t>
+          <t>2026-09-26 04:30:49</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>762.27</v>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>+0.790</t>
+        <v>761.5700000000001</v>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -25059,15 +25059,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25 20:15:35</t>
+          <t>2026-09-26 01:15:26</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>761.48</v>
+        <v>762.27</v>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>+1.200</t>
+          <t>+0.790</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -25082,15 +25082,15 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25 14:42:41</t>
+          <t>2026-09-25 20:15:35</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>760.28</v>
+        <v>761.48</v>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+1.200</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -25105,15 +25105,15 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25 01:40:29</t>
+          <t>2026-09-25 14:42:41</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>760.15</v>
+        <v>760.28</v>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>+0.500</t>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -25128,15 +25128,15 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 20:55:26</t>
+          <t>2026-09-25 01:40:29</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>759.65</v>
-      </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>-1.120</t>
+        <v>760.15</v>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>+0.500</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -25151,15 +25151,15 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 15:50:01</t>
+          <t>2026-09-24 20:55:26</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>760.77</v>
-      </c>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>+1.060</t>
+        <v>759.65</v>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>-1.120</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -25174,15 +25174,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 10:50:22</t>
+          <t>2026-09-24 15:50:01</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>759.71</v>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>-0.200</t>
+        <v>760.77</v>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>+1.060</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -25197,15 +25197,15 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24 07:56:20</t>
+          <t>2026-09-24 10:50:22</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>759.91</v>
+        <v>759.71</v>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -25220,15 +25220,15 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 02:27:02</t>
+          <t>2026-09-24 07:56:20</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>760.46</v>
+        <v>759.91</v>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -25243,15 +25243,15 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 22:21:19</t>
+          <t>2026-09-24 02:27:02</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>760.87</v>
+        <v>760.46</v>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>-1.520</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -25266,15 +25266,15 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 17:31:43</t>
+          <t>2026-09-23 22:21:19</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>762.39</v>
+        <v>760.87</v>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>-0.310</t>
+          <t>-1.520</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -25289,15 +25289,15 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 12:39:24</t>
+          <t>2026-09-23 17:31:43</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>762.7</v>
+        <v>762.39</v>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.310</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -25312,15 +25312,15 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23 05:59:14</t>
+          <t>2026-09-23 12:39:24</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>762.89</v>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>762.7</v>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -25335,15 +25335,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23 03:03:22</t>
+          <t>2026-09-23 05:59:14</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>762.41</v>
-      </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>-1.930</t>
+        <v>762.89</v>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -25358,15 +25358,15 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 23:32:15</t>
+          <t>2026-09-23 03:03:22</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>764.34</v>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>+0.250</t>
+        <v>762.41</v>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>-1.930</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -25381,15 +25381,15 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 19:17:55</t>
+          <t>2026-09-22 23:32:15</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>764.09</v>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>-0.680</t>
+        <v>764.34</v>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -25404,15 +25404,15 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00:07</t>
+          <t>2026-09-22 19:17:55</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>764.77</v>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>+0.880</t>
+        <v>764.09</v>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>-0.680</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -25427,15 +25427,15 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 09:01:08</t>
+          <t>2026-09-22 14:00:07</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>763.89</v>
+        <v>764.77</v>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>+0.880</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -25450,15 +25450,15 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22 06:28:11</t>
+          <t>2026-09-22 09:01:08</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>763.73</v>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>-0.670</t>
+        <v>763.89</v>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -25473,15 +25473,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22 02:58:23</t>
+          <t>2026-09-22 06:28:11</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>764.4</v>
+        <v>763.73</v>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>-0.750</t>
+          <t>-0.670</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -25496,15 +25496,15 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 21:54:34</t>
+          <t>2026-09-22 02:58:23</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>765.15</v>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>+0.510</t>
+        <v>764.4</v>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>-0.750</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -25519,15 +25519,15 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:24</t>
+          <t>2026-09-21 21:54:34</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>764.64</v>
-      </c>
-      <c r="D104" s="16" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>765.15</v>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>+0.510</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -25542,15 +25542,15 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>2026-09-21 09:33:28</t>
+          <t>2026-09-21 15:01:24</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>765.11</v>
+        <v>764.64</v>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -25565,15 +25565,15 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 07:12:19</t>
+          <t>2026-09-21 09:33:28</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>765.54</v>
-      </c>
-      <c r="D106" s="15" t="inlineStr">
-        <is>
-          <t>+0.710</t>
+        <v>765.11</v>
+      </c>
+      <c r="D106" s="16" t="inlineStr">
+        <is>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -25588,15 +25588,15 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>2026-09-19 02:24:14</t>
+          <t>2026-09-19 07:12:19</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>764.83</v>
+        <v>765.54</v>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.710</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -25611,15 +25611,15 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 23:09:03</t>
+          <t>2026-09-19 02:24:14</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>764.54</v>
-      </c>
-      <c r="D108" s="16" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>764.83</v>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -25634,15 +25634,15 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 19:42:06</t>
+          <t>2026-09-18 23:09:03</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>764.62</v>
+        <v>764.54</v>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>-0.770</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -25657,15 +25657,15 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:21</t>
+          <t>2026-09-18 19:42:06</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>765.39</v>
+        <v>764.62</v>
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>-0.620</t>
+          <t>-0.770</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -25680,15 +25680,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:32:25</t>
+          <t>2026-09-18 14:32:21</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>766.01</v>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>765.39</v>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>-0.620</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -25703,15 +25703,15 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18 05:47:34</t>
+          <t>2026-09-18 09:32:25</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>765.63</v>
-      </c>
-      <c r="D112" s="16" t="inlineStr">
-        <is>
-          <t>-0.190</t>
+        <v>766.01</v>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -25726,15 +25726,15 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>2026-09-18 02:45:00</t>
+          <t>2026-09-18 05:47:34</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>765.8200000000001</v>
+        <v>765.63</v>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>-1.020</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -25749,15 +25749,15 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 22:56:26</t>
+          <t>2026-09-18 02:45:00</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>766.84</v>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>+1.260</t>
+        <v>765.8200000000001</v>
+      </c>
+      <c r="D114" s="16" t="inlineStr">
+        <is>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -25772,15 +25772,15 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 18:07:47</t>
+          <t>2026-09-17 22:56:26</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>765.58</v>
+        <v>766.84</v>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>+0.340</t>
+          <t>+1.260</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -25795,15 +25795,15 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 13:22:08</t>
+          <t>2026-09-17 18:07:47</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>765.24</v>
-      </c>
-      <c r="D116" s="16" t="inlineStr">
-        <is>
-          <t>-0.150</t>
+        <v>765.58</v>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -25818,15 +25818,15 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 08:40:02</t>
+          <t>2026-09-17 13:22:08</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>765.39</v>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>+0.340</t>
+        <v>765.24</v>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -25841,15 +25841,15 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 06:22:16</t>
+          <t>2026-09-17 08:40:02</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>765.05</v>
-      </c>
-      <c r="D118" s="16" t="inlineStr">
-        <is>
-          <t>-4.700</t>
+        <v>765.39</v>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>+0.340</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -25864,15 +25864,15 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>2026-09-17 03:44:50</t>
+          <t>2026-09-17 06:22:16</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>769.75</v>
+        <v>765.05</v>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-4.700</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -25887,15 +25887,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17 00:47:45</t>
+          <t>2026-09-17 03:44:50</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>770.04</v>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>769.75</v>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -25910,15 +25910,15 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 20:07:43</t>
+          <t>2026-09-17 00:47:45</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>769.95</v>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>-0.730</t>
+        <v>770.04</v>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -25933,15 +25933,15 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 14:44:39</t>
+          <t>2026-09-16 20:07:43</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>770.6799999999999</v>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>769.95</v>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -25956,15 +25956,15 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:40:23</t>
+          <t>2026-09-16 14:44:39</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>770.47</v>
+        <v>770.6799999999999</v>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -25979,15 +25979,15 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16 07:41:58</t>
+          <t>2026-09-16 09:40:23</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>770.38</v>
-      </c>
-      <c r="D124" s="16" t="inlineStr">
-        <is>
-          <t>-0.420</t>
+        <v>770.47</v>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -26002,15 +26002,15 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>2026-09-16 02:30:34</t>
+          <t>2026-09-16 07:41:58</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>770.8</v>
+        <v>770.38</v>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -26025,15 +26025,15 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:46:32</t>
+          <t>2026-09-16 02:30:34</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>770.8200000000001</v>
-      </c>
-      <c r="D126" s="15" t="inlineStr">
-        <is>
-          <t>+0.400</t>
+        <v>770.8</v>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -26048,15 +26048,15 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:05</t>
+          <t>2026-09-15 22:46:32</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>770.42</v>
+        <v>770.8200000000001</v>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -26071,15 +26071,15 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 13:05:49</t>
+          <t>2026-09-15 18:00:05</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>770.24</v>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>770.42</v>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -26094,11 +26094,11 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15 08:24:53</t>
+          <t>2026-09-15 13:05:49</t>
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>771.05</v>
+        <v>770.24</v>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
@@ -26117,15 +26117,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 02:34:51</t>
+          <t>2026-09-15 08:24:53</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>771.86</v>
-      </c>
-      <c r="D130" s="15" t="inlineStr">
-        <is>
-          <t>+1.540</t>
+        <v>771.05</v>
+      </c>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -26140,15 +26140,15 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>2026-09-14 21:08:32</t>
+          <t>2026-09-15 02:34:51</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
-        <v>770.3200000000001</v>
-      </c>
-      <c r="D131" s="11" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>771.86</v>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -26163,15 +26163,15 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:31</t>
+          <t>2026-09-14 21:08:32</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>771.76</v>
+        <v>770.3200000000001</v>
       </c>
       <c r="D132" s="16" t="inlineStr">
         <is>
-          <t>-2.140</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -26186,15 +26186,15 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12 05:00:53</t>
+          <t>2026-09-14 14:26:31</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>773.9</v>
+        <v>771.76</v>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-2.140</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -26209,15 +26209,15 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15:57</t>
+          <t>2026-09-12 05:00:53</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>774.33</v>
+        <v>773.9</v>
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>-0.730</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -26232,15 +26232,15 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 22:59:16</t>
+          <t>2026-09-12 02:15:57</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>775.0599999999999</v>
-      </c>
-      <c r="D135" s="9" t="inlineStr">
-        <is>
-          <t>+1.400</t>
+        <v>774.33</v>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>-0.730</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -26255,15 +26255,15 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:11:12</t>
+          <t>2026-09-11 22:59:16</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>773.66</v>
-      </c>
-      <c r="D136" s="16" t="inlineStr">
-        <is>
-          <t>-1.440</t>
+        <v>775.0599999999999</v>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>+1.400</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -26278,15 +26278,15 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:05:51</t>
+          <t>2026-09-11 19:11:12</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>775.1</v>
+        <v>773.66</v>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>-0.500</t>
+          <t>-1.440</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -26301,15 +26301,15 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:18:12</t>
+          <t>2026-09-11 14:05:51</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>775.6</v>
+        <v>775.1</v>
       </c>
       <c r="D138" s="16" t="inlineStr">
         <is>
-          <t>-0.410</t>
+          <t>-0.500</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -26324,15 +26324,15 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>2026-09-11 03:37:07</t>
+          <t>2026-09-11 09:18:12</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>776.01</v>
+        <v>775.6</v>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.410</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -26347,15 +26347,15 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 01:07:28</t>
+          <t>2026-09-11 03:37:07</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D140" s="15" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>776.01</v>
+      </c>
+      <c r="D140" s="16" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -26370,15 +26370,15 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 21:32:36</t>
+          <t>2026-09-11 01:07:28</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>775.83</v>
-      </c>
-      <c r="D141" s="11" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>776.38</v>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -26393,15 +26393,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 17:08:11</t>
+          <t>2026-09-10 21:32:36</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>776.53</v>
+        <v>775.83</v>
       </c>
       <c r="D142" s="16" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -26416,15 +26416,15 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 12:36:44</t>
+          <t>2026-09-10 17:08:11</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>776.53</v>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -26439,15 +26439,15 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 06:08:04</t>
+          <t>2026-09-10 12:36:44</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>776.7</v>
-      </c>
-      <c r="D144" s="16" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>776.91</v>
+      </c>
+      <c r="D144" s="15" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -26462,15 +26462,15 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10 01:26:06</t>
+          <t>2026-09-10 06:08:04</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>776.8</v>
+        <v>776.7</v>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -26485,15 +26485,15 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 21:54:49</t>
+          <t>2026-09-10 01:26:06</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>777.27</v>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>+0.760</t>
+        <v>776.8</v>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -26508,15 +26508,15 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 17:41:01</t>
+          <t>2026-09-09 21:54:49</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>776.51</v>
+        <v>777.27</v>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.760</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -26531,15 +26531,15 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:09:54</t>
+          <t>2026-09-09 17:41:01</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>776.29</v>
+        <v>776.51</v>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>+0.390</t>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -26554,15 +26554,15 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:34:12</t>
+          <t>2026-09-09 13:09:54</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>775.9</v>
+        <v>776.29</v>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -26577,15 +26577,15 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 21:48:35</t>
+          <t>2026-09-09 01:34:12</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>775.58</v>
+        <v>775.9</v>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -26600,15 +26600,15 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 17:32:10</t>
+          <t>2026-09-08 21:48:35</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>775.48</v>
-      </c>
-      <c r="D151" s="11" t="inlineStr">
-        <is>
-          <t>-0.810</t>
+        <v>775.58</v>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -26623,15 +26623,15 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:02:09</t>
+          <t>2026-09-08 17:32:10</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>776.29</v>
-      </c>
-      <c r="D152" s="15" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>775.48</v>
+      </c>
+      <c r="D152" s="16" t="inlineStr">
+        <is>
+          <t>-0.810</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -26646,15 +26646,15 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 06:18:23</t>
+          <t>2026-09-08 13:02:09</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>776.0700000000001</v>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>-0.470</t>
+        <v>776.29</v>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -26669,15 +26669,15 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08 03:52:03</t>
+          <t>2026-09-08 06:18:23</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>776.54</v>
+        <v>776.0700000000001</v>
       </c>
       <c r="D154" s="16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -26692,15 +26692,15 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>2026-09-08 00:03:45</t>
+          <t>2026-09-08 03:52:03</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>776.59</v>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>776.54</v>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
@@ -26715,15 +26715,15 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 18:41:42</t>
+          <t>2026-09-08 00:03:45</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>776.13</v>
+        <v>776.59</v>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -26738,15 +26738,15 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:02</t>
+          <t>2026-09-07 18:41:42</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>775.3200000000001</v>
-      </c>
-      <c r="D157" s="11" t="inlineStr">
-        <is>
-          <t>-0.370</t>
+        <v>776.13</v>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -26761,15 +26761,15 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07 08:56:04</t>
+          <t>2026-09-07 13:36:02</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>775.6900000000001</v>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>+0.060</t>
+        <v>775.3200000000001</v>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -26784,15 +26784,15 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05 07:06:50</t>
+          <t>2026-09-07 08:56:04</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>775.63</v>
-      </c>
-      <c r="D159" s="11" t="inlineStr">
-        <is>
-          <t>-0.390</t>
+        <v>775.6900000000001</v>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -26807,15 +26807,15 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>2026-09-05 03:06:50</t>
+          <t>2026-09-05 07:06:50</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>776.02</v>
-      </c>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>775.63</v>
+      </c>
+      <c r="D160" s="16" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -26830,15 +26830,15 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 20:44:16</t>
+          <t>2026-09-05 03:06:50</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>775.76</v>
-      </c>
-      <c r="D161" s="11" t="inlineStr">
-        <is>
-          <t>-0.720</t>
+        <v>776.02</v>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -26853,15 +26853,15 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 16:14:43</t>
+          <t>2026-09-04 20:44:16</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>776.48</v>
+        <v>775.76</v>
       </c>
       <c r="D162" s="16" t="inlineStr">
         <is>
-          <t>-0.580</t>
+          <t>-0.720</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -26876,15 +26876,15 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 11:49:01</t>
+          <t>2026-09-04 16:14:43</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>777.0599999999999</v>
+        <v>776.48</v>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.580</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -26899,15 +26899,15 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 07:59:45</t>
+          <t>2026-09-04 11:49:01</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
-        <v>777.13</v>
+        <v>777.0599999999999</v>
       </c>
       <c r="D164" s="16" t="inlineStr">
         <is>
-          <t>-0.540</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -26922,15 +26922,15 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>2026-09-04 03:55:33</t>
+          <t>2026-09-04 07:59:45</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>777.67</v>
+        <v>777.13</v>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>-0.300</t>
+          <t>-0.540</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -26945,15 +26945,15 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04 01:17:57</t>
+          <t>2026-09-04 03:55:33</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>777.97</v>
-      </c>
-      <c r="D166" s="15" t="inlineStr">
-        <is>
-          <t>+1.580</t>
+        <v>777.67</v>
+      </c>
+      <c r="D166" s="16" t="inlineStr">
+        <is>
+          <t>-0.300</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -26968,15 +26968,15 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:49:08</t>
+          <t>2026-09-04 01:17:57</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>776.39</v>
+        <v>777.97</v>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>+0.380</t>
+          <t>+1.580</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -26991,15 +26991,15 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 17:31:11</t>
+          <t>2026-09-03 21:49:08</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>776.01</v>
+        <v>776.39</v>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>+0.660</t>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -27014,15 +27014,15 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:59:10</t>
+          <t>2026-09-03 17:31:11</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>775.35</v>
+        <v>776.01</v>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>+0.700</t>
+          <t>+0.660</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -27037,15 +27037,15 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 06:35:56</t>
+          <t>2026-09-03 12:59:10</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>774.65</v>
+        <v>775.35</v>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.700</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -27060,15 +27060,15 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>2026-09-03 04:09:22</t>
+          <t>2026-09-03 06:35:56</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>774.64</v>
-      </c>
-      <c r="D171" s="11" t="inlineStr">
-        <is>
-          <t>-0.270</t>
+        <v>774.65</v>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -27083,15 +27083,15 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:52:39</t>
+          <t>2026-09-03 04:09:22</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>774.91</v>
-      </c>
-      <c r="D172" s="15" t="inlineStr">
-        <is>
-          <t>+0.390</t>
+        <v>774.64</v>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>-0.270</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -27106,15 +27106,15 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:08:30</t>
+          <t>2026-09-03 01:52:39</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>774.52</v>
+        <v>774.91</v>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>+0.230</t>
+          <t>+0.390</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -27129,15 +27129,15 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 17:58:25</t>
+          <t>2026-09-02 22:08:30</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>774.29</v>
-      </c>
-      <c r="D174" s="16" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>774.52</v>
+      </c>
+      <c r="D174" s="15" t="inlineStr">
+        <is>
+          <t>+0.230</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -27152,15 +27152,15 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 13:49:09</t>
+          <t>2026-09-02 17:58:25</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>774.36</v>
+        <v>774.29</v>
       </c>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>-0.860</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -27175,15 +27175,15 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02 09:12:41</t>
+          <t>2026-09-02 13:49:09</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D176" s="15" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>774.36</v>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t>-0.860</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -27198,15 +27198,15 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>2026-09-02 02:48:49</t>
+          <t>2026-09-02 09:12:41</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>774.87</v>
-      </c>
-      <c r="D177" s="11" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>775.22</v>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -27221,15 +27221,15 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 23:38:29</t>
+          <t>2026-09-02 02:48:49</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>775.47</v>
-      </c>
-      <c r="D178" s="15" t="inlineStr">
-        <is>
-          <t>+0.220</t>
+        <v>774.87</v>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -27244,15 +27244,15 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:53:27</t>
+          <t>2026-09-01 23:38:29</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>775.25</v>
-      </c>
-      <c r="D179" s="11" t="inlineStr">
-        <is>
-          <t>-1.030</t>
+        <v>775.47</v>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -27267,15 +27267,15 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 14:27:01</t>
+          <t>2026-09-01 19:53:27</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>776.28</v>
+        <v>775.25</v>
       </c>
       <c r="D180" s="16" t="inlineStr">
         <is>
-          <t>-0.280</t>
+          <t>-1.030</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -27290,15 +27290,15 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 09:25:49</t>
+          <t>2026-09-01 14:27:01</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>776.5599999999999</v>
+        <v>776.28</v>
       </c>
       <c r="D181" s="11" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.280</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -27313,15 +27313,15 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2026-09-01 06:48:36</t>
+          <t>2026-09-01 09:25:49</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>776.58</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="D182" s="16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -27336,15 +27336,15 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01 02:10:52</t>
+          <t>2026-09-01 06:48:36</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>776.63</v>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
-        <is>
-          <t>+1.230</t>
+        <v>776.58</v>
+      </c>
+      <c r="D183" s="11" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -27359,15 +27359,15 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:48:25</t>
+          <t>2026-09-01 02:10:52</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>775.4</v>
+        <v>776.63</v>
       </c>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>+0.180</t>
+          <t>+1.230</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -27382,15 +27382,15 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31 13:35:34</t>
+          <t>2026-08-31 19:48:25</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>775.22</v>
-      </c>
-      <c r="D185" s="11" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>775.4</v>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -27405,15 +27405,15 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 08:13:17</t>
+          <t>2026-08-31 13:35:34</t>
         </is>
       </c>
       <c r="C186" s="6" t="n">
-        <v>775.92</v>
-      </c>
-      <c r="D186" s="15" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.22</v>
+      </c>
+      <c r="D186" s="16" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -27428,15 +27428,15 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>2026-08-29 06:26:27</t>
+          <t>2026-08-31 08:13:17</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>775.85</v>
-      </c>
-      <c r="D187" s="11" t="inlineStr">
-        <is>
-          <t>-2.850</t>
+        <v>775.92</v>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -27451,15 +27451,15 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:17:26</t>
+          <t>2026-08-29 06:26:27</t>
         </is>
       </c>
       <c r="C188" s="6" t="n">
-        <v>778.7</v>
+        <v>775.85</v>
       </c>
       <c r="D188" s="16" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-2.850</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -27474,15 +27474,15 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>2026-08-28 08:51:27</t>
+          <t>2026-08-28 20:17:26</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>779.1</v>
-      </c>
-      <c r="D189" s="9" t="inlineStr">
-        <is>
-          <t>+0.380</t>
+        <v>778.7</v>
+      </c>
+      <c r="D189" s="11" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -27497,15 +27497,15 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 00:09:31</t>
+          <t>2026-08-28 08:51:27</t>
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>778.72</v>
-      </c>
-      <c r="D190" s="16" t="inlineStr">
-        <is>
-          <t>-0.640</t>
+        <v>779.1</v>
+      </c>
+      <c r="D190" s="15" t="inlineStr">
+        <is>
+          <t>+0.380</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -27520,15 +27520,15 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 12:58:25</t>
+          <t>2026-08-28 00:09:31</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>779.36</v>
+        <v>778.72</v>
       </c>
       <c r="D191" s="11" t="inlineStr">
         <is>
-          <t>-0.200</t>
+          <t>-0.640</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -27543,15 +27543,15 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27 04:13:31</t>
+          <t>2026-08-27 12:58:25</t>
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>779.5599999999999</v>
-      </c>
-      <c r="D192" s="15" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>779.36</v>
+      </c>
+      <c r="D192" s="16" t="inlineStr">
+        <is>
+          <t>-0.200</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -27566,15 +27566,15 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27 02:21:22</t>
+          <t>2026-08-27 04:13:31</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>779.39</v>
-      </c>
-      <c r="D193" s="11" t="inlineStr">
-        <is>
-          <t>-0.210</t>
+        <v>779.5599999999999</v>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -27589,15 +27589,15 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:10:39</t>
+          <t>2026-08-27 02:21:22</t>
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>779.6</v>
+        <v>779.39</v>
       </c>
       <c r="D194" s="16" t="inlineStr">
         <is>
-          <t>-0.430</t>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -27612,15 +27612,15 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:27:32</t>
+          <t>2026-08-26 22:10:39</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>780.03</v>
+        <v>779.6</v>
       </c>
       <c r="D195" s="11" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.430</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -27635,15 +27635,15 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 18:53:28</t>
+          <t>2026-08-26 21:27:32</t>
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>780.15</v>
+        <v>780.03</v>
       </c>
       <c r="D196" s="16" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -27658,15 +27658,15 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:57:40</t>
+          <t>2026-08-26 18:53:28</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>780.62</v>
-      </c>
-      <c r="D197" s="9" t="inlineStr">
-        <is>
-          <t>+0.560</t>
+        <v>780.15</v>
+      </c>
+      <c r="D197" s="11" t="inlineStr">
+        <is>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -27681,15 +27681,15 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 13:53:59</t>
+          <t>2026-08-26 16:57:40</t>
         </is>
       </c>
       <c r="C198" s="6" t="n">
-        <v>780.0599999999999</v>
-      </c>
-      <c r="D198" s="16" t="inlineStr">
-        <is>
-          <t>-0.110</t>
+        <v>780.62</v>
+      </c>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>+0.560</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -27704,15 +27704,15 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 12:05:12</t>
+          <t>2026-08-26 13:53:59</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>780.17</v>
+        <v>780.0599999999999</v>
       </c>
       <c r="D199" s="11" t="inlineStr">
         <is>
-          <t>-0.210</t>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -27727,15 +27727,15 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 11:15:56</t>
+          <t>2026-08-26 12:05:12</t>
         </is>
       </c>
       <c r="C200" s="6" t="n">
-        <v>780.38</v>
-      </c>
-      <c r="D200" s="15" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>780.17</v>
+      </c>
+      <c r="D200" s="16" t="inlineStr">
+        <is>
+          <t>-0.210</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -27750,15 +27750,15 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 10:07:59</t>
+          <t>2026-08-26 11:15:56</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>780.36</v>
-      </c>
-      <c r="D201" s="11" t="inlineStr">
-        <is>
-          <t>-0.240</t>
+        <v>780.38</v>
+      </c>
+      <c r="D201" s="9" t="inlineStr">
+        <is>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -27773,15 +27773,15 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 07:52:24</t>
+          <t>2026-08-26 10:07:59</t>
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>780.6</v>
-      </c>
-      <c r="D202" s="15" t="inlineStr">
-        <is>
-          <t>+0.170</t>
+        <v>780.36</v>
+      </c>
+      <c r="D202" s="16" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -27796,15 +27796,15 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26 01:49:35</t>
+          <t>2026-08-26 07:52:24</t>
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>780.4299999999999</v>
+        <v>780.6</v>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
@@ -27819,15 +27819,15 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-26 00:09:05</t>
+          <t>2026-08-26 01:49:35</t>
         </is>
       </c>
       <c r="C204" s="6" t="n">
-        <v>780.35</v>
+        <v>780.4299999999999</v>
       </c>
       <c r="D204" s="15" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -27842,15 +27842,15 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 22:49:59</t>
+          <t>2026-08-26 00:09:05</t>
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.35</v>
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>+0.410</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
@@ -27865,15 +27865,15 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:05:53</t>
+          <t>2026-08-25 22:49:59</t>
         </is>
       </c>
       <c r="C206" s="6" t="n">
-        <v>779.9</v>
-      </c>
-      <c r="D206" s="16" t="inlineStr">
-        <is>
-          <t>-0.260</t>
+        <v>780.3099999999999</v>
+      </c>
+      <c r="D206" s="15" t="inlineStr">
+        <is>
+          <t>+0.410</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -27888,15 +27888,15 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 18:51:20</t>
+          <t>2026-08-25 21:05:53</t>
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>780.16</v>
+        <v>779.9</v>
       </c>
       <c r="D207" s="11" t="inlineStr">
         <is>
-          <t>-0.230</t>
+          <t>-0.260</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
@@ -27911,15 +27911,15 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:47:35</t>
+          <t>2026-08-25 18:51:20</t>
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>780.39</v>
-      </c>
-      <c r="D208" s="15" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>780.16</v>
+      </c>
+      <c r="D208" s="16" t="inlineStr">
+        <is>
+          <t>-0.230</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -27934,15 +27934,15 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:06:06</t>
+          <t>2026-08-25 17:47:35</t>
         </is>
       </c>
       <c r="C209" s="8" t="n">
-        <v>780.15</v>
+        <v>780.39</v>
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>+0.540</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
@@ -27957,15 +27957,15 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:26</t>
+          <t>2026-08-25 17:06:06</t>
         </is>
       </c>
       <c r="C210" s="6" t="n">
-        <v>779.61</v>
-      </c>
-      <c r="D210" s="16" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>780.15</v>
+      </c>
+      <c r="D210" s="15" t="inlineStr">
+        <is>
+          <t>+0.540</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -27980,15 +27980,15 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:01:55</t>
+          <t>2026-08-25 15:51:26</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
-        <v>779.65</v>
+        <v>779.61</v>
       </c>
       <c r="D211" s="11" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -28003,15 +28003,15 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 13:38:54</t>
+          <t>2026-08-25 15:01:55</t>
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>779.73</v>
+        <v>779.65</v>
       </c>
       <c r="D212" s="16" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -28026,15 +28026,15 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 11:47:39</t>
+          <t>2026-08-25 13:38:54</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>780.11</v>
+        <v>779.73</v>
       </c>
       <c r="D213" s="11" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
@@ -28049,15 +28049,15 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:57:48</t>
+          <t>2026-08-25 11:47:39</t>
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>780.4</v>
-      </c>
-      <c r="D214" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>780.11</v>
+      </c>
+      <c r="D214" s="16" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -28072,15 +28072,15 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:57:56</t>
+          <t>2026-08-25 10:57:48</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>780.3099999999999</v>
+        <v>780.4</v>
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -28095,15 +28095,15 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 06:50:27</t>
+          <t>2026-08-25 09:57:56</t>
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>780.1900000000001</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="D216" s="15" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -28118,15 +28118,15 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25 01:49:07</t>
+          <t>2026-08-25 06:50:27</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
-        <v>780.1799999999999</v>
-      </c>
-      <c r="D217" s="11" t="inlineStr">
-        <is>
-          <t>-0.450</t>
+        <v>780.1900000000001</v>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -28141,15 +28141,15 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25 00:44:05</t>
+          <t>2026-08-25 01:49:07</t>
         </is>
       </c>
       <c r="C218" s="6" t="n">
-        <v>780.63</v>
-      </c>
-      <c r="D218" s="15" t="inlineStr">
-        <is>
-          <t>+0.460</t>
+        <v>780.1799999999999</v>
+      </c>
+      <c r="D218" s="16" t="inlineStr">
+        <is>
+          <t>-0.450</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -28164,15 +28164,15 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 22:41:53</t>
+          <t>2026-08-25 00:44:05</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>780.17</v>
-      </c>
-      <c r="D219" s="11" t="inlineStr">
-        <is>
-          <t>-0.440</t>
+        <v>780.63</v>
+      </c>
+      <c r="D219" s="9" t="inlineStr">
+        <is>
+          <t>+0.460</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -28187,15 +28187,15 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 21:58:18</t>
+          <t>2026-08-24 22:41:53</t>
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>780.61</v>
-      </c>
-      <c r="D220" s="15" t="inlineStr">
-        <is>
-          <t>+0.470</t>
+        <v>780.17</v>
+      </c>
+      <c r="D220" s="16" t="inlineStr">
+        <is>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -28210,15 +28210,15 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 18:44:43</t>
+          <t>2026-08-24 21:58:18</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>780.14</v>
-      </c>
-      <c r="D221" s="11" t="inlineStr">
-        <is>
-          <t>-0.090</t>
+        <v>780.61</v>
+      </c>
+      <c r="D221" s="9" t="inlineStr">
+        <is>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
@@ -28233,15 +28233,15 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 18:01:29</t>
+          <t>2026-08-24 18:44:43</t>
         </is>
       </c>
       <c r="C222" s="6" t="n">
-        <v>780.23</v>
+        <v>780.14</v>
       </c>
       <c r="D222" s="16" t="inlineStr">
         <is>
-          <t>-0.530</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -28256,15 +28256,15 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:49</t>
+          <t>2026-08-24 18:01:29</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>780.76</v>
+        <v>780.23</v>
       </c>
       <c r="D223" s="11" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.530</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
@@ -28279,15 +28279,15 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:37:17</t>
+          <t>2026-08-24 16:23:49</t>
         </is>
       </c>
       <c r="C224" s="6" t="n">
-        <v>780.91</v>
+        <v>780.76</v>
       </c>
       <c r="D224" s="16" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -28302,15 +28302,15 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 14:27:59</t>
+          <t>2026-08-24 15:37:17</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>781.35</v>
+        <v>780.91</v>
       </c>
       <c r="D225" s="11" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
@@ -28325,15 +28325,15 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 13:52:14</t>
+          <t>2026-08-24 14:27:59</t>
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>781.38</v>
-      </c>
-      <c r="D226" s="15" t="inlineStr">
-        <is>
-          <t>+0.290</t>
+        <v>781.35</v>
+      </c>
+      <c r="D226" s="16" t="inlineStr">
+        <is>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -28348,15 +28348,15 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 12:27:25</t>
+          <t>2026-08-24 13:52:14</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>781.09</v>
-      </c>
-      <c r="D227" s="11" t="inlineStr">
-        <is>
-          <t>-0.350</t>
+        <v>781.38</v>
+      </c>
+      <c r="D227" s="9" t="inlineStr">
+        <is>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
@@ -28371,15 +28371,15 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 11:40:15</t>
+          <t>2026-08-24 12:27:25</t>
         </is>
       </c>
       <c r="C228" s="6" t="n">
-        <v>781.4400000000001</v>
+        <v>781.09</v>
       </c>
       <c r="D228" s="16" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.350</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -28394,15 +28394,15 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>2026-08-24 10:49:54</t>
+          <t>2026-08-24 11:40:15</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>781.55</v>
-      </c>
-      <c r="D229" s="9" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>781.4400000000001</v>
+      </c>
+      <c r="D229" s="11" t="inlineStr">
+        <is>
+          <t>-0.110</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
@@ -28417,15 +28417,15 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24 09:42:15</t>
+          <t>2026-08-24 10:49:54</t>
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>781.23</v>
+        <v>781.55</v>
       </c>
       <c r="D230" s="15" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -28440,15 +28440,15 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 10:32:40</t>
+          <t>2026-08-24 09:42:15</t>
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>781.01</v>
-      </c>
-      <c r="D231" s="11" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>781.23</v>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
@@ -28463,15 +28463,15 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 05:00:11</t>
+          <t>2026-08-22 10:32:40</t>
         </is>
       </c>
       <c r="C232" s="6" t="n">
-        <v>781.11</v>
+        <v>781.01</v>
       </c>
       <c r="D232" s="16" t="inlineStr">
         <is>
-          <t>-0.180</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -28486,15 +28486,15 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22 02:00:51</t>
+          <t>2026-08-22 05:00:11</t>
         </is>
       </c>
       <c r="C233" s="8" t="n">
-        <v>781.29</v>
+        <v>781.11</v>
       </c>
       <c r="D233" s="11" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
@@ -28509,15 +28509,15 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-22 01:03:32</t>
+          <t>2026-08-22 02:00:51</t>
         </is>
       </c>
       <c r="C234" s="6" t="n">
-        <v>781.34</v>
-      </c>
-      <c r="D234" s="15" t="inlineStr">
-        <is>
-          <t>+0.550</t>
+        <v>781.29</v>
+      </c>
+      <c r="D234" s="16" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -28532,15 +28532,15 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 23:57:55</t>
+          <t>2026-08-22 01:03:32</t>
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>780.79</v>
+        <v>781.34</v>
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>+0.110</t>
+          <t>+0.550</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
@@ -28555,15 +28555,15 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 22:55:55</t>
+          <t>2026-08-21 23:57:55</t>
         </is>
       </c>
       <c r="C236" s="6" t="n">
-        <v>780.6799999999999</v>
-      </c>
-      <c r="D236" s="16" t="inlineStr">
-        <is>
-          <t>-0.610</t>
+        <v>780.79</v>
+      </c>
+      <c r="D236" s="15" t="inlineStr">
+        <is>
+          <t>+0.110</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -28578,15 +28578,15 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 22:16:15</t>
+          <t>2026-08-21 22:55:55</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
-        <v>781.29</v>
+        <v>780.6799999999999</v>
       </c>
       <c r="D237" s="11" t="inlineStr">
         <is>
-          <t>-1.420</t>
+          <t>-0.610</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
@@ -28601,15 +28601,15 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 18:47:13</t>
+          <t>2026-08-21 22:16:15</t>
         </is>
       </c>
       <c r="C238" s="6" t="n">
-        <v>782.71</v>
+        <v>781.29</v>
       </c>
       <c r="D238" s="16" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-1.420</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -28624,15 +28624,15 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:45:14</t>
+          <t>2026-08-21 18:47:13</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
-        <v>782.95</v>
-      </c>
-      <c r="D239" s="9" t="inlineStr">
-        <is>
-          <t>+1.080</t>
+        <v>782.71</v>
+      </c>
+      <c r="D239" s="11" t="inlineStr">
+        <is>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
@@ -28647,15 +28647,15 @@
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:01:25</t>
+          <t>2026-08-21 17:45:14</t>
         </is>
       </c>
       <c r="C240" s="6" t="n">
-        <v>781.87</v>
-      </c>
-      <c r="D240" s="16" t="inlineStr">
-        <is>
-          <t>-0.380</t>
+        <v>782.95</v>
+      </c>
+      <c r="D240" s="15" t="inlineStr">
+        <is>
+          <t>+1.080</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -28670,15 +28670,15 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:37:38</t>
+          <t>2026-08-21 17:01:25</t>
         </is>
       </c>
       <c r="C241" s="8" t="n">
-        <v>782.25</v>
-      </c>
-      <c r="D241" s="9" t="inlineStr">
-        <is>
-          <t>+0.260</t>
+        <v>781.87</v>
+      </c>
+      <c r="D241" s="11" t="inlineStr">
+        <is>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
@@ -28693,15 +28693,15 @@
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:56</t>
+          <t>2026-08-21 15:37:38</t>
         </is>
       </c>
       <c r="C242" s="6" t="n">
-        <v>781.99</v>
+        <v>782.25</v>
       </c>
       <c r="D242" s="15" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.260</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -28716,15 +28716,15 @@
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:11</t>
+          <t>2026-08-21 14:55:56</t>
         </is>
       </c>
       <c r="C243" s="8" t="n">
-        <v>781.95</v>
-      </c>
-      <c r="D243" s="11" t="inlineStr">
-        <is>
-          <t>-0.040</t>
+        <v>781.99</v>
+      </c>
+      <c r="D243" s="9" t="inlineStr">
+        <is>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
@@ -28739,15 +28739,15 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 12:57:41</t>
+          <t>2026-08-21 14:00:11</t>
         </is>
       </c>
       <c r="C244" s="6" t="n">
-        <v>781.99</v>
+        <v>781.95</v>
       </c>
       <c r="D244" s="16" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -28762,15 +28762,15 @@
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 10:36:10</t>
+          <t>2026-08-21 12:57:41</t>
         </is>
       </c>
       <c r="C245" s="8" t="n">
-        <v>782.39</v>
-      </c>
-      <c r="D245" s="9" t="inlineStr">
-        <is>
-          <t>+0.360</t>
+        <v>781.99</v>
+      </c>
+      <c r="D245" s="11" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
@@ -28785,15 +28785,15 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:13</t>
+          <t>2026-08-21 10:36:10</t>
         </is>
       </c>
       <c r="C246" s="6" t="n">
-        <v>782.03</v>
+        <v>782.39</v>
       </c>
       <c r="D246" s="15" t="inlineStr">
         <is>
-          <t>+0.400</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
@@ -28808,15 +28808,15 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>2026-08-21 06:49:01</t>
+          <t>2026-08-21 09:10:13</t>
         </is>
       </c>
       <c r="C247" s="8" t="n">
-        <v>781.63</v>
+        <v>782.03</v>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.400</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
@@ -28831,15 +28831,15 @@
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21 01:53:21</t>
+          <t>2026-08-21 06:49:01</t>
         </is>
       </c>
       <c r="C248" s="6" t="n">
-        <v>780.95</v>
-      </c>
-      <c r="D248" s="16" t="inlineStr">
-        <is>
-          <t>-0.780</t>
+        <v>781.63</v>
+      </c>
+      <c r="D248" s="15" t="inlineStr">
+        <is>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -28854,15 +28854,15 @@
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 23:54:27</t>
+          <t>2026-08-21 01:53:21</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
-        <v>781.73</v>
+        <v>780.95</v>
       </c>
       <c r="D249" s="11" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.780</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
@@ -28877,15 +28877,15 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 22:54:08</t>
+          <t>2026-08-20 23:54:27</t>
         </is>
       </c>
       <c r="C250" s="6" t="n">
-        <v>781.79</v>
+        <v>781.73</v>
       </c>
       <c r="D250" s="16" t="inlineStr">
         <is>
-          <t>-0.400</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
@@ -28900,15 +28900,15 @@
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 21:33:30</t>
+          <t>2026-08-20 22:54:08</t>
         </is>
       </c>
       <c r="C251" s="8" t="n">
-        <v>782.1900000000001</v>
-      </c>
-      <c r="D251" s="9" t="inlineStr">
-        <is>
-          <t>+0.150</t>
+        <v>781.79</v>
+      </c>
+      <c r="D251" s="11" t="inlineStr">
+        <is>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
@@ -28923,15 +28923,15 @@
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 19:35:07</t>
+          <t>2026-08-20 21:33:30</t>
         </is>
       </c>
       <c r="C252" s="6" t="n">
-        <v>782.04</v>
-      </c>
-      <c r="D252" s="16" t="inlineStr">
-        <is>
-          <t>-0.700</t>
+        <v>782.1900000000001</v>
+      </c>
+      <c r="D252" s="15" t="inlineStr">
+        <is>
+          <t>+0.150</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
@@ -28946,15 +28946,15 @@
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 17:37:09</t>
+          <t>2026-08-20 19:35:07</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
-        <v>782.74</v>
-      </c>
-      <c r="D253" s="9" t="inlineStr">
-        <is>
-          <t>+0.320</t>
+        <v>782.04</v>
+      </c>
+      <c r="D253" s="11" t="inlineStr">
+        <is>
+          <t>-0.700</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
@@ -28969,15 +28969,15 @@
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 16:59:18</t>
+          <t>2026-08-20 17:37:09</t>
         </is>
       </c>
       <c r="C254" s="6" t="n">
-        <v>782.42</v>
+        <v>782.74</v>
       </c>
       <c r="D254" s="15" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
@@ -28992,15 +28992,15 @@
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 15:43:04</t>
+          <t>2026-08-20 16:59:18</t>
         </is>
       </c>
       <c r="C255" s="8" t="n">
-        <v>781.95</v>
+        <v>782.42</v>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>+0.810</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
@@ -29015,15 +29015,15 @@
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 13:40:10</t>
+          <t>2026-08-20 15:43:04</t>
         </is>
       </c>
       <c r="C256" s="6" t="n">
-        <v>781.14</v>
-      </c>
-      <c r="D256" s="16" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.95</v>
+      </c>
+      <c r="D256" s="15" t="inlineStr">
+        <is>
+          <t>+0.810</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
@@ -29038,15 +29038,15 @@
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 12:28:21</t>
+          <t>2026-08-20 13:40:10</t>
         </is>
       </c>
       <c r="C257" s="8" t="n">
-        <v>781.39</v>
-      </c>
-      <c r="D257" s="9" t="inlineStr">
-        <is>
-          <t>+0.190</t>
+        <v>781.14</v>
+      </c>
+      <c r="D257" s="11" t="inlineStr">
+        <is>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
@@ -29061,15 +29061,15 @@
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 11:55:03</t>
+          <t>2026-08-20 12:28:21</t>
         </is>
       </c>
       <c r="C258" s="6" t="n">
-        <v>781.2</v>
+        <v>781.39</v>
       </c>
       <c r="D258" s="15" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
@@ -29084,15 +29084,15 @@
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 11:06:59</t>
+          <t>2026-08-20 11:55:03</t>
         </is>
       </c>
       <c r="C259" s="8" t="n">
-        <v>781.17</v>
-      </c>
-      <c r="D259" s="11" t="inlineStr">
-        <is>
-          <t>-0.250</t>
+        <v>781.2</v>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
+        <is>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
@@ -29107,15 +29107,15 @@
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 10:06:13</t>
+          <t>2026-08-20 11:06:59</t>
         </is>
       </c>
       <c r="C260" s="6" t="n">
-        <v>781.42</v>
+        <v>781.17</v>
       </c>
       <c r="D260" s="16" t="inlineStr">
         <is>
-          <t>-0.370</t>
+          <t>-0.250</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
@@ -29130,15 +29130,15 @@
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 07:36:53</t>
+          <t>2026-08-20 10:06:13</t>
         </is>
       </c>
       <c r="C261" s="8" t="n">
-        <v>781.79</v>
-      </c>
-      <c r="D261" s="9" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>781.42</v>
+      </c>
+      <c r="D261" s="11" t="inlineStr">
+        <is>
+          <t>-0.370</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
@@ -29153,15 +29153,15 @@
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20 06:33:42</t>
+          <t>2026-08-20 07:36:53</t>
         </is>
       </c>
       <c r="C262" s="6" t="n">
-        <v>781.77</v>
+        <v>781.79</v>
       </c>
       <c r="D262" s="15" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
@@ -29176,15 +29176,15 @@
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>2026-08-20 01:33:05</t>
+          <t>2026-08-20 06:33:42</t>
         </is>
       </c>
       <c r="C263" s="8" t="n">
-        <v>781.45</v>
+        <v>781.77</v>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>+0.850</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
@@ -29199,15 +29199,15 @@
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 22:26:14</t>
+          <t>2026-08-20 01:33:05</t>
         </is>
       </c>
       <c r="C264" s="6" t="n">
-        <v>780.6</v>
+        <v>781.45</v>
       </c>
       <c r="D264" s="15" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.850</t>
         </is>
       </c>
       <c r="E264" s="6" t="inlineStr">
@@ -29222,15 +29222,15 @@
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 21:55:54</t>
+          <t>2026-08-19 22:26:14</t>
         </is>
       </c>
       <c r="C265" s="8" t="n">
-        <v>780.12</v>
+        <v>780.6</v>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>+1.750</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
@@ -29245,15 +29245,15 @@
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 19:26:19</t>
+          <t>2026-08-19 21:55:54</t>
         </is>
       </c>
       <c r="C266" s="6" t="n">
-        <v>778.37</v>
+        <v>780.12</v>
       </c>
       <c r="D266" s="15" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>+1.750</t>
         </is>
       </c>
       <c r="E266" s="6" t="inlineStr">
@@ -29268,15 +29268,15 @@
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 18:36:46</t>
+          <t>2026-08-19 19:26:19</t>
         </is>
       </c>
       <c r="C267" s="8" t="n">
-        <v>778.09</v>
+        <v>778.37</v>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>+0.680</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
@@ -29291,15 +29291,15 @@
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:59</t>
+          <t>2026-08-19 18:36:46</t>
         </is>
       </c>
       <c r="C268" s="6" t="n">
-        <v>777.41</v>
+        <v>778.09</v>
       </c>
       <c r="D268" s="15" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.680</t>
         </is>
       </c>
       <c r="E268" s="6" t="inlineStr">
@@ -29314,15 +29314,15 @@
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 15:09:17</t>
+          <t>2026-08-19 16:18:59</t>
         </is>
       </c>
       <c r="C269" s="8" t="n">
-        <v>777.3200000000001</v>
+        <v>777.41</v>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>+0.220</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
@@ -29337,11 +29337,11 @@
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 14:17:43</t>
+          <t>2026-08-19 15:09:17</t>
         </is>
       </c>
       <c r="C270" s="6" t="n">
-        <v>777.1</v>
+        <v>777.3200000000001</v>
       </c>
       <c r="D270" s="15" t="inlineStr">
         <is>
@@ -29360,15 +29360,15 @@
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 13:15:22</t>
+          <t>2026-08-19 14:17:43</t>
         </is>
       </c>
       <c r="C271" s="8" t="n">
-        <v>776.88</v>
-      </c>
-      <c r="D271" s="11" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.1</v>
+      </c>
+      <c r="D271" s="9" t="inlineStr">
+        <is>
+          <t>+0.220</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
@@ -29383,15 +29383,15 @@
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 11:26:00</t>
+          <t>2026-08-19 13:15:22</t>
         </is>
       </c>
       <c r="C272" s="6" t="n">
-        <v>776.89</v>
-      </c>
-      <c r="D272" s="15" t="inlineStr">
-        <is>
-          <t>+0.050</t>
+        <v>776.88</v>
+      </c>
+      <c r="D272" s="16" t="inlineStr">
+        <is>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
@@ -29406,15 +29406,15 @@
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 10:31:20</t>
+          <t>2026-08-19 11:26:00</t>
         </is>
       </c>
       <c r="C273" s="8" t="n">
-        <v>776.84</v>
-      </c>
-      <c r="D273" s="11" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>776.89</v>
+      </c>
+      <c r="D273" s="9" t="inlineStr">
+        <is>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
@@ -29429,15 +29429,15 @@
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 09:12:00</t>
+          <t>2026-08-19 10:31:20</t>
         </is>
       </c>
       <c r="C274" s="6" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D274" s="15" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.84</v>
+      </c>
+      <c r="D274" s="16" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
@@ -29452,15 +29452,15 @@
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>2026-08-19 06:08:03</t>
+          <t>2026-08-19 09:12:00</t>
         </is>
       </c>
       <c r="C275" s="8" t="n">
-        <v>776.72</v>
-      </c>
-      <c r="D275" s="11" t="inlineStr">
-        <is>
-          <t>-0.460</t>
+        <v>776.9</v>
+      </c>
+      <c r="D275" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
@@ -29475,15 +29475,15 @@
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-19 01:14:28</t>
+          <t>2026-08-19 06:08:03</t>
         </is>
       </c>
       <c r="C276" s="6" t="n">
-        <v>777.1799999999999</v>
-      </c>
-      <c r="D276" s="15" t="inlineStr">
-        <is>
-          <t>+0.630</t>
+        <v>776.72</v>
+      </c>
+      <c r="D276" s="16" t="inlineStr">
+        <is>
+          <t>-0.460</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
@@ -29498,15 +29498,15 @@
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:14</t>
+          <t>2026-08-19 01:14:28</t>
         </is>
       </c>
       <c r="C277" s="8" t="n">
-        <v>776.55</v>
-      </c>
-      <c r="D277" s="11" t="inlineStr">
-        <is>
-          <t>-0.070</t>
+        <v>777.1799999999999</v>
+      </c>
+      <c r="D277" s="9" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
@@ -29521,15 +29521,15 @@
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 17:58:24</t>
+          <t>2026-08-18 21:01:14</t>
         </is>
       </c>
       <c r="C278" s="6" t="n">
-        <v>776.62</v>
-      </c>
-      <c r="D278" s="15" t="inlineStr">
-        <is>
-          <t>+0.090</t>
+        <v>776.55</v>
+      </c>
+      <c r="D278" s="16" t="inlineStr">
+        <is>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
@@ -29544,15 +29544,15 @@
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 16:56:50</t>
+          <t>2026-08-18 17:58:24</t>
         </is>
       </c>
       <c r="C279" s="8" t="n">
-        <v>776.53</v>
+        <v>776.62</v>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
@@ -29567,15 +29567,15 @@
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:46</t>
+          <t>2026-08-18 16:56:50</t>
         </is>
       </c>
       <c r="C280" s="6" t="n">
-        <v>776.36</v>
-      </c>
-      <c r="D280" s="16" t="inlineStr">
-        <is>
-          <t>-0.160</t>
+        <v>776.53</v>
+      </c>
+      <c r="D280" s="15" t="inlineStr">
+        <is>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E280" s="6" t="inlineStr">
@@ -29590,15 +29590,15 @@
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 14:18:13</t>
+          <t>2026-08-18 15:08:46</t>
         </is>
       </c>
       <c r="C281" s="8" t="n">
-        <v>776.52</v>
+        <v>776.36</v>
       </c>
       <c r="D281" s="11" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.160</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
@@ -29613,15 +29613,15 @@
       </c>
       <c r="B282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 12:56:41</t>
+          <t>2026-08-18 14:18:13</t>
         </is>
       </c>
       <c r="C282" s="6" t="n">
-        <v>776.53</v>
+        <v>776.52</v>
       </c>
       <c r="D282" s="16" t="inlineStr">
         <is>
-          <t>-0.390</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
@@ -29636,15 +29636,15 @@
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 11:04:20</t>
+          <t>2026-08-18 12:56:41</t>
         </is>
       </c>
       <c r="C283" s="8" t="n">
-        <v>776.92</v>
-      </c>
-      <c r="D283" s="9" t="inlineStr">
-        <is>
-          <t>+0.100</t>
+        <v>776.53</v>
+      </c>
+      <c r="D283" s="11" t="inlineStr">
+        <is>
+          <t>-0.390</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
@@ -29659,15 +29659,15 @@
       </c>
       <c r="B284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 10:04:24</t>
+          <t>2026-08-18 11:04:20</t>
         </is>
       </c>
       <c r="C284" s="6" t="n">
-        <v>776.8200000000001</v>
+        <v>776.92</v>
       </c>
       <c r="D284" s="15" t="inlineStr">
         <is>
-          <t>+0.210</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
@@ -29682,15 +29682,15 @@
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 07:54:32</t>
+          <t>2026-08-18 10:04:24</t>
         </is>
       </c>
       <c r="C285" s="8" t="n">
-        <v>776.61</v>
-      </c>
-      <c r="D285" s="11" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>776.8200000000001</v>
+      </c>
+      <c r="D285" s="9" t="inlineStr">
+        <is>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
@@ -29705,15 +29705,15 @@
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 05:48:09</t>
+          <t>2026-08-18 07:54:32</t>
         </is>
       </c>
       <c r="C286" s="6" t="n">
-        <v>776.74</v>
-      </c>
-      <c r="D286" s="15" t="inlineStr">
-        <is>
-          <t>+0.180</t>
+        <v>776.61</v>
+      </c>
+      <c r="D286" s="16" t="inlineStr">
+        <is>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
@@ -29728,15 +29728,15 @@
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>2026-08-18 04:58:00</t>
+          <t>2026-08-18 05:48:09</t>
         </is>
       </c>
       <c r="C287" s="8" t="n">
-        <v>776.5599999999999</v>
-      </c>
-      <c r="D287" s="11" t="inlineStr">
-        <is>
-          <t>-0.600</t>
+        <v>776.74</v>
+      </c>
+      <c r="D287" s="9" t="inlineStr">
+        <is>
+          <t>+0.180</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
@@ -29751,15 +29751,15 @@
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 02:00:33</t>
+          <t>2026-08-18 04:58:00</t>
         </is>
       </c>
       <c r="C288" s="6" t="n">
-        <v>777.16</v>
-      </c>
-      <c r="D288" s="15" t="inlineStr">
-        <is>
-          <t>+0.350</t>
+        <v>776.5599999999999</v>
+      </c>
+      <c r="D288" s="16" t="inlineStr">
+        <is>
+          <t>-0.600</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
@@ -29774,15 +29774,15 @@
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 23:53:16</t>
+          <t>2026-08-18 02:00:33</t>
         </is>
       </c>
       <c r="C289" s="8" t="n">
-        <v>776.8099999999999</v>
-      </c>
-      <c r="D289" s="11" t="inlineStr">
-        <is>
-          <t>-0.400</t>
+        <v>777.16</v>
+      </c>
+      <c r="D289" s="9" t="inlineStr">
+        <is>
+          <t>+0.350</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
@@ -29797,15 +29797,15 @@
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:45</t>
+          <t>2026-08-17 23:53:16</t>
         </is>
       </c>
       <c r="C290" s="6" t="n">
-        <v>777.21</v>
+        <v>776.8099999999999</v>
       </c>
       <c r="D290" s="16" t="inlineStr">
         <is>
-          <t>-0.220</t>
+          <t>-0.400</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
@@ -29820,15 +29820,15 @@
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 18:42:12</t>
+          <t>2026-08-17 21:10:45</t>
         </is>
       </c>
       <c r="C291" s="8" t="n">
-        <v>777.4299999999999</v>
+        <v>777.21</v>
       </c>
       <c r="D291" s="11" t="inlineStr">
         <is>
-          <t>-0.090</t>
+          <t>-0.220</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
@@ -29843,15 +29843,15 @@
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 18:03:55</t>
+          <t>2026-08-17 18:42:12</t>
         </is>
       </c>
       <c r="C292" s="6" t="n">
-        <v>777.52</v>
-      </c>
-      <c r="D292" s="15" t="inlineStr">
-        <is>
-          <t>+0.020</t>
+        <v>777.4299999999999</v>
+      </c>
+      <c r="D292" s="16" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
@@ -29866,15 +29866,15 @@
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:59:48</t>
+          <t>2026-08-17 18:03:55</t>
         </is>
       </c>
       <c r="C293" s="8" t="n">
-        <v>777.5</v>
+        <v>777.52</v>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>+0.370</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
@@ -29889,15 +29889,15 @@
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:12:21</t>
+          <t>2026-08-17 15:59:48</t>
         </is>
       </c>
       <c r="C294" s="6" t="n">
-        <v>777.13</v>
+        <v>777.5</v>
       </c>
       <c r="D294" s="15" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.370</t>
         </is>
       </c>
       <c r="E294" s="6" t="inlineStr">
@@ -29912,15 +29912,15 @@
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:42:15</t>
+          <t>2026-08-17 15:12:21</t>
         </is>
       </c>
       <c r="C295" s="8" t="n">
-        <v>777.04</v>
+        <v>777.13</v>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>+0.140</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
@@ -29935,15 +29935,15 @@
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:02:20</t>
+          <t>2026-08-17 13:42:15</t>
         </is>
       </c>
       <c r="C296" s="6" t="n">
-        <v>776.9</v>
-      </c>
-      <c r="D296" s="16" t="inlineStr">
-        <is>
-          <t>-0.010</t>
+        <v>777.04</v>
+      </c>
+      <c r="D296" s="15" t="inlineStr">
+        <is>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E296" s="6" t="inlineStr">
@@ -29958,15 +29958,15 @@
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 12:20:01</t>
+          <t>2026-08-17 13:02:20</t>
         </is>
       </c>
       <c r="C297" s="8" t="n">
-        <v>776.91</v>
+        <v>776.9</v>
       </c>
       <c r="D297" s="11" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
@@ -29981,15 +29981,15 @@
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17 10:35:50</t>
+          <t>2026-08-17 12:20:01</t>
         </is>
       </c>
       <c r="C298" s="6" t="n">
-        <v>776.96</v>
-      </c>
-      <c r="D298" s="15" t="inlineStr">
-        <is>
-          <t>+0.120</t>
+        <v>776.91</v>
+      </c>
+      <c r="D298" s="16" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E298" s="6" t="inlineStr">
@@ -30004,15 +30004,15 @@
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>2026-08-17 09:21:39</t>
+          <t>2026-08-17 10:35:50</t>
         </is>
       </c>
       <c r="C299" s="8" t="n">
-        <v>776.84</v>
+        <v>776.96</v>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>+0.750</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
@@ -30027,15 +30027,15 @@
       </c>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-15 09:43:38</t>
+          <t>2026-08-17 09:21:39</t>
         </is>
       </c>
       <c r="C300" s="6" t="n">
-        <v>776.09</v>
-      </c>
-      <c r="D300" s="16" t="inlineStr">
-        <is>
-          <t>-0.290</t>
+        <v>776.84</v>
+      </c>
+      <c r="D300" s="15" t="inlineStr">
+        <is>
+          <t>+0.750</t>
         </is>
       </c>
       <c r="E300" s="6" t="inlineStr">
@@ -30050,15 +30050,15 @@
       </c>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15 01:08:33</t>
+          <t>2026-08-15 09:43:38</t>
         </is>
       </c>
       <c r="C301" s="8" t="n">
-        <v>776.38</v>
-      </c>
-      <c r="D301" s="9" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>776.09</v>
+      </c>
+      <c r="D301" s="11" t="inlineStr">
+        <is>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
@@ -30073,15 +30073,15 @@
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 21:25:21</t>
+          <t>2026-08-15 01:08:33</t>
         </is>
       </c>
       <c r="C302" s="6" t="n">
-        <v>775.8099999999999</v>
+        <v>776.38</v>
       </c>
       <c r="D302" s="15" t="inlineStr">
         <is>
-          <t>+0.770</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E302" s="6" t="inlineStr">
@@ -30096,15 +30096,15 @@
       </c>
       <c r="B303" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 19:23:33</t>
+          <t>2026-08-14 21:25:21</t>
         </is>
       </c>
       <c r="C303" s="8" t="n">
-        <v>775.04</v>
+        <v>775.8099999999999</v>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.770</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
@@ -30119,15 +30119,15 @@
       </c>
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 17:32:40</t>
+          <t>2026-08-14 19:23:33</t>
         </is>
       </c>
       <c r="C304" s="6" t="n">
-        <v>774.92</v>
+        <v>775.04</v>
       </c>
       <c r="D304" s="15" t="inlineStr">
         <is>
-          <t>+0.360</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E304" s="6" t="inlineStr">
@@ -30142,15 +30142,15 @@
       </c>
       <c r="B305" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 16:24:22</t>
+          <t>2026-08-14 17:32:40</t>
         </is>
       </c>
       <c r="C305" s="8" t="n">
-        <v>774.5599999999999</v>
+        <v>774.92</v>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
@@ -30165,15 +30165,15 @@
       </c>
       <c r="B306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 15:05:16</t>
+          <t>2026-08-14 16:24:22</t>
         </is>
       </c>
       <c r="C306" s="6" t="n">
-        <v>774.4400000000001</v>
-      </c>
-      <c r="D306" s="16" t="inlineStr">
-        <is>
-          <t>-0.020</t>
+        <v>774.5599999999999</v>
+      </c>
+      <c r="D306" s="15" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E306" s="6" t="inlineStr">
@@ -30188,15 +30188,15 @@
       </c>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 13:53:50</t>
+          <t>2026-08-14 15:05:16</t>
         </is>
       </c>
       <c r="C307" s="8" t="n">
-        <v>774.46</v>
-      </c>
-      <c r="D307" s="9" t="inlineStr">
-        <is>
-          <t>+0.210</t>
+        <v>774.4400000000001</v>
+      </c>
+      <c r="D307" s="11" t="inlineStr">
+        <is>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
@@ -30211,15 +30211,15 @@
       </c>
       <c r="B308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 12:26:38</t>
+          <t>2026-08-14 13:53:50</t>
         </is>
       </c>
       <c r="C308" s="6" t="n">
-        <v>774.25</v>
+        <v>774.46</v>
       </c>
       <c r="D308" s="15" t="inlineStr">
         <is>
-          <t>+0.310</t>
+          <t>+0.210</t>
         </is>
       </c>
       <c r="E308" s="6" t="inlineStr">
@@ -30234,15 +30234,15 @@
       </c>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 10:39:02</t>
+          <t>2026-08-14 12:26:38</t>
         </is>
       </c>
       <c r="C309" s="8" t="n">
-        <v>773.9400000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.310</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
@@ -30257,15 +30257,15 @@
       </c>
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 08:05:13</t>
+          <t>2026-08-14 10:39:02</t>
         </is>
       </c>
       <c r="C310" s="6" t="n">
-        <v>773.9</v>
+        <v>773.9400000000001</v>
       </c>
       <c r="D310" s="15" t="inlineStr">
         <is>
-          <t>+0.170</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E310" s="6" t="inlineStr">
@@ -30280,15 +30280,15 @@
       </c>
       <c r="B311" s="8" t="inlineStr">
         <is>
-          <t>2026-08-14 07:24:16</t>
+          <t>2026-08-14 08:05:13</t>
         </is>
       </c>
       <c r="C311" s="8" t="n">
-        <v>773.73</v>
+        <v>773.9</v>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>+0.200</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
@@ -30303,15 +30303,15 @@
       </c>
       <c r="B312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14 02:37:10</t>
+          <t>2026-08-14 07:24:16</t>
         </is>
       </c>
       <c r="C312" s="6" t="n">
-        <v>773.53</v>
-      </c>
-      <c r="D312" s="16" t="inlineStr">
-        <is>
-          <t>-0.790</t>
+        <v>773.73</v>
+      </c>
+      <c r="D312" s="15" t="inlineStr">
+        <is>
+          <t>+0.200</t>
         </is>
       </c>
       <c r="E312" s="6" t="inlineStr">
@@ -30326,15 +30326,15 @@
       </c>
       <c r="B313" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 22:55:54</t>
+          <t>2026-08-14 02:37:10</t>
         </is>
       </c>
       <c r="C313" s="8" t="n">
-        <v>774.3200000000001</v>
-      </c>
-      <c r="D313" s="9" t="inlineStr">
-        <is>
-          <t>+0.570</t>
+        <v>773.53</v>
+      </c>
+      <c r="D313" s="11" t="inlineStr">
+        <is>
+          <t>-0.790</t>
         </is>
       </c>
       <c r="E313" s="8" t="inlineStr">
@@ -30349,15 +30349,15 @@
       </c>
       <c r="B314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 18:47:11</t>
+          <t>2026-08-13 22:55:54</t>
         </is>
       </c>
       <c r="C314" s="6" t="n">
-        <v>773.75</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="D314" s="15" t="inlineStr">
         <is>
-          <t>+0.050</t>
+          <t>+0.570</t>
         </is>
       </c>
       <c r="E314" s="6" t="inlineStr">
@@ -30372,15 +30372,15 @@
       </c>
       <c r="B315" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 17:50:37</t>
+          <t>2026-08-13 18:47:11</t>
         </is>
       </c>
       <c r="C315" s="8" t="n">
-        <v>773.7</v>
+        <v>773.75</v>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E315" s="8" t="inlineStr">
@@ -30395,15 +30395,15 @@
       </c>
       <c r="B316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 16:51:15</t>
+          <t>2026-08-13 17:50:37</t>
         </is>
       </c>
       <c r="C316" s="6" t="n">
-        <v>773.58</v>
+        <v>773.7</v>
       </c>
       <c r="D316" s="15" t="inlineStr">
         <is>
-          <t>+0.250</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E316" s="6" t="inlineStr">
@@ -30418,15 +30418,15 @@
       </c>
       <c r="B317" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 15:29:05</t>
+          <t>2026-08-13 16:51:15</t>
         </is>
       </c>
       <c r="C317" s="8" t="n">
-        <v>773.33</v>
-      </c>
-      <c r="D317" s="11" t="inlineStr">
-        <is>
-          <t>-0.060</t>
+        <v>773.58</v>
+      </c>
+      <c r="D317" s="9" t="inlineStr">
+        <is>
+          <t>+0.250</t>
         </is>
       </c>
       <c r="E317" s="8" t="inlineStr">
@@ -30441,15 +30441,15 @@
       </c>
       <c r="B318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 13:58:37</t>
+          <t>2026-08-13 15:29:05</t>
         </is>
       </c>
       <c r="C318" s="6" t="n">
-        <v>773.39</v>
-      </c>
-      <c r="D318" s="15" t="inlineStr">
-        <is>
-          <t>+0.280</t>
+        <v>773.33</v>
+      </c>
+      <c r="D318" s="16" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E318" s="6" t="inlineStr">
@@ -30464,15 +30464,15 @@
       </c>
       <c r="B319" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29:25</t>
+          <t>2026-08-13 13:58:37</t>
         </is>
       </c>
       <c r="C319" s="8" t="n">
-        <v>773.11</v>
-      </c>
-      <c r="D319" s="11" t="inlineStr">
-        <is>
-          <t>-0.130</t>
+        <v>773.39</v>
+      </c>
+      <c r="D319" s="9" t="inlineStr">
+        <is>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="E319" s="8" t="inlineStr">
@@ -30487,15 +30487,15 @@
       </c>
       <c r="B320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 10:41:01</t>
+          <t>2026-08-13 12:29:25</t>
         </is>
       </c>
       <c r="C320" s="6" t="n">
-        <v>773.24</v>
+        <v>773.11</v>
       </c>
       <c r="D320" s="16" t="inlineStr">
         <is>
-          <t>-0.340</t>
+          <t>-0.130</t>
         </is>
       </c>
       <c r="E320" s="6" t="inlineStr">
@@ -30510,15 +30510,15 @@
       </c>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05:34</t>
+          <t>2026-08-13 10:41:01</t>
         </is>
       </c>
       <c r="C321" s="8" t="n">
-        <v>773.58</v>
+        <v>773.24</v>
       </c>
       <c r="D321" s="11" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E321" s="8" t="inlineStr">
@@ -30533,15 +30533,15 @@
       </c>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13 01:36:52</t>
+          <t>2026-08-13 08:05:34</t>
         </is>
       </c>
       <c r="C322" s="6" t="n">
-        <v>773.64</v>
+        <v>773.58</v>
       </c>
       <c r="D322" s="16" t="inlineStr">
         <is>
-          <t>-0.470</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E322" s="6" t="inlineStr">
@@ -30556,15 +30556,15 @@
       </c>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13 00:37:13</t>
+          <t>2026-08-13 01:36:52</t>
         </is>
       </c>
       <c r="C323" s="8" t="n">
-        <v>774.11</v>
+        <v>773.64</v>
       </c>
       <c r="D323" s="11" t="inlineStr">
         <is>
-          <t>-0.190</t>
+          <t>-0.470</t>
         </is>
       </c>
       <c r="E323" s="8" t="inlineStr">
@@ -30579,15 +30579,15 @@
       </c>
       <c r="B324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 23:44:07</t>
+          <t>2026-08-13 00:37:13</t>
         </is>
       </c>
       <c r="C324" s="6" t="n">
-        <v>774.3</v>
+        <v>774.11</v>
       </c>
       <c r="D324" s="16" t="inlineStr">
         <is>
-          <t>-0.740</t>
+          <t>-0.190</t>
         </is>
       </c>
       <c r="E324" s="6" t="inlineStr">
@@ -30602,15 +30602,15 @@
       </c>
       <c r="B325" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 22:51:05</t>
+          <t>2026-08-12 23:44:07</t>
         </is>
       </c>
       <c r="C325" s="8" t="n">
-        <v>775.04</v>
-      </c>
-      <c r="D325" s="9" t="inlineStr">
-        <is>
-          <t>+0.140</t>
+        <v>774.3</v>
+      </c>
+      <c r="D325" s="11" t="inlineStr">
+        <is>
+          <t>-0.740</t>
         </is>
       </c>
       <c r="E325" s="8" t="inlineStr">
@@ -30625,15 +30625,15 @@
       </c>
       <c r="B326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 21:54:56</t>
+          <t>2026-08-12 22:51:05</t>
         </is>
       </c>
       <c r="C326" s="6" t="n">
-        <v>774.9</v>
+        <v>775.04</v>
       </c>
       <c r="D326" s="15" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>+0.140</t>
         </is>
       </c>
       <c r="E326" s="6" t="inlineStr">
@@ -30648,15 +30648,15 @@
       </c>
       <c r="B327" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 18:43:09</t>
+          <t>2026-08-12 21:54:56</t>
         </is>
       </c>
       <c r="C327" s="8" t="n">
-        <v>774.66</v>
+        <v>774.9</v>
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>+0.320</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
@@ -30671,15 +30671,15 @@
       </c>
       <c r="B328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 16:36:31</t>
+          <t>2026-08-12 18:43:09</t>
         </is>
       </c>
       <c r="C328" s="6" t="n">
-        <v>774.34</v>
+        <v>774.66</v>
       </c>
       <c r="D328" s="15" t="inlineStr">
         <is>
-          <t>+0.190</t>
+          <t>+0.320</t>
         </is>
       </c>
       <c r="E328" s="6" t="inlineStr">
@@ -30694,15 +30694,15 @@
       </c>
       <c r="B329" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 15:04:06</t>
+          <t>2026-08-12 16:36:31</t>
         </is>
       </c>
       <c r="C329" s="8" t="n">
-        <v>774.15</v>
-      </c>
-      <c r="D329" s="11" t="inlineStr">
-        <is>
-          <t>-0.100</t>
+        <v>774.34</v>
+      </c>
+      <c r="D329" s="9" t="inlineStr">
+        <is>
+          <t>+0.190</t>
         </is>
       </c>
       <c r="E329" s="8" t="inlineStr">
@@ -30717,15 +30717,15 @@
       </c>
       <c r="B330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 13:53:42</t>
+          <t>2026-08-12 15:04:06</t>
         </is>
       </c>
       <c r="C330" s="6" t="n">
-        <v>774.25</v>
+        <v>774.15</v>
       </c>
       <c r="D330" s="16" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.100</t>
         </is>
       </c>
       <c r="E330" s="6" t="inlineStr">
@@ -30740,15 +30740,15 @@
       </c>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 10:39:06</t>
+          <t>2026-08-12 13:53:42</t>
         </is>
       </c>
       <c r="C331" s="8" t="n">
-        <v>774.3200000000001</v>
+        <v>774.25</v>
       </c>
       <c r="D331" s="11" t="inlineStr">
         <is>
-          <t>-0.420</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
@@ -30763,15 +30763,15 @@
       </c>
       <c r="B332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 07:25:14</t>
+          <t>2026-08-12 10:39:06</t>
         </is>
       </c>
       <c r="C332" s="6" t="n">
-        <v>774.74</v>
-      </c>
-      <c r="D332" s="15" t="inlineStr">
-        <is>
-          <t>+0.240</t>
+        <v>774.3200000000001</v>
+      </c>
+      <c r="D332" s="16" t="inlineStr">
+        <is>
+          <t>-0.420</t>
         </is>
       </c>
       <c r="E332" s="6" t="inlineStr">
@@ -30786,15 +30786,15 @@
       </c>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12 01:28:47</t>
+          <t>2026-08-12 07:25:14</t>
         </is>
       </c>
       <c r="C333" s="8" t="n">
-        <v>774.5</v>
+        <v>774.74</v>
       </c>
       <c r="D333" s="9" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>+0.240</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
@@ -30809,15 +30809,15 @@
       </c>
       <c r="B334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12 00:29:04</t>
+          <t>2026-08-12 01:28:47</t>
         </is>
       </c>
       <c r="C334" s="6" t="n">
-        <v>774.37</v>
-      </c>
-      <c r="D334" s="16" t="inlineStr">
-        <is>
-          <t>-0.340</t>
+        <v>774.5</v>
+      </c>
+      <c r="D334" s="15" t="inlineStr">
+        <is>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E334" s="6" t="inlineStr">
@@ -30832,15 +30832,15 @@
       </c>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>2026-08-11 23:35:31</t>
+          <t>2026-08-12 00:29:04</t>
         </is>
       </c>
       <c r="C335" s="8" t="n">
-        <v>774.71</v>
-      </c>
-      <c r="D335" s="9" t="inlineStr">
-        <is>
-          <t>+1.160</t>
+        <v>774.37</v>
+      </c>
+      <c r="D335" s="11" t="inlineStr">
+        <is>
+          <t>-0.340</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
@@ -30855,15 +30855,15 @@
       </c>
       <c r="B336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 11:30:51</t>
+          <t>2026-08-11 23:35:31</t>
         </is>
       </c>
       <c r="C336" s="6" t="n">
-        <v>773.55</v>
-      </c>
-      <c r="D336" s="16" t="inlineStr">
-        <is>
-          <t>-0.520</t>
+        <v>774.71</v>
+      </c>
+      <c r="D336" s="15" t="inlineStr">
+        <is>
+          <t>+1.160</t>
         </is>
       </c>
       <c r="E336" s="6" t="inlineStr">
@@ -30878,15 +30878,15 @@
       </c>
       <c r="B337" s="8" t="inlineStr">
         <is>
-          <t>2026-08-07 08:29:46</t>
+          <t>2026-08-07 11:30:51</t>
         </is>
       </c>
       <c r="C337" s="8" t="n">
-        <v>774.0700000000001</v>
+        <v>773.55</v>
       </c>
       <c r="D337" s="11" t="inlineStr">
         <is>
-          <t>-0.690</t>
+          <t>-0.520</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
@@ -30901,15 +30901,15 @@
       </c>
       <c r="B338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 19:30:41</t>
+          <t>2026-08-07 08:29:46</t>
         </is>
       </c>
       <c r="C338" s="6" t="n">
-        <v>774.76</v>
+        <v>774.0700000000001</v>
       </c>
       <c r="D338" s="16" t="inlineStr">
         <is>
-          <t>-0.550</t>
+          <t>-0.690</t>
         </is>
       </c>
       <c r="E338" s="6" t="inlineStr">
@@ -30924,15 +30924,15 @@
       </c>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 17:05:58</t>
+          <t>2026-08-06 19:30:41</t>
         </is>
       </c>
       <c r="C339" s="8" t="n">
-        <v>775.3099999999999</v>
+        <v>774.76</v>
       </c>
       <c r="D339" s="11" t="inlineStr">
         <is>
-          <t>-0.150</t>
+          <t>-0.550</t>
         </is>
       </c>
       <c r="E339" s="8" t="inlineStr">
@@ -30947,15 +30947,15 @@
       </c>
       <c r="B340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 14:12:09</t>
+          <t>2026-08-06 17:05:58</t>
         </is>
       </c>
       <c r="C340" s="6" t="n">
-        <v>775.46</v>
+        <v>775.3099999999999</v>
       </c>
       <c r="D340" s="16" t="inlineStr">
         <is>
-          <t>-0.380</t>
+          <t>-0.150</t>
         </is>
       </c>
       <c r="E340" s="6" t="inlineStr">
@@ -30970,15 +30970,15 @@
       </c>
       <c r="B341" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 11:30:20</t>
+          <t>2026-08-06 14:12:09</t>
         </is>
       </c>
       <c r="C341" s="8" t="n">
-        <v>775.84</v>
+        <v>775.46</v>
       </c>
       <c r="D341" s="11" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>-0.380</t>
         </is>
       </c>
       <c r="E341" s="8" t="inlineStr">
@@ -30993,15 +30993,15 @@
       </c>
       <c r="B342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 08:05:33</t>
+          <t>2026-08-06 11:30:20</t>
         </is>
       </c>
       <c r="C342" s="6" t="n">
-        <v>775.9</v>
-      </c>
-      <c r="D342" s="15" t="inlineStr">
-        <is>
-          <t>+0.070</t>
+        <v>775.84</v>
+      </c>
+      <c r="D342" s="16" t="inlineStr">
+        <is>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E342" s="6" t="inlineStr">
@@ -31016,15 +31016,15 @@
       </c>
       <c r="B343" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 07:01:15</t>
+          <t>2026-08-06 08:05:33</t>
         </is>
       </c>
       <c r="C343" s="8" t="n">
-        <v>775.83</v>
+        <v>775.9</v>
       </c>
       <c r="D343" s="9" t="inlineStr">
         <is>
-          <t>+0.630</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E343" s="8" t="inlineStr">
@@ -31039,15 +31039,15 @@
       </c>
       <c r="B344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06 01:59:39</t>
+          <t>2026-08-06 07:01:15</t>
         </is>
       </c>
       <c r="C344" s="6" t="n">
-        <v>775.2</v>
-      </c>
-      <c r="D344" s="16" t="inlineStr">
-        <is>
-          <t>-0.080</t>
+        <v>775.83</v>
+      </c>
+      <c r="D344" s="15" t="inlineStr">
+        <is>
+          <t>+0.630</t>
         </is>
       </c>
       <c r="E344" s="6" t="inlineStr">
@@ -31062,15 +31062,15 @@
       </c>
       <c r="B345" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06 00:22:48</t>
+          <t>2026-08-06 01:59:39</t>
         </is>
       </c>
       <c r="C345" s="8" t="n">
-        <v>775.28</v>
-      </c>
-      <c r="D345" s="9" t="inlineStr">
-        <is>
-          <t>+0.160</t>
+        <v>775.2</v>
+      </c>
+      <c r="D345" s="11" t="inlineStr">
+        <is>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="E345" s="8" t="inlineStr">
@@ -31085,15 +31085,15 @@
       </c>
       <c r="B346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44:37</t>
+          <t>2026-08-06 00:22:48</t>
         </is>
       </c>
       <c r="C346" s="6" t="n">
-        <v>775.12</v>
+        <v>775.28</v>
       </c>
       <c r="D346" s="15" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E346" s="6" t="inlineStr">
@@ -31108,11 +31108,11 @@
       </c>
       <c r="B347" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 20:26:00</t>
+          <t>2026-08-05 22:44:37</t>
         </is>
       </c>
       <c r="C347" s="8" t="n">
-        <v>775.09</v>
+        <v>775.12</v>
       </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
@@ -31131,15 +31131,15 @@
       </c>
       <c r="B348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 18:37:13</t>
+          <t>2026-08-05 20:26:00</t>
         </is>
       </c>
       <c r="C348" s="6" t="n">
-        <v>775.0599999999999</v>
+        <v>775.09</v>
       </c>
       <c r="D348" s="15" t="inlineStr">
         <is>
-          <t>+0.480</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E348" s="6" t="inlineStr">
@@ -31154,15 +31154,15 @@
       </c>
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 15:58:51</t>
+          <t>2026-08-05 18:37:13</t>
         </is>
       </c>
       <c r="C349" s="8" t="n">
-        <v>774.58</v>
+        <v>775.0599999999999</v>
       </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
-          <t>+0.290</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E349" s="8" t="inlineStr">
@@ -31177,15 +31177,15 @@
       </c>
       <c r="B350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05 13:22:16</t>
+          <t>2026-08-05 15:58:51</t>
         </is>
       </c>
       <c r="C350" s="6" t="n">
-        <v>774.29</v>
+        <v>774.58</v>
       </c>
       <c r="D350" s="15" t="inlineStr">
         <is>
-          <t>+0.490</t>
+          <t>+0.290</t>
         </is>
       </c>
       <c r="E350" s="6" t="inlineStr">
@@ -31200,15 +31200,15 @@
       </c>
       <c r="B351" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05 10:02:00</t>
+          <t>2026-08-05 13:22:16</t>
         </is>
       </c>
       <c r="C351" s="8" t="n">
-        <v>773.8</v>
-      </c>
-      <c r="D351" s="11" t="inlineStr">
-        <is>
-          <t>-0.590</t>
+        <v>774.29</v>
+      </c>
+      <c r="D351" s="9" t="inlineStr">
+        <is>
+          <t>+0.490</t>
         </is>
       </c>
       <c r="E351" s="8" t="inlineStr">
@@ -31223,14 +31223,37 @@
       </c>
       <c r="B352" s="6" t="inlineStr">
         <is>
+          <t>2026-08-05 10:02:00</t>
+        </is>
+      </c>
+      <c r="C352" s="6" t="n">
+        <v>773.8</v>
+      </c>
+      <c r="D352" s="16" t="inlineStr">
+        <is>
+          <t>-0.590</t>
+        </is>
+      </c>
+      <c r="E352" s="6" t="inlineStr">
+        <is>
+          <t>5waihui.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="8" t="n">
+        <v>349</v>
+      </c>
+      <c r="B353" s="8" t="inlineStr">
+        <is>
           <t>2026-08-05 01:51:39</t>
         </is>
       </c>
-      <c r="C352" s="6" t="n">
+      <c r="C353" s="8" t="n">
         <v>774.39</v>
       </c>
-      <c r="D352" s="6" t="inlineStr"/>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="D353" s="8" t="inlineStr"/>
+      <c r="E353" s="8" t="inlineStr">
         <is>
           <t>5waihui.com</t>
         </is>

--- a/外汇牌价监控数据.xlsx
+++ b/外汇牌价监控数据.xlsx
@@ -577,7 +577,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-21 03:00:58</t>
+          <t>更新时间: 2026-10-21 06:12:20</t>
         </is>
       </c>
     </row>
@@ -737,15 +737,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>746.63</v>
+        <v>746.54</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-21 03:00:52</t>
+          <t>2026-10-21 06:12:15</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E357"/>
+  <dimension ref="A1:E358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23389,7 +23389,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>最新价: 746.63 | 最高: 782.950 | 最低: 741.220 | 总记录数: 353</t>
+          <t>最新价: 746.54 | 最高: 782.950 | 最低: 741.220 | 总记录数: 354</t>
         </is>
       </c>
     </row>
@@ -23426,15 +23426,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-10-21 03:00:52</t>
+          <t>2026-10-21 06:12:15</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>746.63</v>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>+0.900</t>
+        <v>746.54</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -23449,15 +23449,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 22:59:00</t>
+          <t>2026-10-21 03:00:52</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>745.73</v>
+        <v>746.63</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>+0.360</t>
+          <t>+0.900</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -23472,15 +23472,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20 18:05:27</t>
+          <t>2026-10-20 22:59:00</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>745.37</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>-0.880</t>
+        <v>745.73</v>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>+0.360</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -23495,15 +23495,15 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 13:13:50</t>
+          <t>2026-10-20 18:05:27</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>746.25</v>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>+0.480</t>
+        <v>745.37</v>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>-0.880</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -23518,15 +23518,15 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20 08:37:37</t>
+          <t>2026-10-20 13:13:50</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>745.77</v>
+        <v>746.25</v>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>+0.470</t>
+          <t>+0.480</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -23541,15 +23541,15 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 05:38:30</t>
+          <t>2026-10-20 08:37:37</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>745.3</v>
+        <v>745.77</v>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>+0.160</t>
+          <t>+0.470</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -23564,15 +23564,15 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20 01:25:07</t>
+          <t>2026-10-20 05:38:30</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>745.14</v>
+        <v>745.3</v>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.160</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -23587,15 +23587,15 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 19:02:37</t>
+          <t>2026-10-20 01:25:07</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>745.02</v>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>-1.730</t>
+        <v>745.14</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E12" s="